--- a/sts_ml_paper_tracker.xlsx
+++ b/sts_ml_paper_tracker.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>+0.50%</t>
+          <t>+0.26%</t>
         </is>
       </c>
     </row>
@@ -581,7 +581,7 @@
         <v>-0.55</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.43</v>
+        <v>-1.68</v>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="n">
@@ -604,7 +604,7 @@
         <v>4.34</v>
       </c>
       <c r="D13" t="n">
-        <v>3.53</v>
+        <v>3.29</v>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="n">
@@ -627,7 +627,7 @@
         <v>5.6</v>
       </c>
       <c r="D14" t="n">
-        <v>4.59</v>
+        <v>4.35</v>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="n">
@@ -690,7 +690,7 @@
         <v>42.17</v>
       </c>
       <c r="E17" t="n">
-        <v>0.72</v>
+        <v>0.48</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
@@ -713,7 +713,7 @@
         <v>44.44</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.68</v>
+        <v>-1.93</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
@@ -736,7 +736,7 @@
         <v>50</v>
       </c>
       <c r="E19" t="n">
-        <v>1.05</v>
+        <v>0.8</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
@@ -759,7 +759,7 @@
         <v>41.67</v>
       </c>
       <c r="E20" t="n">
-        <v>0.92</v>
+        <v>0.68</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
@@ -983,7 +983,7 @@
         <v>50</v>
       </c>
       <c r="E31" t="n">
-        <v>4.71</v>
+        <v>4.46</v>
       </c>
       <c r="F31" t="n">
         <v>-11.1</v>
@@ -1005,7 +1005,7 @@
         <v>33.33</v>
       </c>
       <c r="E32" t="n">
-        <v>-6.15</v>
+        <v>-6.39</v>
       </c>
       <c r="F32" t="n">
         <v>-13.2</v>
@@ -1027,7 +1027,7 @@
         <v>47.37</v>
       </c>
       <c r="E33" t="n">
-        <v>4.32</v>
+        <v>4.07</v>
       </c>
       <c r="F33" t="n">
         <v>-10.05</v>
@@ -2075,10 +2075,10 @@
         </is>
       </c>
       <c r="S46" t="n">
-        <v>3.82</v>
+        <v>3.83</v>
       </c>
       <c r="T46" t="n">
-        <v>3.82</v>
+        <v>3.83</v>
       </c>
       <c r="U46" t="inlineStr"/>
       <c r="V46" t="inlineStr"/>
@@ -2104,7 +2104,7 @@
         <v>-0.97</v>
       </c>
       <c r="AD46" t="n">
-        <v>3.82</v>
+        <v>3.83</v>
       </c>
       <c r="AE46" t="n">
         <v>2</v>
@@ -2115,11 +2115,11 @@
       <c r="AG46" t="inlineStr"/>
       <c r="AH46" t="inlineStr"/>
       <c r="AI46" t="n">
-        <v>-0.19</v>
+        <v>0.06</v>
       </c>
       <c r="AJ46" t="inlineStr"/>
       <c r="AK46" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="AL46" t="inlineStr"/>
     </row>
@@ -2225,11 +2225,11 @@
       <c r="AG47" t="inlineStr"/>
       <c r="AH47" t="inlineStr"/>
       <c r="AI47" t="n">
-        <v>-0.19</v>
+        <v>0.06</v>
       </c>
       <c r="AJ47" t="inlineStr"/>
       <c r="AK47" t="n">
-        <v>-0.08</v>
+        <v>-0.33</v>
       </c>
       <c r="AL47" t="inlineStr"/>
     </row>
@@ -2335,11 +2335,11 @@
       <c r="AG48" t="inlineStr"/>
       <c r="AH48" t="inlineStr"/>
       <c r="AI48" t="n">
-        <v>-0.19</v>
+        <v>0.06</v>
       </c>
       <c r="AJ48" t="inlineStr"/>
       <c r="AK48" t="n">
-        <v>-0.64</v>
+        <v>-0.88</v>
       </c>
       <c r="AL48" t="inlineStr"/>
     </row>
@@ -2445,11 +2445,11 @@
       <c r="AG49" t="inlineStr"/>
       <c r="AH49" t="inlineStr"/>
       <c r="AI49" t="n">
-        <v>-0.19</v>
+        <v>0.06</v>
       </c>
       <c r="AJ49" t="inlineStr"/>
       <c r="AK49" t="n">
-        <v>-4.24</v>
+        <v>-4.49</v>
       </c>
       <c r="AL49" t="inlineStr"/>
     </row>
@@ -2559,11 +2559,11 @@
       <c r="AG50" t="inlineStr"/>
       <c r="AH50" t="inlineStr"/>
       <c r="AI50" t="n">
-        <v>-0.19</v>
+        <v>0.06</v>
       </c>
       <c r="AJ50" t="inlineStr"/>
       <c r="AK50" t="n">
-        <v>-0.38</v>
+        <v>-0.63</v>
       </c>
       <c r="AL50" t="inlineStr"/>
     </row>
@@ -2671,11 +2671,11 @@
       <c r="AG51" t="inlineStr"/>
       <c r="AH51" t="inlineStr"/>
       <c r="AI51" t="n">
-        <v>0.29</v>
+        <v>0.54</v>
       </c>
       <c r="AJ51" t="inlineStr"/>
       <c r="AK51" t="n">
-        <v>4.44</v>
+        <v>4.19</v>
       </c>
       <c r="AL51" t="inlineStr"/>
     </row>
@@ -2781,11 +2781,11 @@
       <c r="AG52" t="inlineStr"/>
       <c r="AH52" t="inlineStr"/>
       <c r="AI52" t="n">
-        <v>0.29</v>
+        <v>0.54</v>
       </c>
       <c r="AJ52" t="inlineStr"/>
       <c r="AK52" t="n">
-        <v>-4.19</v>
+        <v>-4.44</v>
       </c>
       <c r="AL52" t="inlineStr"/>
     </row>
@@ -2891,11 +2891,11 @@
       <c r="AG53" t="inlineStr"/>
       <c r="AH53" t="inlineStr"/>
       <c r="AI53" t="n">
-        <v>0.29</v>
+        <v>0.54</v>
       </c>
       <c r="AJ53" t="inlineStr"/>
       <c r="AK53" t="n">
-        <v>1.67</v>
+        <v>1.42</v>
       </c>
       <c r="AL53" t="inlineStr"/>
     </row>
@@ -3001,11 +3001,11 @@
       <c r="AG54" t="inlineStr"/>
       <c r="AH54" t="inlineStr"/>
       <c r="AI54" t="n">
-        <v>0.29</v>
+        <v>0.54</v>
       </c>
       <c r="AJ54" t="inlineStr"/>
       <c r="AK54" t="n">
-        <v>-1.31</v>
+        <v>-1.56</v>
       </c>
       <c r="AL54" t="inlineStr"/>
     </row>
@@ -3117,11 +3117,11 @@
       <c r="AG55" t="inlineStr"/>
       <c r="AH55" t="inlineStr"/>
       <c r="AI55" t="n">
-        <v>0.21</v>
+        <v>0.46</v>
       </c>
       <c r="AJ55" t="inlineStr"/>
       <c r="AK55" t="n">
-        <v>5.58</v>
+        <v>5.33</v>
       </c>
       <c r="AL55" t="inlineStr"/>
     </row>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="S56" t="n">
-        <v>3.46</v>
+        <v>3.47</v>
       </c>
       <c r="T56" t="n">
-        <v>3.46</v>
+        <v>3.47</v>
       </c>
       <c r="U56" t="inlineStr"/>
       <c r="V56" t="inlineStr"/>
@@ -3216,7 +3216,7 @@
         <v>-4.75</v>
       </c>
       <c r="AD56" t="n">
-        <v>3.46</v>
+        <v>3.47</v>
       </c>
       <c r="AE56" t="n">
         <v>4</v>
@@ -3227,11 +3227,11 @@
       <c r="AG56" t="inlineStr"/>
       <c r="AH56" t="inlineStr"/>
       <c r="AI56" t="n">
-        <v>0.21</v>
+        <v>0.46</v>
       </c>
       <c r="AJ56" t="inlineStr"/>
       <c r="AK56" t="n">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="AL56" t="inlineStr"/>
     </row>
@@ -3341,11 +3341,11 @@
       <c r="AG57" t="inlineStr"/>
       <c r="AH57" t="inlineStr"/>
       <c r="AI57" t="n">
-        <v>0.21</v>
+        <v>0.46</v>
       </c>
       <c r="AJ57" t="inlineStr"/>
       <c r="AK57" t="n">
-        <v>7.09</v>
+        <v>6.84</v>
       </c>
       <c r="AL57" t="inlineStr"/>
     </row>
@@ -3385,7 +3385,7 @@
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="n">
-        <v>-7.45</v>
+        <v>-7.49</v>
       </c>
       <c r="L58" t="n">
         <v>-10.3</v>
@@ -3437,7 +3437,7 @@
         <v>-6.84</v>
       </c>
       <c r="AC58" t="n">
-        <v>-7.45</v>
+        <v>-7.49</v>
       </c>
       <c r="AD58" t="n">
         <v>3.38</v>
@@ -3451,11 +3451,11 @@
       <c r="AG58" t="inlineStr"/>
       <c r="AH58" t="inlineStr"/>
       <c r="AI58" t="n">
-        <v>0.21</v>
+        <v>0.46</v>
       </c>
       <c r="AJ58" t="inlineStr"/>
       <c r="AK58" t="n">
-        <v>-7.05</v>
+        <v>-7.3</v>
       </c>
       <c r="AL58" t="inlineStr"/>
     </row>
@@ -3565,11 +3565,11 @@
       <c r="AG59" t="inlineStr"/>
       <c r="AH59" t="inlineStr"/>
       <c r="AI59" t="n">
-        <v>0.21</v>
+        <v>0.46</v>
       </c>
       <c r="AJ59" t="inlineStr"/>
       <c r="AK59" t="n">
-        <v>-5.06</v>
+        <v>-5.31</v>
       </c>
       <c r="AL59" t="inlineStr"/>
     </row>
@@ -3677,11 +3677,11 @@
       <c r="AG60" t="inlineStr"/>
       <c r="AH60" t="inlineStr"/>
       <c r="AI60" t="n">
-        <v>0.35</v>
+        <v>0.6</v>
       </c>
       <c r="AJ60" t="inlineStr"/>
       <c r="AK60" t="n">
-        <v>-5.99</v>
+        <v>-6.24</v>
       </c>
       <c r="AL60" t="inlineStr"/>
     </row>
@@ -3721,7 +3721,7 @@
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="n">
-        <v>-3.99</v>
+        <v>-4</v>
       </c>
       <c r="L61" t="n">
         <v>6.2</v>
@@ -3773,7 +3773,7 @@
         <v>-3.71</v>
       </c>
       <c r="AC61" t="n">
-        <v>-3.99</v>
+        <v>-4</v>
       </c>
       <c r="AD61" t="n">
         <v>1.86</v>
@@ -3787,11 +3787,11 @@
       <c r="AG61" t="inlineStr"/>
       <c r="AH61" t="inlineStr"/>
       <c r="AI61" t="n">
-        <v>0.35</v>
+        <v>0.6</v>
       </c>
       <c r="AJ61" t="inlineStr"/>
       <c r="AK61" t="n">
-        <v>-4.06</v>
+        <v>-4.31</v>
       </c>
       <c r="AL61" t="inlineStr"/>
     </row>
@@ -3897,11 +3897,11 @@
       <c r="AG62" t="inlineStr"/>
       <c r="AH62" t="inlineStr"/>
       <c r="AI62" t="n">
-        <v>0.35</v>
+        <v>0.6</v>
       </c>
       <c r="AJ62" t="inlineStr"/>
       <c r="AK62" t="n">
-        <v>-3.62</v>
+        <v>-3.87</v>
       </c>
       <c r="AL62" t="inlineStr"/>
     </row>
@@ -4011,11 +4011,11 @@
       <c r="AG63" t="inlineStr"/>
       <c r="AH63" t="inlineStr"/>
       <c r="AI63" t="n">
-        <v>-0.4</v>
+        <v>-0.15</v>
       </c>
       <c r="AJ63" t="inlineStr"/>
       <c r="AK63" t="n">
-        <v>-6.6</v>
+        <v>-6.85</v>
       </c>
       <c r="AL63" t="inlineStr"/>
     </row>
@@ -4121,11 +4121,11 @@
       <c r="AG64" t="inlineStr"/>
       <c r="AH64" t="inlineStr"/>
       <c r="AI64" t="n">
-        <v>-0.4</v>
+        <v>-0.15</v>
       </c>
       <c r="AJ64" t="inlineStr"/>
       <c r="AK64" t="n">
-        <v>-20.22</v>
+        <v>-20.47</v>
       </c>
       <c r="AL64" t="inlineStr">
         <is>
@@ -4235,11 +4235,11 @@
       <c r="AG65" t="inlineStr"/>
       <c r="AH65" t="inlineStr"/>
       <c r="AI65" t="n">
-        <v>0.48</v>
+        <v>0.73</v>
       </c>
       <c r="AJ65" t="inlineStr"/>
       <c r="AK65" t="n">
-        <v>-6.54</v>
+        <v>-6.79</v>
       </c>
       <c r="AL65" t="inlineStr"/>
     </row>
@@ -4349,11 +4349,11 @@
       <c r="AG66" t="inlineStr"/>
       <c r="AH66" t="inlineStr"/>
       <c r="AI66" t="n">
-        <v>0.48</v>
+        <v>0.73</v>
       </c>
       <c r="AJ66" t="inlineStr"/>
       <c r="AK66" t="n">
-        <v>6.02</v>
+        <v>5.77</v>
       </c>
       <c r="AL66" t="inlineStr"/>
     </row>
@@ -4459,11 +4459,11 @@
       <c r="AG67" t="inlineStr"/>
       <c r="AH67" t="inlineStr"/>
       <c r="AI67" t="n">
-        <v>-0.31</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AJ67" t="inlineStr"/>
       <c r="AK67" t="n">
-        <v>-6.12</v>
+        <v>-6.37</v>
       </c>
       <c r="AL67" t="inlineStr"/>
     </row>
@@ -4569,11 +4569,11 @@
       <c r="AG68" t="inlineStr"/>
       <c r="AH68" t="inlineStr"/>
       <c r="AI68" t="n">
-        <v>-0.31</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AJ68" t="inlineStr"/>
       <c r="AK68" t="n">
-        <v>0.61</v>
+        <v>0.37</v>
       </c>
       <c r="AL68" t="inlineStr"/>
     </row>
@@ -4679,11 +4679,11 @@
       <c r="AG69" t="inlineStr"/>
       <c r="AH69" t="inlineStr"/>
       <c r="AI69" t="n">
-        <v>-0.31</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AJ69" t="inlineStr"/>
       <c r="AK69" t="n">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="AL69" t="inlineStr"/>
     </row>
@@ -4789,11 +4789,11 @@
       <c r="AG70" t="inlineStr"/>
       <c r="AH70" t="inlineStr"/>
       <c r="AI70" t="n">
-        <v>-0.31</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AJ70" t="inlineStr"/>
       <c r="AK70" t="n">
-        <v>-6.26</v>
+        <v>-6.51</v>
       </c>
       <c r="AL70" t="inlineStr"/>
     </row>
@@ -4907,11 +4907,11 @@
       <c r="AG71" t="inlineStr"/>
       <c r="AH71" t="inlineStr"/>
       <c r="AI71" t="n">
-        <v>-0.96</v>
+        <v>-0.71</v>
       </c>
       <c r="AJ71" t="inlineStr"/>
       <c r="AK71" t="n">
-        <v>20.1</v>
+        <v>19.85</v>
       </c>
       <c r="AL71" t="inlineStr"/>
     </row>
@@ -4951,7 +4951,7 @@
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="n">
-        <v>-11.77</v>
+        <v>-11.81</v>
       </c>
       <c r="L72" t="n">
         <v>-32.6</v>
@@ -5003,7 +5003,7 @@
         <v>-11.74</v>
       </c>
       <c r="AC72" t="n">
-        <v>-11.77</v>
+        <v>-11.81</v>
       </c>
       <c r="AD72" t="n">
         <v>0.42</v>
@@ -5017,11 +5017,11 @@
       <c r="AG72" t="inlineStr"/>
       <c r="AH72" t="inlineStr"/>
       <c r="AI72" t="n">
-        <v>-0.96</v>
+        <v>-0.71</v>
       </c>
       <c r="AJ72" t="inlineStr"/>
       <c r="AK72" t="n">
-        <v>-10.78</v>
+        <v>-11.03</v>
       </c>
       <c r="AL72" t="inlineStr"/>
     </row>
@@ -5133,11 +5133,11 @@
       <c r="AG73" t="inlineStr"/>
       <c r="AH73" t="inlineStr"/>
       <c r="AI73" t="n">
-        <v>-1.34</v>
+        <v>-1.09</v>
       </c>
       <c r="AJ73" t="inlineStr"/>
       <c r="AK73" t="n">
-        <v>-6.09</v>
+        <v>-6.34</v>
       </c>
       <c r="AL73" t="inlineStr"/>
     </row>
@@ -5251,11 +5251,11 @@
       <c r="AG74" t="inlineStr"/>
       <c r="AH74" t="inlineStr"/>
       <c r="AI74" t="n">
-        <v>-1.34</v>
+        <v>-1.09</v>
       </c>
       <c r="AJ74" t="inlineStr"/>
       <c r="AK74" t="n">
-        <v>7.2</v>
+        <v>6.95</v>
       </c>
       <c r="AL74" t="inlineStr">
         <is>
@@ -5365,11 +5365,11 @@
       <c r="AG75" t="inlineStr"/>
       <c r="AH75" t="inlineStr"/>
       <c r="AI75" t="n">
-        <v>-1.34</v>
+        <v>-1.09</v>
       </c>
       <c r="AJ75" t="inlineStr"/>
       <c r="AK75" t="n">
-        <v>-6.29</v>
+        <v>-6.54</v>
       </c>
       <c r="AL75" t="inlineStr"/>
     </row>
@@ -5481,11 +5481,11 @@
       <c r="AG76" t="inlineStr"/>
       <c r="AH76" t="inlineStr"/>
       <c r="AI76" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="AJ76" t="inlineStr"/>
       <c r="AK76" t="n">
-        <v>-23.33</v>
+        <v>-23.57</v>
       </c>
       <c r="AL76" t="inlineStr">
         <is>
@@ -5599,11 +5599,11 @@
       <c r="AG77" t="inlineStr"/>
       <c r="AH77" t="inlineStr"/>
       <c r="AI77" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="AJ77" t="inlineStr"/>
       <c r="AK77" t="n">
-        <v>2.08</v>
+        <v>1.83</v>
       </c>
       <c r="AL77" t="inlineStr"/>
     </row>
@@ -5713,11 +5713,11 @@
       <c r="AG78" t="inlineStr"/>
       <c r="AH78" t="inlineStr"/>
       <c r="AI78" t="n">
-        <v>-0.1</v>
+        <v>0.15</v>
       </c>
       <c r="AJ78" t="inlineStr"/>
       <c r="AK78" t="n">
-        <v>0.34</v>
+        <v>0.09</v>
       </c>
       <c r="AL78" t="inlineStr"/>
     </row>
@@ -5827,11 +5827,11 @@
       <c r="AG79" t="inlineStr"/>
       <c r="AH79" t="inlineStr"/>
       <c r="AI79" t="n">
-        <v>-0.1</v>
+        <v>0.15</v>
       </c>
       <c r="AJ79" t="inlineStr"/>
       <c r="AK79" t="n">
-        <v>0.04</v>
+        <v>-0.21</v>
       </c>
       <c r="AL79" t="inlineStr"/>
     </row>
@@ -5943,11 +5943,11 @@
       <c r="AG80" t="inlineStr"/>
       <c r="AH80" t="inlineStr"/>
       <c r="AI80" t="n">
-        <v>-0.04</v>
+        <v>0.21</v>
       </c>
       <c r="AJ80" t="inlineStr"/>
       <c r="AK80" t="n">
-        <v>8.029999999999999</v>
+        <v>7.78</v>
       </c>
       <c r="AL80" t="inlineStr"/>
     </row>
@@ -6055,11 +6055,11 @@
       <c r="AG81" t="inlineStr"/>
       <c r="AH81" t="inlineStr"/>
       <c r="AI81" t="n">
-        <v>-0.74</v>
+        <v>-0.49</v>
       </c>
       <c r="AJ81" t="inlineStr"/>
       <c r="AK81" t="n">
-        <v>-10.53</v>
+        <v>-10.78</v>
       </c>
       <c r="AL81" t="inlineStr">
         <is>
@@ -6171,11 +6171,11 @@
       <c r="AG82" t="inlineStr"/>
       <c r="AH82" t="inlineStr"/>
       <c r="AI82" t="n">
-        <v>-0.74</v>
+        <v>-0.49</v>
       </c>
       <c r="AJ82" t="inlineStr"/>
       <c r="AK82" t="n">
-        <v>-7.42</v>
+        <v>-7.66</v>
       </c>
       <c r="AL82" t="inlineStr"/>
     </row>
@@ -6287,11 +6287,11 @@
       <c r="AG83" t="inlineStr"/>
       <c r="AH83" t="inlineStr"/>
       <c r="AI83" t="n">
-        <v>-0.74</v>
+        <v>-0.49</v>
       </c>
       <c r="AJ83" t="inlineStr"/>
       <c r="AK83" t="n">
-        <v>-2.67</v>
+        <v>-2.91</v>
       </c>
       <c r="AL83" t="inlineStr"/>
     </row>
@@ -6407,11 +6407,11 @@
       <c r="AG84" t="inlineStr"/>
       <c r="AH84" t="inlineStr"/>
       <c r="AI84" t="n">
-        <v>-1.3</v>
+        <v>-1.06</v>
       </c>
       <c r="AJ84" t="inlineStr"/>
       <c r="AK84" t="n">
-        <v>16.17</v>
+        <v>15.93</v>
       </c>
       <c r="AL84" t="inlineStr"/>
     </row>
@@ -6527,11 +6527,11 @@
       <c r="AG85" t="inlineStr"/>
       <c r="AH85" t="inlineStr"/>
       <c r="AI85" t="n">
-        <v>-1.3</v>
+        <v>-1.06</v>
       </c>
       <c r="AJ85" t="inlineStr"/>
       <c r="AK85" t="n">
-        <v>3.25</v>
+        <v>3.01</v>
       </c>
       <c r="AL85" t="inlineStr"/>
     </row>
@@ -6639,11 +6639,11 @@
       <c r="AG86" t="inlineStr"/>
       <c r="AH86" t="inlineStr"/>
       <c r="AI86" t="n">
-        <v>-1.3</v>
+        <v>-1.06</v>
       </c>
       <c r="AJ86" t="inlineStr"/>
       <c r="AK86" t="n">
-        <v>-2.98</v>
+        <v>-3.22</v>
       </c>
       <c r="AL86" t="inlineStr"/>
     </row>
@@ -6751,11 +6751,11 @@
       <c r="AG87" t="inlineStr"/>
       <c r="AH87" t="inlineStr"/>
       <c r="AI87" t="n">
-        <v>-1.3</v>
+        <v>-1.06</v>
       </c>
       <c r="AJ87" t="inlineStr"/>
       <c r="AK87" t="n">
-        <v>-8.720000000000001</v>
+        <v>-8.970000000000001</v>
       </c>
       <c r="AL87" t="inlineStr">
         <is>
@@ -6871,11 +6871,11 @@
       <c r="AG88" t="inlineStr"/>
       <c r="AH88" t="inlineStr"/>
       <c r="AI88" t="n">
-        <v>-0.89</v>
+        <v>-0.64</v>
       </c>
       <c r="AJ88" t="inlineStr"/>
       <c r="AK88" t="n">
-        <v>25.56</v>
+        <v>25.31</v>
       </c>
       <c r="AL88" t="inlineStr"/>
     </row>
@@ -6987,11 +6987,11 @@
       <c r="AG89" t="inlineStr"/>
       <c r="AH89" t="inlineStr"/>
       <c r="AI89" t="n">
-        <v>-0.4</v>
+        <v>-0.15</v>
       </c>
       <c r="AJ89" t="inlineStr"/>
       <c r="AK89" t="n">
-        <v>16.9</v>
+        <v>16.66</v>
       </c>
       <c r="AL89" t="inlineStr">
         <is>
@@ -7107,11 +7107,11 @@
       <c r="AG90" t="inlineStr"/>
       <c r="AH90" t="inlineStr"/>
       <c r="AI90" t="n">
-        <v>-0.4</v>
+        <v>-0.15</v>
       </c>
       <c r="AJ90" t="inlineStr"/>
       <c r="AK90" t="n">
-        <v>-9.76</v>
+        <v>-10</v>
       </c>
       <c r="AL90" t="inlineStr">
         <is>
@@ -7227,11 +7227,11 @@
       <c r="AG91" t="inlineStr"/>
       <c r="AH91" t="inlineStr"/>
       <c r="AI91" t="n">
-        <v>-0.58</v>
+        <v>-0.34</v>
       </c>
       <c r="AJ91" t="inlineStr"/>
       <c r="AK91" t="n">
-        <v>23.82</v>
+        <v>23.58</v>
       </c>
       <c r="AL91" t="inlineStr"/>
     </row>
@@ -7347,11 +7347,11 @@
       <c r="AG92" t="inlineStr"/>
       <c r="AH92" t="inlineStr"/>
       <c r="AI92" t="n">
-        <v>-0.58</v>
+        <v>-0.34</v>
       </c>
       <c r="AJ92" t="inlineStr"/>
       <c r="AK92" t="n">
-        <v>11.01</v>
+        <v>10.76</v>
       </c>
       <c r="AL92" t="inlineStr"/>
     </row>
@@ -7459,11 +7459,11 @@
       <c r="AG93" t="inlineStr"/>
       <c r="AH93" t="inlineStr"/>
       <c r="AI93" t="n">
-        <v>-0.58</v>
+        <v>-0.34</v>
       </c>
       <c r="AJ93" t="inlineStr"/>
       <c r="AK93" t="n">
-        <v>-4.09</v>
+        <v>-4.33</v>
       </c>
       <c r="AL93" t="inlineStr"/>
     </row>
@@ -7571,11 +7571,11 @@
       <c r="AG94" t="inlineStr"/>
       <c r="AH94" t="inlineStr"/>
       <c r="AI94" t="n">
-        <v>-0.58</v>
+        <v>-0.34</v>
       </c>
       <c r="AJ94" t="inlineStr"/>
       <c r="AK94" t="n">
-        <v>-9.029999999999999</v>
+        <v>-9.279999999999999</v>
       </c>
       <c r="AL94" t="inlineStr">
         <is>
@@ -7691,11 +7691,11 @@
       <c r="AG95" t="inlineStr"/>
       <c r="AH95" t="inlineStr"/>
       <c r="AI95" t="n">
-        <v>-0.4</v>
+        <v>-0.16</v>
       </c>
       <c r="AJ95" t="inlineStr"/>
       <c r="AK95" t="n">
-        <v>3.32</v>
+        <v>3.07</v>
       </c>
       <c r="AL95" t="inlineStr">
         <is>
@@ -7809,11 +7809,11 @@
       <c r="AG96" t="inlineStr"/>
       <c r="AH96" t="inlineStr"/>
       <c r="AI96" t="n">
-        <v>-0.4</v>
+        <v>-0.16</v>
       </c>
       <c r="AJ96" t="inlineStr"/>
       <c r="AK96" t="n">
-        <v>-1.28</v>
+        <v>-1.53</v>
       </c>
       <c r="AL96" t="inlineStr"/>
     </row>
@@ -7925,11 +7925,11 @@
       <c r="AG97" t="inlineStr"/>
       <c r="AH97" t="inlineStr"/>
       <c r="AI97" t="n">
-        <v>-0.4</v>
+        <v>-0.16</v>
       </c>
       <c r="AJ97" t="inlineStr"/>
       <c r="AK97" t="n">
-        <v>-9.050000000000001</v>
+        <v>-9.289999999999999</v>
       </c>
       <c r="AL97" t="inlineStr"/>
     </row>
@@ -8037,11 +8037,11 @@
       <c r="AG98" t="inlineStr"/>
       <c r="AH98" t="inlineStr"/>
       <c r="AI98" t="n">
-        <v>-0.4</v>
+        <v>-0.16</v>
       </c>
       <c r="AJ98" t="inlineStr"/>
       <c r="AK98" t="n">
-        <v>-5.43</v>
+        <v>-5.67</v>
       </c>
       <c r="AL98" t="inlineStr"/>
     </row>
@@ -8155,11 +8155,11 @@
       <c r="AG99" t="inlineStr"/>
       <c r="AH99" t="inlineStr"/>
       <c r="AI99" t="n">
-        <v>-0.4</v>
+        <v>-0.16</v>
       </c>
       <c r="AJ99" t="inlineStr"/>
       <c r="AK99" t="n">
-        <v>-1.41</v>
+        <v>-1.66</v>
       </c>
       <c r="AL99" t="inlineStr"/>
     </row>
@@ -8267,11 +8267,11 @@
       <c r="AG100" t="inlineStr"/>
       <c r="AH100" t="inlineStr"/>
       <c r="AI100" t="n">
-        <v>-0.4</v>
+        <v>-0.16</v>
       </c>
       <c r="AJ100" t="inlineStr"/>
       <c r="AK100" t="n">
-        <v>-11.37</v>
+        <v>-11.61</v>
       </c>
       <c r="AL100" t="inlineStr"/>
     </row>
@@ -8383,11 +8383,11 @@
       <c r="AG101" t="inlineStr"/>
       <c r="AH101" t="inlineStr"/>
       <c r="AI101" t="n">
-        <v>-0.4</v>
+        <v>-0.16</v>
       </c>
       <c r="AJ101" t="inlineStr"/>
       <c r="AK101" t="n">
-        <v>7.29</v>
+        <v>7.04</v>
       </c>
       <c r="AL101" t="inlineStr"/>
     </row>
@@ -8497,11 +8497,11 @@
       <c r="AG102" t="inlineStr"/>
       <c r="AH102" t="inlineStr"/>
       <c r="AI102" t="n">
-        <v>-0.4</v>
+        <v>-0.16</v>
       </c>
       <c r="AJ102" t="inlineStr"/>
       <c r="AK102" t="n">
-        <v>-9.08</v>
+        <v>-9.33</v>
       </c>
       <c r="AL102" t="inlineStr"/>
     </row>
@@ -8543,7 +8543,7 @@
       </c>
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="n">
-        <v>-25.32</v>
+        <v>-25.33</v>
       </c>
       <c r="L103" t="n">
         <v>9</v>
@@ -8597,7 +8597,7 @@
         <v>-24.47</v>
       </c>
       <c r="AC103" t="n">
-        <v>-25.32</v>
+        <v>-25.33</v>
       </c>
       <c r="AD103" t="n">
         <v>6.36</v>
@@ -8611,11 +8611,11 @@
       <c r="AG103" t="inlineStr"/>
       <c r="AH103" t="inlineStr"/>
       <c r="AI103" t="n">
-        <v>-0.4</v>
+        <v>-0.16</v>
       </c>
       <c r="AJ103" t="inlineStr"/>
       <c r="AK103" t="n">
-        <v>-24.06</v>
+        <v>-24.31</v>
       </c>
       <c r="AL103" t="inlineStr">
         <is>
@@ -8644,7 +8644,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F104" t="n">
@@ -8690,7 +8690,7 @@
         <v>6.58</v>
       </c>
       <c r="T104" t="n">
-        <v>13.84</v>
+        <v>13.85</v>
       </c>
       <c r="U104" t="n">
         <v>-5.81</v>
@@ -8720,7 +8720,7 @@
         <v>-14.62</v>
       </c>
       <c r="AD104" t="n">
-        <v>13.84</v>
+        <v>13.85</v>
       </c>
       <c r="AE104" t="n">
         <v>20</v>
@@ -8731,11 +8731,11 @@
       <c r="AG104" t="inlineStr"/>
       <c r="AH104" t="inlineStr"/>
       <c r="AI104" t="n">
-        <v>-0.57</v>
+        <v>-0.32</v>
       </c>
       <c r="AJ104" t="inlineStr"/>
       <c r="AK104" t="n">
-        <v>13.73</v>
+        <v>13.48</v>
       </c>
       <c r="AL104" t="inlineStr">
         <is>
@@ -8764,7 +8764,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F105" t="n">
@@ -8851,11 +8851,11 @@
       <c r="AG105" t="inlineStr"/>
       <c r="AH105" t="inlineStr"/>
       <c r="AI105" t="n">
-        <v>-0.57</v>
+        <v>-0.32</v>
       </c>
       <c r="AJ105" t="inlineStr"/>
       <c r="AK105" t="n">
-        <v>5.48</v>
+        <v>5.24</v>
       </c>
       <c r="AL105" t="inlineStr"/>
     </row>
@@ -8880,7 +8880,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F106" t="n">
@@ -8965,11 +8965,11 @@
       <c r="AG106" t="inlineStr"/>
       <c r="AH106" t="inlineStr"/>
       <c r="AI106" t="n">
-        <v>-0.57</v>
+        <v>-0.32</v>
       </c>
       <c r="AJ106" t="inlineStr"/>
       <c r="AK106" t="n">
-        <v>-14.31</v>
+        <v>-14.56</v>
       </c>
       <c r="AL106" t="inlineStr">
         <is>
@@ -9087,11 +9087,11 @@
       <c r="AG107" t="inlineStr"/>
       <c r="AH107" t="inlineStr"/>
       <c r="AI107" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.31</v>
       </c>
       <c r="AJ107" t="inlineStr"/>
       <c r="AK107" t="n">
-        <v>-0.66</v>
+        <v>-0.9</v>
       </c>
       <c r="AL107" t="inlineStr"/>
     </row>
@@ -9205,11 +9205,11 @@
       <c r="AG108" t="inlineStr"/>
       <c r="AH108" t="inlineStr"/>
       <c r="AI108" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.31</v>
       </c>
       <c r="AJ108" t="inlineStr"/>
       <c r="AK108" t="n">
-        <v>5.52</v>
+        <v>5.27</v>
       </c>
       <c r="AL108" t="inlineStr"/>
     </row>
@@ -9319,11 +9319,11 @@
       <c r="AG109" t="inlineStr"/>
       <c r="AH109" t="inlineStr"/>
       <c r="AI109" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.31</v>
       </c>
       <c r="AJ109" t="inlineStr"/>
       <c r="AK109" t="n">
-        <v>-12.32</v>
+        <v>-12.57</v>
       </c>
       <c r="AL109" t="inlineStr">
         <is>
@@ -9437,11 +9437,11 @@
       <c r="AG110" t="inlineStr"/>
       <c r="AH110" t="inlineStr"/>
       <c r="AI110" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.31</v>
       </c>
       <c r="AJ110" t="inlineStr"/>
       <c r="AK110" t="n">
-        <v>-20.13</v>
+        <v>-20.38</v>
       </c>
       <c r="AL110" t="inlineStr">
         <is>
@@ -9489,7 +9489,7 @@
         <v>-17.17</v>
       </c>
       <c r="K111" t="n">
-        <v>-17.36</v>
+        <v>-17.38</v>
       </c>
       <c r="L111" t="n">
         <v>-9.5</v>
@@ -9541,7 +9541,7 @@
         <v>-17.17</v>
       </c>
       <c r="AC111" t="n">
-        <v>-17.36</v>
+        <v>-17.38</v>
       </c>
       <c r="AD111" t="n">
         <v>1.98</v>
@@ -9555,11 +9555,11 @@
       <c r="AG111" t="inlineStr"/>
       <c r="AH111" t="inlineStr"/>
       <c r="AI111" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.31</v>
       </c>
       <c r="AJ111" t="inlineStr"/>
       <c r="AK111" t="n">
-        <v>-16.62</v>
+        <v>-16.86</v>
       </c>
       <c r="AL111" t="inlineStr">
         <is>
@@ -9675,11 +9675,11 @@
       <c r="AG112" t="inlineStr"/>
       <c r="AH112" t="inlineStr"/>
       <c r="AI112" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.31</v>
       </c>
       <c r="AJ112" t="inlineStr"/>
       <c r="AK112" t="n">
-        <v>-10.57</v>
+        <v>-10.82</v>
       </c>
       <c r="AL112" t="inlineStr">
         <is>
@@ -9793,11 +9793,11 @@
       <c r="AG113" t="inlineStr"/>
       <c r="AH113" t="inlineStr"/>
       <c r="AI113" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.31</v>
       </c>
       <c r="AJ113" t="inlineStr"/>
       <c r="AK113" t="n">
-        <v>-6.28</v>
+        <v>-6.53</v>
       </c>
       <c r="AL113" t="inlineStr"/>
     </row>
@@ -9907,11 +9907,11 @@
       <c r="AG114" t="inlineStr"/>
       <c r="AH114" t="inlineStr"/>
       <c r="AI114" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.31</v>
       </c>
       <c r="AJ114" t="inlineStr"/>
       <c r="AK114" t="n">
-        <v>-19.7</v>
+        <v>-19.95</v>
       </c>
       <c r="AL114" t="inlineStr">
         <is>
@@ -10025,11 +10025,11 @@
       <c r="AG115" t="inlineStr"/>
       <c r="AH115" t="inlineStr"/>
       <c r="AI115" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.31</v>
       </c>
       <c r="AJ115" t="inlineStr"/>
       <c r="AK115" t="n">
-        <v>-7.47</v>
+        <v>-7.72</v>
       </c>
       <c r="AL115" t="inlineStr"/>
     </row>
@@ -10139,11 +10139,11 @@
       <c r="AG116" t="inlineStr"/>
       <c r="AH116" t="inlineStr"/>
       <c r="AI116" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.31</v>
       </c>
       <c r="AJ116" t="inlineStr"/>
       <c r="AK116" t="n">
-        <v>-8.59</v>
+        <v>-8.84</v>
       </c>
       <c r="AL116" t="inlineStr"/>
     </row>
@@ -10257,11 +10257,11 @@
       <c r="AG117" t="inlineStr"/>
       <c r="AH117" t="inlineStr"/>
       <c r="AI117" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.31</v>
       </c>
       <c r="AJ117" t="inlineStr"/>
       <c r="AK117" t="n">
-        <v>12.84</v>
+        <v>12.59</v>
       </c>
       <c r="AL117" t="inlineStr"/>
     </row>
@@ -10373,11 +10373,11 @@
       <c r="AG118" t="inlineStr"/>
       <c r="AH118" t="inlineStr"/>
       <c r="AI118" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.31</v>
       </c>
       <c r="AJ118" t="inlineStr"/>
       <c r="AK118" t="n">
-        <v>-3.73</v>
+        <v>-3.98</v>
       </c>
       <c r="AL118" t="inlineStr"/>
     </row>
@@ -10491,11 +10491,11 @@
       <c r="AG119" t="inlineStr"/>
       <c r="AH119" t="inlineStr"/>
       <c r="AI119" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.31</v>
       </c>
       <c r="AJ119" t="inlineStr"/>
       <c r="AK119" t="n">
-        <v>-9.859999999999999</v>
+        <v>-10.11</v>
       </c>
       <c r="AL119" t="inlineStr"/>
     </row>
@@ -10607,11 +10607,11 @@
       <c r="AG120" t="inlineStr"/>
       <c r="AH120" t="inlineStr"/>
       <c r="AI120" t="n">
-        <v>-1.13</v>
+        <v>-0.88</v>
       </c>
       <c r="AJ120" t="inlineStr"/>
       <c r="AK120" t="n">
-        <v>-9.42</v>
+        <v>-9.67</v>
       </c>
       <c r="AL120" t="inlineStr">
         <is>
@@ -10718,7 +10718,7 @@
         <v>-1.82</v>
       </c>
       <c r="AD121" t="n">
-        <v>30.46</v>
+        <v>30.91</v>
       </c>
       <c r="AE121" t="n">
         <v>24</v>
@@ -10729,11 +10729,11 @@
       <c r="AG121" t="inlineStr"/>
       <c r="AH121" t="inlineStr"/>
       <c r="AI121" t="n">
-        <v>-1.87</v>
+        <v>-1.62</v>
       </c>
       <c r="AJ121" t="inlineStr"/>
       <c r="AK121" t="n">
-        <v>27.32</v>
+        <v>27.07</v>
       </c>
       <c r="AL121" t="inlineStr"/>
     </row>
@@ -10847,11 +10847,11 @@
       <c r="AG122" t="inlineStr"/>
       <c r="AH122" t="inlineStr"/>
       <c r="AI122" t="n">
-        <v>-2.16</v>
+        <v>-1.92</v>
       </c>
       <c r="AJ122" t="inlineStr"/>
       <c r="AK122" t="n">
-        <v>1.12</v>
+        <v>0.88</v>
       </c>
       <c r="AL122" t="inlineStr"/>
     </row>
@@ -10967,11 +10967,11 @@
       <c r="AG123" t="inlineStr"/>
       <c r="AH123" t="inlineStr"/>
       <c r="AI123" t="n">
-        <v>-2.16</v>
+        <v>-1.92</v>
       </c>
       <c r="AJ123" t="inlineStr"/>
       <c r="AK123" t="n">
-        <v>-25.22</v>
+        <v>-25.47</v>
       </c>
       <c r="AL123" t="inlineStr">
         <is>
@@ -11089,11 +11089,11 @@
       <c r="AG124" t="inlineStr"/>
       <c r="AH124" t="inlineStr"/>
       <c r="AI124" t="n">
-        <v>-2.16</v>
+        <v>-1.92</v>
       </c>
       <c r="AJ124" t="inlineStr"/>
       <c r="AK124" t="n">
-        <v>-31.79</v>
+        <v>-32.03</v>
       </c>
       <c r="AL124" t="inlineStr">
         <is>
@@ -11209,11 +11209,11 @@
       <c r="AG125" t="inlineStr"/>
       <c r="AH125" t="inlineStr"/>
       <c r="AI125" t="n">
-        <v>-2.16</v>
+        <v>-1.92</v>
       </c>
       <c r="AJ125" t="inlineStr"/>
       <c r="AK125" t="n">
-        <v>6.01</v>
+        <v>5.77</v>
       </c>
       <c r="AL125" t="inlineStr">
         <is>
@@ -11317,7 +11317,7 @@
         <v>-15.34</v>
       </c>
       <c r="AC126" t="n">
-        <v>-15.43</v>
+        <v>-15.45</v>
       </c>
       <c r="AD126" t="n">
         <v>3.67</v>
@@ -11331,11 +11331,11 @@
       <c r="AG126" t="inlineStr"/>
       <c r="AH126" t="inlineStr"/>
       <c r="AI126" t="n">
-        <v>-2.16</v>
+        <v>-1.92</v>
       </c>
       <c r="AJ126" t="inlineStr"/>
       <c r="AK126" t="n">
-        <v>-13.17</v>
+        <v>-13.42</v>
       </c>
       <c r="AL126" t="inlineStr">
         <is>
@@ -11453,11 +11453,11 @@
       <c r="AG127" t="inlineStr"/>
       <c r="AH127" t="inlineStr"/>
       <c r="AI127" t="n">
-        <v>-2.16</v>
+        <v>-1.92</v>
       </c>
       <c r="AJ127" t="inlineStr"/>
       <c r="AK127" t="n">
-        <v>24.43</v>
+        <v>24.19</v>
       </c>
       <c r="AL127" t="inlineStr"/>
     </row>
@@ -11567,11 +11567,11 @@
       <c r="AG128" t="inlineStr"/>
       <c r="AH128" t="inlineStr"/>
       <c r="AI128" t="n">
-        <v>-2.16</v>
+        <v>-1.92</v>
       </c>
       <c r="AJ128" t="inlineStr"/>
       <c r="AK128" t="n">
-        <v>-17.87</v>
+        <v>-18.11</v>
       </c>
       <c r="AL128" t="inlineStr">
         <is>
@@ -11685,11 +11685,11 @@
       <c r="AG129" t="inlineStr"/>
       <c r="AH129" t="inlineStr"/>
       <c r="AI129" t="n">
-        <v>-2.16</v>
+        <v>-1.92</v>
       </c>
       <c r="AJ129" t="inlineStr"/>
       <c r="AK129" t="n">
-        <v>-1.87</v>
+        <v>-2.12</v>
       </c>
       <c r="AL129" t="inlineStr"/>
     </row>
@@ -11801,11 +11801,11 @@
       <c r="AG130" t="inlineStr"/>
       <c r="AH130" t="inlineStr"/>
       <c r="AI130" t="n">
-        <v>-2.16</v>
+        <v>-1.92</v>
       </c>
       <c r="AJ130" t="inlineStr"/>
       <c r="AK130" t="n">
-        <v>-16.71</v>
+        <v>-16.95</v>
       </c>
       <c r="AL130" t="inlineStr">
         <is>
@@ -11919,11 +11919,11 @@
       <c r="AG131" t="inlineStr"/>
       <c r="AH131" t="inlineStr"/>
       <c r="AI131" t="n">
-        <v>-2.16</v>
+        <v>-1.92</v>
       </c>
       <c r="AJ131" t="inlineStr"/>
       <c r="AK131" t="n">
-        <v>-12.33</v>
+        <v>-12.57</v>
       </c>
       <c r="AL131" t="inlineStr">
         <is>
@@ -12045,11 +12045,11 @@
       <c r="AG132" t="inlineStr"/>
       <c r="AH132" t="inlineStr"/>
       <c r="AI132" t="n">
-        <v>-2.16</v>
+        <v>-1.92</v>
       </c>
       <c r="AJ132" t="inlineStr"/>
       <c r="AK132" t="n">
-        <v>-13.89</v>
+        <v>-14.14</v>
       </c>
       <c r="AL132" t="inlineStr">
         <is>
@@ -12156,7 +12156,7 @@
         <v>-7.59</v>
       </c>
       <c r="AD133" t="n">
-        <v>27.98</v>
+        <v>28</v>
       </c>
       <c r="AE133" t="n">
         <v>25</v>
@@ -12167,11 +12167,11 @@
       <c r="AG133" t="inlineStr"/>
       <c r="AH133" t="inlineStr"/>
       <c r="AI133" t="n">
-        <v>-2.16</v>
+        <v>-1.92</v>
       </c>
       <c r="AJ133" t="inlineStr"/>
       <c r="AK133" t="n">
-        <v>28.36</v>
+        <v>28.12</v>
       </c>
       <c r="AL133" t="inlineStr"/>
     </row>
@@ -12285,11 +12285,11 @@
       <c r="AG134" t="inlineStr"/>
       <c r="AH134" t="inlineStr"/>
       <c r="AI134" t="n">
-        <v>-2.16</v>
+        <v>-1.92</v>
       </c>
       <c r="AJ134" t="inlineStr"/>
       <c r="AK134" t="n">
-        <v>8.25</v>
+        <v>8.01</v>
       </c>
       <c r="AL134" t="inlineStr"/>
     </row>
@@ -12399,11 +12399,11 @@
       <c r="AG135" t="inlineStr"/>
       <c r="AH135" t="inlineStr"/>
       <c r="AI135" t="n">
-        <v>-2.16</v>
+        <v>-1.92</v>
       </c>
       <c r="AJ135" t="inlineStr"/>
       <c r="AK135" t="n">
-        <v>-13.18</v>
+        <v>-13.43</v>
       </c>
       <c r="AL135" t="inlineStr">
         <is>
@@ -12521,11 +12521,11 @@
       <c r="AG136" t="inlineStr"/>
       <c r="AH136" t="inlineStr"/>
       <c r="AI136" t="n">
-        <v>-2.16</v>
+        <v>-1.92</v>
       </c>
       <c r="AJ136" t="inlineStr"/>
       <c r="AK136" t="n">
-        <v>22.68</v>
+        <v>22.44</v>
       </c>
       <c r="AL136" t="inlineStr"/>
     </row>
@@ -12639,11 +12639,11 @@
       <c r="AG137" t="inlineStr"/>
       <c r="AH137" t="inlineStr"/>
       <c r="AI137" t="n">
-        <v>-2.16</v>
+        <v>-1.92</v>
       </c>
       <c r="AJ137" t="inlineStr"/>
       <c r="AK137" t="n">
-        <v>6.92</v>
+        <v>6.68</v>
       </c>
       <c r="AL137" t="inlineStr"/>
     </row>
@@ -12757,11 +12757,11 @@
       <c r="AG138" t="inlineStr"/>
       <c r="AH138" t="inlineStr"/>
       <c r="AI138" t="n">
-        <v>-1.7</v>
+        <v>-1.46</v>
       </c>
       <c r="AJ138" t="inlineStr"/>
       <c r="AK138" t="n">
-        <v>25.05</v>
+        <v>24.81</v>
       </c>
       <c r="AL138" t="inlineStr"/>
     </row>
@@ -12875,11 +12875,11 @@
       <c r="AG139" t="inlineStr"/>
       <c r="AH139" t="inlineStr"/>
       <c r="AI139" t="n">
-        <v>-1.66</v>
+        <v>-1.41</v>
       </c>
       <c r="AJ139" t="inlineStr"/>
       <c r="AK139" t="n">
-        <v>1.48</v>
+        <v>1.24</v>
       </c>
       <c r="AL139" t="inlineStr"/>
     </row>
@@ -12993,11 +12993,11 @@
       <c r="AG140" t="inlineStr"/>
       <c r="AH140" t="inlineStr"/>
       <c r="AI140" t="n">
-        <v>-1.41</v>
+        <v>-1.17</v>
       </c>
       <c r="AJ140" t="inlineStr"/>
       <c r="AK140" t="n">
-        <v>10.92</v>
+        <v>10.68</v>
       </c>
       <c r="AL140" t="inlineStr"/>
     </row>
@@ -13109,11 +13109,11 @@
       <c r="AG141" t="inlineStr"/>
       <c r="AH141" t="inlineStr"/>
       <c r="AI141" t="n">
-        <v>-1.41</v>
+        <v>-1.17</v>
       </c>
       <c r="AJ141" t="inlineStr"/>
       <c r="AK141" t="n">
-        <v>-13.17</v>
+        <v>-13.42</v>
       </c>
       <c r="AL141" t="inlineStr">
         <is>
@@ -13217,7 +13217,7 @@
         <v>-5.62</v>
       </c>
       <c r="AC142" t="n">
-        <v>-5.67</v>
+        <v>-5.68</v>
       </c>
       <c r="AD142" t="n">
         <v>13.31</v>
@@ -13231,11 +13231,11 @@
       <c r="AG142" t="inlineStr"/>
       <c r="AH142" t="inlineStr"/>
       <c r="AI142" t="n">
-        <v>-1.41</v>
+        <v>-1.17</v>
       </c>
       <c r="AJ142" t="inlineStr"/>
       <c r="AK142" t="n">
-        <v>-4.21</v>
+        <v>-4.46</v>
       </c>
       <c r="AL142" t="inlineStr"/>
     </row>
@@ -13347,11 +13347,11 @@
       <c r="AG143" t="inlineStr"/>
       <c r="AH143" t="inlineStr"/>
       <c r="AI143" t="n">
-        <v>-1.41</v>
+        <v>-1.17</v>
       </c>
       <c r="AJ143" t="inlineStr"/>
       <c r="AK143" t="n">
-        <v>-4.76</v>
+        <v>-5</v>
       </c>
       <c r="AL143" t="inlineStr"/>
     </row>
@@ -13465,11 +13465,11 @@
       <c r="AG144" t="inlineStr"/>
       <c r="AH144" t="inlineStr"/>
       <c r="AI144" t="n">
-        <v>-1.41</v>
+        <v>-1.17</v>
       </c>
       <c r="AJ144" t="inlineStr"/>
       <c r="AK144" t="n">
-        <v>-6.35</v>
+        <v>-6.59</v>
       </c>
       <c r="AL144" t="inlineStr">
         <is>
@@ -13587,11 +13587,11 @@
       <c r="AG145" t="inlineStr"/>
       <c r="AH145" t="inlineStr"/>
       <c r="AI145" t="n">
-        <v>-1.21</v>
+        <v>-0.96</v>
       </c>
       <c r="AJ145" t="inlineStr"/>
       <c r="AK145" t="n">
-        <v>12.19</v>
+        <v>11.94</v>
       </c>
       <c r="AL145" t="inlineStr"/>
     </row>
@@ -13705,11 +13705,11 @@
       <c r="AG146" t="inlineStr"/>
       <c r="AH146" t="inlineStr"/>
       <c r="AI146" t="n">
-        <v>-1.21</v>
+        <v>-0.96</v>
       </c>
       <c r="AJ146" t="inlineStr"/>
       <c r="AK146" t="n">
-        <v>2.69</v>
+        <v>2.45</v>
       </c>
       <c r="AL146" t="inlineStr"/>
     </row>
@@ -13819,11 +13819,11 @@
       <c r="AG147" t="inlineStr"/>
       <c r="AH147" t="inlineStr"/>
       <c r="AI147" t="n">
-        <v>-1.11</v>
+        <v>-0.86</v>
       </c>
       <c r="AJ147" t="inlineStr"/>
       <c r="AK147" t="n">
-        <v>-0.59</v>
+        <v>-0.83</v>
       </c>
       <c r="AL147" t="inlineStr"/>
     </row>
@@ -13937,11 +13937,11 @@
       <c r="AG148" t="inlineStr"/>
       <c r="AH148" t="inlineStr"/>
       <c r="AI148" t="n">
-        <v>-1.83</v>
+        <v>-1.58</v>
       </c>
       <c r="AJ148" t="inlineStr"/>
       <c r="AK148" t="n">
-        <v>6.36</v>
+        <v>6.12</v>
       </c>
       <c r="AL148" t="inlineStr"/>
     </row>
@@ -14055,11 +14055,11 @@
       <c r="AG149" t="inlineStr"/>
       <c r="AH149" t="inlineStr"/>
       <c r="AI149" t="n">
-        <v>-1.83</v>
+        <v>-1.58</v>
       </c>
       <c r="AJ149" t="inlineStr"/>
       <c r="AK149" t="n">
-        <v>7.25</v>
+        <v>7.01</v>
       </c>
       <c r="AL149" t="inlineStr"/>
     </row>
@@ -14171,11 +14171,11 @@
       <c r="AG150" t="inlineStr"/>
       <c r="AH150" t="inlineStr"/>
       <c r="AI150" t="n">
-        <v>1.63</v>
+        <v>1.89</v>
       </c>
       <c r="AJ150" t="inlineStr"/>
       <c r="AK150" t="n">
-        <v>3.71</v>
+        <v>3.45</v>
       </c>
       <c r="AL150" t="inlineStr"/>
     </row>
@@ -14289,11 +14289,11 @@
       <c r="AG151" t="inlineStr"/>
       <c r="AH151" t="inlineStr"/>
       <c r="AI151" t="n">
-        <v>1.63</v>
+        <v>1.89</v>
       </c>
       <c r="AJ151" t="inlineStr"/>
       <c r="AK151" t="n">
-        <v>31.63</v>
+        <v>31.38</v>
       </c>
       <c r="AL151" t="inlineStr"/>
     </row>
@@ -14407,11 +14407,11 @@
       <c r="AG152" t="inlineStr"/>
       <c r="AH152" t="inlineStr"/>
       <c r="AI152" t="n">
-        <v>1.63</v>
+        <v>1.89</v>
       </c>
       <c r="AJ152" t="inlineStr"/>
       <c r="AK152" t="n">
-        <v>3.64</v>
+        <v>3.39</v>
       </c>
       <c r="AL152" t="inlineStr">
         <is>
@@ -14527,11 +14527,11 @@
       <c r="AG153" t="inlineStr"/>
       <c r="AH153" t="inlineStr"/>
       <c r="AI153" t="n">
-        <v>1.63</v>
+        <v>1.89</v>
       </c>
       <c r="AJ153" t="inlineStr"/>
       <c r="AK153" t="n">
-        <v>-19.45</v>
+        <v>-19.71</v>
       </c>
       <c r="AL153" t="inlineStr">
         <is>
@@ -14649,11 +14649,11 @@
       <c r="AG154" t="inlineStr"/>
       <c r="AH154" t="inlineStr"/>
       <c r="AI154" t="n">
-        <v>1.63</v>
+        <v>1.89</v>
       </c>
       <c r="AJ154" t="inlineStr"/>
       <c r="AK154" t="n">
-        <v>15.27</v>
+        <v>15.01</v>
       </c>
       <c r="AL154" t="inlineStr"/>
     </row>
@@ -14767,11 +14767,11 @@
       <c r="AG155" t="inlineStr"/>
       <c r="AH155" t="inlineStr"/>
       <c r="AI155" t="n">
-        <v>2.28</v>
+        <v>2.54</v>
       </c>
       <c r="AJ155" t="inlineStr"/>
       <c r="AK155" t="n">
-        <v>-4.41</v>
+        <v>-4.67</v>
       </c>
       <c r="AL155" t="inlineStr"/>
     </row>
@@ -14889,11 +14889,11 @@
       <c r="AG156" t="inlineStr"/>
       <c r="AH156" t="inlineStr"/>
       <c r="AI156" t="n">
-        <v>2.28</v>
+        <v>2.54</v>
       </c>
       <c r="AJ156" t="inlineStr"/>
       <c r="AK156" t="n">
-        <v>6.84</v>
+        <v>6.59</v>
       </c>
       <c r="AL156" t="inlineStr"/>
     </row>
@@ -15011,11 +15011,11 @@
       <c r="AG157" t="inlineStr"/>
       <c r="AH157" t="inlineStr"/>
       <c r="AI157" t="n">
-        <v>2.28</v>
+        <v>2.54</v>
       </c>
       <c r="AJ157" t="inlineStr"/>
       <c r="AK157" t="n">
-        <v>27.89</v>
+        <v>27.64</v>
       </c>
       <c r="AL157" t="inlineStr"/>
     </row>
@@ -15125,11 +15125,11 @@
       <c r="AG158" t="inlineStr"/>
       <c r="AH158" t="inlineStr"/>
       <c r="AI158" t="n">
-        <v>2.28</v>
+        <v>2.54</v>
       </c>
       <c r="AJ158" t="inlineStr"/>
       <c r="AK158" t="n">
-        <v>-16.85</v>
+        <v>-17.1</v>
       </c>
       <c r="AL158" t="inlineStr">
         <is>
@@ -15243,11 +15243,11 @@
       <c r="AG159" t="inlineStr"/>
       <c r="AH159" t="inlineStr"/>
       <c r="AI159" t="n">
-        <v>3.48</v>
+        <v>3.74</v>
       </c>
       <c r="AJ159" t="inlineStr"/>
       <c r="AK159" t="n">
-        <v>-25.17</v>
+        <v>-25.43</v>
       </c>
       <c r="AL159" t="inlineStr">
         <is>
@@ -15363,11 +15363,11 @@
       <c r="AG160" t="inlineStr"/>
       <c r="AH160" t="inlineStr"/>
       <c r="AI160" t="n">
-        <v>3.48</v>
+        <v>3.74</v>
       </c>
       <c r="AJ160" t="inlineStr"/>
       <c r="AK160" t="n">
-        <v>-6.67</v>
+        <v>-6.92</v>
       </c>
       <c r="AL160" t="inlineStr"/>
     </row>
@@ -15479,11 +15479,11 @@
       <c r="AG161" t="inlineStr"/>
       <c r="AH161" t="inlineStr"/>
       <c r="AI161" t="n">
-        <v>3.48</v>
+        <v>3.74</v>
       </c>
       <c r="AJ161" t="inlineStr"/>
       <c r="AK161" t="n">
-        <v>-9.75</v>
+        <v>-10.01</v>
       </c>
       <c r="AL161" t="inlineStr"/>
     </row>
@@ -15597,11 +15597,11 @@
       <c r="AG162" t="inlineStr"/>
       <c r="AH162" t="inlineStr"/>
       <c r="AI162" t="n">
-        <v>3.48</v>
+        <v>3.74</v>
       </c>
       <c r="AJ162" t="inlineStr"/>
       <c r="AK162" t="n">
-        <v>-3.07</v>
+        <v>-3.33</v>
       </c>
       <c r="AL162" t="inlineStr"/>
     </row>
@@ -15713,11 +15713,11 @@
       <c r="AG163" t="inlineStr"/>
       <c r="AH163" t="inlineStr"/>
       <c r="AI163" t="n">
-        <v>3.48</v>
+        <v>3.74</v>
       </c>
       <c r="AJ163" t="inlineStr"/>
       <c r="AK163" t="n">
-        <v>-10.01</v>
+        <v>-10.27</v>
       </c>
       <c r="AL163" t="inlineStr">
         <is>
@@ -15833,11 +15833,11 @@
       <c r="AG164" t="inlineStr"/>
       <c r="AH164" t="inlineStr"/>
       <c r="AI164" t="n">
-        <v>2.94</v>
+        <v>3.19</v>
       </c>
       <c r="AJ164" t="inlineStr"/>
       <c r="AK164" t="n">
-        <v>-14.36</v>
+        <v>-14.61</v>
       </c>
       <c r="AL164" t="inlineStr"/>
     </row>
@@ -15949,11 +15949,11 @@
       <c r="AG165" t="inlineStr"/>
       <c r="AH165" t="inlineStr"/>
       <c r="AI165" t="n">
-        <v>2.94</v>
+        <v>3.19</v>
       </c>
       <c r="AJ165" t="inlineStr"/>
       <c r="AK165" t="n">
-        <v>-3.45</v>
+        <v>-3.7</v>
       </c>
       <c r="AL165" t="inlineStr"/>
     </row>
@@ -16067,11 +16067,11 @@
       <c r="AG166" t="inlineStr"/>
       <c r="AH166" t="inlineStr"/>
       <c r="AI166" t="n">
-        <v>2.94</v>
+        <v>3.19</v>
       </c>
       <c r="AJ166" t="inlineStr"/>
       <c r="AK166" t="n">
-        <v>-9.460000000000001</v>
+        <v>-9.710000000000001</v>
       </c>
       <c r="AL166" t="inlineStr"/>
     </row>
@@ -16185,11 +16185,11 @@
       <c r="AG167" t="inlineStr"/>
       <c r="AH167" t="inlineStr"/>
       <c r="AI167" t="n">
-        <v>2.94</v>
+        <v>3.19</v>
       </c>
       <c r="AJ167" t="inlineStr"/>
       <c r="AK167" t="n">
-        <v>-3.49</v>
+        <v>-3.74</v>
       </c>
       <c r="AL167" t="inlineStr"/>
     </row>
@@ -16303,11 +16303,11 @@
       <c r="AG168" t="inlineStr"/>
       <c r="AH168" t="inlineStr"/>
       <c r="AI168" t="n">
-        <v>3.04</v>
+        <v>3.3</v>
       </c>
       <c r="AJ168" t="inlineStr"/>
       <c r="AK168" t="n">
-        <v>-4.98</v>
+        <v>-5.24</v>
       </c>
       <c r="AL168" t="inlineStr"/>
     </row>
@@ -16425,11 +16425,11 @@
       <c r="AG169" t="inlineStr"/>
       <c r="AH169" t="inlineStr"/>
       <c r="AI169" t="n">
-        <v>3.04</v>
+        <v>3.3</v>
       </c>
       <c r="AJ169" t="inlineStr"/>
       <c r="AK169" t="n">
-        <v>-3.21</v>
+        <v>-3.47</v>
       </c>
       <c r="AL169" t="inlineStr"/>
     </row>
@@ -16547,11 +16547,11 @@
       <c r="AG170" t="inlineStr"/>
       <c r="AH170" t="inlineStr"/>
       <c r="AI170" t="n">
-        <v>3.04</v>
+        <v>3.3</v>
       </c>
       <c r="AJ170" t="inlineStr"/>
       <c r="AK170" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="AL170" t="inlineStr"/>
     </row>
@@ -16663,11 +16663,11 @@
       <c r="AG171" t="inlineStr"/>
       <c r="AH171" t="inlineStr"/>
       <c r="AI171" t="n">
-        <v>3.14</v>
+        <v>3.39</v>
       </c>
       <c r="AJ171" t="inlineStr"/>
       <c r="AK171" t="n">
-        <v>-14</v>
+        <v>-14.25</v>
       </c>
       <c r="AL171" t="inlineStr">
         <is>
@@ -16785,11 +16785,11 @@
       <c r="AG172" t="inlineStr"/>
       <c r="AH172" t="inlineStr"/>
       <c r="AI172" t="n">
-        <v>3.02</v>
+        <v>3.27</v>
       </c>
       <c r="AJ172" t="inlineStr"/>
       <c r="AK172" t="n">
-        <v>4.95</v>
+        <v>4.69</v>
       </c>
       <c r="AL172" t="inlineStr"/>
     </row>
@@ -16903,11 +16903,11 @@
       <c r="AG173" t="inlineStr"/>
       <c r="AH173" t="inlineStr"/>
       <c r="AI173" t="n">
-        <v>3.02</v>
+        <v>3.27</v>
       </c>
       <c r="AJ173" t="inlineStr"/>
       <c r="AK173" t="n">
-        <v>-5.24</v>
+        <v>-5.5</v>
       </c>
       <c r="AL173" t="inlineStr"/>
     </row>
@@ -17021,11 +17021,11 @@
       <c r="AG174" t="inlineStr"/>
       <c r="AH174" t="inlineStr"/>
       <c r="AI174" t="n">
-        <v>2.02</v>
+        <v>2.27</v>
       </c>
       <c r="AJ174" t="inlineStr"/>
       <c r="AK174" t="n">
-        <v>27.08</v>
+        <v>26.83</v>
       </c>
       <c r="AL174" t="inlineStr"/>
     </row>
@@ -17139,11 +17139,11 @@
       <c r="AG175" t="inlineStr"/>
       <c r="AH175" t="inlineStr"/>
       <c r="AI175" t="n">
-        <v>2.02</v>
+        <v>2.27</v>
       </c>
       <c r="AJ175" t="inlineStr"/>
       <c r="AK175" t="n">
-        <v>0.91</v>
+        <v>0.66</v>
       </c>
       <c r="AL175" t="inlineStr"/>
     </row>
@@ -17257,11 +17257,11 @@
       <c r="AG176" t="inlineStr"/>
       <c r="AH176" t="inlineStr"/>
       <c r="AI176" t="n">
-        <v>2.06</v>
+        <v>2.32</v>
       </c>
       <c r="AJ176" t="inlineStr"/>
       <c r="AK176" t="n">
-        <v>18.3</v>
+        <v>18.05</v>
       </c>
       <c r="AL176" t="inlineStr"/>
     </row>
@@ -17371,11 +17371,11 @@
       <c r="AG177" t="inlineStr"/>
       <c r="AH177" t="inlineStr"/>
       <c r="AI177" t="n">
-        <v>2.06</v>
+        <v>2.32</v>
       </c>
       <c r="AJ177" t="inlineStr"/>
       <c r="AK177" t="n">
-        <v>-15.81</v>
+        <v>-16.07</v>
       </c>
       <c r="AL177" t="inlineStr">
         <is>
@@ -17493,11 +17493,11 @@
       <c r="AG178" t="inlineStr"/>
       <c r="AH178" t="inlineStr"/>
       <c r="AI178" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ178" t="inlineStr"/>
       <c r="AK178" t="n">
-        <v>-0.63</v>
+        <v>-0.88</v>
       </c>
       <c r="AL178" t="inlineStr">
         <is>
@@ -17611,11 +17611,11 @@
       <c r="AG179" t="inlineStr"/>
       <c r="AH179" t="inlineStr"/>
       <c r="AI179" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ179" t="inlineStr"/>
       <c r="AK179" t="n">
-        <v>24.59</v>
+        <v>24.34</v>
       </c>
       <c r="AL179" t="inlineStr">
         <is>
@@ -17729,11 +17729,11 @@
       <c r="AG180" t="inlineStr"/>
       <c r="AH180" t="inlineStr"/>
       <c r="AI180" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ180" t="inlineStr"/>
       <c r="AK180" t="n">
-        <v>-12.11</v>
+        <v>-12.36</v>
       </c>
       <c r="AL180" t="inlineStr">
         <is>
@@ -17851,11 +17851,11 @@
       <c r="AG181" t="inlineStr"/>
       <c r="AH181" t="inlineStr"/>
       <c r="AI181" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ181" t="inlineStr"/>
       <c r="AK181" t="n">
-        <v>25.23</v>
+        <v>24.98</v>
       </c>
       <c r="AL181" t="inlineStr">
         <is>
@@ -17973,11 +17973,11 @@
       <c r="AG182" t="inlineStr"/>
       <c r="AH182" t="inlineStr"/>
       <c r="AI182" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ182" t="inlineStr"/>
       <c r="AK182" t="n">
-        <v>-3.94</v>
+        <v>-4.2</v>
       </c>
       <c r="AL182" t="inlineStr">
         <is>
@@ -18091,11 +18091,11 @@
       <c r="AG183" t="inlineStr"/>
       <c r="AH183" t="inlineStr"/>
       <c r="AI183" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ183" t="inlineStr"/>
       <c r="AK183" t="n">
-        <v>12.75</v>
+        <v>12.49</v>
       </c>
       <c r="AL183" t="inlineStr">
         <is>
@@ -18209,11 +18209,11 @@
       <c r="AG184" t="inlineStr"/>
       <c r="AH184" t="inlineStr"/>
       <c r="AI184" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ184" t="inlineStr"/>
       <c r="AK184" t="n">
-        <v>30.12</v>
+        <v>29.86</v>
       </c>
       <c r="AL184" t="inlineStr"/>
     </row>
@@ -18327,11 +18327,11 @@
       <c r="AG185" t="inlineStr"/>
       <c r="AH185" t="inlineStr"/>
       <c r="AI185" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ185" t="inlineStr"/>
       <c r="AK185" t="n">
-        <v>17.6</v>
+        <v>17.35</v>
       </c>
       <c r="AL185" t="inlineStr">
         <is>
@@ -18445,11 +18445,11 @@
       <c r="AG186" t="inlineStr"/>
       <c r="AH186" t="inlineStr"/>
       <c r="AI186" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ186" t="inlineStr"/>
       <c r="AK186" t="n">
-        <v>4.06</v>
+        <v>3.81</v>
       </c>
       <c r="AL186" t="inlineStr">
         <is>
@@ -18563,11 +18563,11 @@
       <c r="AG187" t="inlineStr"/>
       <c r="AH187" t="inlineStr"/>
       <c r="AI187" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ187" t="inlineStr"/>
       <c r="AK187" t="n">
-        <v>-6.68</v>
+        <v>-6.93</v>
       </c>
       <c r="AL187" t="inlineStr">
         <is>
@@ -18679,11 +18679,11 @@
       <c r="AG188" t="inlineStr"/>
       <c r="AH188" t="inlineStr"/>
       <c r="AI188" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ188" t="inlineStr"/>
       <c r="AK188" t="n">
-        <v>-20.39</v>
+        <v>-20.65</v>
       </c>
       <c r="AL188" t="inlineStr">
         <is>
@@ -18797,11 +18797,11 @@
       <c r="AG189" t="inlineStr"/>
       <c r="AH189" t="inlineStr"/>
       <c r="AI189" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ189" t="inlineStr"/>
       <c r="AK189" t="n">
-        <v>9.33</v>
+        <v>9.08</v>
       </c>
       <c r="AL189" t="inlineStr">
         <is>
@@ -18915,11 +18915,11 @@
       <c r="AG190" t="inlineStr"/>
       <c r="AH190" t="inlineStr"/>
       <c r="AI190" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ190" t="inlineStr"/>
       <c r="AK190" t="n">
-        <v>19.87</v>
+        <v>19.61</v>
       </c>
       <c r="AL190" t="inlineStr">
         <is>
@@ -19033,11 +19033,11 @@
       <c r="AG191" t="inlineStr"/>
       <c r="AH191" t="inlineStr"/>
       <c r="AI191" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ191" t="inlineStr"/>
       <c r="AK191" t="n">
-        <v>40.19</v>
+        <v>39.94</v>
       </c>
       <c r="AL191" t="inlineStr"/>
     </row>
@@ -19145,11 +19145,11 @@
       <c r="AG192" t="inlineStr"/>
       <c r="AH192" t="inlineStr"/>
       <c r="AI192" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ192" t="inlineStr"/>
       <c r="AK192" t="n">
-        <v>-11.84</v>
+        <v>-12.09</v>
       </c>
       <c r="AL192" t="inlineStr">
         <is>
@@ -19267,11 +19267,11 @@
       <c r="AG193" t="inlineStr"/>
       <c r="AH193" t="inlineStr"/>
       <c r="AI193" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ193" t="inlineStr"/>
       <c r="AK193" t="n">
-        <v>-4.69</v>
+        <v>-4.94</v>
       </c>
       <c r="AL193" t="inlineStr">
         <is>
@@ -19381,11 +19381,11 @@
       <c r="AG194" t="inlineStr"/>
       <c r="AH194" t="inlineStr"/>
       <c r="AI194" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ194" t="inlineStr"/>
       <c r="AK194" t="n">
-        <v>-20.47</v>
+        <v>-20.73</v>
       </c>
       <c r="AL194" t="inlineStr">
         <is>
@@ -19503,11 +19503,11 @@
       <c r="AG195" t="inlineStr"/>
       <c r="AH195" t="inlineStr"/>
       <c r="AI195" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ195" t="inlineStr"/>
       <c r="AK195" t="n">
-        <v>4.99</v>
+        <v>4.74</v>
       </c>
       <c r="AL195" t="inlineStr">
         <is>
@@ -19621,11 +19621,11 @@
       <c r="AG196" t="inlineStr"/>
       <c r="AH196" t="inlineStr"/>
       <c r="AI196" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ196" t="inlineStr"/>
       <c r="AK196" t="n">
-        <v>7.99</v>
+        <v>7.73</v>
       </c>
       <c r="AL196" t="inlineStr">
         <is>
@@ -19732,7 +19732,7 @@
         <v>-21.66</v>
       </c>
       <c r="AD197" t="n">
-        <v>20.21</v>
+        <v>20.22</v>
       </c>
       <c r="AE197" t="n">
         <v>44</v>
@@ -19743,11 +19743,11 @@
       <c r="AG197" t="inlineStr"/>
       <c r="AH197" t="inlineStr"/>
       <c r="AI197" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ197" t="inlineStr"/>
       <c r="AK197" t="n">
-        <v>17.54</v>
+        <v>17.28</v>
       </c>
       <c r="AL197" t="inlineStr">
         <is>
@@ -19861,11 +19861,11 @@
       <c r="AG198" t="inlineStr"/>
       <c r="AH198" t="inlineStr"/>
       <c r="AI198" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ198" t="inlineStr"/>
       <c r="AK198" t="n">
-        <v>148.68</v>
+        <v>148.42</v>
       </c>
       <c r="AL198" t="inlineStr">
         <is>
@@ -19979,11 +19979,11 @@
       <c r="AG199" t="inlineStr"/>
       <c r="AH199" t="inlineStr"/>
       <c r="AI199" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ199" t="inlineStr"/>
       <c r="AK199" t="n">
-        <v>-8.949999999999999</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="AL199" t="inlineStr">
         <is>
@@ -20101,11 +20101,11 @@
       <c r="AG200" t="inlineStr"/>
       <c r="AH200" t="inlineStr"/>
       <c r="AI200" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ200" t="inlineStr"/>
       <c r="AK200" t="n">
-        <v>-0.87</v>
+        <v>-1.12</v>
       </c>
       <c r="AL200" t="inlineStr">
         <is>
@@ -20219,11 +20219,11 @@
       <c r="AG201" t="inlineStr"/>
       <c r="AH201" t="inlineStr"/>
       <c r="AI201" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ201" t="inlineStr"/>
       <c r="AK201" t="n">
-        <v>58.58</v>
+        <v>58.32</v>
       </c>
       <c r="AL201" t="inlineStr"/>
     </row>
@@ -20333,11 +20333,11 @@
       <c r="AG202" t="inlineStr"/>
       <c r="AH202" t="inlineStr"/>
       <c r="AI202" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ202" t="inlineStr"/>
       <c r="AK202" t="n">
-        <v>8.9</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="AL202" t="inlineStr"/>
     </row>
@@ -20445,11 +20445,11 @@
       <c r="AG203" t="inlineStr"/>
       <c r="AH203" t="inlineStr"/>
       <c r="AI203" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ203" t="inlineStr"/>
       <c r="AK203" t="n">
-        <v>-12.25</v>
+        <v>-12.5</v>
       </c>
       <c r="AL203" t="inlineStr">
         <is>
@@ -20561,11 +20561,11 @@
       <c r="AG204" t="inlineStr"/>
       <c r="AH204" t="inlineStr"/>
       <c r="AI204" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ204" t="inlineStr"/>
       <c r="AK204" t="n">
-        <v>6.32</v>
+        <v>6.07</v>
       </c>
       <c r="AL204" t="inlineStr">
         <is>
@@ -20681,11 +20681,11 @@
       <c r="AG205" t="inlineStr"/>
       <c r="AH205" t="inlineStr"/>
       <c r="AI205" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ205" t="inlineStr"/>
       <c r="AK205" t="n">
-        <v>-11.43</v>
+        <v>-11.68</v>
       </c>
       <c r="AL205" t="inlineStr">
         <is>
@@ -20803,11 +20803,11 @@
       <c r="AG206" t="inlineStr"/>
       <c r="AH206" t="inlineStr"/>
       <c r="AI206" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ206" t="inlineStr"/>
       <c r="AK206" t="n">
-        <v>-17.23</v>
+        <v>-17.48</v>
       </c>
       <c r="AL206" t="inlineStr">
         <is>
@@ -20925,11 +20925,11 @@
       <c r="AG207" t="inlineStr"/>
       <c r="AH207" t="inlineStr"/>
       <c r="AI207" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ207" t="inlineStr"/>
       <c r="AK207" t="n">
-        <v>-26.36</v>
+        <v>-26.61</v>
       </c>
       <c r="AL207" t="inlineStr">
         <is>
@@ -21039,11 +21039,11 @@
       <c r="AG208" t="inlineStr"/>
       <c r="AH208" t="inlineStr"/>
       <c r="AI208" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ208" t="inlineStr"/>
       <c r="AK208" t="n">
-        <v>-24.1</v>
+        <v>-24.35</v>
       </c>
       <c r="AL208" t="inlineStr">
         <is>
@@ -21157,11 +21157,11 @@
       <c r="AG209" t="inlineStr"/>
       <c r="AH209" t="inlineStr"/>
       <c r="AI209" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ209" t="inlineStr"/>
       <c r="AK209" t="n">
-        <v>-37.21</v>
+        <v>-37.46</v>
       </c>
       <c r="AL209" t="inlineStr">
         <is>
@@ -21279,11 +21279,11 @@
       <c r="AG210" t="inlineStr"/>
       <c r="AH210" t="inlineStr"/>
       <c r="AI210" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ210" t="inlineStr"/>
       <c r="AK210" t="n">
-        <v>-10.73</v>
+        <v>-10.98</v>
       </c>
       <c r="AL210" t="inlineStr"/>
     </row>
@@ -21379,7 +21379,7 @@
         <v>-16.43</v>
       </c>
       <c r="AC211" t="n">
-        <v>-17.51</v>
+        <v>-17.52</v>
       </c>
       <c r="AD211" t="n">
         <v>4.41</v>
@@ -21393,11 +21393,11 @@
       <c r="AG211" t="inlineStr"/>
       <c r="AH211" t="inlineStr"/>
       <c r="AI211" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ211" t="inlineStr"/>
       <c r="AK211" t="n">
-        <v>-18.39</v>
+        <v>-18.64</v>
       </c>
       <c r="AL211" t="inlineStr">
         <is>
@@ -21513,11 +21513,11 @@
       <c r="AG212" t="inlineStr"/>
       <c r="AH212" t="inlineStr"/>
       <c r="AI212" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ212" t="inlineStr"/>
       <c r="AK212" t="n">
-        <v>-1.2</v>
+        <v>-1.45</v>
       </c>
       <c r="AL212" t="inlineStr"/>
     </row>
@@ -21635,11 +21635,11 @@
       <c r="AG213" t="inlineStr"/>
       <c r="AH213" t="inlineStr"/>
       <c r="AI213" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ213" t="inlineStr"/>
       <c r="AK213" t="n">
-        <v>29.31</v>
+        <v>29.05</v>
       </c>
       <c r="AL213" t="inlineStr"/>
     </row>
@@ -21753,11 +21753,11 @@
       <c r="AG214" t="inlineStr"/>
       <c r="AH214" t="inlineStr"/>
       <c r="AI214" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ214" t="inlineStr"/>
       <c r="AK214" t="n">
-        <v>24.64</v>
+        <v>24.39</v>
       </c>
       <c r="AL214" t="inlineStr"/>
     </row>
@@ -21871,11 +21871,11 @@
       <c r="AG215" t="inlineStr"/>
       <c r="AH215" t="inlineStr"/>
       <c r="AI215" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ215" t="inlineStr"/>
       <c r="AK215" t="n">
-        <v>5.23</v>
+        <v>4.97</v>
       </c>
       <c r="AL215" t="inlineStr">
         <is>
@@ -21989,11 +21989,11 @@
       <c r="AG216" t="inlineStr"/>
       <c r="AH216" t="inlineStr"/>
       <c r="AI216" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ216" t="inlineStr"/>
       <c r="AK216" t="n">
-        <v>16.82</v>
+        <v>16.57</v>
       </c>
       <c r="AL216" t="inlineStr"/>
     </row>
@@ -22107,11 +22107,11 @@
       <c r="AG217" t="inlineStr"/>
       <c r="AH217" t="inlineStr"/>
       <c r="AI217" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ217" t="inlineStr"/>
       <c r="AK217" t="n">
-        <v>-7.54</v>
+        <v>-7.8</v>
       </c>
       <c r="AL217" t="inlineStr">
         <is>
@@ -22225,11 +22225,11 @@
       <c r="AG218" t="inlineStr"/>
       <c r="AH218" t="inlineStr"/>
       <c r="AI218" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ218" t="inlineStr"/>
       <c r="AK218" t="n">
-        <v>-30.83</v>
+        <v>-31.08</v>
       </c>
       <c r="AL218" t="inlineStr">
         <is>
@@ -22347,11 +22347,11 @@
       <c r="AG219" t="inlineStr"/>
       <c r="AH219" t="inlineStr"/>
       <c r="AI219" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ219" t="inlineStr"/>
       <c r="AK219" t="n">
-        <v>-4.3</v>
+        <v>-4.55</v>
       </c>
       <c r="AL219" t="inlineStr">
         <is>
@@ -22451,7 +22451,7 @@
         <v>-6.54</v>
       </c>
       <c r="AC220" t="n">
-        <v>-6.64</v>
+        <v>-6.63</v>
       </c>
       <c r="AD220" t="n">
         <v>12.16</v>
@@ -22465,11 +22465,11 @@
       <c r="AG220" t="inlineStr"/>
       <c r="AH220" t="inlineStr"/>
       <c r="AI220" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ220" t="inlineStr"/>
       <c r="AK220" t="n">
-        <v>-8.49</v>
+        <v>-8.75</v>
       </c>
       <c r="AL220" t="inlineStr"/>
     </row>
@@ -22579,11 +22579,11 @@
       <c r="AG221" t="inlineStr"/>
       <c r="AH221" t="inlineStr"/>
       <c r="AI221" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ221" t="inlineStr"/>
       <c r="AK221" t="n">
-        <v>4.17</v>
+        <v>3.92</v>
       </c>
       <c r="AL221" t="inlineStr"/>
     </row>
@@ -22697,11 +22697,11 @@
       <c r="AG222" t="inlineStr"/>
       <c r="AH222" t="inlineStr"/>
       <c r="AI222" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ222" t="inlineStr"/>
       <c r="AK222" t="n">
-        <v>109.05</v>
+        <v>108.8</v>
       </c>
       <c r="AL222" t="inlineStr"/>
     </row>
@@ -22815,11 +22815,11 @@
       <c r="AG223" t="inlineStr"/>
       <c r="AH223" t="inlineStr"/>
       <c r="AI223" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ223" t="inlineStr"/>
       <c r="AK223" t="n">
-        <v>-5.3</v>
+        <v>-5.56</v>
       </c>
       <c r="AL223" t="inlineStr"/>
     </row>
@@ -22929,11 +22929,11 @@
       <c r="AG224" t="inlineStr"/>
       <c r="AH224" t="inlineStr"/>
       <c r="AI224" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ224" t="inlineStr"/>
       <c r="AK224" t="n">
-        <v>32.66</v>
+        <v>32.41</v>
       </c>
       <c r="AL224" t="inlineStr"/>
     </row>
@@ -23047,11 +23047,11 @@
       <c r="AG225" t="inlineStr"/>
       <c r="AH225" t="inlineStr"/>
       <c r="AI225" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ225" t="inlineStr"/>
       <c r="AK225" t="n">
-        <v>-2.21</v>
+        <v>-2.47</v>
       </c>
       <c r="AL225" t="inlineStr"/>
     </row>
@@ -23165,11 +23165,11 @@
       <c r="AG226" t="inlineStr"/>
       <c r="AH226" t="inlineStr"/>
       <c r="AI226" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ226" t="inlineStr"/>
       <c r="AK226" t="n">
-        <v>5.43</v>
+        <v>5.17</v>
       </c>
       <c r="AL226" t="inlineStr">
         <is>
@@ -23283,11 +23283,11 @@
       <c r="AG227" t="inlineStr"/>
       <c r="AH227" t="inlineStr"/>
       <c r="AI227" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ227" t="inlineStr"/>
       <c r="AK227" t="n">
-        <v>-17.53</v>
+        <v>-17.78</v>
       </c>
       <c r="AL227" t="inlineStr">
         <is>
@@ -23521,11 +23521,11 @@
       <c r="AG229" t="inlineStr"/>
       <c r="AH229" t="inlineStr"/>
       <c r="AI229" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ229" t="inlineStr"/>
       <c r="AK229" t="n">
-        <v>-3.6</v>
+        <v>-3.85</v>
       </c>
       <c r="AL229" t="inlineStr">
         <is>
@@ -23639,11 +23639,11 @@
       <c r="AG230" t="inlineStr"/>
       <c r="AH230" t="inlineStr"/>
       <c r="AI230" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ230" t="inlineStr"/>
       <c r="AK230" t="n">
-        <v>-3.39</v>
+        <v>-3.65</v>
       </c>
       <c r="AL230" t="inlineStr"/>
     </row>
@@ -23877,11 +23877,11 @@
       <c r="AG232" t="inlineStr"/>
       <c r="AH232" t="inlineStr"/>
       <c r="AI232" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ232" t="inlineStr"/>
       <c r="AK232" t="n">
-        <v>2.23</v>
+        <v>1.98</v>
       </c>
       <c r="AL232" t="inlineStr">
         <is>
@@ -23997,11 +23997,11 @@
       <c r="AG233" t="inlineStr"/>
       <c r="AH233" t="inlineStr"/>
       <c r="AI233" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ233" t="inlineStr"/>
       <c r="AK233" t="n">
-        <v>-10</v>
+        <v>-10.25</v>
       </c>
       <c r="AL233" t="inlineStr">
         <is>
@@ -24113,11 +24113,11 @@
       <c r="AG234" t="inlineStr"/>
       <c r="AH234" t="inlineStr"/>
       <c r="AI234" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ234" t="inlineStr"/>
       <c r="AK234" t="n">
-        <v>-17.4</v>
+        <v>-17.65</v>
       </c>
       <c r="AL234" t="inlineStr">
         <is>
@@ -24229,11 +24229,11 @@
       <c r="AG235" t="inlineStr"/>
       <c r="AH235" t="inlineStr"/>
       <c r="AI235" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ235" t="inlineStr"/>
       <c r="AK235" t="n">
-        <v>-6.81</v>
+        <v>-7.06</v>
       </c>
       <c r="AL235" t="inlineStr">
         <is>
@@ -24347,11 +24347,11 @@
       <c r="AG236" t="inlineStr"/>
       <c r="AH236" t="inlineStr"/>
       <c r="AI236" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ236" t="inlineStr"/>
       <c r="AK236" t="n">
-        <v>14.6</v>
+        <v>14.35</v>
       </c>
       <c r="AL236" t="inlineStr">
         <is>
@@ -24463,11 +24463,11 @@
       <c r="AG237" t="inlineStr"/>
       <c r="AH237" t="inlineStr"/>
       <c r="AI237" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ237" t="inlineStr"/>
       <c r="AK237" t="n">
-        <v>3.77</v>
+        <v>3.52</v>
       </c>
       <c r="AL237" t="inlineStr"/>
     </row>
@@ -24577,11 +24577,11 @@
       <c r="AG238" t="inlineStr"/>
       <c r="AH238" t="inlineStr"/>
       <c r="AI238" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ238" t="inlineStr"/>
       <c r="AK238" t="n">
-        <v>-2.23</v>
+        <v>-2.48</v>
       </c>
       <c r="AL238" t="inlineStr"/>
     </row>
@@ -24691,11 +24691,11 @@
       <c r="AG239" t="inlineStr"/>
       <c r="AH239" t="inlineStr"/>
       <c r="AI239" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ239" t="inlineStr"/>
       <c r="AK239" t="n">
-        <v>20.84</v>
+        <v>20.58</v>
       </c>
       <c r="AL239" t="inlineStr"/>
     </row>
@@ -24805,11 +24805,11 @@
       <c r="AG240" t="inlineStr"/>
       <c r="AH240" t="inlineStr"/>
       <c r="AI240" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ240" t="inlineStr"/>
       <c r="AK240" t="n">
-        <v>9.77</v>
+        <v>9.52</v>
       </c>
       <c r="AL240" t="inlineStr"/>
     </row>
@@ -24923,11 +24923,11 @@
       <c r="AG241" t="inlineStr"/>
       <c r="AH241" t="inlineStr"/>
       <c r="AI241" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ241" t="inlineStr"/>
       <c r="AK241" t="n">
-        <v>-1.25</v>
+        <v>-1.51</v>
       </c>
       <c r="AL241" t="inlineStr"/>
     </row>
@@ -25033,11 +25033,11 @@
       <c r="AG242" t="inlineStr"/>
       <c r="AH242" t="inlineStr"/>
       <c r="AI242" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ242" t="inlineStr"/>
       <c r="AK242" t="n">
-        <v>-23.94</v>
+        <v>-24.2</v>
       </c>
       <c r="AL242" t="inlineStr">
         <is>
@@ -25151,11 +25151,11 @@
       <c r="AG243" t="inlineStr"/>
       <c r="AH243" t="inlineStr"/>
       <c r="AI243" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ243" t="inlineStr"/>
       <c r="AK243" t="n">
-        <v>-41.41</v>
+        <v>-41.66</v>
       </c>
       <c r="AL243" t="inlineStr">
         <is>
@@ -25265,11 +25265,11 @@
       <c r="AG244" t="inlineStr"/>
       <c r="AH244" t="inlineStr"/>
       <c r="AI244" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ244" t="inlineStr"/>
       <c r="AK244" t="n">
-        <v>-24.19</v>
+        <v>-24.45</v>
       </c>
       <c r="AL244" t="inlineStr">
         <is>
@@ -25387,11 +25387,11 @@
       <c r="AG245" t="inlineStr"/>
       <c r="AH245" t="inlineStr"/>
       <c r="AI245" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ245" t="inlineStr"/>
       <c r="AK245" t="n">
-        <v>-1.63</v>
+        <v>-1.88</v>
       </c>
       <c r="AL245" t="inlineStr"/>
     </row>
@@ -25509,11 +25509,11 @@
       <c r="AG246" t="inlineStr"/>
       <c r="AH246" t="inlineStr"/>
       <c r="AI246" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ246" t="inlineStr"/>
       <c r="AK246" t="n">
-        <v>-21.72</v>
+        <v>-21.97</v>
       </c>
       <c r="AL246" t="inlineStr">
         <is>
@@ -25627,11 +25627,11 @@
       <c r="AG247" t="inlineStr"/>
       <c r="AH247" t="inlineStr"/>
       <c r="AI247" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ247" t="inlineStr"/>
       <c r="AK247" t="n">
-        <v>-13.05</v>
+        <v>-13.3</v>
       </c>
       <c r="AL247" t="inlineStr">
         <is>
@@ -25745,11 +25745,11 @@
       <c r="AG248" t="inlineStr"/>
       <c r="AH248" t="inlineStr"/>
       <c r="AI248" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ248" t="inlineStr"/>
       <c r="AK248" t="n">
-        <v>2.48</v>
+        <v>2.23</v>
       </c>
       <c r="AL248" t="inlineStr"/>
     </row>
@@ -25859,11 +25859,11 @@
       <c r="AG249" t="inlineStr"/>
       <c r="AH249" t="inlineStr"/>
       <c r="AI249" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ249" t="inlineStr"/>
       <c r="AK249" t="n">
-        <v>0.54</v>
+        <v>0.29</v>
       </c>
       <c r="AL249" t="inlineStr">
         <is>
@@ -25977,11 +25977,11 @@
       <c r="AG250" t="inlineStr"/>
       <c r="AH250" t="inlineStr"/>
       <c r="AI250" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ250" t="inlineStr"/>
       <c r="AK250" t="n">
-        <v>-4.77</v>
+        <v>-5.02</v>
       </c>
       <c r="AL250" t="inlineStr"/>
     </row>
@@ -26085,7 +26085,7 @@
         <v>-13.68</v>
       </c>
       <c r="AC251" t="n">
-        <v>-14.65</v>
+        <v>-14.67</v>
       </c>
       <c r="AD251" t="n">
         <v>52.35</v>
@@ -26099,11 +26099,11 @@
       <c r="AG251" t="inlineStr"/>
       <c r="AH251" t="inlineStr"/>
       <c r="AI251" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ251" t="inlineStr"/>
       <c r="AK251" t="n">
-        <v>-15.64</v>
+        <v>-15.89</v>
       </c>
       <c r="AL251" t="inlineStr">
         <is>
@@ -26219,11 +26219,11 @@
       <c r="AG252" t="inlineStr"/>
       <c r="AH252" t="inlineStr"/>
       <c r="AI252" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ252" t="inlineStr"/>
       <c r="AK252" t="n">
-        <v>-38.42</v>
+        <v>-38.67</v>
       </c>
       <c r="AL252" t="inlineStr">
         <is>
@@ -26341,11 +26341,11 @@
       <c r="AG253" t="inlineStr"/>
       <c r="AH253" t="inlineStr"/>
       <c r="AI253" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ253" t="inlineStr"/>
       <c r="AK253" t="n">
-        <v>-8</v>
+        <v>-8.26</v>
       </c>
       <c r="AL253" t="inlineStr"/>
     </row>
@@ -26455,11 +26455,11 @@
       <c r="AG254" t="inlineStr"/>
       <c r="AH254" t="inlineStr"/>
       <c r="AI254" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ254" t="inlineStr"/>
       <c r="AK254" t="n">
-        <v>18.8</v>
+        <v>18.55</v>
       </c>
       <c r="AL254" t="inlineStr"/>
     </row>
@@ -26573,11 +26573,11 @@
       <c r="AG255" t="inlineStr"/>
       <c r="AH255" t="inlineStr"/>
       <c r="AI255" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ255" t="inlineStr"/>
       <c r="AK255" t="n">
-        <v>-12.7</v>
+        <v>-12.95</v>
       </c>
       <c r="AL255" t="inlineStr">
         <is>
@@ -26689,11 +26689,11 @@
       <c r="AG256" t="inlineStr"/>
       <c r="AH256" t="inlineStr"/>
       <c r="AI256" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ256" t="inlineStr"/>
       <c r="AK256" t="n">
-        <v>4.27</v>
+        <v>4.02</v>
       </c>
       <c r="AL256" t="inlineStr"/>
     </row>
@@ -26803,11 +26803,11 @@
       <c r="AG257" t="inlineStr"/>
       <c r="AH257" t="inlineStr"/>
       <c r="AI257" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ257" t="inlineStr"/>
       <c r="AK257" t="n">
-        <v>32.81</v>
+        <v>32.56</v>
       </c>
       <c r="AL257" t="inlineStr"/>
     </row>
@@ -26921,11 +26921,11 @@
       <c r="AG258" t="inlineStr"/>
       <c r="AH258" t="inlineStr"/>
       <c r="AI258" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ258" t="inlineStr"/>
       <c r="AK258" t="n">
-        <v>10.28</v>
+        <v>10.02</v>
       </c>
       <c r="AL258" t="inlineStr"/>
     </row>
@@ -27039,11 +27039,11 @@
       <c r="AG259" t="inlineStr"/>
       <c r="AH259" t="inlineStr"/>
       <c r="AI259" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ259" t="inlineStr"/>
       <c r="AK259" t="n">
-        <v>-13.25</v>
+        <v>-13.5</v>
       </c>
       <c r="AL259" t="inlineStr">
         <is>
@@ -27159,11 +27159,11 @@
       <c r="AG260" t="inlineStr"/>
       <c r="AH260" t="inlineStr"/>
       <c r="AI260" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ260" t="inlineStr"/>
       <c r="AK260" t="n">
-        <v>-14.01</v>
+        <v>-14.26</v>
       </c>
       <c r="AL260" t="inlineStr">
         <is>
@@ -27275,11 +27275,11 @@
       <c r="AG261" t="inlineStr"/>
       <c r="AH261" t="inlineStr"/>
       <c r="AI261" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ261" t="inlineStr"/>
       <c r="AK261" t="n">
-        <v>-9.99</v>
+        <v>-10.24</v>
       </c>
       <c r="AL261" t="inlineStr"/>
     </row>
@@ -27387,11 +27387,11 @@
       <c r="AG262" t="inlineStr"/>
       <c r="AH262" t="inlineStr"/>
       <c r="AI262" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ262" t="inlineStr"/>
       <c r="AK262" t="n">
-        <v>45.93</v>
+        <v>45.67</v>
       </c>
       <c r="AL262" t="inlineStr"/>
     </row>
@@ -27501,11 +27501,11 @@
       <c r="AG263" t="inlineStr"/>
       <c r="AH263" t="inlineStr"/>
       <c r="AI263" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ263" t="inlineStr"/>
       <c r="AK263" t="n">
-        <v>-0.17</v>
+        <v>-0.42</v>
       </c>
       <c r="AL263" t="inlineStr">
         <is>
@@ -27627,11 +27627,11 @@
       <c r="AG264" t="inlineStr"/>
       <c r="AH264" t="inlineStr"/>
       <c r="AI264" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ264" t="inlineStr"/>
       <c r="AK264" t="n">
-        <v>52.93</v>
+        <v>52.68</v>
       </c>
       <c r="AL264" t="inlineStr"/>
     </row>
@@ -27741,11 +27741,11 @@
       <c r="AG265" t="inlineStr"/>
       <c r="AH265" t="inlineStr"/>
       <c r="AI265" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ265" t="inlineStr"/>
       <c r="AK265" t="n">
-        <v>14.95</v>
+        <v>14.7</v>
       </c>
       <c r="AL265" t="inlineStr">
         <is>
@@ -27855,11 +27855,11 @@
       <c r="AG266" t="inlineStr"/>
       <c r="AH266" t="inlineStr"/>
       <c r="AI266" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ266" t="inlineStr"/>
       <c r="AK266" t="n">
-        <v>-15.17</v>
+        <v>-15.42</v>
       </c>
       <c r="AL266" t="inlineStr">
         <is>
@@ -27977,11 +27977,11 @@
       <c r="AG267" t="inlineStr"/>
       <c r="AH267" t="inlineStr"/>
       <c r="AI267" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ267" t="inlineStr"/>
       <c r="AK267" t="n">
-        <v>3.39</v>
+        <v>3.14</v>
       </c>
       <c r="AL267" t="inlineStr">
         <is>
@@ -28095,11 +28095,11 @@
       <c r="AG268" t="inlineStr"/>
       <c r="AH268" t="inlineStr"/>
       <c r="AI268" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ268" t="inlineStr"/>
       <c r="AK268" t="n">
-        <v>8.6</v>
+        <v>8.34</v>
       </c>
       <c r="AL268" t="inlineStr"/>
     </row>
@@ -28207,11 +28207,11 @@
       <c r="AG269" t="inlineStr"/>
       <c r="AH269" t="inlineStr"/>
       <c r="AI269" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ269" t="inlineStr"/>
       <c r="AK269" t="n">
-        <v>-1.56</v>
+        <v>-1.81</v>
       </c>
       <c r="AL269" t="inlineStr"/>
     </row>
@@ -28323,11 +28323,11 @@
       <c r="AG270" t="inlineStr"/>
       <c r="AH270" t="inlineStr"/>
       <c r="AI270" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ270" t="inlineStr"/>
       <c r="AK270" t="n">
-        <v>-15.97</v>
+        <v>-16.22</v>
       </c>
       <c r="AL270" t="inlineStr">
         <is>
@@ -28445,11 +28445,11 @@
       <c r="AG271" t="inlineStr"/>
       <c r="AH271" t="inlineStr"/>
       <c r="AI271" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ271" t="inlineStr"/>
       <c r="AK271" t="n">
-        <v>0.68</v>
+        <v>0.43</v>
       </c>
       <c r="AL271" t="inlineStr"/>
     </row>
@@ -28563,11 +28563,11 @@
       <c r="AG272" t="inlineStr"/>
       <c r="AH272" t="inlineStr"/>
       <c r="AI272" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ272" t="inlineStr"/>
       <c r="AK272" t="n">
-        <v>-9.84</v>
+        <v>-10.09</v>
       </c>
       <c r="AL272" t="inlineStr">
         <is>
@@ -28681,11 +28681,11 @@
       <c r="AG273" t="inlineStr"/>
       <c r="AH273" t="inlineStr"/>
       <c r="AI273" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ273" t="inlineStr"/>
       <c r="AK273" t="n">
-        <v>-23.17</v>
+        <v>-23.43</v>
       </c>
       <c r="AL273" t="inlineStr">
         <is>
@@ -28807,11 +28807,11 @@
       <c r="AG274" t="inlineStr"/>
       <c r="AH274" t="inlineStr"/>
       <c r="AI274" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ274" t="inlineStr"/>
       <c r="AK274" t="n">
-        <v>49.1</v>
+        <v>48.85</v>
       </c>
       <c r="AL274" t="inlineStr"/>
     </row>
@@ -28925,11 +28925,11 @@
       <c r="AG275" t="inlineStr"/>
       <c r="AH275" t="inlineStr"/>
       <c r="AI275" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ275" t="inlineStr"/>
       <c r="AK275" t="n">
-        <v>38.96</v>
+        <v>38.71</v>
       </c>
       <c r="AL275" t="inlineStr"/>
     </row>
@@ -29039,11 +29039,11 @@
       <c r="AG276" t="inlineStr"/>
       <c r="AH276" t="inlineStr"/>
       <c r="AI276" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ276" t="inlineStr"/>
       <c r="AK276" t="n">
-        <v>-8.949999999999999</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="AL276" t="inlineStr"/>
     </row>
@@ -29161,11 +29161,11 @@
       <c r="AG277" t="inlineStr"/>
       <c r="AH277" t="inlineStr"/>
       <c r="AI277" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ277" t="inlineStr"/>
       <c r="AK277" t="n">
-        <v>-2.83</v>
+        <v>-3.08</v>
       </c>
       <c r="AL277" t="inlineStr"/>
     </row>
@@ -29277,11 +29277,11 @@
       <c r="AG278" t="inlineStr"/>
       <c r="AH278" t="inlineStr"/>
       <c r="AI278" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ278" t="inlineStr"/>
       <c r="AK278" t="n">
-        <v>-15.85</v>
+        <v>-16.11</v>
       </c>
       <c r="AL278" t="inlineStr">
         <is>
@@ -29399,11 +29399,11 @@
       <c r="AG279" t="inlineStr"/>
       <c r="AH279" t="inlineStr"/>
       <c r="AI279" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ279" t="inlineStr"/>
       <c r="AK279" t="n">
-        <v>10.21</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="AL279" t="inlineStr"/>
     </row>
@@ -29517,11 +29517,11 @@
       <c r="AG280" t="inlineStr"/>
       <c r="AH280" t="inlineStr"/>
       <c r="AI280" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ280" t="inlineStr"/>
       <c r="AK280" t="n">
-        <v>-26.34</v>
+        <v>-26.59</v>
       </c>
       <c r="AL280" t="inlineStr">
         <is>
@@ -29639,11 +29639,11 @@
       <c r="AG281" t="inlineStr"/>
       <c r="AH281" t="inlineStr"/>
       <c r="AI281" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ281" t="inlineStr"/>
       <c r="AK281" t="n">
-        <v>-22.01</v>
+        <v>-22.26</v>
       </c>
       <c r="AL281" t="inlineStr">
         <is>
@@ -29759,11 +29759,11 @@
       <c r="AG282" t="inlineStr"/>
       <c r="AH282" t="inlineStr"/>
       <c r="AI282" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ282" t="inlineStr"/>
       <c r="AK282" t="n">
-        <v>-2.13</v>
+        <v>-2.39</v>
       </c>
       <c r="AL282" t="inlineStr"/>
     </row>
@@ -29871,11 +29871,11 @@
       <c r="AG283" t="inlineStr"/>
       <c r="AH283" t="inlineStr"/>
       <c r="AI283" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ283" t="inlineStr"/>
       <c r="AK283" t="n">
-        <v>-4.27</v>
+        <v>-4.52</v>
       </c>
       <c r="AL283" t="inlineStr"/>
     </row>
@@ -29985,11 +29985,11 @@
       <c r="AG284" t="inlineStr"/>
       <c r="AH284" t="inlineStr"/>
       <c r="AI284" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ284" t="inlineStr"/>
       <c r="AK284" t="n">
-        <v>3.25</v>
+        <v>2.99</v>
       </c>
       <c r="AL284" t="inlineStr"/>
     </row>
@@ -30097,11 +30097,11 @@
       <c r="AG285" t="inlineStr"/>
       <c r="AH285" t="inlineStr"/>
       <c r="AI285" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ285" t="inlineStr"/>
       <c r="AK285" t="n">
-        <v>28.15</v>
+        <v>27.89</v>
       </c>
       <c r="AL285" t="inlineStr"/>
     </row>
@@ -30211,11 +30211,11 @@
       <c r="AG286" t="inlineStr"/>
       <c r="AH286" t="inlineStr"/>
       <c r="AI286" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ286" t="inlineStr"/>
       <c r="AK286" t="n">
-        <v>-10.87</v>
+        <v>-11.13</v>
       </c>
       <c r="AL286" t="inlineStr"/>
     </row>
@@ -30323,11 +30323,11 @@
       <c r="AG287" t="inlineStr"/>
       <c r="AH287" t="inlineStr"/>
       <c r="AI287" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ287" t="inlineStr"/>
       <c r="AK287" t="n">
-        <v>-11.06</v>
+        <v>-11.31</v>
       </c>
       <c r="AL287" t="inlineStr">
         <is>
@@ -30445,11 +30445,11 @@
       <c r="AG288" t="inlineStr"/>
       <c r="AH288" t="inlineStr"/>
       <c r="AI288" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ288" t="inlineStr"/>
       <c r="AK288" t="n">
-        <v>59.01</v>
+        <v>58.76</v>
       </c>
       <c r="AL288" t="inlineStr"/>
     </row>
@@ -30559,11 +30559,11 @@
       <c r="AG289" t="inlineStr"/>
       <c r="AH289" t="inlineStr"/>
       <c r="AI289" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ289" t="inlineStr"/>
       <c r="AK289" t="n">
-        <v>-23.17</v>
+        <v>-23.43</v>
       </c>
       <c r="AL289" t="inlineStr">
         <is>
@@ -30681,11 +30681,11 @@
       <c r="AG290" t="inlineStr"/>
       <c r="AH290" t="inlineStr"/>
       <c r="AI290" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ290" t="inlineStr"/>
       <c r="AK290" t="n">
-        <v>-9.539999999999999</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="AL290" t="inlineStr"/>
     </row>
@@ -30791,11 +30791,11 @@
       <c r="AG291" t="inlineStr"/>
       <c r="AH291" t="inlineStr"/>
       <c r="AI291" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ291" t="inlineStr"/>
       <c r="AK291" t="n">
-        <v>-20.33</v>
+        <v>-20.58</v>
       </c>
       <c r="AL291" t="inlineStr">
         <is>
@@ -30909,11 +30909,11 @@
       <c r="AG292" t="inlineStr"/>
       <c r="AH292" t="inlineStr"/>
       <c r="AI292" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ292" t="inlineStr"/>
       <c r="AK292" t="n">
-        <v>-10.6</v>
+        <v>-10.85</v>
       </c>
       <c r="AL292" t="inlineStr">
         <is>
@@ -31027,11 +31027,11 @@
       <c r="AG293" t="inlineStr"/>
       <c r="AH293" t="inlineStr"/>
       <c r="AI293" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ293" t="inlineStr"/>
       <c r="AK293" t="n">
-        <v>-13.75</v>
+        <v>-14</v>
       </c>
       <c r="AL293" t="inlineStr">
         <is>
@@ -31149,11 +31149,11 @@
       <c r="AG294" t="inlineStr"/>
       <c r="AH294" t="inlineStr"/>
       <c r="AI294" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ294" t="inlineStr"/>
       <c r="AK294" t="n">
-        <v>-4.6</v>
+        <v>-4.85</v>
       </c>
       <c r="AL294" t="inlineStr">
         <is>
@@ -31271,11 +31271,11 @@
       <c r="AG295" t="inlineStr"/>
       <c r="AH295" t="inlineStr"/>
       <c r="AI295" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ295" t="inlineStr"/>
       <c r="AK295" t="n">
-        <v>15.06</v>
+        <v>14.81</v>
       </c>
       <c r="AL295" t="inlineStr">
         <is>
@@ -31397,11 +31397,11 @@
       <c r="AG296" t="inlineStr"/>
       <c r="AH296" t="inlineStr"/>
       <c r="AI296" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ296" t="inlineStr"/>
       <c r="AK296" t="n">
-        <v>41.44</v>
+        <v>41.19</v>
       </c>
       <c r="AL296" t="inlineStr"/>
     </row>
@@ -31515,11 +31515,11 @@
       <c r="AG297" t="inlineStr"/>
       <c r="AH297" t="inlineStr"/>
       <c r="AI297" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ297" t="inlineStr"/>
       <c r="AK297" t="n">
-        <v>31.97</v>
+        <v>31.71</v>
       </c>
       <c r="AL297" t="inlineStr"/>
     </row>
@@ -31635,11 +31635,11 @@
       <c r="AG298" t="inlineStr"/>
       <c r="AH298" t="inlineStr"/>
       <c r="AI298" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ298" t="inlineStr"/>
       <c r="AK298" t="n">
-        <v>-30.03</v>
+        <v>-30.28</v>
       </c>
       <c r="AL298" t="inlineStr">
         <is>

--- a/sts_ml_paper_tracker.xlsx
+++ b/sts_ml_paper_tracker.xlsx
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>$46,153.86  (+3.80% price-weighted)</t>
+          <t>$46,153.91  (+3.80% price-weighted)</t>
         </is>
       </c>
     </row>
@@ -491,7 +491,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-0.30%</t>
+          <t>-0.29%</t>
         </is>
       </c>
     </row>
@@ -753,7 +753,7 @@
         <v>127</v>
       </c>
       <c r="C20" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="D20" t="n">
         <v>43.31</v>
@@ -999,7 +999,7 @@
         <v>12</v>
       </c>
       <c r="C32" t="n">
-        <v>-6.52</v>
+        <v>-6.51</v>
       </c>
       <c r="D32" t="n">
         <v>41.67</v>
@@ -1449,7 +1449,7 @@
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="n">
-        <v>-2.57</v>
+        <v>-2.54</v>
       </c>
       <c r="L38" t="n">
         <v>-3.7</v>
@@ -1505,7 +1505,7 @@
         <v>0.97</v>
       </c>
       <c r="AC38" t="n">
-        <v>-2.57</v>
+        <v>-2.54</v>
       </c>
       <c r="AD38" t="n">
         <v>1.51</v>
@@ -1895,7 +1895,7 @@
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="n">
-        <v>-4.82</v>
+        <v>-4.83</v>
       </c>
       <c r="L42" t="n">
         <v>-12.9</v>
@@ -1947,7 +1947,7 @@
         <v>-4.67</v>
       </c>
       <c r="AC42" t="n">
-        <v>-4.82</v>
+        <v>-4.83</v>
       </c>
       <c r="AD42" t="n">
         <v>4.59</v>
@@ -2695,10 +2695,10 @@
         </is>
       </c>
       <c r="S49" t="n">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="T49" t="n">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="U49" t="inlineStr"/>
       <c r="V49" t="inlineStr"/>
@@ -2724,7 +2724,7 @@
         <v>-6.45</v>
       </c>
       <c r="AD49" t="n">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="AE49" t="n">
         <v>6</v>
@@ -3113,7 +3113,7 @@
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="n">
-        <v>-3.74</v>
+        <v>-3.73</v>
       </c>
       <c r="L53" t="n">
         <v>-23</v>
@@ -3165,7 +3165,7 @@
         <v>-3.33</v>
       </c>
       <c r="AC53" t="n">
-        <v>-3.74</v>
+        <v>-3.73</v>
       </c>
       <c r="AD53" t="n">
         <v>1.72</v>
@@ -5518,7 +5518,7 @@
         <v>4.79</v>
       </c>
       <c r="T74" t="n">
-        <v>8.050000000000001</v>
+        <v>8.09</v>
       </c>
       <c r="U74" t="n">
         <v>-5.89</v>
@@ -5546,7 +5546,7 @@
         <v>-5.89</v>
       </c>
       <c r="AD74" t="n">
-        <v>8.050000000000001</v>
+        <v>8.09</v>
       </c>
       <c r="AE74" t="n">
         <v>13</v>
@@ -6425,7 +6425,7 @@
       </c>
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="n">
-        <v>-28.91</v>
+        <v>-28.87</v>
       </c>
       <c r="L82" t="n">
         <v>-0.6</v>
@@ -6481,7 +6481,7 @@
         <v>-27.97</v>
       </c>
       <c r="AC82" t="n">
-        <v>-28.91</v>
+        <v>-28.87</v>
       </c>
       <c r="AD82" t="n">
         <v>0.9</v>
@@ -9648,13 +9648,13 @@
         <v>17.29</v>
       </c>
       <c r="Z109" t="n">
-        <v>13.45</v>
+        <v>13.46</v>
       </c>
       <c r="AA109" t="n">
-        <v>13.45</v>
+        <v>13.46</v>
       </c>
       <c r="AB109" t="n">
-        <v>-22.18</v>
+        <v>-22.15</v>
       </c>
       <c r="AC109" t="n">
         <v>-25.97</v>
@@ -9675,7 +9675,7 @@
       </c>
       <c r="AJ109" t="inlineStr"/>
       <c r="AK109" t="n">
-        <v>-23.29</v>
+        <v>-23.26</v>
       </c>
       <c r="AL109" t="inlineStr">
         <is>
@@ -11490,7 +11490,7 @@
         <v>3.9</v>
       </c>
       <c r="H125" t="n">
-        <v>-1.2</v>
+        <v>-1.1</v>
       </c>
       <c r="I125" t="n">
         <v>3.16</v>
@@ -11546,10 +11546,10 @@
         <v>80.14</v>
       </c>
       <c r="Z125" t="n">
-        <v>71.14</v>
+        <v>71.15000000000001</v>
       </c>
       <c r="AA125" t="n">
-        <v>71.14</v>
+        <v>71.15000000000001</v>
       </c>
       <c r="AB125" t="n">
         <v>-11.22</v>
@@ -11573,7 +11573,7 @@
       </c>
       <c r="AJ125" t="inlineStr"/>
       <c r="AK125" t="n">
-        <v>-12.18</v>
+        <v>-12.17</v>
       </c>
       <c r="AL125" t="inlineStr"/>
     </row>
@@ -17192,7 +17192,7 @@
         <v>-20.5</v>
       </c>
       <c r="H173" t="n">
-        <v>-1.2</v>
+        <v>-1.1</v>
       </c>
       <c r="I173" t="n">
         <v>2.8</v>
@@ -17248,13 +17248,13 @@
         <v>72.19</v>
       </c>
       <c r="Z173" t="n">
-        <v>71.14</v>
+        <v>71.15000000000001</v>
       </c>
       <c r="AA173" t="n">
-        <v>71.14</v>
+        <v>71.15000000000001</v>
       </c>
       <c r="AB173" t="n">
-        <v>-1.45</v>
+        <v>-1.44</v>
       </c>
       <c r="AC173" t="n">
         <v>-2.88</v>
@@ -17275,7 +17275,7 @@
       </c>
       <c r="AJ173" t="inlineStr"/>
       <c r="AK173" t="n">
-        <v>-5.95</v>
+        <v>-5.94</v>
       </c>
       <c r="AL173" t="inlineStr"/>
     </row>
@@ -18674,10 +18674,10 @@
         <v>193.01</v>
       </c>
       <c r="Z185" t="n">
-        <v>261.93</v>
+        <v>261.94</v>
       </c>
       <c r="AA185" t="n">
-        <v>261.93</v>
+        <v>261.94</v>
       </c>
       <c r="AB185" t="n">
         <v>35.71</v>
@@ -18701,7 +18701,7 @@
       </c>
       <c r="AJ185" t="inlineStr"/>
       <c r="AK185" t="n">
-        <v>32.2</v>
+        <v>32.21</v>
       </c>
       <c r="AL185" t="inlineStr">
         <is>
@@ -21638,7 +21638,7 @@
         <v>-17.98</v>
       </c>
       <c r="AD210" t="n">
-        <v>23.59</v>
+        <v>23.6</v>
       </c>
       <c r="AE210" t="n">
         <v>49</v>
@@ -22353,7 +22353,7 @@
         <v>-13.38</v>
       </c>
       <c r="AC216" t="n">
-        <v>-14.51</v>
+        <v>-14.47</v>
       </c>
       <c r="AD216" t="n">
         <v>21.7</v>
@@ -27170,13 +27170,13 @@
         <v>15.13</v>
       </c>
       <c r="Z257" t="n">
-        <v>13.45</v>
+        <v>13.46</v>
       </c>
       <c r="AA257" t="n">
-        <v>13.45</v>
+        <v>13.46</v>
       </c>
       <c r="AB257" t="n">
-        <v>-11.07</v>
+        <v>-11.04</v>
       </c>
       <c r="AC257" t="n">
         <v>-15.4</v>
@@ -27197,7 +27197,7 @@
       </c>
       <c r="AJ257" t="inlineStr"/>
       <c r="AK257" t="n">
-        <v>-14.58</v>
+        <v>-14.55</v>
       </c>
       <c r="AL257" t="inlineStr">
         <is>
@@ -31875,7 +31875,7 @@
         <v>-29.66</v>
       </c>
       <c r="AC297" t="n">
-        <v>-30.32</v>
+        <v>-30.31</v>
       </c>
       <c r="AD297" t="n">
         <v>1.81</v>

--- a/sts_ml_paper_tracker.xlsx
+++ b/sts_ml_paper_tracker.xlsx
@@ -1261,7 +1261,7 @@
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="n">
-        <v>-0.89</v>
+        <v>-0.92</v>
       </c>
       <c r="L36" t="n">
         <v>-9.5</v>
@@ -1317,7 +1317,7 @@
         <v>4.49</v>
       </c>
       <c r="AC36" t="n">
-        <v>-0.89</v>
+        <v>-0.92</v>
       </c>
       <c r="AD36" t="n">
         <v>4.9</v>
@@ -2265,7 +2265,7 @@
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="n">
-        <v>-6.7</v>
+        <v>-6.71</v>
       </c>
       <c r="L45" t="n">
         <v>-12.9</v>
@@ -2317,7 +2317,7 @@
         <v>-6.41</v>
       </c>
       <c r="AC45" t="n">
-        <v>-6.7</v>
+        <v>-6.71</v>
       </c>
       <c r="AD45" t="n">
         <v>4.59</v>
@@ -3483,7 +3483,7 @@
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="n">
-        <v>-5.77</v>
+        <v>-5.79</v>
       </c>
       <c r="L56" t="n">
         <v>-23</v>
@@ -3535,7 +3535,7 @@
         <v>-5.27</v>
       </c>
       <c r="AC56" t="n">
-        <v>-5.77</v>
+        <v>-5.79</v>
       </c>
       <c r="AD56" t="n">
         <v>1.72</v>
@@ -4151,7 +4151,7 @@
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="n">
-        <v>-2.1</v>
+        <v>-2.13</v>
       </c>
       <c r="L62" t="n">
         <v>6.7</v>
@@ -4205,7 +4205,7 @@
         <v>2.02</v>
       </c>
       <c r="AC62" t="n">
-        <v>-2.1</v>
+        <v>-2.13</v>
       </c>
       <c r="AD62" t="n">
         <v>6.29</v>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="n">
-        <v>-9.66</v>
+        <v>-9.67</v>
       </c>
       <c r="L68" t="n">
         <v>-3.9</v>
@@ -4901,7 +4901,7 @@
         <v>-7.04</v>
       </c>
       <c r="AC68" t="n">
-        <v>-9.66</v>
+        <v>-9.67</v>
       </c>
       <c r="AD68" t="n">
         <v>3.73</v>
@@ -8165,7 +8165,7 @@
         <v>-15.15</v>
       </c>
       <c r="AC96" t="n">
-        <v>-16.08</v>
+        <v>-16.09</v>
       </c>
       <c r="AD96" t="n">
         <v>1.66</v>
@@ -9605,7 +9605,7 @@
         <v>-4.07</v>
       </c>
       <c r="AC108" t="n">
-        <v>-6.78</v>
+        <v>-6.79</v>
       </c>
       <c r="AD108" t="n">
         <v>7.04</v>
@@ -29953,7 +29953,7 @@
         <v>-6.9</v>
       </c>
       <c r="AC280" t="n">
-        <v>-7.04</v>
+        <v>-7.03</v>
       </c>
       <c r="AD280" t="n">
         <v>45.11</v>
@@ -32193,7 +32193,7 @@
         <v>-10.82</v>
       </c>
       <c r="AC299" t="n">
-        <v>-12.02</v>
+        <v>-12</v>
       </c>
       <c r="AD299" t="n">
         <v>18.6</v>
@@ -32786,13 +32786,13 @@
         <v>-14.25</v>
       </c>
       <c r="AD304" t="n">
-        <v>29.93</v>
+        <v>31.82</v>
       </c>
       <c r="AE304" t="n">
         <v>51</v>
       </c>
       <c r="AF304" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="AG304" t="inlineStr"/>
       <c r="AH304" t="inlineStr"/>

--- a/sts_ml_paper_tracker.xlsx
+++ b/sts_ml_paper_tracker.xlsx
@@ -455,7 +455,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>$46,629.13</t>
+          <t>$46,629.12</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
         <v>38.98</v>
       </c>
       <c r="G12" t="n">
-        <v>-12.44</v>
+        <v>-12.45</v>
       </c>
     </row>
     <row r="13">
@@ -694,7 +694,7 @@
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
-        <v>-15.44</v>
+        <v>-15.45</v>
       </c>
     </row>
     <row r="18">
@@ -717,7 +717,7 @@
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
-        <v>-12.54</v>
+        <v>-12.55</v>
       </c>
     </row>
     <row r="19">
@@ -845,19 +845,19 @@
         <v>33</v>
       </c>
       <c r="C25" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="D25" t="n">
         <v>55</v>
       </c>
       <c r="E25" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="F25" t="n">
         <v>48</v>
       </c>
       <c r="G25" t="n">
-        <v>-9.49</v>
+        <v>-9.51</v>
       </c>
     </row>
     <row r="26">
@@ -926,7 +926,7 @@
         <v>55</v>
       </c>
       <c r="E28" t="n">
-        <v>4.6</v>
+        <v>4.59</v>
       </c>
       <c r="F28" t="n">
         <v>57</v>
@@ -1008,7 +1008,7 @@
         <v>-7.74</v>
       </c>
       <c r="F32" t="n">
-        <v>-14.58</v>
+        <v>-14.59</v>
       </c>
     </row>
     <row r="33">
@@ -1439,23 +1439,23 @@
         </is>
       </c>
       <c r="S38" t="n">
-        <v>5.28</v>
+        <v>5.29</v>
       </c>
       <c r="T38" t="n">
-        <v>5.28</v>
+        <v>5.29</v>
       </c>
       <c r="U38" t="n">
         <v>-4.16</v>
       </c>
       <c r="V38" t="inlineStr"/>
       <c r="W38" t="n">
-        <v>12.39</v>
+        <v>12.38</v>
       </c>
       <c r="X38" t="n">
         <v>1</v>
       </c>
       <c r="Y38" t="n">
-        <v>12.39</v>
+        <v>12.38</v>
       </c>
       <c r="Z38" t="n">
         <v>11.92</v>
@@ -1470,7 +1470,7 @@
         <v>-4.16</v>
       </c>
       <c r="AD38" t="n">
-        <v>5.28</v>
+        <v>5.29</v>
       </c>
       <c r="AE38" t="n">
         <v>1</v>
@@ -1525,7 +1525,7 @@
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="n">
-        <v>-5.1</v>
+        <v>-5.14</v>
       </c>
       <c r="L39" t="n">
         <v>3.4</v>
@@ -1577,7 +1577,7 @@
         <v>0.95</v>
       </c>
       <c r="AC39" t="n">
-        <v>-5.1</v>
+        <v>-5.14</v>
       </c>
       <c r="AD39" t="n">
         <v>1.76</v>
@@ -1997,10 +1997,10 @@
         </is>
       </c>
       <c r="S43" t="n">
-        <v>6.69</v>
+        <v>6.72</v>
       </c>
       <c r="T43" t="n">
-        <v>6.69</v>
+        <v>6.72</v>
       </c>
       <c r="U43" t="n">
         <v>-5.13</v>
@@ -2028,7 +2028,7 @@
         <v>-5.13</v>
       </c>
       <c r="AD43" t="n">
-        <v>6.69</v>
+        <v>6.72</v>
       </c>
       <c r="AE43" t="n">
         <v>5</v>
@@ -2561,10 +2561,10 @@
         </is>
       </c>
       <c r="S48" t="n">
-        <v>6.41</v>
+        <v>6.42</v>
       </c>
       <c r="T48" t="n">
-        <v>6.41</v>
+        <v>6.42</v>
       </c>
       <c r="U48" t="n">
         <v>-0.24</v>
@@ -2592,7 +2592,7 @@
         <v>-0.24</v>
       </c>
       <c r="AD48" t="n">
-        <v>6.41</v>
+        <v>6.42</v>
       </c>
       <c r="AE48" t="n">
         <v>9</v>
@@ -2647,7 +2647,7 @@
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="n">
-        <v>-8.66</v>
+        <v>-8.789999999999999</v>
       </c>
       <c r="L49" t="n">
         <v>-12.9</v>
@@ -2699,7 +2699,7 @@
         <v>-8.050000000000001</v>
       </c>
       <c r="AC49" t="n">
-        <v>-8.66</v>
+        <v>-8.789999999999999</v>
       </c>
       <c r="AD49" t="n">
         <v>4.59</v>
@@ -4673,7 +4673,7 @@
       </c>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="n">
-        <v>-5.69</v>
+        <v>-5.71</v>
       </c>
       <c r="L67" t="n">
         <v>-34.1</v>
@@ -4727,7 +4727,7 @@
         <v>-4.65</v>
       </c>
       <c r="AC67" t="n">
-        <v>-5.69</v>
+        <v>-5.71</v>
       </c>
       <c r="AD67" t="n">
         <v>5.22</v>
@@ -6326,7 +6326,7 @@
         <v>4.79</v>
       </c>
       <c r="T81" t="n">
-        <v>14.16</v>
+        <v>14.17</v>
       </c>
       <c r="U81" t="n">
         <v>-5.89</v>
@@ -6356,7 +6356,7 @@
         <v>-5.89</v>
       </c>
       <c r="AD81" t="n">
-        <v>14.16</v>
+        <v>14.17</v>
       </c>
       <c r="AE81" t="n">
         <v>18</v>
@@ -6442,7 +6442,7 @@
         <v>9.52</v>
       </c>
       <c r="T82" t="n">
-        <v>11.16</v>
+        <v>11.19</v>
       </c>
       <c r="U82" t="n">
         <v>-0.79</v>
@@ -6472,7 +6472,7 @@
         <v>-0.79</v>
       </c>
       <c r="AD82" t="n">
-        <v>11.16</v>
+        <v>11.19</v>
       </c>
       <c r="AE82" t="n">
         <v>18</v>
@@ -9850,29 +9850,29 @@
         <v>48</v>
       </c>
       <c r="H111" t="n">
-        <v>-2.9</v>
+        <v>-2.7</v>
       </c>
       <c r="I111" t="n">
-        <v>-7.36</v>
+        <v>-7.6</v>
       </c>
       <c r="J111" t="n">
-        <v>-9.800000000000001</v>
+        <v>-10.04</v>
       </c>
       <c r="K111" t="n">
-        <v>-12.98</v>
+        <v>-13.21</v>
       </c>
       <c r="L111" t="n">
-        <v>15.7</v>
+        <v>16</v>
       </c>
       <c r="M111" t="n">
-        <v>-1.1</v>
+        <v>-0.9</v>
       </c>
       <c r="N111" t="inlineStr"/>
       <c r="O111" t="n">
         <v>-20.2</v>
       </c>
       <c r="P111" t="n">
-        <v>187.03</v>
+        <v>186.54</v>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
@@ -9885,10 +9885,10 @@
         </is>
       </c>
       <c r="S111" t="n">
-        <v>2.19</v>
+        <v>1.93</v>
       </c>
       <c r="T111" t="n">
-        <v>2.19</v>
+        <v>1.93</v>
       </c>
       <c r="U111" t="inlineStr"/>
       <c r="V111" t="inlineStr"/>
@@ -9914,7 +9914,7 @@
         <v>-15.36</v>
       </c>
       <c r="AD111" t="n">
-        <v>2.19</v>
+        <v>1.93</v>
       </c>
       <c r="AE111" t="n">
         <v>29</v>
@@ -10509,7 +10509,7 @@
         <v>-27.99</v>
       </c>
       <c r="AC116" t="n">
-        <v>-28.74</v>
+        <v>-28.8</v>
       </c>
       <c r="AD116" t="n">
         <v>6.36</v>
@@ -17342,29 +17342,29 @@
         <v>15.3</v>
       </c>
       <c r="H174" t="n">
-        <v>-7.1</v>
+        <v>-6.9</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.04</v>
+        <v>-0.29</v>
       </c>
       <c r="J174" t="n">
-        <v>6.29</v>
+        <v>6.03</v>
       </c>
       <c r="K174" t="n">
-        <v>-4.12</v>
+        <v>-4.36</v>
       </c>
       <c r="L174" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="M174" t="n">
-        <v>-3.7</v>
+        <v>-3.5</v>
       </c>
       <c r="N174" t="inlineStr"/>
       <c r="O174" t="n">
         <v>-20.1</v>
       </c>
       <c r="P174" t="n">
-        <v>382.54</v>
+        <v>381.58</v>
       </c>
       <c r="Q174" t="inlineStr">
         <is>
@@ -17377,13 +17377,13 @@
         </is>
       </c>
       <c r="S174" t="n">
-        <v>2.04</v>
+        <v>1.78</v>
       </c>
       <c r="T174" t="n">
-        <v>6.62</v>
+        <v>6.35</v>
       </c>
       <c r="U174" t="n">
-        <v>-4.12</v>
+        <v>-4.36</v>
       </c>
       <c r="V174" t="inlineStr"/>
       <c r="W174" t="n">
@@ -17405,10 +17405,10 @@
         <v>-10.9</v>
       </c>
       <c r="AC174" t="n">
-        <v>-12.63</v>
+        <v>-12.85</v>
       </c>
       <c r="AD174" t="n">
-        <v>8.029999999999999</v>
+        <v>7.76</v>
       </c>
       <c r="AE174" t="n">
         <v>46</v>
@@ -18768,29 +18768,29 @@
         <v>-9.800000000000001</v>
       </c>
       <c r="H186" t="n">
-        <v>-3.5</v>
+        <v>-3.1</v>
       </c>
       <c r="I186" t="n">
-        <v>7.93</v>
+        <v>7.51</v>
       </c>
       <c r="J186" t="n">
-        <v>-2.15</v>
+        <v>-2.53</v>
       </c>
       <c r="K186" t="n">
-        <v>-2.47</v>
+        <v>-2.85</v>
       </c>
       <c r="L186" t="n">
-        <v>28</v>
+        <v>28.5</v>
       </c>
       <c r="M186" t="n">
-        <v>15.3</v>
+        <v>15.7</v>
       </c>
       <c r="N186" t="inlineStr"/>
       <c r="O186" t="n">
         <v>27</v>
       </c>
       <c r="P186" t="n">
-        <v>87.48</v>
+        <v>87.14</v>
       </c>
       <c r="Q186" t="inlineStr">
         <is>
@@ -18803,16 +18803,16 @@
         </is>
       </c>
       <c r="S186" t="n">
-        <v>10.9</v>
+        <v>10.47</v>
       </c>
       <c r="T186" t="n">
-        <v>11.35</v>
+        <v>10.92</v>
       </c>
       <c r="U186" t="n">
-        <v>-0.3</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="V186" t="n">
-        <v>-0.3</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="W186" t="n">
         <v>112</v>
@@ -18833,10 +18833,10 @@
         <v>0.18</v>
       </c>
       <c r="AC186" t="n">
-        <v>-6.69</v>
+        <v>-7.05</v>
       </c>
       <c r="AD186" t="n">
-        <v>11.35</v>
+        <v>10.92</v>
       </c>
       <c r="AE186" t="n">
         <v>51</v>
@@ -22152,7 +22152,7 @@
         <v>-2.38</v>
       </c>
       <c r="AD214" t="n">
-        <v>83.09999999999999</v>
+        <v>83.12</v>
       </c>
       <c r="AE214" t="n">
         <v>54</v>
@@ -22266,7 +22266,7 @@
         <v>-10.21</v>
       </c>
       <c r="AD215" t="n">
-        <v>34.82</v>
+        <v>34.85</v>
       </c>
       <c r="AE215" t="n">
         <v>54</v>
@@ -28045,7 +28045,7 @@
         <v>-17.71</v>
       </c>
       <c r="AC264" t="n">
-        <v>-18.57</v>
+        <v>-18.64</v>
       </c>
       <c r="AD264" t="n">
         <v>52.35</v>

--- a/sts_ml_paper_tracker.xlsx
+++ b/sts_ml_paper_tracker.xlsx
@@ -1300,7 +1300,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L7" t="n">
         <v>3.6</v>
@@ -1372,7 +1372,7 @@
         <v>1.49</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL7" t="n">
         <v>2.47</v>

--- a/sts_ml_paper_tracker.xlsx
+++ b/sts_ml_paper_tracker.xlsx
@@ -438,7 +438,7 @@
     <col width="6" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
     <col width="17" customWidth="1" min="16" max="16"/>
-    <col width="9" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
     <col width="60" customWidth="1" min="18" max="18"/>
     <col width="12" customWidth="1" min="19" max="19"/>
     <col width="12" customWidth="1" min="20" max="20"/>
@@ -711,21 +711,9 @@
           <t>SMCI</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>D200G</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
         <v>3.2</v>
       </c>
@@ -736,18 +724,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="n">
-        <v>8.1</v>
-      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
-      <c r="O2" t="n">
-        <v>8.1</v>
-      </c>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>NO PRICE</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -770,9 +754,7 @@
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="n">
-        <v>35.09000015258789</v>
-      </c>
+      <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="inlineStr"/>
@@ -795,21 +777,9 @@
           <t>GLOB</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>DLB</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
         <v>2.7</v>
       </c>
@@ -820,22 +790,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="n">
-        <v>-9.699999999999999</v>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>WR20</t>
-        </is>
-      </c>
-      <c r="O3" t="n">
-        <v>-25.7</v>
-      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>NO PRICE</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -858,9 +820,7 @@
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="inlineStr"/>
-      <c r="AH3" t="n">
-        <v>39.22999954223633</v>
-      </c>
+      <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="inlineStr"/>
       <c r="AJ3" t="inlineStr"/>
       <c r="AK3" t="inlineStr"/>
@@ -915,9 +875,7 @@
       <c r="L4" t="n">
         <v>1.5</v>
       </c>
-      <c r="M4" t="n">
-        <v>11.5</v>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
         <v>-22.3</v>
@@ -1049,9 +1007,7 @@
       <c r="L5" t="n">
         <v>1.2</v>
       </c>
-      <c r="M5" t="n">
-        <v>2.8</v>
-      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
         <v>2.8</v>
@@ -1179,9 +1135,7 @@
       <c r="L6" t="n">
         <v>-8.300000000000001</v>
       </c>
-      <c r="M6" t="n">
-        <v>-3.2</v>
-      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -1317,9 +1271,7 @@
       <c r="L7" t="n">
         <v>20.1</v>
       </c>
-      <c r="M7" t="n">
-        <v>24.4</v>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="n">
         <v>2.6</v>
@@ -1447,9 +1399,7 @@
       <c r="L8" t="n">
         <v>-8.4</v>
       </c>
-      <c r="M8" t="n">
-        <v>-6.1</v>
-      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="n">
         <v>-13.4</v>
@@ -1581,9 +1531,7 @@
       <c r="L9" t="n">
         <v>3.6</v>
       </c>
-      <c r="M9" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="n">
         <v>-6.7</v>
@@ -1710,14 +1658,12 @@
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="n">
-        <v>-4.35</v>
+        <v>-4.37</v>
       </c>
       <c r="L10" t="n">
         <v>-9.199999999999999</v>
       </c>
-      <c r="M10" t="n">
-        <v>-5</v>
-      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>WR40</t>
@@ -1786,7 +1732,7 @@
         <v>4.03</v>
       </c>
       <c r="AK10" t="n">
-        <v>-4.35</v>
+        <v>-4.37</v>
       </c>
       <c r="AL10" t="n">
         <v>4.3</v>
@@ -1849,9 +1795,7 @@
       <c r="L11" t="n">
         <v>1</v>
       </c>
-      <c r="M11" t="n">
-        <v>5.2</v>
-      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="n">
         <v>-5.4</v>
@@ -1979,9 +1923,7 @@
       <c r="L12" t="n">
         <v>-5.1</v>
       </c>
-      <c r="M12" t="n">
-        <v>0.7</v>
-      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -2117,9 +2059,7 @@
       <c r="L13" t="n">
         <v>-22.7</v>
       </c>
-      <c r="M13" t="n">
-        <v>-25.4</v>
-      </c>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="n">
         <v>-32.1</v>
@@ -2247,9 +2187,7 @@
       <c r="L14" t="n">
         <v>-3.2</v>
       </c>
-      <c r="M14" t="n">
-        <v>-24</v>
-      </c>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -2385,9 +2323,7 @@
       <c r="L15" t="n">
         <v>1.5</v>
       </c>
-      <c r="M15" t="n">
-        <v>-3.2</v>
-      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="n">
         <v>-12.8</v>
@@ -2519,9 +2455,7 @@
       <c r="L16" t="n">
         <v>0.3</v>
       </c>
-      <c r="M16" t="n">
-        <v>-0</v>
-      </c>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="n">
         <v>-14.8</v>
@@ -2653,9 +2587,7 @@
       <c r="L17" t="n">
         <v>-0.6</v>
       </c>
-      <c r="M17" t="n">
-        <v>8.6</v>
-      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="n">
         <v>-3.8</v>
@@ -2789,9 +2721,7 @@
       <c r="L18" t="n">
         <v>2.2</v>
       </c>
-      <c r="M18" t="n">
-        <v>18.8</v>
-      </c>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="n">
         <v>-16.6</v>
@@ -2925,9 +2855,7 @@
       <c r="L19" t="n">
         <v>-8</v>
       </c>
-      <c r="M19" t="n">
-        <v>-7</v>
-      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="n">
         <v>-9.199999999999999</v>
@@ -3055,9 +2983,7 @@
       <c r="L20" t="n">
         <v>-29.1</v>
       </c>
-      <c r="M20" t="n">
-        <v>-20.6</v>
-      </c>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="n">
         <v>-29.3</v>
@@ -3191,9 +3117,7 @@
       <c r="L21" t="n">
         <v>-0.3</v>
       </c>
-      <c r="M21" t="n">
-        <v>5.9</v>
-      </c>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="n">
         <v>-1.9</v>
@@ -3325,9 +3249,7 @@
       <c r="L22" t="n">
         <v>5.1</v>
       </c>
-      <c r="M22" t="n">
-        <v>7.9</v>
-      </c>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="n">
         <v>-1</v>
@@ -3461,9 +3383,7 @@
       <c r="L23" t="n">
         <v>3.4</v>
       </c>
-      <c r="M23" t="n">
-        <v>7.7</v>
-      </c>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="n">
         <v>-2.8</v>
@@ -3599,9 +3519,7 @@
       <c r="L24" t="n">
         <v>-8.800000000000001</v>
       </c>
-      <c r="M24" t="n">
-        <v>-2.7</v>
-      </c>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -3739,9 +3657,7 @@
       <c r="L25" t="n">
         <v>-35.8</v>
       </c>
-      <c r="M25" t="n">
-        <v>-35.9</v>
-      </c>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="n">
         <v>-38.7</v>
@@ -3871,9 +3787,7 @@
       <c r="L26" t="n">
         <v>-6.9</v>
       </c>
-      <c r="M26" t="n">
-        <v>1.3</v>
-      </c>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="n">
         <v>-7.1</v>
@@ -4009,9 +3923,7 @@
       <c r="L27" t="n">
         <v>-12.6</v>
       </c>
-      <c r="M27" t="n">
-        <v>2.4</v>
-      </c>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="n">
         <v>-15</v>
@@ -4055,7 +3967,7 @@
         <v>10.82</v>
       </c>
       <c r="AB27" t="n">
-        <v>15.79</v>
+        <v>15.81</v>
       </c>
       <c r="AC27" t="n">
         <v>-5.13</v>
@@ -4085,7 +3997,7 @@
         <v>-5.13</v>
       </c>
       <c r="AL27" t="n">
-        <v>15.79</v>
+        <v>15.81</v>
       </c>
       <c r="AM27" t="n">
         <v>14</v>
@@ -4147,9 +4059,7 @@
       <c r="L28" t="n">
         <v>-8.6</v>
       </c>
-      <c r="M28" t="n">
-        <v>-32.1</v>
-      </c>
+      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -4291,9 +4201,7 @@
       <c r="L29" t="n">
         <v>-3.7</v>
       </c>
-      <c r="M29" t="n">
-        <v>-6</v>
-      </c>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -4427,9 +4335,7 @@
       <c r="L30" t="n">
         <v>3.6</v>
       </c>
-      <c r="M30" t="n">
-        <v>17.5</v>
-      </c>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="n">
         <v>-8.6</v>
@@ -4565,9 +4471,7 @@
       <c r="L31" t="n">
         <v>1.2</v>
       </c>
-      <c r="M31" t="n">
-        <v>-3.8</v>
-      </c>
+      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="n">
         <v>-9.1</v>
@@ -4703,9 +4607,7 @@
       <c r="L32" t="n">
         <v>-25.1</v>
       </c>
-      <c r="M32" t="n">
-        <v>-18.2</v>
-      </c>
+      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="n">
         <v>-26.9</v>
@@ -4839,9 +4741,7 @@
       <c r="L33" t="n">
         <v>-12.9</v>
       </c>
-      <c r="M33" t="n">
-        <v>-13.5</v>
-      </c>
+      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="n">
         <v>-19.3</v>
@@ -4971,9 +4871,7 @@
       <c r="L34" t="n">
         <v>17.3</v>
       </c>
-      <c r="M34" t="n">
-        <v>20.3</v>
-      </c>
+      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="n">
         <v>11.4</v>
@@ -5103,9 +5001,7 @@
       <c r="L35" t="n">
         <v>-12.3</v>
       </c>
-      <c r="M35" t="n">
-        <v>-0.8</v>
-      </c>
+      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="n">
         <v>-16.1</v>
@@ -5241,9 +5137,7 @@
       <c r="L36" t="n">
         <v>-18.4</v>
       </c>
-      <c r="M36" t="n">
-        <v>-23.4</v>
-      </c>
+      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="n">
         <v>-19.9</v>
@@ -5373,9 +5267,7 @@
       <c r="L37" t="n">
         <v>-17</v>
       </c>
-      <c r="M37" t="n">
-        <v>-11.5</v>
-      </c>
+      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="n">
         <v>-20.1</v>
@@ -5509,9 +5401,7 @@
       <c r="L38" t="n">
         <v>7.7</v>
       </c>
-      <c r="M38" t="n">
-        <v>12.8</v>
-      </c>
+      <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="n">
         <v>5.6</v>
@@ -5645,9 +5535,7 @@
       <c r="L39" t="n">
         <v>3.5</v>
       </c>
-      <c r="M39" t="n">
-        <v>19.9</v>
-      </c>
+      <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="n">
         <v>-30.3</v>
@@ -5783,9 +5671,7 @@
       <c r="L40" t="n">
         <v>2.4</v>
       </c>
-      <c r="M40" t="n">
-        <v>9.1</v>
-      </c>
+      <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="n">
         <v>-4.8</v>
@@ -5915,9 +5801,7 @@
       <c r="L41" t="n">
         <v>-17.5</v>
       </c>
-      <c r="M41" t="n">
-        <v>-15.2</v>
-      </c>
+      <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="n">
         <v>-20</v>
@@ -6051,9 +5935,7 @@
       <c r="L42" t="n">
         <v>4.6</v>
       </c>
-      <c r="M42" t="n">
-        <v>7.2</v>
-      </c>
+      <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="n">
         <v>-8.6</v>
@@ -6185,9 +6067,7 @@
       <c r="L43" t="n">
         <v>-10.8</v>
       </c>
-      <c r="M43" t="n">
-        <v>32.4</v>
-      </c>
+      <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="n">
         <v>-27.7</v>
@@ -6329,9 +6209,7 @@
       <c r="L44" t="n">
         <v>-23</v>
       </c>
-      <c r="M44" t="n">
-        <v>-19.8</v>
-      </c>
+      <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="n">
         <v>-28</v>
@@ -6463,9 +6341,7 @@
       <c r="L45" t="n">
         <v>-10.3</v>
       </c>
-      <c r="M45" t="n">
-        <v>3.9</v>
-      </c>
+      <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="n">
         <v>-19.9</v>
@@ -6607,9 +6483,7 @@
       <c r="L46" t="n">
         <v>-5.4</v>
       </c>
-      <c r="M46" t="n">
-        <v>-10.4</v>
-      </c>
+      <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="n">
         <v>-12.5</v>
@@ -6745,9 +6619,7 @@
       <c r="L47" t="n">
         <v>-5.7</v>
       </c>
-      <c r="M47" t="n">
-        <v>-1.2</v>
-      </c>
+      <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -6883,9 +6755,7 @@
       <c r="L48" t="n">
         <v>10</v>
       </c>
-      <c r="M48" t="n">
-        <v>-13</v>
-      </c>
+      <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="n">
         <v>7.9</v>
@@ -7031,9 +6901,7 @@
       <c r="L49" t="n">
         <v>1.2</v>
       </c>
-      <c r="M49" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="n">
         <v>-32.7</v>
@@ -7173,9 +7041,7 @@
       <c r="L50" t="n">
         <v>6.7</v>
       </c>
-      <c r="M50" t="n">
-        <v>9.5</v>
-      </c>
+      <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="O50" t="n">
         <v>6.2</v>
@@ -7317,9 +7183,7 @@
       <c r="L51" t="n">
         <v>-34.1</v>
       </c>
-      <c r="M51" t="n">
-        <v>-29.1</v>
-      </c>
+      <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="n">
         <v>-36.2</v>
@@ -7459,9 +7323,7 @@
       <c r="L52" t="n">
         <v>-3.6</v>
       </c>
-      <c r="M52" t="n">
-        <v>0.7</v>
-      </c>
+      <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr">
         <is>
           <t>WR30</t>
@@ -7607,9 +7469,7 @@
       <c r="L53" t="n">
         <v>5.1</v>
       </c>
-      <c r="M53" t="n">
-        <v>-1.3</v>
-      </c>
+      <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="n">
         <v>2.1</v>
@@ -7751,9 +7611,7 @@
       <c r="L54" t="n">
         <v>1.9</v>
       </c>
-      <c r="M54" t="n">
-        <v>7.2</v>
-      </c>
+      <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="O54" t="n">
         <v>-19.9</v>
@@ -7895,9 +7753,7 @@
       <c r="L55" t="n">
         <v>-10.3</v>
       </c>
-      <c r="M55" t="n">
-        <v>-3.2</v>
-      </c>
+      <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="O55" t="n">
         <v>-41.2</v>
@@ -8033,9 +7889,7 @@
       <c r="L56" t="n">
         <v>-3.1</v>
       </c>
-      <c r="M56" t="n">
-        <v>18.8</v>
-      </c>
+      <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr">
         <is>
           <t>WR30</t>
@@ -8181,9 +8035,7 @@
       <c r="L57" t="n">
         <v>9.9</v>
       </c>
-      <c r="M57" t="n">
-        <v>9.4</v>
-      </c>
+      <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="O57" t="n">
         <v>-21</v>
@@ -8327,9 +8179,7 @@
       <c r="L58" t="n">
         <v>6.2</v>
       </c>
-      <c r="M58" t="n">
-        <v>4.4</v>
-      </c>
+      <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="O58" t="n">
         <v>-12.3</v>
@@ -8461,9 +8311,7 @@
       <c r="L59" t="n">
         <v>31.8</v>
       </c>
-      <c r="M59" t="n">
-        <v>30.6</v>
-      </c>
+      <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="O59" t="n">
         <v>26.6</v>
@@ -8539,7 +8387,7 @@
         <v>-11.66</v>
       </c>
       <c r="AL59" t="n">
-        <v>5.48</v>
+        <v>5.5</v>
       </c>
       <c r="AM59" t="n">
         <v>24</v>
@@ -8603,9 +8451,7 @@
       <c r="L60" t="n">
         <v>-3.3</v>
       </c>
-      <c r="M60" t="n">
-        <v>-13.1</v>
-      </c>
+      <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -8745,9 +8591,7 @@
       <c r="L61" t="n">
         <v>16.3</v>
       </c>
-      <c r="M61" t="n">
-        <v>-18.9</v>
-      </c>
+      <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="O61" t="n">
         <v>13.8</v>
@@ -8883,9 +8727,7 @@
       <c r="L62" t="n">
         <v>1.4</v>
       </c>
-      <c r="M62" t="n">
-        <v>-8.800000000000001</v>
-      </c>
+      <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="O62" t="n">
         <v>-9.800000000000001</v>
@@ -8950,7 +8792,7 @@
         <v>-13.47</v>
       </c>
       <c r="AK62" t="n">
-        <v>-16.29</v>
+        <v>-16.3</v>
       </c>
       <c r="AL62" t="n">
         <v>0.74</v>
@@ -9021,9 +8863,7 @@
       <c r="L63" t="n">
         <v>0.4</v>
       </c>
-      <c r="M63" t="n">
-        <v>13.6</v>
-      </c>
+      <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
       <c r="O63" t="n">
         <v>2.1</v>
@@ -9165,9 +9005,7 @@
       <c r="L64" t="n">
         <v>-30.4</v>
       </c>
-      <c r="M64" t="n">
-        <v>-33</v>
-      </c>
+      <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
       <c r="O64" t="n">
         <v>-33.7</v>
@@ -9299,9 +9137,7 @@
       <c r="L65" t="n">
         <v>-4.9</v>
       </c>
-      <c r="M65" t="n">
-        <v>-5.7</v>
-      </c>
+      <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="O65" t="n">
         <v>-6.3</v>
@@ -9429,29 +9265,27 @@
         <v>-9.6</v>
       </c>
       <c r="H66" t="n">
-        <v>-3.4</v>
+        <v>-3.2</v>
       </c>
       <c r="I66" t="n">
-        <v>5.48</v>
+        <v>5.19</v>
       </c>
       <c r="J66" t="n">
-        <v>7.06</v>
+        <v>6.76</v>
       </c>
       <c r="K66" t="n">
-        <v>-0.79</v>
+        <v>-1.07</v>
       </c>
       <c r="L66" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="M66" t="n">
-        <v>2.7</v>
-      </c>
+        <v>4.9</v>
+      </c>
+      <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="O66" t="n">
         <v>3.8</v>
       </c>
       <c r="P66" t="n">
-        <v>74.11</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
@@ -9488,16 +9322,16 @@
         </is>
       </c>
       <c r="AA66" t="n">
-        <v>9.52</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="AB66" t="n">
-        <v>11.19</v>
+        <v>10.88</v>
       </c>
       <c r="AC66" t="n">
-        <v>-0.79</v>
+        <v>-1.07</v>
       </c>
       <c r="AD66" t="n">
-        <v>-0.79</v>
+        <v>-1.07</v>
       </c>
       <c r="AE66" t="n">
         <v>77.5</v>
@@ -9521,7 +9355,7 @@
         <v>-2.53</v>
       </c>
       <c r="AL66" t="n">
-        <v>11.19</v>
+        <v>10.88</v>
       </c>
       <c r="AM66" t="n">
         <v>27</v>
@@ -9585,9 +9419,7 @@
       <c r="L67" t="n">
         <v>4.1</v>
       </c>
-      <c r="M67" t="n">
-        <v>-12.5</v>
-      </c>
+      <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="O67" t="n">
         <v>-6.5</v>
@@ -9723,9 +9555,7 @@
       <c r="L68" t="n">
         <v>-3.6</v>
       </c>
-      <c r="M68" t="n">
-        <v>32.8</v>
-      </c>
+      <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -9871,9 +9701,7 @@
       <c r="L69" t="n">
         <v>-32.6</v>
       </c>
-      <c r="M69" t="n">
-        <v>-27.2</v>
-      </c>
+      <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="O69" t="n">
         <v>-40.5</v>
@@ -10005,9 +9833,7 @@
       <c r="L70" t="n">
         <v>-4.7</v>
       </c>
-      <c r="M70" t="n">
-        <v>-15.6</v>
-      </c>
+      <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr">
         <is>
           <t>WR30</t>
@@ -10084,7 +9910,7 @@
         <v>-15.67</v>
       </c>
       <c r="AK70" t="n">
-        <v>-19.73</v>
+        <v>-19.98</v>
       </c>
       <c r="AL70" t="n">
         <v>6.65</v>
@@ -10155,9 +9981,7 @@
       <c r="L71" t="n">
         <v>-5.7</v>
       </c>
-      <c r="M71" t="n">
-        <v>-44.9</v>
-      </c>
+      <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -10307,9 +10131,7 @@
       <c r="L72" t="n">
         <v>-29.7</v>
       </c>
-      <c r="M72" t="n">
-        <v>-25.6</v>
-      </c>
+      <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
       <c r="O72" t="n">
         <v>-44.3</v>
@@ -10441,9 +10263,7 @@
       <c r="L73" t="n">
         <v>0.3</v>
       </c>
-      <c r="M73" t="n">
-        <v>-56.1</v>
-      </c>
+      <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
       <c r="O73" t="n">
         <v>-32.8</v>
@@ -10508,7 +10328,7 @@
         <v>-57.74</v>
       </c>
       <c r="AK73" t="n">
-        <v>-63.57</v>
+        <v>-63.53</v>
       </c>
       <c r="AL73" t="n">
         <v>0.01</v>
@@ -10579,9 +10399,7 @@
       <c r="L74" t="n">
         <v>10.7</v>
       </c>
-      <c r="M74" t="n">
-        <v>7.7</v>
-      </c>
+      <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
       <c r="O74" t="n">
         <v>-10.6</v>
@@ -10727,9 +10545,7 @@
       <c r="L75" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="M75" t="n">
-        <v>-1.7</v>
-      </c>
+      <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
       <c r="O75" t="n">
         <v>8.5</v>
@@ -10871,9 +10687,7 @@
       <c r="L76" t="n">
         <v>3.3</v>
       </c>
-      <c r="M76" t="n">
-        <v>14.7</v>
-      </c>
+      <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
       <c r="O76" t="n">
         <v>-14.5</v>
@@ -11013,9 +10827,7 @@
       <c r="L77" t="n">
         <v>-0.9</v>
       </c>
-      <c r="M77" t="n">
-        <v>6.1</v>
-      </c>
+      <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
       <c r="O77" t="n">
         <v>-12.1</v>
@@ -11157,9 +10969,7 @@
       <c r="L78" t="n">
         <v>53.6</v>
       </c>
-      <c r="M78" t="n">
-        <v>47.6</v>
-      </c>
+      <c r="M78" t="inlineStr"/>
       <c r="N78" t="inlineStr"/>
       <c r="O78" t="n">
         <v>-11.8</v>
@@ -11295,9 +11105,7 @@
       <c r="L79" t="n">
         <v>-20.5</v>
       </c>
-      <c r="M79" t="n">
-        <v>-30.1</v>
-      </c>
+      <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr"/>
       <c r="O79" t="n">
         <v>-27.1</v>
@@ -11433,9 +11241,7 @@
       <c r="L80" t="n">
         <v>1.1</v>
       </c>
-      <c r="M80" t="n">
-        <v>-19.9</v>
-      </c>
+      <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
       <c r="O80" t="n">
         <v>-9.199999999999999</v>
@@ -11581,9 +11387,7 @@
       <c r="L81" t="n">
         <v>-5</v>
       </c>
-      <c r="M81" t="n">
-        <v>11.5</v>
-      </c>
+      <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr">
         <is>
           <t>WR40</t>
@@ -11729,9 +11533,7 @@
       <c r="L82" t="n">
         <v>-4.1</v>
       </c>
-      <c r="M82" t="n">
-        <v>19.9</v>
-      </c>
+      <c r="M82" t="inlineStr"/>
       <c r="N82" t="inlineStr">
         <is>
           <t>WR30</t>
@@ -11877,9 +11679,7 @@
       <c r="L83" t="n">
         <v>1.4</v>
       </c>
-      <c r="M83" t="n">
-        <v>-6.2</v>
-      </c>
+      <c r="M83" t="inlineStr"/>
       <c r="N83" t="inlineStr"/>
       <c r="O83" t="n">
         <v>-3.5</v>
@@ -12011,9 +11811,7 @@
       <c r="L84" t="n">
         <v>4</v>
       </c>
-      <c r="M84" t="n">
-        <v>-13.1</v>
-      </c>
+      <c r="M84" t="inlineStr"/>
       <c r="N84" t="inlineStr"/>
       <c r="O84" t="n">
         <v>-14.9</v>
@@ -12149,9 +11947,7 @@
       <c r="L85" t="n">
         <v>24.9</v>
       </c>
-      <c r="M85" t="n">
-        <v>30.9</v>
-      </c>
+      <c r="M85" t="inlineStr"/>
       <c r="N85" t="inlineStr"/>
       <c r="O85" t="n">
         <v>-0.9</v>
@@ -12293,9 +12089,7 @@
       <c r="L86" t="n">
         <v>-1.2</v>
       </c>
-      <c r="M86" t="n">
-        <v>-25.4</v>
-      </c>
+      <c r="M86" t="inlineStr"/>
       <c r="N86" t="inlineStr"/>
       <c r="O86" t="n">
         <v>-10.6</v>
@@ -12441,9 +12235,7 @@
       <c r="L87" t="n">
         <v>-9.699999999999999</v>
       </c>
-      <c r="M87" t="n">
-        <v>-14.7</v>
-      </c>
+      <c r="M87" t="inlineStr"/>
       <c r="N87" t="inlineStr">
         <is>
           <t>WR30</t>
@@ -12583,9 +12375,7 @@
       <c r="L88" t="n">
         <v>9.1</v>
       </c>
-      <c r="M88" t="n">
-        <v>-7.2</v>
-      </c>
+      <c r="M88" t="inlineStr"/>
       <c r="N88" t="inlineStr"/>
       <c r="O88" t="n">
         <v>8.6</v>
@@ -12731,9 +12521,7 @@
       <c r="L89" t="n">
         <v>-0.4</v>
       </c>
-      <c r="M89" t="n">
-        <v>7.2</v>
-      </c>
+      <c r="M89" t="inlineStr"/>
       <c r="N89" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -12879,9 +12667,7 @@
       <c r="L90" t="n">
         <v>15</v>
       </c>
-      <c r="M90" t="n">
-        <v>14.5</v>
-      </c>
+      <c r="M90" t="inlineStr"/>
       <c r="N90" t="inlineStr"/>
       <c r="O90" t="n">
         <v>11.6</v>
@@ -12911,7 +12697,9 @@
       <c r="V90" t="b">
         <v>0</v>
       </c>
-      <c r="W90" t="inlineStr"/>
+      <c r="W90" s="1" t="n">
+        <v>46399</v>
+      </c>
       <c r="X90" t="inlineStr"/>
       <c r="Y90" t="n">
         <v>0</v>
@@ -13011,9 +12799,7 @@
       <c r="L91" t="n">
         <v>6.2</v>
       </c>
-      <c r="M91" t="n">
-        <v>-11.2</v>
-      </c>
+      <c r="M91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
       <c r="O91" t="n">
         <v>-3.5</v>
@@ -13149,9 +12935,7 @@
       <c r="L92" t="n">
         <v>-4.6</v>
       </c>
-      <c r="M92" t="n">
-        <v>0.7</v>
-      </c>
+      <c r="M92" t="inlineStr"/>
       <c r="N92" t="inlineStr">
         <is>
           <t>WR30</t>
@@ -13301,9 +13085,7 @@
       <c r="L93" t="n">
         <v>6.9</v>
       </c>
-      <c r="M93" t="n">
-        <v>-3.4</v>
-      </c>
+      <c r="M93" t="inlineStr"/>
       <c r="N93" t="inlineStr"/>
       <c r="O93" t="n">
         <v>5.4</v>
@@ -13445,9 +13227,7 @@
       <c r="L94" t="n">
         <v>-8.5</v>
       </c>
-      <c r="M94" t="n">
-        <v>-18.1</v>
-      </c>
+      <c r="M94" t="inlineStr"/>
       <c r="N94" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -13516,7 +13296,7 @@
         <v>-19.43</v>
       </c>
       <c r="AK94" t="n">
-        <v>-25.92</v>
+        <v>-26</v>
       </c>
       <c r="AL94" t="n">
         <v>4.08</v>
@@ -13587,9 +13367,7 @@
       <c r="L95" t="n">
         <v>16</v>
       </c>
-      <c r="M95" t="n">
-        <v>13.3</v>
-      </c>
+      <c r="M95" t="inlineStr"/>
       <c r="N95" t="inlineStr"/>
       <c r="O95" t="n">
         <v>-20.2</v>
@@ -13725,9 +13503,7 @@
       <c r="L96" t="n">
         <v>-8</v>
       </c>
-      <c r="M96" t="n">
-        <v>18.8</v>
-      </c>
+      <c r="M96" t="inlineStr"/>
       <c r="N96" t="inlineStr">
         <is>
           <t>WR40</t>
@@ -13873,9 +13649,7 @@
       <c r="L97" t="n">
         <v>4.3</v>
       </c>
-      <c r="M97" t="n">
-        <v>-17.9</v>
-      </c>
+      <c r="M97" t="inlineStr"/>
       <c r="N97" t="inlineStr"/>
       <c r="O97" t="n">
         <v>-8.9</v>
@@ -14011,9 +13785,7 @@
       <c r="L98" t="n">
         <v>32.9</v>
       </c>
-      <c r="M98" t="n">
-        <v>36.4</v>
-      </c>
+      <c r="M98" t="inlineStr"/>
       <c r="N98" t="inlineStr"/>
       <c r="O98" t="n">
         <v>8.300000000000001</v>
@@ -14155,9 +13927,7 @@
       <c r="L99" t="n">
         <v>1.8</v>
       </c>
-      <c r="M99" t="n">
-        <v>-1.2</v>
-      </c>
+      <c r="M99" t="inlineStr"/>
       <c r="N99" t="inlineStr"/>
       <c r="O99" t="n">
         <v>-29.3</v>
@@ -14301,9 +14071,7 @@
       <c r="L100" t="n">
         <v>9</v>
       </c>
-      <c r="M100" t="n">
-        <v>-16.1</v>
-      </c>
+      <c r="M100" t="inlineStr"/>
       <c r="N100" t="inlineStr"/>
       <c r="O100" t="n">
         <v>-13.5</v>
@@ -14447,9 +14215,7 @@
       <c r="L101" t="n">
         <v>5.4</v>
       </c>
-      <c r="M101" t="n">
-        <v>-24</v>
-      </c>
+      <c r="M101" t="inlineStr"/>
       <c r="N101" t="inlineStr"/>
       <c r="O101" t="n">
         <v>-20</v>
@@ -14595,9 +14361,7 @@
       <c r="L102" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="M102" t="n">
-        <v>9.300000000000001</v>
-      </c>
+      <c r="M102" t="inlineStr"/>
       <c r="N102" t="inlineStr"/>
       <c r="O102" t="n">
         <v>7.8</v>
@@ -14739,9 +14503,7 @@
       <c r="L103" t="n">
         <v>4.2</v>
       </c>
-      <c r="M103" t="n">
-        <v>-13.1</v>
-      </c>
+      <c r="M103" t="inlineStr"/>
       <c r="N103" t="inlineStr"/>
       <c r="O103" t="n">
         <v>-31.3</v>
@@ -14885,9 +14647,7 @@
       <c r="L104" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="M104" t="n">
-        <v>-9.5</v>
-      </c>
+      <c r="M104" t="inlineStr"/>
       <c r="N104" t="inlineStr"/>
       <c r="O104" t="n">
         <v>-7.7</v>
@@ -15029,9 +14789,7 @@
       <c r="L105" t="n">
         <v>4.9</v>
       </c>
-      <c r="M105" t="n">
-        <v>-13.2</v>
-      </c>
+      <c r="M105" t="inlineStr"/>
       <c r="N105" t="inlineStr"/>
       <c r="O105" t="n">
         <v>-9</v>
@@ -15177,9 +14935,7 @@
       <c r="L106" t="n">
         <v>8.9</v>
       </c>
-      <c r="M106" t="n">
-        <v>-10.7</v>
-      </c>
+      <c r="M106" t="inlineStr"/>
       <c r="N106" t="inlineStr"/>
       <c r="O106" t="n">
         <v>-5.4</v>
@@ -15325,9 +15081,7 @@
       <c r="L107" t="n">
         <v>-10.4</v>
       </c>
-      <c r="M107" t="n">
-        <v>-37.1</v>
-      </c>
+      <c r="M107" t="inlineStr"/>
       <c r="N107" t="inlineStr"/>
       <c r="O107" t="n">
         <v>-13.3</v>
@@ -15463,9 +15217,7 @@
       <c r="L108" t="n">
         <v>-9.5</v>
       </c>
-      <c r="M108" t="n">
-        <v>-16</v>
-      </c>
+      <c r="M108" t="inlineStr"/>
       <c r="N108" t="inlineStr"/>
       <c r="O108" t="n">
         <v>-16.6</v>
@@ -15601,9 +15353,7 @@
       <c r="L109" t="n">
         <v>30.3</v>
       </c>
-      <c r="M109" t="n">
-        <v>33.7</v>
-      </c>
+      <c r="M109" t="inlineStr"/>
       <c r="N109" t="inlineStr"/>
       <c r="O109" t="n">
         <v>20.7</v>
@@ -15749,9 +15499,7 @@
       <c r="L110" t="n">
         <v>3.7</v>
       </c>
-      <c r="M110" t="n">
-        <v>-17.8</v>
-      </c>
+      <c r="M110" t="inlineStr"/>
       <c r="N110" t="inlineStr"/>
       <c r="O110" t="n">
         <v>1.7</v>
@@ -15897,9 +15645,7 @@
       <c r="L111" t="n">
         <v>-12.7</v>
       </c>
-      <c r="M111" t="n">
-        <v>-24.5</v>
-      </c>
+      <c r="M111" t="inlineStr"/>
       <c r="N111" t="inlineStr"/>
       <c r="O111" t="n">
         <v>-15.8</v>
@@ -16035,9 +15781,7 @@
       <c r="L112" t="n">
         <v>-29.6</v>
       </c>
-      <c r="M112" t="n">
-        <v>-23.9</v>
-      </c>
+      <c r="M112" t="inlineStr"/>
       <c r="N112" t="inlineStr"/>
       <c r="O112" t="n">
         <v>-39.2</v>
@@ -16173,9 +15917,7 @@
       <c r="L113" t="n">
         <v>-19.2</v>
       </c>
-      <c r="M113" t="n">
-        <v>-30.4</v>
-      </c>
+      <c r="M113" t="inlineStr"/>
       <c r="N113" t="inlineStr"/>
       <c r="O113" t="n">
         <v>-21.1</v>
@@ -16311,9 +16053,7 @@
       <c r="L114" t="n">
         <v>48</v>
       </c>
-      <c r="M114" t="n">
-        <v>52.7</v>
-      </c>
+      <c r="M114" t="inlineStr"/>
       <c r="N114" t="inlineStr"/>
       <c r="O114" t="n">
         <v>11.9</v>
@@ -16455,9 +16195,7 @@
       <c r="L115" t="n">
         <v>-25.1</v>
       </c>
-      <c r="M115" t="n">
-        <v>-23.7</v>
-      </c>
+      <c r="M115" t="inlineStr"/>
       <c r="N115" t="inlineStr"/>
       <c r="O115" t="n">
         <v>-31.4</v>
@@ -16601,9 +16339,7 @@
       <c r="L116" t="n">
         <v>-9.5</v>
       </c>
-      <c r="M116" t="n">
-        <v>-12.5</v>
-      </c>
+      <c r="M116" t="inlineStr"/>
       <c r="N116" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -16743,9 +16479,7 @@
       <c r="L117" t="n">
         <v>3.9</v>
       </c>
-      <c r="M117" t="n">
-        <v>12.5</v>
-      </c>
+      <c r="M117" t="inlineStr"/>
       <c r="N117" t="inlineStr"/>
       <c r="O117" t="n">
         <v>-18</v>
@@ -16889,9 +16623,7 @@
       <c r="L118" t="n">
         <v>31.7</v>
       </c>
-      <c r="M118" t="n">
-        <v>58.5</v>
-      </c>
+      <c r="M118" t="inlineStr"/>
       <c r="N118" t="inlineStr"/>
       <c r="O118" t="n">
         <v>27</v>
@@ -17033,9 +16765,7 @@
       <c r="L119" t="n">
         <v>4.4</v>
       </c>
-      <c r="M119" t="n">
-        <v>18.4</v>
-      </c>
+      <c r="M119" t="inlineStr"/>
       <c r="N119" t="inlineStr"/>
       <c r="O119" t="n">
         <v>-31</v>
@@ -17177,9 +16907,7 @@
       <c r="L120" t="n">
         <v>-0.7</v>
       </c>
-      <c r="M120" t="n">
-        <v>-42.6</v>
-      </c>
+      <c r="M120" t="inlineStr"/>
       <c r="N120" t="inlineStr">
         <is>
           <t>WR40</t>
@@ -17327,9 +17055,7 @@
       <c r="L121" t="n">
         <v>-5.6</v>
       </c>
-      <c r="M121" t="n">
-        <v>-46.6</v>
-      </c>
+      <c r="M121" t="inlineStr"/>
       <c r="N121" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -17469,9 +17195,7 @@
       <c r="L122" t="n">
         <v>3.8</v>
       </c>
-      <c r="M122" t="n">
-        <v>32.8</v>
-      </c>
+      <c r="M122" t="inlineStr"/>
       <c r="N122" t="inlineStr"/>
       <c r="O122" t="n">
         <v>-41.2</v>
@@ -17617,9 +17341,7 @@
       <c r="L123" t="n">
         <v>-5.3</v>
       </c>
-      <c r="M123" t="n">
-        <v>-22.9</v>
-      </c>
+      <c r="M123" t="inlineStr"/>
       <c r="N123" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -17759,9 +17481,7 @@
       <c r="L124" t="n">
         <v>0.8</v>
       </c>
-      <c r="M124" t="n">
-        <v>10.8</v>
-      </c>
+      <c r="M124" t="inlineStr"/>
       <c r="N124" t="inlineStr"/>
       <c r="O124" t="n">
         <v>-13</v>
@@ -17903,9 +17623,7 @@
       <c r="L125" t="n">
         <v>3.7</v>
       </c>
-      <c r="M125" t="n">
-        <v>8.1</v>
-      </c>
+      <c r="M125" t="inlineStr"/>
       <c r="N125" t="inlineStr"/>
       <c r="O125" t="n">
         <v>-20.6</v>
@@ -18041,9 +17759,7 @@
       <c r="L126" t="n">
         <v>3</v>
       </c>
-      <c r="M126" t="n">
-        <v>16.2</v>
-      </c>
+      <c r="M126" t="inlineStr"/>
       <c r="N126" t="inlineStr"/>
       <c r="O126" t="n">
         <v>-30.4</v>
@@ -18183,9 +17899,7 @@
       <c r="L127" t="n">
         <v>1.5</v>
       </c>
-      <c r="M127" t="n">
-        <v>-32.1</v>
-      </c>
+      <c r="M127" t="inlineStr"/>
       <c r="N127" t="inlineStr"/>
       <c r="O127" t="n">
         <v>-24.7</v>
@@ -18329,9 +18043,7 @@
       <c r="L128" t="n">
         <v>7.1</v>
       </c>
-      <c r="M128" t="n">
-        <v>-9.6</v>
-      </c>
+      <c r="M128" t="inlineStr"/>
       <c r="N128" t="inlineStr"/>
       <c r="O128" t="n">
         <v>1.9</v>
@@ -18475,9 +18187,7 @@
       <c r="L129" t="n">
         <v>-2.7</v>
       </c>
-      <c r="M129" t="n">
-        <v>-26.1</v>
-      </c>
+      <c r="M129" t="inlineStr"/>
       <c r="N129" t="inlineStr">
         <is>
           <t>WR30</t>
@@ -18627,9 +18337,7 @@
       <c r="L130" t="n">
         <v>1.7</v>
       </c>
-      <c r="M130" t="n">
-        <v>-20.5</v>
-      </c>
+      <c r="M130" t="inlineStr"/>
       <c r="N130" t="inlineStr"/>
       <c r="O130" t="n">
         <v>-1.6</v>
@@ -18775,9 +18483,7 @@
       <c r="L131" t="n">
         <v>4.8</v>
       </c>
-      <c r="M131" t="n">
-        <v>29.1</v>
-      </c>
+      <c r="M131" t="inlineStr"/>
       <c r="N131" t="inlineStr"/>
       <c r="O131" t="n">
         <v>-33.7</v>
@@ -18919,9 +18625,7 @@
       <c r="L132" t="n">
         <v>1.7</v>
       </c>
-      <c r="M132" t="n">
-        <v>-25.2</v>
-      </c>
+      <c r="M132" t="inlineStr"/>
       <c r="N132" t="inlineStr"/>
       <c r="O132" t="n">
         <v>-12.3</v>
@@ -18986,7 +18690,7 @@
         <v>-24.68</v>
       </c>
       <c r="AK132" t="n">
-        <v>-30.14</v>
+        <v>-30.13</v>
       </c>
       <c r="AL132" t="n">
         <v>1.78</v>
@@ -19057,9 +18761,7 @@
       <c r="L133" t="n">
         <v>52.9</v>
       </c>
-      <c r="M133" t="n">
-        <v>63.7</v>
-      </c>
+      <c r="M133" t="inlineStr"/>
       <c r="N133" t="inlineStr"/>
       <c r="O133" t="n">
         <v>18.6</v>
@@ -19201,9 +18903,7 @@
       <c r="L134" t="n">
         <v>1.4</v>
       </c>
-      <c r="M134" t="n">
-        <v>-3</v>
-      </c>
+      <c r="M134" t="inlineStr"/>
       <c r="N134" t="inlineStr"/>
       <c r="O134" t="n">
         <v>-14.9</v>
@@ -19345,9 +19045,7 @@
       <c r="L135" t="n">
         <v>52.3</v>
       </c>
-      <c r="M135" t="n">
-        <v>74.2</v>
-      </c>
+      <c r="M135" t="inlineStr"/>
       <c r="N135" t="inlineStr"/>
       <c r="O135" t="n">
         <v>18</v>
@@ -19489,9 +19187,7 @@
       <c r="L136" t="n">
         <v>-1.3</v>
       </c>
-      <c r="M136" t="n">
-        <v>7.2</v>
-      </c>
+      <c r="M136" t="inlineStr"/>
       <c r="N136" t="inlineStr"/>
       <c r="O136" t="n">
         <v>-19.9</v>
@@ -19633,9 +19329,7 @@
       <c r="L137" t="n">
         <v>37</v>
       </c>
-      <c r="M137" t="n">
-        <v>30.8</v>
-      </c>
+      <c r="M137" t="inlineStr"/>
       <c r="N137" t="inlineStr"/>
       <c r="O137" t="n">
         <v>5.2</v>
@@ -19777,9 +19471,7 @@
       <c r="L138" t="n">
         <v>13.5</v>
       </c>
-      <c r="M138" t="n">
-        <v>37.4</v>
-      </c>
+      <c r="M138" t="inlineStr"/>
       <c r="N138" t="inlineStr"/>
       <c r="O138" t="n">
         <v>-21.7</v>
@@ -19925,9 +19617,7 @@
       <c r="L139" t="n">
         <v>-11.1</v>
       </c>
-      <c r="M139" t="n">
-        <v>-3.2</v>
-      </c>
+      <c r="M139" t="inlineStr"/>
       <c r="N139" t="inlineStr"/>
       <c r="O139" t="n">
         <v>-25.3</v>
@@ -20069,9 +19759,7 @@
       <c r="L140" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="M140" t="n">
-        <v>-1.8</v>
-      </c>
+      <c r="M140" t="inlineStr"/>
       <c r="N140" t="inlineStr"/>
       <c r="O140" t="n">
         <v>3.2</v>
@@ -20211,9 +19899,7 @@
       <c r="L141" t="n">
         <v>-24.2</v>
       </c>
-      <c r="M141" t="n">
-        <v>-34.3</v>
-      </c>
+      <c r="M141" t="inlineStr"/>
       <c r="N141" t="inlineStr"/>
       <c r="O141" t="n">
         <v>-24.4</v>
@@ -20359,9 +20045,7 @@
       <c r="L142" t="n">
         <v>5.1</v>
       </c>
-      <c r="M142" t="n">
-        <v>31.4</v>
-      </c>
+      <c r="M142" t="inlineStr"/>
       <c r="N142" t="inlineStr"/>
       <c r="O142" t="n">
         <v>-32.6</v>
@@ -20503,9 +20187,7 @@
       <c r="L143" t="n">
         <v>-14.4</v>
       </c>
-      <c r="M143" t="n">
-        <v>-0</v>
-      </c>
+      <c r="M143" t="inlineStr"/>
       <c r="N143" t="inlineStr"/>
       <c r="O143" t="n">
         <v>-14.3</v>
@@ -20647,9 +20329,7 @@
       <c r="L144" t="n">
         <v>18.1</v>
       </c>
-      <c r="M144" t="n">
-        <v>6.8</v>
-      </c>
+      <c r="M144" t="inlineStr"/>
       <c r="N144" t="inlineStr"/>
       <c r="O144" t="n">
         <v>16.9</v>
@@ -20781,9 +20461,7 @@
       <c r="L145" t="n">
         <v>-11.4</v>
       </c>
-      <c r="M145" t="n">
-        <v>19.9</v>
-      </c>
+      <c r="M145" t="inlineStr"/>
       <c r="N145" t="inlineStr"/>
       <c r="O145" t="n">
         <v>-30.7</v>
@@ -20925,9 +20603,7 @@
       <c r="L146" t="n">
         <v>10.3</v>
       </c>
-      <c r="M146" t="n">
-        <v>15.9</v>
-      </c>
+      <c r="M146" t="inlineStr"/>
       <c r="N146" t="inlineStr"/>
       <c r="O146" t="n">
         <v>10.8</v>
@@ -21069,9 +20745,7 @@
       <c r="L147" t="n">
         <v>30.9</v>
       </c>
-      <c r="M147" t="n">
-        <v>23.6</v>
-      </c>
+      <c r="M147" t="inlineStr"/>
       <c r="N147" t="inlineStr"/>
       <c r="O147" t="n">
         <v>12.6</v>
@@ -21211,9 +20885,7 @@
       <c r="L148" t="n">
         <v>-22.2</v>
       </c>
-      <c r="M148" t="n">
-        <v>-6</v>
-      </c>
+      <c r="M148" t="inlineStr"/>
       <c r="N148" t="inlineStr"/>
       <c r="O148" t="n">
         <v>-24.1</v>
@@ -21355,9 +21027,7 @@
       <c r="L149" t="n">
         <v>-25.3</v>
       </c>
-      <c r="M149" t="n">
-        <v>-3.2</v>
-      </c>
+      <c r="M149" t="inlineStr"/>
       <c r="N149" t="inlineStr"/>
       <c r="O149" t="n">
         <v>-50.8</v>
@@ -21503,9 +21173,7 @@
       <c r="L150" t="n">
         <v>14.7</v>
       </c>
-      <c r="M150" t="n">
-        <v>-10.4</v>
-      </c>
+      <c r="M150" t="inlineStr"/>
       <c r="N150" t="inlineStr"/>
       <c r="O150" t="n">
         <v>-0.5</v>
@@ -21649,9 +21317,7 @@
       <c r="L151" t="n">
         <v>0.4</v>
       </c>
-      <c r="M151" t="n">
-        <v>26.1</v>
-      </c>
+      <c r="M151" t="inlineStr"/>
       <c r="N151" t="inlineStr"/>
       <c r="O151" t="n">
         <v>-36.9</v>
@@ -21793,9 +21459,7 @@
       <c r="L152" t="n">
         <v>-11.6</v>
       </c>
-      <c r="M152" t="n">
-        <v>-13.1</v>
-      </c>
+      <c r="M152" t="inlineStr"/>
       <c r="N152" t="inlineStr"/>
       <c r="O152" t="n">
         <v>-32.4</v>
@@ -21941,9 +21605,7 @@
       <c r="L153" t="n">
         <v>-4</v>
       </c>
-      <c r="M153" t="n">
-        <v>9.4</v>
-      </c>
+      <c r="M153" t="inlineStr"/>
       <c r="N153" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -22089,9 +21751,7 @@
       <c r="L154" t="n">
         <v>-3</v>
       </c>
-      <c r="M154" t="n">
-        <v>44.2</v>
-      </c>
+      <c r="M154" t="inlineStr"/>
       <c r="N154" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -22237,9 +21897,7 @@
       <c r="L155" t="n">
         <v>-29.1</v>
       </c>
-      <c r="M155" t="n">
-        <v>-25.6</v>
-      </c>
+      <c r="M155" t="inlineStr"/>
       <c r="N155" t="inlineStr"/>
       <c r="O155" t="n">
         <v>-45.6</v>
@@ -22375,9 +22033,7 @@
       <c r="L156" t="n">
         <v>-11.2</v>
       </c>
-      <c r="M156" t="n">
-        <v>-18.7</v>
-      </c>
+      <c r="M156" t="inlineStr"/>
       <c r="N156" t="inlineStr"/>
       <c r="O156" t="n">
         <v>-31.4</v>
@@ -22513,9 +22169,7 @@
       <c r="L157" t="n">
         <v>23.1</v>
       </c>
-      <c r="M157" t="n">
-        <v>10.6</v>
-      </c>
+      <c r="M157" t="inlineStr"/>
       <c r="N157" t="inlineStr"/>
       <c r="O157" t="n">
         <v>21</v>
@@ -22655,9 +22309,7 @@
       <c r="L158" t="n">
         <v>4.2</v>
       </c>
-      <c r="M158" t="n">
-        <v>5.2</v>
-      </c>
+      <c r="M158" t="inlineStr"/>
       <c r="N158" t="inlineStr"/>
       <c r="O158" t="n">
         <v>-20.1</v>
@@ -22797,9 +22449,7 @@
       <c r="L159" t="n">
         <v>7.3</v>
       </c>
-      <c r="M159" t="n">
-        <v>13.6</v>
-      </c>
+      <c r="M159" t="inlineStr"/>
       <c r="N159" t="inlineStr"/>
       <c r="O159" t="n">
         <v>-6.2</v>
@@ -22941,9 +22591,7 @@
       <c r="L160" t="n">
         <v>-24</v>
       </c>
-      <c r="M160" t="n">
-        <v>-13.6</v>
-      </c>
+      <c r="M160" t="inlineStr"/>
       <c r="N160" t="inlineStr"/>
       <c r="O160" t="n">
         <v>-25.9</v>
@@ -23102,7 +22750,7 @@
         <v>46241</v>
       </c>
       <c r="Y161" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z161" t="inlineStr"/>
       <c r="AA161" t="n">
@@ -23127,13 +22775,13 @@
         <v>8.76</v>
       </c>
       <c r="AH161" t="n">
-        <v>7.06</v>
+        <v>7.26</v>
       </c>
       <c r="AI161" t="n">
-        <v>7.06</v>
+        <v>7.26</v>
       </c>
       <c r="AJ161" t="n">
-        <v>-19.4</v>
+        <v>-17.12</v>
       </c>
       <c r="AK161" t="n">
         <v>-24.31</v>
@@ -23142,7 +22790,7 @@
         <v>26.14</v>
       </c>
       <c r="AM161" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AN161" t="n">
         <v>4</v>
@@ -23150,11 +22798,11 @@
       <c r="AO161" t="inlineStr"/>
       <c r="AP161" t="inlineStr"/>
       <c r="AQ161" t="n">
-        <v>4.92</v>
+        <v>4.42</v>
       </c>
       <c r="AR161" t="inlineStr"/>
       <c r="AS161" t="n">
-        <v>-24.32</v>
+        <v>-21.54</v>
       </c>
       <c r="AT161" t="inlineStr">
         <is>
@@ -23207,9 +22855,7 @@
       <c r="L162" t="n">
         <v>-14.9</v>
       </c>
-      <c r="M162" t="n">
-        <v>-16.8</v>
-      </c>
+      <c r="M162" t="inlineStr"/>
       <c r="N162" t="inlineStr"/>
       <c r="O162" t="n">
         <v>-27</v>
@@ -23353,9 +22999,7 @@
       <c r="L163" t="n">
         <v>47.6</v>
       </c>
-      <c r="M163" t="n">
-        <v>44.2</v>
-      </c>
+      <c r="M163" t="inlineStr"/>
       <c r="N163" t="inlineStr"/>
       <c r="O163" t="n">
         <v>31.8</v>
@@ -23497,9 +23141,7 @@
       <c r="L164" t="n">
         <v>25</v>
       </c>
-      <c r="M164" t="n">
-        <v>22.3</v>
-      </c>
+      <c r="M164" t="inlineStr"/>
       <c r="N164" t="inlineStr"/>
       <c r="O164" t="n">
         <v>-6.8</v>
@@ -23641,9 +23283,7 @@
       <c r="L165" t="n">
         <v>-21.4</v>
       </c>
-      <c r="M165" t="n">
-        <v>-12.5</v>
-      </c>
+      <c r="M165" t="inlineStr"/>
       <c r="N165" t="inlineStr"/>
       <c r="O165" t="n">
         <v>-27.7</v>
@@ -23785,9 +23425,7 @@
       <c r="L166" t="n">
         <v>-12.9</v>
       </c>
-      <c r="M166" t="n">
-        <v>5</v>
-      </c>
+      <c r="M166" t="inlineStr"/>
       <c r="N166" t="inlineStr"/>
       <c r="O166" t="n">
         <v>-17.4</v>
@@ -23929,9 +23567,7 @@
       <c r="L167" t="n">
         <v>-8.4</v>
       </c>
-      <c r="M167" t="n">
-        <v>12.5</v>
-      </c>
+      <c r="M167" t="inlineStr"/>
       <c r="N167" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -24077,9 +23713,7 @@
       <c r="L168" t="n">
         <v>-3.5</v>
       </c>
-      <c r="M168" t="n">
-        <v>4.4</v>
-      </c>
+      <c r="M168" t="inlineStr"/>
       <c r="N168" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -24225,9 +23859,7 @@
       <c r="L169" t="n">
         <v>-24.2</v>
       </c>
-      <c r="M169" t="n">
-        <v>-20.7</v>
-      </c>
+      <c r="M169" t="inlineStr"/>
       <c r="N169" t="inlineStr"/>
       <c r="O169" t="n">
         <v>-25.7</v>
@@ -24371,9 +24003,7 @@
       <c r="L170" t="n">
         <v>-28.8</v>
       </c>
-      <c r="M170" t="n">
-        <v>-14.7</v>
-      </c>
+      <c r="M170" t="inlineStr"/>
       <c r="N170" t="inlineStr"/>
       <c r="O170" t="n">
         <v>-42.4</v>
@@ -24515,9 +24145,7 @@
       <c r="L171" t="n">
         <v>28.5</v>
       </c>
-      <c r="M171" t="n">
-        <v>11.3</v>
-      </c>
+      <c r="M171" t="inlineStr"/>
       <c r="N171" t="inlineStr"/>
       <c r="O171" t="n">
         <v>27</v>
@@ -24659,9 +24287,7 @@
       <c r="L172" t="n">
         <v>52.9</v>
       </c>
-      <c r="M172" t="n">
-        <v>76.7</v>
-      </c>
+      <c r="M172" t="inlineStr"/>
       <c r="N172" t="inlineStr"/>
       <c r="O172" t="n">
         <v>5.4</v>
@@ -24807,9 +24433,7 @@
       <c r="L173" t="n">
         <v>-37.8</v>
       </c>
-      <c r="M173" t="n">
-        <v>-11.6</v>
-      </c>
+      <c r="M173" t="inlineStr"/>
       <c r="N173" t="inlineStr"/>
       <c r="O173" t="n">
         <v>-50.4</v>
@@ -24955,9 +24579,7 @@
       <c r="L174" t="n">
         <v>-14.6</v>
       </c>
-      <c r="M174" t="n">
-        <v>-3</v>
-      </c>
+      <c r="M174" t="inlineStr"/>
       <c r="N174" t="inlineStr"/>
       <c r="O174" t="n">
         <v>-14.7</v>
@@ -25103,9 +24725,7 @@
       <c r="L175" t="n">
         <v>9</v>
       </c>
-      <c r="M175" t="n">
-        <v>-17.9</v>
-      </c>
+      <c r="M175" t="inlineStr"/>
       <c r="N175" t="inlineStr"/>
       <c r="O175" t="n">
         <v>-7.5</v>
@@ -25249,9 +24869,7 @@
       <c r="L176" t="n">
         <v>46.7</v>
       </c>
-      <c r="M176" t="n">
-        <v>9.800000000000001</v>
-      </c>
+      <c r="M176" t="inlineStr"/>
       <c r="N176" t="inlineStr"/>
       <c r="O176" t="n">
         <v>42.3</v>
@@ -25401,9 +25019,7 @@
       <c r="L177" t="n">
         <v>48.1</v>
       </c>
-      <c r="M177" t="n">
-        <v>37.8</v>
-      </c>
+      <c r="M177" t="inlineStr"/>
       <c r="N177" t="inlineStr"/>
       <c r="O177" t="n">
         <v>45.4</v>
@@ -25549,9 +25165,7 @@
       <c r="L178" t="n">
         <v>56.6</v>
       </c>
-      <c r="M178" t="n">
-        <v>-13</v>
-      </c>
+      <c r="M178" t="inlineStr"/>
       <c r="N178" t="inlineStr"/>
       <c r="O178" t="n">
         <v>50.5</v>
@@ -25697,9 +25311,7 @@
       <c r="L179" t="n">
         <v>78.8</v>
       </c>
-      <c r="M179" t="n">
-        <v>15.7</v>
-      </c>
+      <c r="M179" t="inlineStr"/>
       <c r="N179" t="inlineStr"/>
       <c r="O179" t="n">
         <v>73.3</v>
@@ -25849,9 +25461,7 @@
       <c r="L180" t="n">
         <v>51.9</v>
       </c>
-      <c r="M180" t="n">
-        <v>21.2</v>
-      </c>
+      <c r="M180" t="inlineStr"/>
       <c r="N180" t="inlineStr"/>
       <c r="O180" t="n">
         <v>49.5</v>
@@ -26001,9 +25611,7 @@
       <c r="L181" t="n">
         <v>82.09999999999999</v>
       </c>
-      <c r="M181" t="n">
-        <v>30.3</v>
-      </c>
+      <c r="M181" t="inlineStr"/>
       <c r="N181" t="inlineStr"/>
       <c r="O181" t="n">
         <v>75.8</v>
@@ -26149,9 +25757,7 @@
       <c r="L182" t="n">
         <v>63.2</v>
       </c>
-      <c r="M182" t="n">
-        <v>51.4</v>
-      </c>
+      <c r="M182" t="inlineStr"/>
       <c r="N182" t="inlineStr"/>
       <c r="O182" t="n">
         <v>43.2</v>
@@ -26293,9 +25899,7 @@
       <c r="L183" t="n">
         <v>35.3</v>
       </c>
-      <c r="M183" t="n">
-        <v>8.5</v>
-      </c>
+      <c r="M183" t="inlineStr"/>
       <c r="N183" t="inlineStr"/>
       <c r="O183" t="n">
         <v>24.9</v>
@@ -26445,9 +26049,7 @@
       <c r="L184" t="n">
         <v>65.3</v>
       </c>
-      <c r="M184" t="n">
-        <v>2.8</v>
-      </c>
+      <c r="M184" t="inlineStr"/>
       <c r="N184" t="inlineStr"/>
       <c r="O184" t="n">
         <v>53.9</v>
@@ -26593,9 +26195,7 @@
       <c r="L185" t="n">
         <v>19.3</v>
       </c>
-      <c r="M185" t="n">
-        <v>-9.5</v>
-      </c>
+      <c r="M185" t="inlineStr"/>
       <c r="N185" t="inlineStr"/>
       <c r="O185" t="n">
         <v>15.7</v>
@@ -26741,9 +26341,7 @@
       <c r="L186" t="n">
         <v>51.8</v>
       </c>
-      <c r="M186" t="n">
-        <v>-1.7</v>
-      </c>
+      <c r="M186" t="inlineStr"/>
       <c r="N186" t="inlineStr"/>
       <c r="O186" t="n">
         <v>46.3</v>
@@ -26887,9 +26485,7 @@
       <c r="L187" t="n">
         <v>51.3</v>
       </c>
-      <c r="M187" t="n">
-        <v>13.1</v>
-      </c>
+      <c r="M187" t="inlineStr"/>
       <c r="N187" t="inlineStr"/>
       <c r="O187" t="n">
         <v>48.1</v>
@@ -27035,9 +26631,7 @@
       <c r="L188" t="n">
         <v>32.8</v>
       </c>
-      <c r="M188" t="n">
-        <v>12.2</v>
-      </c>
+      <c r="M188" t="inlineStr"/>
       <c r="N188" t="inlineStr"/>
       <c r="O188" t="n">
         <v>24</v>
@@ -27183,9 +26777,7 @@
       <c r="L189" t="n">
         <v>98.2</v>
       </c>
-      <c r="M189" t="n">
-        <v>51.8</v>
-      </c>
+      <c r="M189" t="inlineStr"/>
       <c r="N189" t="inlineStr"/>
       <c r="O189" t="n">
         <v>70.09999999999999</v>
@@ -27327,9 +26919,7 @@
       <c r="L190" t="n">
         <v>40.9</v>
       </c>
-      <c r="M190" t="n">
-        <v>-3.3</v>
-      </c>
+      <c r="M190" t="inlineStr"/>
       <c r="N190" t="inlineStr"/>
       <c r="O190" t="n">
         <v>40</v>
@@ -27473,9 +27063,7 @@
       <c r="L191" t="n">
         <v>51.1</v>
       </c>
-      <c r="M191" t="n">
-        <v>-7.2</v>
-      </c>
+      <c r="M191" t="inlineStr"/>
       <c r="N191" t="inlineStr"/>
       <c r="O191" t="n">
         <v>36.8</v>
@@ -27625,9 +27213,7 @@
       <c r="L192" t="n">
         <v>37.5</v>
       </c>
-      <c r="M192" t="n">
-        <v>-3.4</v>
-      </c>
+      <c r="M192" t="inlineStr"/>
       <c r="N192" t="inlineStr"/>
       <c r="O192" t="n">
         <v>31.2</v>
@@ -27767,9 +27353,7 @@
       <c r="L193" t="n">
         <v>-14.6</v>
       </c>
-      <c r="M193" t="n">
-        <v>18.4</v>
-      </c>
+      <c r="M193" t="inlineStr"/>
       <c r="N193" t="inlineStr"/>
       <c r="O193" t="n">
         <v>-45.2</v>
@@ -27919,9 +27503,7 @@
       <c r="L194" t="n">
         <v>16.5</v>
       </c>
-      <c r="M194" t="n">
-        <v>-14.8</v>
-      </c>
+      <c r="M194" t="inlineStr"/>
       <c r="N194" t="inlineStr"/>
       <c r="O194" t="n">
         <v>12.5</v>
@@ -28067,9 +27649,7 @@
       <c r="L195" t="n">
         <v>-8.800000000000001</v>
       </c>
-      <c r="M195" t="n">
-        <v>-24</v>
-      </c>
+      <c r="M195" t="inlineStr"/>
       <c r="N195" t="inlineStr"/>
       <c r="O195" t="n">
         <v>-12.3</v>
@@ -28219,9 +27799,7 @@
       <c r="L196" t="n">
         <v>41.1</v>
       </c>
-      <c r="M196" t="n">
-        <v>209.3</v>
-      </c>
+      <c r="M196" t="inlineStr"/>
       <c r="N196" t="inlineStr"/>
       <c r="O196" t="n">
         <v>20.1</v>
@@ -28367,9 +27945,7 @@
       <c r="L197" t="n">
         <v>9.9</v>
       </c>
-      <c r="M197" t="n">
-        <v>-10.7</v>
-      </c>
+      <c r="M197" t="inlineStr"/>
       <c r="N197" t="inlineStr"/>
       <c r="O197" t="n">
         <v>10.1</v>
@@ -28515,9 +28091,7 @@
       <c r="L198" t="n">
         <v>-27.9</v>
       </c>
-      <c r="M198" t="n">
-        <v>-42.6</v>
-      </c>
+      <c r="M198" t="inlineStr"/>
       <c r="N198" t="inlineStr"/>
       <c r="O198" t="n">
         <v>-29.5</v>
@@ -28667,9 +28241,7 @@
       <c r="L199" t="n">
         <v>-28.3</v>
       </c>
-      <c r="M199" t="n">
-        <v>8.1</v>
-      </c>
+      <c r="M199" t="inlineStr"/>
       <c r="N199" t="inlineStr"/>
       <c r="O199" t="n">
         <v>-29.8</v>
@@ -28811,9 +28383,7 @@
       <c r="L200" t="n">
         <v>19.8</v>
       </c>
-      <c r="M200" t="n">
-        <v>-0.2</v>
-      </c>
+      <c r="M200" t="inlineStr"/>
       <c r="N200" t="inlineStr"/>
       <c r="O200" t="n">
         <v>15.6</v>
@@ -28955,9 +28525,7 @@
       <c r="L201" t="n">
         <v>37.4</v>
       </c>
-      <c r="M201" t="n">
-        <v>-1.3</v>
-      </c>
+      <c r="M201" t="inlineStr"/>
       <c r="N201" t="inlineStr"/>
       <c r="O201" t="n">
         <v>31.2</v>
@@ -29101,9 +28669,7 @@
       <c r="L202" t="n">
         <v>73.3</v>
       </c>
-      <c r="M202" t="n">
-        <v>43.2</v>
-      </c>
+      <c r="M202" t="inlineStr"/>
       <c r="N202" t="inlineStr"/>
       <c r="O202" t="n">
         <v>67.09999999999999</v>
@@ -29249,9 +28815,7 @@
       <c r="L203" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="M203" t="n">
-        <v>-30.4</v>
-      </c>
+      <c r="M203" t="inlineStr"/>
       <c r="N203" t="inlineStr"/>
       <c r="O203" t="n">
         <v>4.4</v>
@@ -29399,9 +28963,7 @@
       <c r="L204" t="n">
         <v>-20.5</v>
       </c>
-      <c r="M204" t="n">
-        <v>-20.7</v>
-      </c>
+      <c r="M204" t="inlineStr"/>
       <c r="N204" t="inlineStr"/>
       <c r="O204" t="n">
         <v>-34.2</v>
@@ -29541,9 +29103,7 @@
       <c r="L205" t="n">
         <v>-15.1</v>
       </c>
-      <c r="M205" t="n">
-        <v>-46.6</v>
-      </c>
+      <c r="M205" t="inlineStr"/>
       <c r="N205" t="inlineStr"/>
       <c r="O205" t="n">
         <v>-13.4</v>
@@ -29693,9 +29253,7 @@
       <c r="L206" t="n">
         <v>22.6</v>
       </c>
-      <c r="M206" t="n">
-        <v>-9.6</v>
-      </c>
+      <c r="M206" t="inlineStr"/>
       <c r="N206" t="inlineStr"/>
       <c r="O206" t="n">
         <v>18.2</v>
@@ -29835,9 +29393,7 @@
       <c r="L207" t="n">
         <v>26.4</v>
       </c>
-      <c r="M207" t="n">
-        <v>-25.7</v>
-      </c>
+      <c r="M207" t="inlineStr"/>
       <c r="N207" t="inlineStr"/>
       <c r="O207" t="n">
         <v>14.8</v>
@@ -29981,9 +29537,7 @@
       <c r="L208" t="n">
         <v>-28.1</v>
       </c>
-      <c r="M208" t="n">
-        <v>-56.1</v>
-      </c>
+      <c r="M208" t="inlineStr"/>
       <c r="N208" t="inlineStr"/>
       <c r="O208" t="n">
         <v>-42.6</v>
@@ -30058,7 +29612,7 @@
         <v>-49.19</v>
       </c>
       <c r="AK208" t="n">
-        <v>-56.19</v>
+        <v>-56.15</v>
       </c>
       <c r="AL208" t="n">
         <v>20.63</v>
@@ -30133,9 +29687,7 @@
       <c r="L209" t="n">
         <v>3.7</v>
       </c>
-      <c r="M209" t="n">
-        <v>-25.2</v>
-      </c>
+      <c r="M209" t="inlineStr"/>
       <c r="N209" t="inlineStr"/>
       <c r="O209" t="n">
         <v>-1.3</v>
@@ -30204,7 +29756,7 @@
         <v>-25.65</v>
       </c>
       <c r="AK209" t="n">
-        <v>-31.04</v>
+        <v>-31.03</v>
       </c>
       <c r="AL209" t="n">
         <v>4.41</v>
@@ -30279,9 +29831,7 @@
       <c r="L210" t="n">
         <v>61.4</v>
       </c>
-      <c r="M210" t="n">
-        <v>17.9</v>
-      </c>
+      <c r="M210" t="inlineStr"/>
       <c r="N210" t="inlineStr"/>
       <c r="O210" t="n">
         <v>59.4</v>
@@ -30425,9 +29975,7 @@
       <c r="L211" t="n">
         <v>-8.199999999999999</v>
       </c>
-      <c r="M211" t="n">
-        <v>45.9</v>
-      </c>
+      <c r="M211" t="inlineStr"/>
       <c r="N211" t="inlineStr">
         <is>
           <t>WR40</t>
@@ -30577,9 +30125,7 @@
       <c r="L212" t="n">
         <v>1.4</v>
       </c>
-      <c r="M212" t="n">
-        <v>-20.5</v>
-      </c>
+      <c r="M212" t="inlineStr"/>
       <c r="N212" t="inlineStr"/>
       <c r="O212" t="n">
         <v>-1.3</v>
@@ -30729,9 +30275,7 @@
       <c r="L213" t="n">
         <v>1.6</v>
       </c>
-      <c r="M213" t="n">
-        <v>-25.4</v>
-      </c>
+      <c r="M213" t="inlineStr"/>
       <c r="N213" t="inlineStr"/>
       <c r="O213" t="n">
         <v>-7.1</v>
@@ -30881,9 +30425,7 @@
       <c r="L214" t="n">
         <v>-34.2</v>
       </c>
-      <c r="M214" t="n">
-        <v>-15.6</v>
-      </c>
+      <c r="M214" t="inlineStr"/>
       <c r="N214" t="inlineStr"/>
       <c r="O214" t="n">
         <v>-35.9</v>
@@ -31025,9 +30567,7 @@
       <c r="L215" t="n">
         <v>-11.8</v>
       </c>
-      <c r="M215" t="n">
-        <v>-32.1</v>
-      </c>
+      <c r="M215" t="inlineStr"/>
       <c r="N215" t="inlineStr"/>
       <c r="O215" t="n">
         <v>-15.2</v>
@@ -31177,9 +30717,7 @@
       <c r="L216" t="n">
         <v>-30.4</v>
       </c>
-      <c r="M216" t="n">
-        <v>-22.9</v>
-      </c>
+      <c r="M216" t="inlineStr"/>
       <c r="N216" t="inlineStr"/>
       <c r="O216" t="n">
         <v>-44.5</v>
@@ -31323,9 +30861,7 @@
       <c r="L217" t="n">
         <v>2.3</v>
       </c>
-      <c r="M217" t="n">
-        <v>-44.9</v>
-      </c>
+      <c r="M217" t="inlineStr"/>
       <c r="N217" t="inlineStr"/>
       <c r="O217" t="n">
         <v>-4.2</v>
@@ -31475,9 +31011,7 @@
       <c r="L218" t="n">
         <v>-24.2</v>
       </c>
-      <c r="M218" t="n">
-        <v>-15.3</v>
-      </c>
+      <c r="M218" t="inlineStr"/>
       <c r="N218" t="inlineStr"/>
       <c r="O218" t="n">
         <v>-37.2</v>
@@ -31623,9 +31157,7 @@
       <c r="L219" t="n">
         <v>-1.1</v>
       </c>
-      <c r="M219" t="n">
-        <v>-13.2</v>
-      </c>
+      <c r="M219" t="inlineStr"/>
       <c r="N219" t="inlineStr"/>
       <c r="O219" t="n">
         <v>-16.6</v>
@@ -31771,9 +31303,7 @@
       <c r="L220" t="n">
         <v>-18.3</v>
       </c>
-      <c r="M220" t="n">
-        <v>90.09999999999999</v>
-      </c>
+      <c r="M220" t="inlineStr"/>
       <c r="N220" t="inlineStr"/>
       <c r="O220" t="n">
         <v>-36.7</v>
@@ -31851,7 +31381,7 @@
         <v>-12.09</v>
       </c>
       <c r="AL220" t="n">
-        <v>138.65</v>
+        <v>138.74</v>
       </c>
       <c r="AM220" t="n">
         <v>63</v>
@@ -31919,9 +31449,7 @@
       <c r="L221" t="n">
         <v>-28.4</v>
       </c>
-      <c r="M221" t="n">
-        <v>-24.3</v>
-      </c>
+      <c r="M221" t="inlineStr"/>
       <c r="N221" t="inlineStr"/>
       <c r="O221" t="n">
         <v>-36.4</v>
@@ -32071,9 +31599,7 @@
       <c r="L222" t="n">
         <v>-26.9</v>
       </c>
-      <c r="M222" t="n">
-        <v>21.6</v>
-      </c>
+      <c r="M222" t="inlineStr"/>
       <c r="N222" t="inlineStr"/>
       <c r="O222" t="n">
         <v>-37.1</v>
@@ -32147,7 +31673,7 @@
         <v>-6.68</v>
       </c>
       <c r="AL222" t="n">
-        <v>51.25</v>
+        <v>51.28</v>
       </c>
       <c r="AM222" t="n">
         <v>63</v>
@@ -32215,9 +31741,7 @@
       <c r="L223" t="n">
         <v>-11.5</v>
       </c>
-      <c r="M223" t="n">
-        <v>12.9</v>
-      </c>
+      <c r="M223" t="inlineStr"/>
       <c r="N223" t="inlineStr"/>
       <c r="O223" t="n">
         <v>-33.1</v>
@@ -32353,9 +31877,7 @@
       <c r="L224" t="n">
         <v>-22.5</v>
       </c>
-      <c r="M224" t="n">
-        <v>-24.7</v>
-      </c>
+      <c r="M224" t="inlineStr"/>
       <c r="N224" t="inlineStr"/>
       <c r="O224" t="n">
         <v>-25.8</v>
@@ -32505,9 +32027,7 @@
       <c r="L225" t="n">
         <v>1.1</v>
       </c>
-      <c r="M225" t="n">
-        <v>4.8</v>
-      </c>
+      <c r="M225" t="inlineStr"/>
       <c r="N225" t="inlineStr"/>
       <c r="O225" t="n">
         <v>-22.3</v>
@@ -32799,9 +32319,7 @@
       <c r="L227" t="n">
         <v>-34.3</v>
       </c>
-      <c r="M227" t="n">
-        <v>-35.4</v>
-      </c>
+      <c r="M227" t="inlineStr"/>
       <c r="N227" t="inlineStr"/>
       <c r="O227" t="n">
         <v>-41.1</v>
@@ -32947,9 +32465,7 @@
       <c r="L228" t="n">
         <v>11.2</v>
       </c>
-      <c r="M228" t="n">
-        <v>-5.8</v>
-      </c>
+      <c r="M228" t="inlineStr"/>
       <c r="N228" t="inlineStr"/>
       <c r="O228" t="n">
         <v>10.3</v>
@@ -33239,9 +32755,7 @@
       <c r="L230" t="n">
         <v>-25.2</v>
       </c>
-      <c r="M230" t="n">
-        <v>-26.1</v>
-      </c>
+      <c r="M230" t="inlineStr"/>
       <c r="N230" t="inlineStr"/>
       <c r="O230" t="n">
         <v>-25.6</v>
@@ -33391,9 +32905,7 @@
       <c r="L231" t="n">
         <v>-29.2</v>
       </c>
-      <c r="M231" t="n">
-        <v>-5</v>
-      </c>
+      <c r="M231" t="inlineStr"/>
       <c r="N231" t="inlineStr"/>
       <c r="O231" t="n">
         <v>-50.8</v>
@@ -33541,9 +33053,7 @@
       <c r="L232" t="n">
         <v>22.2</v>
       </c>
-      <c r="M232" t="n">
-        <v>-19.9</v>
-      </c>
+      <c r="M232" t="inlineStr"/>
       <c r="N232" t="inlineStr"/>
       <c r="O232" t="n">
         <v>20.3</v>
@@ -33687,9 +33197,7 @@
       <c r="L233" t="n">
         <v>7.4</v>
       </c>
-      <c r="M233" t="n">
-        <v>-8.1</v>
-      </c>
+      <c r="M233" t="inlineStr"/>
       <c r="N233" t="inlineStr"/>
       <c r="O233" t="n">
         <v>5</v>
@@ -33833,9 +33341,7 @@
       <c r="L234" t="n">
         <v>64.90000000000001</v>
       </c>
-      <c r="M234" t="n">
-        <v>47.4</v>
-      </c>
+      <c r="M234" t="inlineStr"/>
       <c r="N234" t="inlineStr"/>
       <c r="O234" t="n">
         <v>51.1</v>
@@ -33977,9 +33483,7 @@
       <c r="L235" t="n">
         <v>22.5</v>
       </c>
-      <c r="M235" t="n">
-        <v>10</v>
-      </c>
+      <c r="M235" t="inlineStr"/>
       <c r="N235" t="inlineStr"/>
       <c r="O235" t="n">
         <v>17.1</v>
@@ -34113,9 +33617,7 @@
       <c r="L236" t="n">
         <v>-28.7</v>
       </c>
-      <c r="M236" t="n">
-        <v>0.7</v>
-      </c>
+      <c r="M236" t="inlineStr"/>
       <c r="N236" t="inlineStr"/>
       <c r="O236" t="n">
         <v>-39.4</v>
@@ -34257,9 +33759,7 @@
       <c r="L237" t="n">
         <v>3.4</v>
       </c>
-      <c r="M237" t="n">
-        <v>22.1</v>
-      </c>
+      <c r="M237" t="inlineStr"/>
       <c r="N237" t="inlineStr"/>
       <c r="O237" t="n">
         <v>-17.1</v>
@@ -34401,9 +33901,7 @@
       <c r="L238" t="n">
         <v>-30.2</v>
       </c>
-      <c r="M238" t="n">
-        <v>-44.5</v>
-      </c>
+      <c r="M238" t="inlineStr"/>
       <c r="N238" t="inlineStr"/>
       <c r="O238" t="n">
         <v>-33.9</v>
@@ -34553,9 +34051,7 @@
       <c r="L239" t="n">
         <v>-24.2</v>
       </c>
-      <c r="M239" t="n">
-        <v>-35.6</v>
-      </c>
+      <c r="M239" t="inlineStr"/>
       <c r="N239" t="inlineStr"/>
       <c r="O239" t="n">
         <v>-32.4</v>
@@ -34695,9 +34191,7 @@
       <c r="L240" t="n">
         <v>13.7</v>
       </c>
-      <c r="M240" t="n">
-        <v>-17</v>
-      </c>
+      <c r="M240" t="inlineStr"/>
       <c r="N240" t="inlineStr"/>
       <c r="O240" t="n">
         <v>-28.1</v>
@@ -34841,9 +34335,7 @@
       <c r="L241" t="n">
         <v>55.8</v>
       </c>
-      <c r="M241" t="n">
-        <v>9.300000000000001</v>
-      </c>
+      <c r="M241" t="inlineStr"/>
       <c r="N241" t="inlineStr"/>
       <c r="O241" t="n">
         <v>35.7</v>
@@ -34983,9 +34475,7 @@
       <c r="L242" t="n">
         <v>-20.1</v>
       </c>
-      <c r="M242" t="n">
-        <v>-29.6</v>
-      </c>
+      <c r="M242" t="inlineStr"/>
       <c r="N242" t="inlineStr"/>
       <c r="O242" t="n">
         <v>-21.7</v>
@@ -35015,9 +34505,7 @@
       <c r="V242" t="b">
         <v>0</v>
       </c>
-      <c r="W242" s="1" t="n">
-        <v>46310</v>
-      </c>
+      <c r="W242" t="inlineStr"/>
       <c r="X242" s="1" t="n">
         <v>46225</v>
       </c>
@@ -35060,7 +34548,7 @@
         <v>-8.73</v>
       </c>
       <c r="AK242" t="n">
-        <v>-12.21</v>
+        <v>-12.27</v>
       </c>
       <c r="AL242" t="n">
         <v>24.31</v>
@@ -35131,9 +34619,7 @@
       <c r="L243" t="n">
         <v>-0.4</v>
       </c>
-      <c r="M243" t="n">
-        <v>8.1</v>
-      </c>
+      <c r="M243" t="inlineStr"/>
       <c r="N243" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -35287,9 +34773,7 @@
       <c r="L244" t="n">
         <v>58.8</v>
       </c>
-      <c r="M244" t="n">
-        <v>39.3</v>
-      </c>
+      <c r="M244" t="inlineStr"/>
       <c r="N244" t="inlineStr"/>
       <c r="O244" t="n">
         <v>44.2</v>
@@ -35435,9 +34919,7 @@
       <c r="L245" t="n">
         <v>28.6</v>
       </c>
-      <c r="M245" t="n">
-        <v>17</v>
-      </c>
+      <c r="M245" t="inlineStr"/>
       <c r="N245" t="inlineStr"/>
       <c r="O245" t="n">
         <v>21.9</v>
@@ -35579,9 +35061,7 @@
       <c r="L246" t="n">
         <v>69.59999999999999</v>
       </c>
-      <c r="M246" t="n">
-        <v>42.5</v>
-      </c>
+      <c r="M246" t="inlineStr"/>
       <c r="N246" t="inlineStr"/>
       <c r="O246" t="n">
         <v>31.9</v>
@@ -35727,9 +35207,7 @@
       <c r="L247" t="n">
         <v>25.2</v>
       </c>
-      <c r="M247" t="n">
-        <v>-6.7</v>
-      </c>
+      <c r="M247" t="inlineStr"/>
       <c r="N247" t="inlineStr"/>
       <c r="O247" t="n">
         <v>23.7</v>
@@ -35875,9 +35353,7 @@
       <c r="L248" t="n">
         <v>-5.5</v>
       </c>
-      <c r="M248" t="n">
-        <v>-16.1</v>
-      </c>
+      <c r="M248" t="inlineStr"/>
       <c r="N248" t="inlineStr">
         <is>
           <t>WR30</t>
@@ -36031,9 +35507,7 @@
       <c r="L249" t="n">
         <v>15.6</v>
       </c>
-      <c r="M249" t="n">
-        <v>-37.1</v>
-      </c>
+      <c r="M249" t="inlineStr"/>
       <c r="N249" t="inlineStr"/>
       <c r="O249" t="n">
         <v>13.1</v>
@@ -36181,9 +35655,7 @@
       <c r="L250" t="n">
         <v>-29.9</v>
       </c>
-      <c r="M250" t="n">
-        <v>-7.4</v>
-      </c>
+      <c r="M250" t="inlineStr"/>
       <c r="N250" t="inlineStr"/>
       <c r="O250" t="n">
         <v>-41.6</v>
@@ -36329,9 +35801,7 @@
       <c r="L251" t="n">
         <v>39.4</v>
       </c>
-      <c r="M251" t="n">
-        <v>49.7</v>
-      </c>
+      <c r="M251" t="inlineStr"/>
       <c r="N251" t="inlineStr"/>
       <c r="O251" t="n">
         <v>13.8</v>
@@ -36473,9 +35943,7 @@
       <c r="L252" t="n">
         <v>-4.2</v>
       </c>
-      <c r="M252" t="n">
-        <v>-14.8</v>
-      </c>
+      <c r="M252" t="inlineStr"/>
       <c r="N252" t="inlineStr">
         <is>
           <t>WR30</t>
@@ -36623,9 +36091,7 @@
       <c r="L253" t="n">
         <v>4.1</v>
       </c>
-      <c r="M253" t="n">
-        <v>1.4</v>
-      </c>
+      <c r="M253" t="inlineStr"/>
       <c r="N253" t="inlineStr"/>
       <c r="O253" t="n">
         <v>-6.3</v>
@@ -36767,9 +36233,7 @@
       <c r="L254" t="n">
         <v>-21.7</v>
       </c>
-      <c r="M254" t="n">
-        <v>29.1</v>
-      </c>
+      <c r="M254" t="inlineStr"/>
       <c r="N254" t="inlineStr"/>
       <c r="O254" t="n">
         <v>-33.7</v>
@@ -36911,9 +36375,7 @@
       <c r="L255" t="n">
         <v>-38.3</v>
       </c>
-      <c r="M255" t="n">
-        <v>-9.699999999999999</v>
-      </c>
+      <c r="M255" t="inlineStr"/>
       <c r="N255" t="inlineStr"/>
       <c r="O255" t="n">
         <v>-48.2</v>
@@ -37059,9 +36521,7 @@
       <c r="L256" t="n">
         <v>-0.4</v>
       </c>
-      <c r="M256" t="n">
-        <v>-18.6</v>
-      </c>
+      <c r="M256" t="inlineStr"/>
       <c r="N256" t="inlineStr"/>
       <c r="O256" t="n">
         <v>-14.2</v>
@@ -37211,9 +36671,7 @@
       <c r="L257" t="n">
         <v>-12</v>
       </c>
-      <c r="M257" t="n">
-        <v>-22.9</v>
-      </c>
+      <c r="M257" t="inlineStr"/>
       <c r="N257" t="inlineStr"/>
       <c r="O257" t="n">
         <v>-24.6</v>
@@ -37359,9 +36817,7 @@
       <c r="L258" t="n">
         <v>-19.7</v>
       </c>
-      <c r="M258" t="n">
-        <v>-35.7</v>
-      </c>
+      <c r="M258" t="inlineStr"/>
       <c r="N258" t="inlineStr"/>
       <c r="O258" t="n">
         <v>-21.6</v>
@@ -37432,7 +36888,7 @@
         <v>-18.59</v>
       </c>
       <c r="AK258" t="n">
-        <v>-21.23</v>
+        <v>-21.26</v>
       </c>
       <c r="AL258" t="n">
         <v>19.06</v>
@@ -37505,9 +36961,7 @@
       <c r="L259" t="n">
         <v>-6.4</v>
       </c>
-      <c r="M259" t="n">
-        <v>19.7</v>
-      </c>
+      <c r="M259" t="inlineStr"/>
       <c r="N259" t="inlineStr"/>
       <c r="O259" t="n">
         <v>-12.3</v>
@@ -37649,9 +37103,7 @@
       <c r="L260" t="n">
         <v>4.6</v>
       </c>
-      <c r="M260" t="n">
-        <v>6.1</v>
-      </c>
+      <c r="M260" t="inlineStr"/>
       <c r="N260" t="inlineStr"/>
       <c r="O260" t="n">
         <v>1.5</v>
@@ -37797,9 +37249,7 @@
       <c r="L261" t="n">
         <v>-0.2</v>
       </c>
-      <c r="M261" t="n">
-        <v>60.5</v>
-      </c>
+      <c r="M261" t="inlineStr"/>
       <c r="N261" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -37949,9 +37399,7 @@
       <c r="L262" t="n">
         <v>0.9</v>
       </c>
-      <c r="M262" t="n">
-        <v>10.8</v>
-      </c>
+      <c r="M262" t="inlineStr"/>
       <c r="N262" t="inlineStr"/>
       <c r="O262" t="n">
         <v>-29.6</v>
@@ -38095,9 +37543,7 @@
       <c r="L263" t="n">
         <v>16.5</v>
       </c>
-      <c r="M263" t="n">
-        <v>-17.8</v>
-      </c>
+      <c r="M263" t="inlineStr"/>
       <c r="N263" t="inlineStr"/>
       <c r="O263" t="n">
         <v>11.6</v>
@@ -38241,9 +37687,7 @@
       <c r="L264" t="n">
         <v>-9.6</v>
       </c>
-      <c r="M264" t="n">
-        <v>16.2</v>
-      </c>
+      <c r="M264" t="inlineStr"/>
       <c r="N264" t="inlineStr">
         <is>
           <t>WR30</t>
@@ -38393,9 +37837,7 @@
       <c r="L265" t="n">
         <v>-11.3</v>
       </c>
-      <c r="M265" t="n">
-        <v>-20.8</v>
-      </c>
+      <c r="M265" t="inlineStr"/>
       <c r="N265" t="inlineStr"/>
       <c r="O265" t="n">
         <v>-25.4</v>
@@ -38539,9 +37981,7 @@
       <c r="L266" t="n">
         <v>14.9</v>
       </c>
-      <c r="M266" t="n">
-        <v>4.1</v>
-      </c>
+      <c r="M266" t="inlineStr"/>
       <c r="N266" t="inlineStr"/>
       <c r="O266" t="n">
         <v>14.1</v>
@@ -38683,9 +38123,7 @@
       <c r="L267" t="n">
         <v>-32.8</v>
       </c>
-      <c r="M267" t="n">
-        <v>-33.2</v>
-      </c>
+      <c r="M267" t="inlineStr"/>
       <c r="N267" t="inlineStr"/>
       <c r="O267" t="n">
         <v>-50.4</v>
@@ -38833,9 +38271,7 @@
       <c r="L268" t="n">
         <v>-40.3</v>
       </c>
-      <c r="M268" t="n">
-        <v>-39.5</v>
-      </c>
+      <c r="M268" t="inlineStr"/>
       <c r="N268" t="inlineStr"/>
       <c r="O268" t="n">
         <v>-41.9</v>
@@ -38985,9 +38421,7 @@
       <c r="L269" t="n">
         <v>-48.5</v>
       </c>
-      <c r="M269" t="n">
-        <v>-47.7</v>
-      </c>
+      <c r="M269" t="inlineStr"/>
       <c r="N269" t="inlineStr"/>
       <c r="O269" t="n">
         <v>-48.8</v>
@@ -39137,9 +38571,7 @@
       <c r="L270" t="n">
         <v>-26.7</v>
       </c>
-      <c r="M270" t="n">
-        <v>-36.2</v>
-      </c>
+      <c r="M270" t="inlineStr"/>
       <c r="N270" t="inlineStr"/>
       <c r="O270" t="n">
         <v>-36.4</v>
@@ -39283,9 +38715,7 @@
       <c r="L271" t="n">
         <v>-0.5</v>
       </c>
-      <c r="M271" t="n">
-        <v>69.40000000000001</v>
-      </c>
+      <c r="M271" t="inlineStr"/>
       <c r="N271" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -39435,9 +38865,7 @@
       <c r="L272" t="n">
         <v>7.1</v>
       </c>
-      <c r="M272" t="n">
-        <v>48.4</v>
-      </c>
+      <c r="M272" t="inlineStr"/>
       <c r="N272" t="inlineStr"/>
       <c r="O272" t="n">
         <v>-17.9</v>
@@ -39583,9 +39011,7 @@
       <c r="L273" t="n">
         <v>7.6</v>
       </c>
-      <c r="M273" t="n">
-        <v>14.7</v>
-      </c>
+      <c r="M273" t="inlineStr"/>
       <c r="N273" t="inlineStr"/>
       <c r="O273" t="n">
         <v>-26.5</v>
@@ -39727,9 +39153,7 @@
       <c r="L274" t="n">
         <v>-2.1</v>
       </c>
-      <c r="M274" t="n">
-        <v>9.1</v>
-      </c>
+      <c r="M274" t="inlineStr"/>
       <c r="N274" t="inlineStr">
         <is>
           <t>WR30</t>
@@ -39879,9 +39303,7 @@
       <c r="L275" t="n">
         <v>-9</v>
       </c>
-      <c r="M275" t="n">
-        <v>-2.7</v>
-      </c>
+      <c r="M275" t="inlineStr"/>
       <c r="N275" t="inlineStr"/>
       <c r="O275" t="n">
         <v>-18</v>
@@ -40029,9 +39451,7 @@
       <c r="L276" t="n">
         <v>-42.2</v>
       </c>
-      <c r="M276" t="n">
-        <v>-37.2</v>
-      </c>
+      <c r="M276" t="inlineStr"/>
       <c r="N276" t="inlineStr"/>
       <c r="O276" t="n">
         <v>-46.7</v>
@@ -40106,7 +39526,7 @@
         <v>-13.59</v>
       </c>
       <c r="AK276" t="n">
-        <v>-18.36</v>
+        <v>-18.35</v>
       </c>
       <c r="AL276" t="n">
         <v>45.74</v>
@@ -40181,9 +39601,7 @@
       <c r="L277" t="n">
         <v>-3.4</v>
       </c>
-      <c r="M277" t="n">
-        <v>-23.2</v>
-      </c>
+      <c r="M277" t="inlineStr"/>
       <c r="N277" t="inlineStr"/>
       <c r="O277" t="n">
         <v>-10.1</v>
@@ -40333,9 +39751,7 @@
       <c r="L278" t="n">
         <v>2.9</v>
       </c>
-      <c r="M278" t="n">
-        <v>-13.8</v>
-      </c>
+      <c r="M278" t="inlineStr"/>
       <c r="N278" t="inlineStr"/>
       <c r="O278" t="n">
         <v>-0.1</v>
@@ -40485,9 +39901,7 @@
       <c r="L279" t="n">
         <v>-8.800000000000001</v>
       </c>
-      <c r="M279" t="n">
-        <v>-9.5</v>
-      </c>
+      <c r="M279" t="inlineStr"/>
       <c r="N279" t="inlineStr"/>
       <c r="O279" t="n">
         <v>-10.8</v>
@@ -40629,9 +40043,7 @@
       <c r="L280" t="n">
         <v>0.2</v>
       </c>
-      <c r="M280" t="n">
-        <v>-6.4</v>
-      </c>
+      <c r="M280" t="inlineStr"/>
       <c r="N280" t="inlineStr"/>
       <c r="O280" t="n">
         <v>-7.8</v>
@@ -40773,9 +40185,7 @@
       <c r="L281" t="n">
         <v>21.4</v>
       </c>
-      <c r="M281" t="n">
-        <v>10.3</v>
-      </c>
+      <c r="M281" t="inlineStr"/>
       <c r="N281" t="inlineStr"/>
       <c r="O281" t="n">
         <v>19.8</v>
@@ -40915,9 +40325,7 @@
       <c r="L282" t="n">
         <v>13.6</v>
       </c>
-      <c r="M282" t="n">
-        <v>31</v>
-      </c>
+      <c r="M282" t="inlineStr"/>
       <c r="N282" t="inlineStr"/>
       <c r="O282" t="n">
         <v>6.5</v>
@@ -41059,9 +40467,7 @@
       <c r="L283" t="n">
         <v>-8.6</v>
       </c>
-      <c r="M283" t="n">
-        <v>-18.8</v>
-      </c>
+      <c r="M283" t="inlineStr"/>
       <c r="N283" t="inlineStr"/>
       <c r="O283" t="n">
         <v>-12.7</v>
@@ -41207,9 +40613,7 @@
       <c r="L284" t="n">
         <v>23.7</v>
       </c>
-      <c r="M284" t="n">
-        <v>-8.4</v>
-      </c>
+      <c r="M284" t="inlineStr"/>
       <c r="N284" t="inlineStr"/>
       <c r="O284" t="n">
         <v>20.2</v>
@@ -41353,9 +40757,7 @@
       <c r="L285" t="n">
         <v>-43.3</v>
       </c>
-      <c r="M285" t="n">
-        <v>11.5</v>
-      </c>
+      <c r="M285" t="inlineStr"/>
       <c r="N285" t="inlineStr"/>
       <c r="O285" t="n">
         <v>-55.7</v>
@@ -41501,9 +40903,7 @@
       <c r="L286" t="n">
         <v>29.3</v>
       </c>
-      <c r="M286" t="n">
-        <v>-9.300000000000001</v>
-      </c>
+      <c r="M286" t="inlineStr"/>
       <c r="N286" t="inlineStr"/>
       <c r="O286" t="n">
         <v>5.2</v>
@@ -41647,9 +41047,7 @@
       <c r="L287" t="n">
         <v>-0.9</v>
       </c>
-      <c r="M287" t="n">
-        <v>-7.9</v>
-      </c>
+      <c r="M287" t="inlineStr"/>
       <c r="N287" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -41799,9 +41197,7 @@
       <c r="L288" t="n">
         <v>23</v>
       </c>
-      <c r="M288" t="n">
-        <v>-25.2</v>
-      </c>
+      <c r="M288" t="inlineStr"/>
       <c r="N288" t="inlineStr"/>
       <c r="O288" t="n">
         <v>5.7</v>
@@ -41941,9 +41337,7 @@
       <c r="L289" t="n">
         <v>12.2</v>
       </c>
-      <c r="M289" t="n">
-        <v>-3.8</v>
-      </c>
+      <c r="M289" t="inlineStr"/>
       <c r="N289" t="inlineStr"/>
       <c r="O289" t="n">
         <v>8.800000000000001</v>
@@ -42089,9 +41483,7 @@
       <c r="L290" t="n">
         <v>45.6</v>
       </c>
-      <c r="M290" t="n">
-        <v>15.8</v>
-      </c>
+      <c r="M290" t="inlineStr"/>
       <c r="N290" t="inlineStr"/>
       <c r="O290" t="n">
         <v>25</v>
@@ -42235,9 +41627,7 @@
       <c r="L291" t="n">
         <v>-20</v>
       </c>
-      <c r="M291" t="n">
-        <v>-18.1</v>
-      </c>
+      <c r="M291" t="inlineStr"/>
       <c r="N291" t="inlineStr"/>
       <c r="O291" t="n">
         <v>-33</v>
@@ -42312,7 +41702,7 @@
         <v>-13.38</v>
       </c>
       <c r="AK291" t="n">
-        <v>-20.35</v>
+        <v>-20.44</v>
       </c>
       <c r="AL291" t="n">
         <v>11.91</v>
@@ -42387,9 +41777,7 @@
       <c r="L292" t="n">
         <v>56.3</v>
       </c>
-      <c r="M292" t="n">
-        <v>52.8</v>
-      </c>
+      <c r="M292" t="inlineStr"/>
       <c r="N292" t="inlineStr"/>
       <c r="O292" t="n">
         <v>34.3</v>
@@ -42539,9 +41927,7 @@
       <c r="L293" t="n">
         <v>-9</v>
       </c>
-      <c r="M293" t="n">
-        <v>35.8</v>
-      </c>
+      <c r="M293" t="inlineStr"/>
       <c r="N293" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -42691,9 +42077,7 @@
       <c r="L294" t="n">
         <v>-25.3</v>
       </c>
-      <c r="M294" t="n">
-        <v>32.8</v>
-      </c>
+      <c r="M294" t="inlineStr"/>
       <c r="N294" t="inlineStr"/>
       <c r="O294" t="n">
         <v>-43.3</v>
@@ -42839,9 +42223,7 @@
       <c r="L295" t="n">
         <v>-4.1</v>
       </c>
-      <c r="M295" t="n">
-        <v>-19.5</v>
-      </c>
+      <c r="M295" t="inlineStr"/>
       <c r="N295" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -42991,7 +42373,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>292 (+2 pending)</t>
+          <t>292 (+0 pending)</t>
         </is>
       </c>
     </row>
@@ -43015,7 +42397,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>$49,544.27  (+0.17% price-weighted)</t>
+          <t>$49,544.47  (+0.17% price-weighted)</t>
         </is>
       </c>
     </row>
@@ -43027,7 +42409,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-0.04%  &lt;- judge the system by this line</t>
+          <t>-0.03%  &lt;- judge the system by this line</t>
         </is>
       </c>
     </row>
@@ -43039,7 +42421,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-2.21%</t>
+          <t>-2.20%</t>
         </is>
       </c>
     </row>
@@ -43152,10 +42534,10 @@
         <v>74</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.87</v>
+        <v>-0.84</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.16</v>
+        <v>-3.12</v>
       </c>
       <c r="E13" t="n">
         <v>5.06</v>
@@ -43340,13 +42722,13 @@
         <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>-19.4</v>
+        <v>-17.12</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>-24.32</v>
+        <v>-21.54</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
@@ -43439,13 +42821,13 @@
         <v>65</v>
       </c>
       <c r="E26" t="n">
-        <v>4.32</v>
+        <v>4.31</v>
       </c>
       <c r="F26" t="n">
         <v>58</v>
       </c>
       <c r="G26" t="n">
-        <v>-8.6</v>
+        <v>-8.609999999999999</v>
       </c>
     </row>
     <row r="27">
@@ -43575,7 +42957,7 @@
         <v>10.7</v>
       </c>
       <c r="F32" t="n">
-        <v>-13.72</v>
+        <v>-13.73</v>
       </c>
     </row>
     <row r="33">
@@ -43597,7 +42979,7 @@
         <v>-4.52</v>
       </c>
       <c r="F33" t="n">
-        <v>-16.48</v>
+        <v>-16.51</v>
       </c>
     </row>
     <row r="34">

--- a/sts_ml_paper_tracker.xlsx
+++ b/sts_ml_paper_tracker.xlsx
@@ -771,7 +771,7 @@
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="n">
-        <v>89.84999999999999</v>
+        <v>89.84999847412109</v>
       </c>
       <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="inlineStr"/>
@@ -1697,7 +1697,7 @@
         <v>-8.800000000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>-10.1</v>
+        <v>-8.6</v>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
@@ -1708,7 +1708,7 @@
         <v>-8.4</v>
       </c>
       <c r="M10" t="n">
-        <v>-6.1</v>
+        <v>-4.1</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="n">
@@ -1746,7 +1746,7 @@
         <v>46310</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="n">
@@ -1769,13 +1769,13 @@
         <v>13.84</v>
       </c>
       <c r="AH10" t="n">
-        <v>14.18</v>
+        <v>14.47</v>
       </c>
       <c r="AI10" t="n">
-        <v>14.18</v>
+        <v>14.47</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2.46</v>
+        <v>4.55</v>
       </c>
       <c r="AK10" t="n">
         <v>-1.66</v>
@@ -1784,7 +1784,7 @@
         <v>6.21</v>
       </c>
       <c r="AM10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN10" t="n">
         <v>1</v>
@@ -1792,11 +1792,11 @@
       <c r="AO10" t="inlineStr"/>
       <c r="AP10" t="inlineStr"/>
       <c r="AQ10" t="n">
-        <v>-0.4</v>
+        <v>-1.51</v>
       </c>
       <c r="AR10" t="inlineStr"/>
       <c r="AS10" t="n">
-        <v>2.86</v>
+        <v>6.06</v>
       </c>
       <c r="AT10" t="inlineStr"/>
     </row>
@@ -3047,7 +3047,7 @@
         <v>14.7</v>
       </c>
       <c r="H20" t="n">
-        <v>26.2</v>
+        <v>30.1</v>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
@@ -3058,14 +3058,14 @@
         <v>2.1</v>
       </c>
       <c r="M20" t="n">
-        <v>18.7</v>
+        <v>21.3</v>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="n">
-        <v>-16.7</v>
+        <v>-16.6</v>
       </c>
       <c r="P20" t="n">
-        <v>191.37</v>
+        <v>191.33</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -3096,14 +3096,14 @@
         <v>46303</v>
       </c>
       <c r="Y20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="n">
-        <v>16.59</v>
+        <v>18.39</v>
       </c>
       <c r="AB20" t="n">
-        <v>16.59</v>
+        <v>18.39</v>
       </c>
       <c r="AC20" t="n">
         <v>-2.24</v>
@@ -3121,34 +3121,34 @@
         <v>195.43</v>
       </c>
       <c r="AH20" t="n">
-        <v>224.92</v>
+        <v>229.68</v>
       </c>
       <c r="AI20" t="n">
-        <v>224.92</v>
+        <v>229.68</v>
       </c>
       <c r="AJ20" t="n">
-        <v>15.09</v>
+        <v>17.53</v>
       </c>
       <c r="AK20" t="n">
         <v>-2.24</v>
       </c>
       <c r="AL20" t="n">
-        <v>16.59</v>
+        <v>18.39</v>
       </c>
       <c r="AM20" t="n">
+        <v>9</v>
+      </c>
+      <c r="AN20" t="n">
         <v>8</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>7</v>
       </c>
       <c r="AO20" t="inlineStr"/>
       <c r="AP20" t="inlineStr"/>
       <c r="AQ20" t="n">
-        <v>-0.82</v>
+        <v>-1.91</v>
       </c>
       <c r="AR20" t="inlineStr"/>
       <c r="AS20" t="n">
-        <v>15.91</v>
+        <v>19.44</v>
       </c>
       <c r="AT20" t="inlineStr"/>
     </row>
@@ -3859,7 +3859,7 @@
         <v>2.8</v>
       </c>
       <c r="H26" t="n">
-        <v>11.5</v>
+        <v>15.6</v>
       </c>
       <c r="I26" t="n">
         <v>2.42</v>
@@ -3872,7 +3872,7 @@
         <v>-8.800000000000001</v>
       </c>
       <c r="M26" t="n">
-        <v>-2.7</v>
+        <v>-2.9</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -3883,7 +3883,7 @@
         <v>-25.6</v>
       </c>
       <c r="P26" t="n">
-        <v>19.05</v>
+        <v>19.04</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -3914,7 +3914,7 @@
         <v>46295</v>
       </c>
       <c r="Y26" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z26" t="inlineStr"/>
       <c r="AA26" t="n">
@@ -3937,13 +3937,13 @@
         <v>17.36</v>
       </c>
       <c r="AH26" t="n">
-        <v>18.05</v>
+        <v>17.98</v>
       </c>
       <c r="AI26" t="n">
-        <v>18.05</v>
+        <v>17.98</v>
       </c>
       <c r="AJ26" t="n">
-        <v>3.97</v>
+        <v>3.57</v>
       </c>
       <c r="AK26" t="n">
         <v>-1.61</v>
@@ -3952,7 +3952,7 @@
         <v>6.86</v>
       </c>
       <c r="AM26" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AN26" t="n">
         <v>1</v>
@@ -3960,11 +3960,11 @@
       <c r="AO26" t="inlineStr"/>
       <c r="AP26" t="inlineStr"/>
       <c r="AQ26" t="n">
-        <v>0.65</v>
+        <v>-0.47</v>
       </c>
       <c r="AR26" t="inlineStr"/>
       <c r="AS26" t="n">
-        <v>3.33</v>
+        <v>4.04</v>
       </c>
       <c r="AT26" t="inlineStr"/>
     </row>
@@ -5099,7 +5099,7 @@
         <v>-0.9</v>
       </c>
       <c r="H35" t="n">
-        <v>-11.3</v>
+        <v>-14</v>
       </c>
       <c r="I35" t="n">
         <v>-3.75</v>
@@ -5112,7 +5112,7 @@
         <v>-12.9</v>
       </c>
       <c r="M35" t="n">
-        <v>-13.5</v>
+        <v>-14.9</v>
       </c>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="n">
@@ -5169,13 +5169,13 @@
         <v>115.12</v>
       </c>
       <c r="AH35" t="n">
-        <v>111.13</v>
+        <v>109.11</v>
       </c>
       <c r="AI35" t="n">
-        <v>111.13</v>
+        <v>109.11</v>
       </c>
       <c r="AJ35" t="n">
-        <v>-3.47</v>
+        <v>-5.22</v>
       </c>
       <c r="AK35" t="n">
         <v>-9.01</v>
@@ -5184,7 +5184,7 @@
         <v>4.59</v>
       </c>
       <c r="AM35" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AN35" t="n">
         <v>1</v>
@@ -5192,11 +5192,11 @@
       <c r="AO35" t="inlineStr"/>
       <c r="AP35" t="inlineStr"/>
       <c r="AQ35" t="n">
-        <v>0.72</v>
+        <v>-0.39</v>
       </c>
       <c r="AR35" t="inlineStr"/>
       <c r="AS35" t="n">
-        <v>-4.19</v>
+        <v>-4.83</v>
       </c>
       <c r="AT35" t="inlineStr"/>
     </row>
@@ -5216,7 +5216,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Extended</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -5231,7 +5231,7 @@
         <v>20.7</v>
       </c>
       <c r="H36" t="n">
-        <v>-4.1</v>
+        <v>-3.7</v>
       </c>
       <c r="I36" t="n">
         <v>-1.49</v>
@@ -5244,7 +5244,7 @@
         <v>17.3</v>
       </c>
       <c r="M36" t="n">
-        <v>20.3</v>
+        <v>19.8</v>
       </c>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="n">
@@ -5278,7 +5278,9 @@
       <c r="W36" s="1" t="n">
         <v>46331</v>
       </c>
-      <c r="X36" t="inlineStr"/>
+      <c r="X36" s="1" t="n">
+        <v>46311</v>
+      </c>
       <c r="Y36" t="n">
         <v>0</v>
       </c>
@@ -5287,9 +5289,11 @@
         <v>1.83</v>
       </c>
       <c r="AB36" t="n">
-        <v>4.98</v>
-      </c>
-      <c r="AC36" t="inlineStr"/>
+        <v>6.26</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>-10.54</v>
+      </c>
       <c r="AD36" t="inlineStr"/>
       <c r="AE36" t="n">
         <v>166.56</v>
@@ -5301,34 +5305,34 @@
         <v>166.56</v>
       </c>
       <c r="AH36" t="n">
-        <v>174.28</v>
+        <v>173.7</v>
       </c>
       <c r="AI36" t="n">
-        <v>174.28</v>
+        <v>173.7</v>
       </c>
       <c r="AJ36" t="n">
-        <v>4.63</v>
+        <v>4.29</v>
       </c>
       <c r="AK36" t="n">
         <v>-10.54</v>
       </c>
       <c r="AL36" t="n">
-        <v>4.98</v>
+        <v>6.26</v>
       </c>
       <c r="AM36" t="n">
+        <v>20</v>
+      </c>
+      <c r="AN36" t="n">
         <v>19</v>
-      </c>
-      <c r="AN36" t="n">
-        <v>18</v>
       </c>
       <c r="AO36" t="inlineStr"/>
       <c r="AP36" t="inlineStr"/>
       <c r="AQ36" t="n">
-        <v>0.72</v>
+        <v>-0.39</v>
       </c>
       <c r="AR36" t="inlineStr"/>
       <c r="AS36" t="n">
-        <v>3.91</v>
+        <v>4.68</v>
       </c>
       <c r="AT36" t="inlineStr"/>
     </row>
@@ -5890,7 +5894,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Extended</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -5905,12 +5909,14 @@
         <v>31.3</v>
       </c>
       <c r="H41" t="n">
-        <v>19.6</v>
+        <v>12.2</v>
       </c>
       <c r="I41" t="n">
         <v>1.47</v>
       </c>
-      <c r="J41" t="inlineStr"/>
+      <c r="J41" t="n">
+        <v>4.33</v>
+      </c>
       <c r="K41" t="n">
         <v>-5.99</v>
       </c>
@@ -5918,7 +5924,7 @@
         <v>3.5</v>
       </c>
       <c r="M41" t="n">
-        <v>19.9</v>
+        <v>11.8</v>
       </c>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="n">
@@ -5956,9 +5962,13 @@
         <v>46301</v>
       </c>
       <c r="Y41" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z41" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>ran</t>
+        </is>
+      </c>
       <c r="AA41" t="n">
         <v>4.88</v>
       </c>
@@ -5981,13 +5991,13 @@
         <v>10.85</v>
       </c>
       <c r="AH41" t="n">
-        <v>12.16</v>
+        <v>11.32</v>
       </c>
       <c r="AI41" t="n">
-        <v>12.16</v>
+        <v>11.32</v>
       </c>
       <c r="AJ41" t="n">
-        <v>12.07</v>
+        <v>4.33</v>
       </c>
       <c r="AK41" t="n">
         <v>-5.99</v>
@@ -5996,7 +6006,7 @@
         <v>18.71</v>
       </c>
       <c r="AM41" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AN41" t="n">
         <v>16</v>
@@ -6004,11 +6014,11 @@
       <c r="AO41" t="inlineStr"/>
       <c r="AP41" t="inlineStr"/>
       <c r="AQ41" t="n">
-        <v>1.38</v>
+        <v>0.25</v>
       </c>
       <c r="AR41" t="inlineStr"/>
       <c r="AS41" t="n">
-        <v>10.7</v>
+        <v>4.08</v>
       </c>
       <c r="AT41" t="inlineStr"/>
     </row>
@@ -6739,7 +6749,7 @@
         <v>4.6</v>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="I47" t="n">
         <v>-3.41</v>
@@ -6754,7 +6764,7 @@
         <v>-10.3</v>
       </c>
       <c r="M47" t="n">
-        <v>3.9</v>
+        <v>1.8</v>
       </c>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="n">
@@ -6792,7 +6802,7 @@
         <v>46301</v>
       </c>
       <c r="Y47" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
@@ -6821,34 +6831,34 @@
         <v>218.76</v>
       </c>
       <c r="AH47" t="n">
-        <v>245.16</v>
+        <v>239.9</v>
       </c>
       <c r="AI47" t="n">
-        <v>245.16</v>
+        <v>239.9</v>
       </c>
       <c r="AJ47" t="n">
-        <v>12.07</v>
+        <v>9.66</v>
       </c>
       <c r="AK47" t="n">
         <v>-8.949999999999999</v>
       </c>
       <c r="AL47" t="n">
-        <v>12.79</v>
+        <v>15.08</v>
       </c>
       <c r="AM47" t="n">
+        <v>22</v>
+      </c>
+      <c r="AN47" t="n">
         <v>21</v>
-      </c>
-      <c r="AN47" t="n">
-        <v>20</v>
       </c>
       <c r="AO47" t="inlineStr"/>
       <c r="AP47" t="inlineStr"/>
       <c r="AQ47" t="n">
-        <v>1.38</v>
+        <v>0.26</v>
       </c>
       <c r="AR47" t="inlineStr"/>
       <c r="AS47" t="n">
-        <v>10.68</v>
+        <v>9.4</v>
       </c>
       <c r="AT47" t="inlineStr"/>
     </row>
@@ -7021,7 +7031,7 @@
         <v>10.5</v>
       </c>
       <c r="H49" t="n">
-        <v>-5.2</v>
+        <v>-7.5</v>
       </c>
       <c r="I49" t="n">
         <v>-3.62</v>
@@ -7036,7 +7046,7 @@
         <v>-5.7</v>
       </c>
       <c r="M49" t="n">
-        <v>-1.2</v>
+        <v>-3.5</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
@@ -7097,34 +7107,34 @@
         <v>250.35</v>
       </c>
       <c r="AH49" t="n">
-        <v>251.67</v>
+        <v>245.2</v>
       </c>
       <c r="AI49" t="n">
-        <v>251.67</v>
+        <v>245.2</v>
       </c>
       <c r="AJ49" t="n">
-        <v>0.53</v>
+        <v>-2.06</v>
       </c>
       <c r="AK49" t="n">
         <v>-10.26</v>
       </c>
       <c r="AL49" t="n">
-        <v>1.73</v>
+        <v>2.46</v>
       </c>
       <c r="AM49" t="n">
+        <v>22</v>
+      </c>
+      <c r="AN49" t="n">
         <v>21</v>
-      </c>
-      <c r="AN49" t="n">
-        <v>3</v>
       </c>
       <c r="AO49" t="inlineStr"/>
       <c r="AP49" t="inlineStr"/>
       <c r="AQ49" t="n">
-        <v>1.38</v>
+        <v>0.26</v>
       </c>
       <c r="AR49" t="inlineStr"/>
       <c r="AS49" t="n">
-        <v>-0.86</v>
+        <v>-2.32</v>
       </c>
       <c r="AT49" t="inlineStr"/>
     </row>
@@ -8309,7 +8319,7 @@
         <v>35.1</v>
       </c>
       <c r="H58" t="n">
-        <v>26.2</v>
+        <v>30.1</v>
       </c>
       <c r="I58" t="n">
         <v>-7.78</v>
@@ -8324,7 +8334,7 @@
         <v>-3.2</v>
       </c>
       <c r="M58" t="n">
-        <v>18.7</v>
+        <v>21.3</v>
       </c>
       <c r="N58" t="inlineStr">
         <is>
@@ -8332,10 +8342,10 @@
         </is>
       </c>
       <c r="O58" t="n">
-        <v>-34</v>
+        <v>-33.9</v>
       </c>
       <c r="P58" t="n">
-        <v>196.88</v>
+        <v>196.83</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -8366,7 +8376,7 @@
         <v>46296</v>
       </c>
       <c r="Y58" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z58" t="inlineStr">
         <is>
@@ -8395,34 +8405,34 @@
         <v>190.53</v>
       </c>
       <c r="AH58" t="n">
-        <v>224.92</v>
+        <v>229.68</v>
       </c>
       <c r="AI58" t="n">
-        <v>224.92</v>
+        <v>229.68</v>
       </c>
       <c r="AJ58" t="n">
-        <v>18.05</v>
+        <v>20.55</v>
       </c>
       <c r="AK58" t="n">
         <v>-10.39</v>
       </c>
       <c r="AL58" t="n">
-        <v>19.59</v>
+        <v>21.43</v>
       </c>
       <c r="AM58" t="n">
+        <v>24</v>
+      </c>
+      <c r="AN58" t="n">
         <v>23</v>
-      </c>
-      <c r="AN58" t="n">
-        <v>22</v>
       </c>
       <c r="AO58" t="inlineStr"/>
       <c r="AP58" t="inlineStr"/>
       <c r="AQ58" t="n">
-        <v>1.79</v>
+        <v>0.66</v>
       </c>
       <c r="AR58" t="inlineStr"/>
       <c r="AS58" t="n">
-        <v>16.26</v>
+        <v>19.89</v>
       </c>
       <c r="AT58" t="inlineStr"/>
     </row>
@@ -9021,7 +9031,7 @@
         <v>15.1</v>
       </c>
       <c r="H63" t="n">
-        <v>-32.1</v>
+        <v>-33.6</v>
       </c>
       <c r="I63" t="n">
         <v>-21.29</v>
@@ -9036,7 +9046,7 @@
         <v>16.3</v>
       </c>
       <c r="M63" t="n">
-        <v>-18.9</v>
+        <v>-22.5</v>
       </c>
       <c r="N63" t="inlineStr"/>
       <c r="O63" t="n">
@@ -9093,22 +9103,22 @@
         <v>83.75</v>
       </c>
       <c r="AH63" t="n">
-        <v>58.5</v>
+        <v>55.9</v>
       </c>
       <c r="AI63" t="n">
-        <v>58.5</v>
+        <v>55.9</v>
       </c>
       <c r="AJ63" t="n">
-        <v>-30.15</v>
+        <v>-33.25</v>
       </c>
       <c r="AK63" t="n">
-        <v>-31.77</v>
+        <v>-33.34</v>
       </c>
       <c r="AL63" t="n">
         <v>2.66</v>
       </c>
       <c r="AM63" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AN63" t="n">
         <v>0</v>
@@ -9116,11 +9126,11 @@
       <c r="AO63" t="inlineStr"/>
       <c r="AP63" t="inlineStr"/>
       <c r="AQ63" t="n">
-        <v>1.18</v>
+        <v>0.06</v>
       </c>
       <c r="AR63" t="inlineStr"/>
       <c r="AS63" t="n">
-        <v>-31.32</v>
+        <v>-33.31</v>
       </c>
       <c r="AT63" t="inlineStr">
         <is>
@@ -9159,7 +9169,7 @@
         <v>11.1</v>
       </c>
       <c r="H64" t="n">
-        <v>-17</v>
+        <v>-16.6</v>
       </c>
       <c r="I64" t="n">
         <v>-8.85</v>
@@ -9174,7 +9184,7 @@
         <v>1.4</v>
       </c>
       <c r="M64" t="n">
-        <v>-8.800000000000001</v>
+        <v>-10.1</v>
       </c>
       <c r="N64" t="inlineStr"/>
       <c r="O64" t="n">
@@ -9231,13 +9241,13 @@
         <v>131.78</v>
       </c>
       <c r="AH64" t="n">
-        <v>114.03</v>
+        <v>112.27</v>
       </c>
       <c r="AI64" t="n">
-        <v>114.03</v>
+        <v>112.27</v>
       </c>
       <c r="AJ64" t="n">
-        <v>-13.47</v>
+        <v>-14.8</v>
       </c>
       <c r="AK64" t="n">
         <v>-16.3</v>
@@ -9246,7 +9256,7 @@
         <v>0.74</v>
       </c>
       <c r="AM64" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AN64" t="n">
         <v>1</v>
@@ -9254,11 +9264,11 @@
       <c r="AO64" t="inlineStr"/>
       <c r="AP64" t="inlineStr"/>
       <c r="AQ64" t="n">
-        <v>2.07</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR64" t="inlineStr"/>
       <c r="AS64" t="n">
-        <v>-15.54</v>
+        <v>-15.74</v>
       </c>
       <c r="AT64" t="inlineStr">
         <is>
@@ -9297,7 +9307,7 @@
         <v>-19.9</v>
       </c>
       <c r="H65" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="I65" t="n">
         <v>7.04</v>
@@ -9312,7 +9322,7 @@
         <v>0.4</v>
       </c>
       <c r="M65" t="n">
-        <v>13.6</v>
+        <v>10.8</v>
       </c>
       <c r="N65" t="inlineStr"/>
       <c r="O65" t="n">
@@ -9350,7 +9360,7 @@
         <v>46276</v>
       </c>
       <c r="Y65" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Z65" t="inlineStr">
         <is>
@@ -9379,13 +9389,13 @@
         <v>66.86</v>
       </c>
       <c r="AH65" t="n">
-        <v>75.92</v>
+        <v>74.01000000000001</v>
       </c>
       <c r="AI65" t="n">
-        <v>75.92</v>
+        <v>74.01000000000001</v>
       </c>
       <c r="AJ65" t="n">
-        <v>13.55</v>
+        <v>10.69</v>
       </c>
       <c r="AK65" t="n">
         <v>-1.24</v>
@@ -9394,7 +9404,7 @@
         <v>21.85</v>
       </c>
       <c r="AM65" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AN65" t="n">
         <v>22</v>
@@ -9402,11 +9412,11 @@
       <c r="AO65" t="inlineStr"/>
       <c r="AP65" t="inlineStr"/>
       <c r="AQ65" t="n">
-        <v>2.07</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR65" t="inlineStr"/>
       <c r="AS65" t="n">
-        <v>11.48</v>
+        <v>9.76</v>
       </c>
       <c r="AT65" t="inlineStr"/>
     </row>
@@ -9441,7 +9451,7 @@
         <v>-9.1</v>
       </c>
       <c r="H66" t="n">
-        <v>-14.2</v>
+        <v>-13.1</v>
       </c>
       <c r="I66" t="n">
         <v>-5.75</v>
@@ -9456,7 +9466,7 @@
         <v>-30.4</v>
       </c>
       <c r="M66" t="n">
-        <v>-33</v>
+        <v>-34.5</v>
       </c>
       <c r="N66" t="inlineStr"/>
       <c r="O66" t="n">
@@ -9513,22 +9523,22 @@
         <v>15.93</v>
       </c>
       <c r="AH66" t="n">
-        <v>14.43</v>
+        <v>14.07</v>
       </c>
       <c r="AI66" t="n">
-        <v>14.43</v>
+        <v>14.07</v>
       </c>
       <c r="AJ66" t="n">
-        <v>-9.390000000000001</v>
+        <v>-11.65</v>
       </c>
       <c r="AK66" t="n">
-        <v>-11.84</v>
+        <v>-12.34</v>
       </c>
       <c r="AL66" t="n">
         <v>0.85</v>
       </c>
       <c r="AM66" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AN66" t="n">
         <v>0</v>
@@ -9536,11 +9546,11 @@
       <c r="AO66" t="inlineStr"/>
       <c r="AP66" t="inlineStr"/>
       <c r="AQ66" t="n">
-        <v>1.26</v>
+        <v>0.14</v>
       </c>
       <c r="AR66" t="inlineStr"/>
       <c r="AS66" t="n">
-        <v>-10.65</v>
+        <v>-11.79</v>
       </c>
       <c r="AT66" t="inlineStr"/>
     </row>
@@ -9719,10 +9729,10 @@
         <v>-9.6</v>
       </c>
       <c r="H68" t="n">
-        <v>-4.6</v>
+        <v>-4.3</v>
       </c>
       <c r="I68" t="n">
-        <v>5.48</v>
+        <v>5.19</v>
       </c>
       <c r="J68" t="n">
         <v>7.06</v>
@@ -9731,17 +9741,17 @@
         <v>-1.07</v>
       </c>
       <c r="L68" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="M68" t="n">
-        <v>-0.8</v>
+        <v>-0.7</v>
       </c>
       <c r="N68" t="inlineStr"/>
       <c r="O68" t="n">
         <v>3.7</v>
       </c>
       <c r="P68" t="n">
-        <v>74.01000000000001</v>
+        <v>73.97</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
@@ -9757,7 +9767,7 @@
         <v>46213</v>
       </c>
       <c r="T68" t="n">
-        <v>-1.81</v>
+        <v>-1.53</v>
       </c>
       <c r="U68" t="n">
         <v>42</v>
@@ -9861,7 +9871,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="H69" t="n">
-        <v>-22.3</v>
+        <v>-22.1</v>
       </c>
       <c r="I69" t="n">
         <v>-10.83</v>
@@ -9876,7 +9886,7 @@
         <v>4.1</v>
       </c>
       <c r="M69" t="n">
-        <v>-12.5</v>
+        <v>-14.4</v>
       </c>
       <c r="N69" t="inlineStr"/>
       <c r="O69" t="n">
@@ -9933,13 +9943,13 @@
         <v>133.75</v>
       </c>
       <c r="AH69" t="n">
-        <v>109.2</v>
+        <v>106.61</v>
       </c>
       <c r="AI69" t="n">
-        <v>109.2</v>
+        <v>106.61</v>
       </c>
       <c r="AJ69" t="n">
-        <v>-18.36</v>
+        <v>-20.29</v>
       </c>
       <c r="AK69" t="n">
         <v>-21.17</v>
@@ -9948,7 +9958,7 @@
         <v>0.08</v>
       </c>
       <c r="AM69" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AN69" t="n">
         <v>0</v>
@@ -9956,11 +9966,11 @@
       <c r="AO69" t="inlineStr"/>
       <c r="AP69" t="inlineStr"/>
       <c r="AQ69" t="n">
-        <v>1.26</v>
+        <v>0.14</v>
       </c>
       <c r="AR69" t="inlineStr"/>
       <c r="AS69" t="n">
-        <v>-19.62</v>
+        <v>-20.43</v>
       </c>
       <c r="AT69" t="inlineStr">
         <is>
@@ -10315,7 +10325,7 @@
         <v>-38.2</v>
       </c>
       <c r="P72" t="n">
-        <v>167.32</v>
+        <v>167.31</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
@@ -10591,7 +10601,7 @@
         <v>1.3</v>
       </c>
       <c r="H74" t="n">
-        <v>-12.7</v>
+        <v>-7.6</v>
       </c>
       <c r="I74" t="n">
         <v>-6.82</v>
@@ -10606,7 +10616,7 @@
         <v>-29.7</v>
       </c>
       <c r="M74" t="n">
-        <v>-25.6</v>
+        <v>-24.9</v>
       </c>
       <c r="N74" t="inlineStr"/>
       <c r="O74" t="n">
@@ -10663,13 +10673,13 @@
         <v>46.92</v>
       </c>
       <c r="AH74" t="n">
-        <v>44.14</v>
+        <v>44.39</v>
       </c>
       <c r="AI74" t="n">
-        <v>44.14</v>
+        <v>44.39</v>
       </c>
       <c r="AJ74" t="n">
-        <v>-5.92</v>
+        <v>-5.39</v>
       </c>
       <c r="AK74" t="n">
         <v>-11.79</v>
@@ -10678,7 +10688,7 @@
         <v>2.43</v>
       </c>
       <c r="AM74" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AN74" t="n">
         <v>0</v>
@@ -10686,11 +10696,11 @@
       <c r="AO74" t="inlineStr"/>
       <c r="AP74" t="inlineStr"/>
       <c r="AQ74" t="n">
-        <v>0.22</v>
+        <v>-0.89</v>
       </c>
       <c r="AR74" t="inlineStr"/>
       <c r="AS74" t="n">
-        <v>-6.14</v>
+        <v>-4.5</v>
       </c>
       <c r="AT74" t="inlineStr"/>
     </row>
@@ -11011,7 +11021,7 @@
         <v>-26.6</v>
       </c>
       <c r="H77" t="n">
-        <v>-10.8</v>
+        <v>-15.1</v>
       </c>
       <c r="I77" t="n">
         <v>-5.89</v>
@@ -11026,7 +11036,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="M77" t="n">
-        <v>-1.7</v>
+        <v>-6.6</v>
       </c>
       <c r="N77" t="inlineStr"/>
       <c r="O77" t="n">
@@ -11064,7 +11074,7 @@
         <v>46273</v>
       </c>
       <c r="Y77" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Z77" t="inlineStr">
         <is>
@@ -11093,22 +11103,22 @@
         <v>443.5</v>
       </c>
       <c r="AH77" t="n">
-        <v>430.01</v>
+        <v>409.29</v>
       </c>
       <c r="AI77" t="n">
-        <v>430.01</v>
+        <v>409.29</v>
       </c>
       <c r="AJ77" t="n">
-        <v>-3.04</v>
+        <v>-7.71</v>
       </c>
       <c r="AK77" t="n">
-        <v>-7.21</v>
+        <v>-8.17</v>
       </c>
       <c r="AL77" t="n">
         <v>23.39</v>
       </c>
       <c r="AM77" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AN77" t="n">
         <v>21</v>
@@ -11116,11 +11126,11 @@
       <c r="AO77" t="inlineStr"/>
       <c r="AP77" t="inlineStr"/>
       <c r="AQ77" t="n">
-        <v>1.48</v>
+        <v>0.35</v>
       </c>
       <c r="AR77" t="inlineStr"/>
       <c r="AS77" t="n">
-        <v>-4.52</v>
+        <v>-8.07</v>
       </c>
       <c r="AT77" t="inlineStr"/>
     </row>
@@ -11581,7 +11591,7 @@
         <v>-17.1</v>
       </c>
       <c r="H81" t="n">
-        <v>-8.699999999999999</v>
+        <v>-10.4</v>
       </c>
       <c r="I81" t="n">
         <v>-7.68</v>
@@ -11596,7 +11606,7 @@
         <v>-20.5</v>
       </c>
       <c r="M81" t="n">
-        <v>-30.1</v>
+        <v>-32</v>
       </c>
       <c r="N81" t="inlineStr"/>
       <c r="O81" t="n">
@@ -11653,22 +11663,22 @@
         <v>97.91</v>
       </c>
       <c r="AH81" t="n">
-        <v>82.56</v>
+        <v>80.14</v>
       </c>
       <c r="AI81" t="n">
-        <v>82.56</v>
+        <v>80.14</v>
       </c>
       <c r="AJ81" t="n">
-        <v>-15.68</v>
+        <v>-18.15</v>
       </c>
       <c r="AK81" t="n">
-        <v>-18.29</v>
+        <v>-18.62</v>
       </c>
       <c r="AL81" t="n">
         <v>1.77</v>
       </c>
       <c r="AM81" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AN81" t="n">
         <v>4</v>
@@ -11676,11 +11686,11 @@
       <c r="AO81" t="inlineStr"/>
       <c r="AP81" t="inlineStr"/>
       <c r="AQ81" t="n">
-        <v>0.83</v>
+        <v>-0.28</v>
       </c>
       <c r="AR81" t="inlineStr"/>
       <c r="AS81" t="n">
-        <v>-16.51</v>
+        <v>-17.86</v>
       </c>
       <c r="AT81" t="inlineStr">
         <is>
@@ -12015,7 +12025,7 @@
         <v>5.8</v>
       </c>
       <c r="H84" t="n">
-        <v>19.6</v>
+        <v>12.2</v>
       </c>
       <c r="I84" t="n">
         <v>8.66</v>
@@ -12030,7 +12040,7 @@
         <v>-4.1</v>
       </c>
       <c r="M84" t="n">
-        <v>19.9</v>
+        <v>11.8</v>
       </c>
       <c r="N84" t="inlineStr">
         <is>
@@ -12072,7 +12082,7 @@
         <v>46262</v>
       </c>
       <c r="Y84" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="Z84" t="inlineStr">
         <is>
@@ -12101,13 +12111,13 @@
         <v>10.28</v>
       </c>
       <c r="AH84" t="n">
-        <v>12.16</v>
+        <v>11.32</v>
       </c>
       <c r="AI84" t="n">
-        <v>12.16</v>
+        <v>11.32</v>
       </c>
       <c r="AJ84" t="n">
-        <v>18.29</v>
+        <v>10.12</v>
       </c>
       <c r="AK84" t="n">
         <v>-2.14</v>
@@ -12116,7 +12126,7 @@
         <v>25.29</v>
       </c>
       <c r="AM84" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AN84" t="n">
         <v>30</v>
@@ -12124,11 +12134,11 @@
       <c r="AO84" t="inlineStr"/>
       <c r="AP84" t="inlineStr"/>
       <c r="AQ84" t="n">
-        <v>0.25</v>
+        <v>-0.86</v>
       </c>
       <c r="AR84" t="inlineStr"/>
       <c r="AS84" t="n">
-        <v>18.04</v>
+        <v>10.97</v>
       </c>
       <c r="AT84" t="inlineStr"/>
     </row>
@@ -12163,7 +12173,7 @@
         <v>-4.2</v>
       </c>
       <c r="H85" t="n">
-        <v>-2.4</v>
+        <v>-7.1</v>
       </c>
       <c r="I85" t="n">
         <v>-7.73</v>
@@ -12178,7 +12188,7 @@
         <v>1.4</v>
       </c>
       <c r="M85" t="n">
-        <v>-6.2</v>
+        <v>-10.4</v>
       </c>
       <c r="N85" t="inlineStr"/>
       <c r="O85" t="n">
@@ -12235,22 +12245,22 @@
         <v>372.92</v>
       </c>
       <c r="AH85" t="n">
-        <v>344.33</v>
+        <v>328.75</v>
       </c>
       <c r="AI85" t="n">
-        <v>344.33</v>
+        <v>328.75</v>
       </c>
       <c r="AJ85" t="n">
-        <v>-7.67</v>
+        <v>-11.84</v>
       </c>
       <c r="AK85" t="n">
-        <v>-10.27</v>
+        <v>-11.89</v>
       </c>
       <c r="AL85" t="n">
         <v>2.12</v>
       </c>
       <c r="AM85" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AN85" t="n">
         <v>26</v>
@@ -12258,11 +12268,11 @@
       <c r="AO85" t="inlineStr"/>
       <c r="AP85" t="inlineStr"/>
       <c r="AQ85" t="n">
-        <v>0.25</v>
+        <v>-0.86</v>
       </c>
       <c r="AR85" t="inlineStr"/>
       <c r="AS85" t="n">
-        <v>-7.92</v>
+        <v>-10.99</v>
       </c>
       <c r="AT85" t="inlineStr"/>
     </row>
@@ -14013,7 +14023,7 @@
         <v>44.3</v>
       </c>
       <c r="H98" t="n">
-        <v>26.2</v>
+        <v>30.1</v>
       </c>
       <c r="I98" t="n">
         <v>-3.81</v>
@@ -14025,10 +14035,10 @@
         <v>-5.71</v>
       </c>
       <c r="L98" t="n">
-        <v>-8.1</v>
+        <v>-8</v>
       </c>
       <c r="M98" t="n">
-        <v>18.7</v>
+        <v>21.3</v>
       </c>
       <c r="N98" t="inlineStr">
         <is>
@@ -14039,7 +14049,7 @@
         <v>-43.6</v>
       </c>
       <c r="P98" t="n">
-        <v>200.84</v>
+        <v>200.8</v>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
@@ -14070,7 +14080,7 @@
         <v>46279</v>
       </c>
       <c r="Y98" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Z98" t="inlineStr">
         <is>
@@ -14099,34 +14109,34 @@
         <v>184.64</v>
       </c>
       <c r="AH98" t="n">
-        <v>224.92</v>
+        <v>229.68</v>
       </c>
       <c r="AI98" t="n">
-        <v>224.92</v>
+        <v>229.68</v>
       </c>
       <c r="AJ98" t="n">
-        <v>21.82</v>
+        <v>24.39</v>
       </c>
       <c r="AK98" t="n">
         <v>-7.53</v>
       </c>
       <c r="AL98" t="n">
-        <v>23.41</v>
+        <v>25.3</v>
       </c>
       <c r="AM98" t="n">
+        <v>39</v>
+      </c>
+      <c r="AN98" t="n">
         <v>38</v>
-      </c>
-      <c r="AN98" t="n">
-        <v>37</v>
       </c>
       <c r="AO98" t="inlineStr"/>
       <c r="AP98" t="inlineStr"/>
       <c r="AQ98" t="n">
-        <v>1.17</v>
+        <v>0.05</v>
       </c>
       <c r="AR98" t="inlineStr"/>
       <c r="AS98" t="n">
-        <v>20.65</v>
+        <v>24.35</v>
       </c>
       <c r="AT98" t="inlineStr"/>
     </row>
@@ -14443,7 +14453,7 @@
         <v>37.7</v>
       </c>
       <c r="H101" t="n">
-        <v>-5.2</v>
+        <v>-7.5</v>
       </c>
       <c r="I101" t="n">
         <v>-6.45</v>
@@ -14458,7 +14468,7 @@
         <v>1.8</v>
       </c>
       <c r="M101" t="n">
-        <v>-1.2</v>
+        <v>-3.5</v>
       </c>
       <c r="N101" t="inlineStr"/>
       <c r="O101" t="n">
@@ -14496,7 +14506,7 @@
         <v>46261</v>
       </c>
       <c r="Y101" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Z101" t="inlineStr">
         <is>
@@ -14523,13 +14533,13 @@
         <v>275</v>
       </c>
       <c r="AH101" t="n">
-        <v>251.67</v>
+        <v>245.2</v>
       </c>
       <c r="AI101" t="n">
-        <v>251.67</v>
+        <v>245.2</v>
       </c>
       <c r="AJ101" t="n">
-        <v>-8.48</v>
+        <v>-10.84</v>
       </c>
       <c r="AK101" t="n">
         <v>-18.3</v>
@@ -14538,7 +14548,7 @@
         <v>7.1</v>
       </c>
       <c r="AM101" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AN101" t="n">
         <v>6</v>
@@ -14546,11 +14556,11 @@
       <c r="AO101" t="inlineStr"/>
       <c r="AP101" t="inlineStr"/>
       <c r="AQ101" t="n">
-        <v>1.17</v>
+        <v>0.05</v>
       </c>
       <c r="AR101" t="inlineStr"/>
       <c r="AS101" t="n">
-        <v>-9.65</v>
+        <v>-10.88</v>
       </c>
       <c r="AT101" t="inlineStr">
         <is>
@@ -15321,7 +15331,7 @@
         <v>-7.1</v>
       </c>
       <c r="H107" t="n">
-        <v>-12.5</v>
+        <v>-17.8</v>
       </c>
       <c r="I107" t="n">
         <v>2.22</v>
@@ -15336,7 +15346,7 @@
         <v>4.9</v>
       </c>
       <c r="M107" t="n">
-        <v>-13.2</v>
+        <v>-14.6</v>
       </c>
       <c r="N107" t="inlineStr"/>
       <c r="O107" t="n">
@@ -15374,7 +15384,7 @@
         <v>46258</v>
       </c>
       <c r="Y107" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="Z107" t="inlineStr">
         <is>
@@ -15403,22 +15413,22 @@
         <v>50.78</v>
       </c>
       <c r="AH107" t="n">
-        <v>42.34</v>
+        <v>41.62</v>
       </c>
       <c r="AI107" t="n">
-        <v>42.34</v>
+        <v>41.62</v>
       </c>
       <c r="AJ107" t="n">
-        <v>-16.62</v>
+        <v>-18.04</v>
       </c>
       <c r="AK107" t="n">
-        <v>-18.59</v>
+        <v>-19.22</v>
       </c>
       <c r="AL107" t="n">
         <v>11.12</v>
       </c>
       <c r="AM107" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AN107" t="n">
         <v>20</v>
@@ -15426,11 +15436,11 @@
       <c r="AO107" t="inlineStr"/>
       <c r="AP107" t="inlineStr"/>
       <c r="AQ107" t="n">
-        <v>1.01</v>
+        <v>-0.11</v>
       </c>
       <c r="AR107" t="inlineStr"/>
       <c r="AS107" t="n">
-        <v>-17.63</v>
+        <v>-17.93</v>
       </c>
       <c r="AT107" t="inlineStr">
         <is>
@@ -16041,7 +16051,7 @@
         <v>-9.1</v>
       </c>
       <c r="H112" t="n">
-        <v>-15.7</v>
+        <v>-17.8</v>
       </c>
       <c r="I112" t="n">
         <v>-5.07</v>
@@ -16056,7 +16066,7 @@
         <v>3.7</v>
       </c>
       <c r="M112" t="n">
-        <v>-17.8</v>
+        <v>-21.8</v>
       </c>
       <c r="N112" t="inlineStr"/>
       <c r="O112" t="n">
@@ -16094,7 +16104,7 @@
         <v>46287</v>
       </c>
       <c r="Y112" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Z112" t="inlineStr">
         <is>
@@ -16123,13 +16133,13 @@
         <v>112.19</v>
       </c>
       <c r="AH112" t="n">
-        <v>92.31999999999999</v>
+        <v>87.81</v>
       </c>
       <c r="AI112" t="n">
-        <v>92.31999999999999</v>
+        <v>87.81</v>
       </c>
       <c r="AJ112" t="n">
-        <v>-17.71</v>
+        <v>-21.73</v>
       </c>
       <c r="AK112" t="n">
         <v>-23.2</v>
@@ -16138,7 +16148,7 @@
         <v>14.5</v>
       </c>
       <c r="AM112" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AN112" t="n">
         <v>25</v>
@@ -16146,11 +16156,11 @@
       <c r="AO112" t="inlineStr"/>
       <c r="AP112" t="inlineStr"/>
       <c r="AQ112" t="n">
-        <v>1.01</v>
+        <v>-0.11</v>
       </c>
       <c r="AR112" t="inlineStr"/>
       <c r="AS112" t="n">
-        <v>-18.72</v>
+        <v>-21.62</v>
       </c>
       <c r="AT112" t="inlineStr">
         <is>
@@ -16189,7 +16199,7 @@
         <v>-31.8</v>
       </c>
       <c r="H113" t="n">
-        <v>-15.8</v>
+        <v>-14.2</v>
       </c>
       <c r="I113" t="n">
         <v>-7.89</v>
@@ -16204,7 +16214,7 @@
         <v>-12.7</v>
       </c>
       <c r="M113" t="n">
-        <v>-24.5</v>
+        <v>-24.3</v>
       </c>
       <c r="N113" t="inlineStr"/>
       <c r="O113" t="n">
@@ -16261,13 +16271,13 @@
         <v>50.2</v>
       </c>
       <c r="AH113" t="n">
-        <v>41.1</v>
+        <v>41.16</v>
       </c>
       <c r="AI113" t="n">
-        <v>41.1</v>
+        <v>41.16</v>
       </c>
       <c r="AJ113" t="n">
-        <v>-18.13</v>
+        <v>-18.01</v>
       </c>
       <c r="AK113" t="n">
         <v>-27.27</v>
@@ -16276,7 +16286,7 @@
         <v>4.72</v>
       </c>
       <c r="AM113" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AN113" t="n">
         <v>3</v>
@@ -16284,11 +16294,11 @@
       <c r="AO113" t="inlineStr"/>
       <c r="AP113" t="inlineStr"/>
       <c r="AQ113" t="n">
-        <v>1.01</v>
+        <v>-0.11</v>
       </c>
       <c r="AR113" t="inlineStr"/>
       <c r="AS113" t="n">
-        <v>-19.14</v>
+        <v>-17.9</v>
       </c>
       <c r="AT113" t="inlineStr">
         <is>
@@ -16747,7 +16757,7 @@
         <v>-11.7</v>
       </c>
       <c r="H117" t="n">
-        <v>-6.2</v>
+        <v>-6.7</v>
       </c>
       <c r="I117" t="n">
         <v>2.64</v>
@@ -16759,7 +16769,7 @@
         <v>-5.11</v>
       </c>
       <c r="L117" t="n">
-        <v>-25.2</v>
+        <v>-25.1</v>
       </c>
       <c r="M117" t="n">
         <v>-23.7</v>
@@ -16769,7 +16779,7 @@
         <v>-31.5</v>
       </c>
       <c r="P117" t="n">
-        <v>86.54000000000001</v>
+        <v>86.53</v>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
@@ -16800,7 +16810,7 @@
         <v>46262</v>
       </c>
       <c r="Y117" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="Z117" t="inlineStr">
         <is>
@@ -16827,13 +16837,13 @@
         <v>64.77</v>
       </c>
       <c r="AH117" t="n">
-        <v>59.09</v>
+        <v>58.94</v>
       </c>
       <c r="AI117" t="n">
-        <v>59.09</v>
+        <v>58.94</v>
       </c>
       <c r="AJ117" t="n">
-        <v>-8.77</v>
+        <v>-9</v>
       </c>
       <c r="AK117" t="n">
         <v>-13.39</v>
@@ -16842,7 +16852,7 @@
         <v>8.279999999999999</v>
       </c>
       <c r="AM117" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AN117" t="n">
         <v>6</v>
@@ -16850,11 +16860,11 @@
       <c r="AO117" t="inlineStr"/>
       <c r="AP117" t="inlineStr"/>
       <c r="AQ117" t="n">
-        <v>1.01</v>
+        <v>-0.11</v>
       </c>
       <c r="AR117" t="inlineStr"/>
       <c r="AS117" t="n">
-        <v>-9.779999999999999</v>
+        <v>-8.890000000000001</v>
       </c>
       <c r="AT117" t="inlineStr">
         <is>
@@ -21073,7 +21083,7 @@
         <v>-10</v>
       </c>
       <c r="H147" t="n">
-        <v>19.6</v>
+        <v>12.2</v>
       </c>
       <c r="I147" t="n">
         <v>3.54</v>
@@ -21088,7 +21098,7 @@
         <v>-11.4</v>
       </c>
       <c r="M147" t="n">
-        <v>19.9</v>
+        <v>11.8</v>
       </c>
       <c r="N147" t="inlineStr"/>
       <c r="O147" t="n">
@@ -21126,7 +21136,7 @@
         <v>46245</v>
       </c>
       <c r="Y147" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Z147" t="inlineStr">
         <is>
@@ -21155,13 +21165,13 @@
         <v>10.03</v>
       </c>
       <c r="AH147" t="n">
-        <v>12.16</v>
+        <v>11.32</v>
       </c>
       <c r="AI147" t="n">
-        <v>12.16</v>
+        <v>11.32</v>
       </c>
       <c r="AJ147" t="n">
-        <v>21.3</v>
+        <v>12.92</v>
       </c>
       <c r="AK147" t="n">
         <v>-5.44</v>
@@ -21170,7 +21180,7 @@
         <v>28.48</v>
       </c>
       <c r="AM147" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AN147" t="n">
         <v>47</v>
@@ -21178,11 +21188,11 @@
       <c r="AO147" t="inlineStr"/>
       <c r="AP147" t="inlineStr"/>
       <c r="AQ147" t="n">
-        <v>-0.28</v>
+        <v>-1.38</v>
       </c>
       <c r="AR147" t="inlineStr"/>
       <c r="AS147" t="n">
-        <v>21.57</v>
+        <v>14.3</v>
       </c>
       <c r="AT147" t="inlineStr"/>
     </row>
@@ -21795,7 +21805,7 @@
         <v>9.4</v>
       </c>
       <c r="H152" t="n">
-        <v>-9</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="I152" t="n">
         <v>-8.5</v>
@@ -21810,7 +21820,7 @@
         <v>14.7</v>
       </c>
       <c r="M152" t="n">
-        <v>-10.4</v>
+        <v>-13.2</v>
       </c>
       <c r="N152" t="inlineStr"/>
       <c r="O152" t="n">
@@ -21848,7 +21858,7 @@
         <v>46238</v>
       </c>
       <c r="Y152" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Z152" t="inlineStr">
         <is>
@@ -21875,13 +21885,13 @@
         <v>15.77</v>
       </c>
       <c r="AH152" t="n">
-        <v>12.28</v>
+        <v>11.88</v>
       </c>
       <c r="AI152" t="n">
-        <v>12.28</v>
+        <v>11.88</v>
       </c>
       <c r="AJ152" t="n">
-        <v>-22.13</v>
+        <v>-24.67</v>
       </c>
       <c r="AK152" t="n">
         <v>-26.13</v>
@@ -21890,7 +21900,7 @@
         <v>8.5</v>
       </c>
       <c r="AM152" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="AN152" t="n">
         <v>2</v>
@@ -21898,11 +21908,11 @@
       <c r="AO152" t="inlineStr"/>
       <c r="AP152" t="inlineStr"/>
       <c r="AQ152" t="n">
-        <v>3.24</v>
+        <v>2.1</v>
       </c>
       <c r="AR152" t="inlineStr"/>
       <c r="AS152" t="n">
-        <v>-25.37</v>
+        <v>-26.76</v>
       </c>
       <c r="AT152" t="inlineStr">
         <is>
@@ -23089,7 +23099,7 @@
         <v>-7.4</v>
       </c>
       <c r="H161" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="I161" t="n">
         <v>10.43</v>
@@ -23104,7 +23114,7 @@
         <v>7.3</v>
       </c>
       <c r="M161" t="n">
-        <v>13.6</v>
+        <v>10.8</v>
       </c>
       <c r="N161" t="inlineStr"/>
       <c r="O161" t="n">
@@ -23142,7 +23152,7 @@
         <v>46237</v>
       </c>
       <c r="Y161" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Z161" t="inlineStr">
         <is>
@@ -23171,13 +23181,13 @@
         <v>70.92</v>
       </c>
       <c r="AH161" t="n">
-        <v>75.92</v>
+        <v>74.01000000000001</v>
       </c>
       <c r="AI161" t="n">
-        <v>75.92</v>
+        <v>74.01000000000001</v>
       </c>
       <c r="AJ161" t="n">
-        <v>7.05</v>
+        <v>4.36</v>
       </c>
       <c r="AK161" t="n">
         <v>-6.9</v>
@@ -23186,7 +23196,7 @@
         <v>27.52</v>
       </c>
       <c r="AM161" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AN161" t="n">
         <v>21</v>
@@ -23194,11 +23204,11 @@
       <c r="AO161" t="inlineStr"/>
       <c r="AP161" t="inlineStr"/>
       <c r="AQ161" t="n">
-        <v>5.12</v>
+        <v>3.95</v>
       </c>
       <c r="AR161" t="inlineStr"/>
       <c r="AS161" t="n">
-        <v>1.93</v>
+        <v>0.4</v>
       </c>
       <c r="AT161" t="inlineStr"/>
     </row>
@@ -23789,7 +23799,7 @@
         <v>25.1</v>
       </c>
       <c r="H166" t="n">
-        <v>-0.8</v>
+        <v>-1.8</v>
       </c>
       <c r="I166" t="n">
         <v>10.45</v>
@@ -23804,7 +23814,7 @@
         <v>25</v>
       </c>
       <c r="M166" t="n">
-        <v>22.3</v>
+        <v>19.9</v>
       </c>
       <c r="N166" t="inlineStr"/>
       <c r="O166" t="n">
@@ -23842,7 +23852,7 @@
         <v>46233</v>
       </c>
       <c r="Y166" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="Z166" t="inlineStr">
         <is>
@@ -23871,13 +23881,13 @@
         <v>24.39</v>
       </c>
       <c r="AH166" t="n">
-        <v>25.76</v>
+        <v>25.28</v>
       </c>
       <c r="AI166" t="n">
-        <v>25.76</v>
+        <v>25.28</v>
       </c>
       <c r="AJ166" t="n">
-        <v>5.61</v>
+        <v>3.65</v>
       </c>
       <c r="AK166" t="n">
         <v>-7.51</v>
@@ -23886,7 +23896,7 @@
         <v>22.95</v>
       </c>
       <c r="AM166" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AN166" t="n">
         <v>1</v>
@@ -23894,11 +23904,11 @@
       <c r="AO166" t="inlineStr"/>
       <c r="AP166" t="inlineStr"/>
       <c r="AQ166" t="n">
-        <v>4.56</v>
+        <v>3.4</v>
       </c>
       <c r="AR166" t="inlineStr"/>
       <c r="AS166" t="n">
-        <v>1.06</v>
+        <v>0.24</v>
       </c>
       <c r="AT166" t="inlineStr"/>
     </row>
@@ -24517,7 +24527,7 @@
         <v>-11.5</v>
       </c>
       <c r="H171" t="n">
-        <v>-1.1</v>
+        <v>3.5</v>
       </c>
       <c r="I171" t="n">
         <v>-18.43</v>
@@ -24532,7 +24542,7 @@
         <v>-24.2</v>
       </c>
       <c r="M171" t="n">
-        <v>-20.7</v>
+        <v>-21.2</v>
       </c>
       <c r="N171" t="inlineStr"/>
       <c r="O171" t="n">
@@ -24570,7 +24580,7 @@
         <v>46230</v>
       </c>
       <c r="Y171" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Z171" t="inlineStr">
         <is>
@@ -24597,13 +24607,13 @@
         <v>268.74</v>
       </c>
       <c r="AH171" t="n">
-        <v>234.03</v>
+        <v>231.83</v>
       </c>
       <c r="AI171" t="n">
-        <v>234.03</v>
+        <v>231.83</v>
       </c>
       <c r="AJ171" t="n">
-        <v>-12.92</v>
+        <v>-13.73</v>
       </c>
       <c r="AK171" t="n">
         <v>-26.39</v>
@@ -24612,7 +24622,7 @@
         <v>8.130000000000001</v>
       </c>
       <c r="AM171" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AN171" t="n">
         <v>3</v>
@@ -24620,11 +24630,11 @@
       <c r="AO171" t="inlineStr"/>
       <c r="AP171" t="inlineStr"/>
       <c r="AQ171" t="n">
-        <v>4.77</v>
+        <v>3.61</v>
       </c>
       <c r="AR171" t="inlineStr"/>
       <c r="AS171" t="n">
-        <v>-17.68</v>
+        <v>-17.34</v>
       </c>
       <c r="AT171" t="inlineStr">
         <is>
@@ -25723,7 +25733,7 @@
         <v>45.4</v>
       </c>
       <c r="P179" t="n">
-        <v>130.31</v>
+        <v>130.3</v>
       </c>
       <c r="Q179" t="inlineStr">
         <is>
@@ -27041,7 +27051,7 @@
         <v>24.3</v>
       </c>
       <c r="H188" t="n">
-        <v>-10.8</v>
+        <v>-15.1</v>
       </c>
       <c r="I188" t="n">
         <v>-5.03</v>
@@ -27056,7 +27066,7 @@
         <v>51.8</v>
       </c>
       <c r="M188" t="n">
-        <v>-1.7</v>
+        <v>-6.6</v>
       </c>
       <c r="N188" t="inlineStr"/>
       <c r="O188" t="n">
@@ -27090,7 +27100,7 @@
         <v>46226</v>
       </c>
       <c r="Y188" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="Z188" t="inlineStr">
         <is>
@@ -27117,22 +27127,22 @@
         <v>545.05</v>
       </c>
       <c r="AH188" t="n">
-        <v>430.01</v>
+        <v>409.29</v>
       </c>
       <c r="AI188" t="n">
-        <v>430.01</v>
+        <v>409.29</v>
       </c>
       <c r="AJ188" t="n">
-        <v>-21.11</v>
+        <v>-24.91</v>
       </c>
       <c r="AK188" t="n">
-        <v>-24.5</v>
+        <v>-25.28</v>
       </c>
       <c r="AL188" t="n">
         <v>5.66</v>
       </c>
       <c r="AM188" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AN188" t="n">
         <v>3</v>
@@ -27142,13 +27152,13 @@
       </c>
       <c r="AP188" t="inlineStr"/>
       <c r="AQ188" t="n">
-        <v>3.57</v>
+        <v>2.42</v>
       </c>
       <c r="AR188" t="n">
         <v>4.4</v>
       </c>
       <c r="AS188" t="n">
-        <v>-24.67</v>
+        <v>-27.33</v>
       </c>
       <c r="AT188" t="inlineStr">
         <is>
@@ -29401,7 +29411,7 @@
         <v>13.9</v>
       </c>
       <c r="H204" t="n">
-        <v>23</v>
+        <v>15.1</v>
       </c>
       <c r="I204" t="n">
         <v>-6.26</v>
@@ -29416,7 +29426,7 @@
         <v>73.3</v>
       </c>
       <c r="M204" t="n">
-        <v>43.2</v>
+        <v>34.1</v>
       </c>
       <c r="N204" t="inlineStr"/>
       <c r="O204" t="n">
@@ -29450,7 +29460,7 @@
         <v>46224</v>
       </c>
       <c r="Y204" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Z204" t="inlineStr">
         <is>
@@ -29479,13 +29489,13 @@
         <v>517</v>
       </c>
       <c r="AH204" t="n">
-        <v>562.23</v>
+        <v>528.75</v>
       </c>
       <c r="AI204" t="n">
-        <v>562.23</v>
+        <v>528.75</v>
       </c>
       <c r="AJ204" t="n">
-        <v>8.75</v>
+        <v>2.27</v>
       </c>
       <c r="AK204" t="n">
         <v>-17.98</v>
@@ -29494,7 +29504,7 @@
         <v>27.37</v>
       </c>
       <c r="AM204" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AN204" t="n">
         <v>55</v>
@@ -29504,13 +29514,13 @@
       </c>
       <c r="AP204" t="inlineStr"/>
       <c r="AQ204" t="n">
-        <v>3.57</v>
+        <v>2.42</v>
       </c>
       <c r="AR204" t="n">
         <v>4.4</v>
       </c>
       <c r="AS204" t="n">
-        <v>5.18</v>
+        <v>-0.15</v>
       </c>
       <c r="AT204" t="inlineStr">
         <is>
@@ -31203,7 +31213,7 @@
         <v>-35.9</v>
       </c>
       <c r="P216" t="n">
-        <v>188.74</v>
+        <v>188.73</v>
       </c>
       <c r="Q216" t="inlineStr">
         <is>
@@ -31923,7 +31933,7 @@
         <v>3.7</v>
       </c>
       <c r="H221" t="n">
-        <v>-12.5</v>
+        <v>-17.8</v>
       </c>
       <c r="I221" t="n">
         <v>4.03</v>
@@ -31938,7 +31948,7 @@
         <v>-1.1</v>
       </c>
       <c r="M221" t="n">
-        <v>-13.2</v>
+        <v>-14.6</v>
       </c>
       <c r="N221" t="inlineStr"/>
       <c r="O221" t="n">
@@ -31972,7 +31982,7 @@
         <v>46231</v>
       </c>
       <c r="Y221" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="Z221" t="inlineStr">
         <is>
@@ -32001,22 +32011,22 @@
         <v>50.22</v>
       </c>
       <c r="AH221" t="n">
-        <v>42.34</v>
+        <v>41.62</v>
       </c>
       <c r="AI221" t="n">
-        <v>42.34</v>
+        <v>41.62</v>
       </c>
       <c r="AJ221" t="n">
-        <v>-15.69</v>
+        <v>-17.12</v>
       </c>
       <c r="AK221" t="n">
-        <v>-17.68</v>
+        <v>-18.32</v>
       </c>
       <c r="AL221" t="n">
         <v>12.36</v>
       </c>
       <c r="AM221" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AN221" t="n">
         <v>43</v>
@@ -32026,13 +32036,13 @@
       </c>
       <c r="AP221" t="inlineStr"/>
       <c r="AQ221" t="n">
-        <v>3.57</v>
+        <v>2.42</v>
       </c>
       <c r="AR221" t="n">
         <v>4.4</v>
       </c>
       <c r="AS221" t="n">
-        <v>-19.26</v>
+        <v>-19.55</v>
       </c>
       <c r="AT221" t="inlineStr">
         <is>
@@ -32805,7 +32815,7 @@
         <v>24.8</v>
       </c>
       <c r="H227" t="n">
-        <v>7.4</v>
+        <v>6</v>
       </c>
       <c r="I227" t="n">
         <v>0.72</v>
@@ -32820,7 +32830,7 @@
         <v>1.1</v>
       </c>
       <c r="M227" t="n">
-        <v>4.8</v>
+        <v>3.2</v>
       </c>
       <c r="N227" t="inlineStr"/>
       <c r="O227" t="n">
@@ -32881,13 +32891,13 @@
         <v>20.61</v>
       </c>
       <c r="AH227" t="n">
-        <v>20.44</v>
+        <v>20.14</v>
       </c>
       <c r="AI227" t="n">
-        <v>20.44</v>
+        <v>20.14</v>
       </c>
       <c r="AJ227" t="n">
-        <v>-0.82</v>
+        <v>-2.27</v>
       </c>
       <c r="AK227" t="n">
         <v>-23.57</v>
@@ -32896,7 +32906,7 @@
         <v>3.55</v>
       </c>
       <c r="AM227" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AN227" t="n">
         <v>12</v>
@@ -32906,13 +32916,13 @@
       </c>
       <c r="AP227" t="inlineStr"/>
       <c r="AQ227" t="n">
-        <v>3.57</v>
+        <v>2.42</v>
       </c>
       <c r="AR227" t="n">
         <v>4.4</v>
       </c>
       <c r="AS227" t="n">
-        <v>-4.38</v>
+        <v>-4.69</v>
       </c>
       <c r="AT227" t="inlineStr">
         <is>
@@ -34701,7 +34711,7 @@
         <v>-40.6</v>
       </c>
       <c r="H240" t="n">
-        <v>-30.6</v>
+        <v>-35.1</v>
       </c>
       <c r="I240" t="n">
         <v>9.31</v>
@@ -34716,7 +34726,7 @@
         <v>-30.2</v>
       </c>
       <c r="M240" t="n">
-        <v>-44.5</v>
+        <v>-49.2</v>
       </c>
       <c r="N240" t="inlineStr"/>
       <c r="O240" t="n">
@@ -34754,7 +34764,7 @@
         <v>46224</v>
       </c>
       <c r="Y240" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Z240" t="inlineStr">
         <is>
@@ -34783,13 +34793,13 @@
         <v>58.11</v>
       </c>
       <c r="AH240" t="n">
-        <v>44.46</v>
+        <v>40.66</v>
       </c>
       <c r="AI240" t="n">
-        <v>44.46</v>
+        <v>40.66</v>
       </c>
       <c r="AJ240" t="n">
-        <v>-23.49</v>
+        <v>-30.03</v>
       </c>
       <c r="AK240" t="n">
         <v>-31.39</v>
@@ -34798,7 +34808,7 @@
         <v>29.2</v>
       </c>
       <c r="AM240" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AN240" t="n">
         <v>17</v>
@@ -34808,13 +34818,13 @@
       </c>
       <c r="AP240" t="inlineStr"/>
       <c r="AQ240" t="n">
-        <v>3.57</v>
+        <v>2.42</v>
       </c>
       <c r="AR240" t="n">
         <v>4.4</v>
       </c>
       <c r="AS240" t="n">
-        <v>-27.06</v>
+        <v>-32.45</v>
       </c>
       <c r="AT240" t="inlineStr">
         <is>
@@ -35283,7 +35293,7 @@
         <v>-37.4</v>
       </c>
       <c r="H244" t="n">
-        <v>-19.1</v>
+        <v>-15.6</v>
       </c>
       <c r="I244" t="n">
         <v>1.06</v>
@@ -35298,7 +35308,7 @@
         <v>-20.1</v>
       </c>
       <c r="M244" t="n">
-        <v>-29.6</v>
+        <v>-27.7</v>
       </c>
       <c r="N244" t="inlineStr"/>
       <c r="O244" t="n">
@@ -35334,7 +35344,7 @@
         <v>46225</v>
       </c>
       <c r="Y244" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Z244" t="inlineStr">
         <is>
@@ -35363,13 +35373,13 @@
         <v>44.28</v>
       </c>
       <c r="AH244" t="n">
-        <v>40.42</v>
+        <v>41.45</v>
       </c>
       <c r="AI244" t="n">
-        <v>40.42</v>
+        <v>41.45</v>
       </c>
       <c r="AJ244" t="n">
-        <v>-8.73</v>
+        <v>-6.4</v>
       </c>
       <c r="AK244" t="n">
         <v>-12.27</v>
@@ -35378,7 +35388,7 @@
         <v>24.31</v>
       </c>
       <c r="AM244" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AN244" t="n">
         <v>17</v>
@@ -35388,13 +35398,13 @@
       </c>
       <c r="AP244" t="inlineStr"/>
       <c r="AQ244" t="n">
-        <v>3.57</v>
+        <v>2.42</v>
       </c>
       <c r="AR244" t="n">
         <v>4.4</v>
       </c>
       <c r="AS244" t="n">
-        <v>-12.29</v>
+        <v>-8.82</v>
       </c>
       <c r="AT244" t="inlineStr"/>
     </row>
@@ -36649,7 +36659,7 @@
         <v>13.8</v>
       </c>
       <c r="P253" t="n">
-        <v>117.55</v>
+        <v>117.54</v>
       </c>
       <c r="Q253" t="inlineStr">
         <is>
@@ -37357,7 +37367,7 @@
         <v>19.4</v>
       </c>
       <c r="H258" t="n">
-        <v>-9</v>
+        <v>-10.1</v>
       </c>
       <c r="I258" t="n">
         <v>9.869999999999999</v>
@@ -37372,7 +37382,7 @@
         <v>-0.4</v>
       </c>
       <c r="M258" t="n">
-        <v>-18.6</v>
+        <v>-21.5</v>
       </c>
       <c r="N258" t="inlineStr"/>
       <c r="O258" t="n">
@@ -37410,7 +37420,7 @@
         <v>46230</v>
       </c>
       <c r="Y258" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Z258" t="inlineStr">
         <is>
@@ -37439,22 +37449,22 @@
         <v>45.7</v>
       </c>
       <c r="AH258" t="n">
-        <v>36.5</v>
+        <v>35.13</v>
       </c>
       <c r="AI258" t="n">
-        <v>36.5</v>
+        <v>35.13</v>
       </c>
       <c r="AJ258" t="n">
-        <v>-20.13</v>
+        <v>-23.13</v>
       </c>
       <c r="AK258" t="n">
-        <v>-22.04</v>
+        <v>-23.68</v>
       </c>
       <c r="AL258" t="n">
         <v>17.33</v>
       </c>
       <c r="AM258" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AN258" t="n">
         <v>12</v>
@@ -37464,13 +37474,13 @@
       </c>
       <c r="AP258" t="inlineStr"/>
       <c r="AQ258" t="n">
-        <v>3.57</v>
+        <v>2.42</v>
       </c>
       <c r="AR258" t="n">
         <v>4.4</v>
       </c>
       <c r="AS258" t="n">
-        <v>-23.7</v>
+        <v>-25.55</v>
       </c>
       <c r="AT258" t="inlineStr">
         <is>
@@ -37657,7 +37667,7 @@
       </c>
       <c r="G260" t="inlineStr"/>
       <c r="H260" t="n">
-        <v>-24.2</v>
+        <v>-26.2</v>
       </c>
       <c r="I260" t="n">
         <v>-1.89</v>
@@ -37672,7 +37682,7 @@
         <v>-19.7</v>
       </c>
       <c r="M260" t="n">
-        <v>-35.7</v>
+        <v>-37.4</v>
       </c>
       <c r="N260" t="inlineStr"/>
       <c r="O260" t="n">
@@ -37706,7 +37716,7 @@
         <v>46240</v>
       </c>
       <c r="Y260" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Z260" t="inlineStr">
         <is>
@@ -37735,22 +37745,22 @@
         <v>120.59</v>
       </c>
       <c r="AH260" t="n">
-        <v>98.18000000000001</v>
+        <v>95.48</v>
       </c>
       <c r="AI260" t="n">
-        <v>98.18000000000001</v>
+        <v>95.48</v>
       </c>
       <c r="AJ260" t="n">
-        <v>-18.59</v>
+        <v>-20.83</v>
       </c>
       <c r="AK260" t="n">
-        <v>-21.26</v>
+        <v>-21.5</v>
       </c>
       <c r="AL260" t="n">
         <v>19.06</v>
       </c>
       <c r="AM260" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AN260" t="n">
         <v>25</v>
@@ -37760,13 +37770,13 @@
       </c>
       <c r="AP260" t="inlineStr"/>
       <c r="AQ260" t="n">
-        <v>3.57</v>
+        <v>2.42</v>
       </c>
       <c r="AR260" t="n">
         <v>4.4</v>
       </c>
       <c r="AS260" t="n">
-        <v>-22.15</v>
+        <v>-23.25</v>
       </c>
       <c r="AT260" t="inlineStr">
         <is>
@@ -38393,7 +38403,7 @@
       </c>
       <c r="G265" t="inlineStr"/>
       <c r="H265" t="n">
-        <v>-15.7</v>
+        <v>-17.8</v>
       </c>
       <c r="I265" t="n">
         <v>-2.12</v>
@@ -38408,7 +38418,7 @@
         <v>16.5</v>
       </c>
       <c r="M265" t="n">
-        <v>-17.8</v>
+        <v>-21.8</v>
       </c>
       <c r="N265" t="inlineStr"/>
       <c r="O265" t="n">
@@ -38442,7 +38452,7 @@
         <v>46224</v>
       </c>
       <c r="Y265" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Z265" t="inlineStr">
         <is>
@@ -38469,13 +38479,13 @@
         <v>120.43</v>
       </c>
       <c r="AH265" t="n">
-        <v>92.31999999999999</v>
+        <v>87.81</v>
       </c>
       <c r="AI265" t="n">
-        <v>92.31999999999999</v>
+        <v>87.81</v>
       </c>
       <c r="AJ265" t="n">
-        <v>-23.34</v>
+        <v>-27.09</v>
       </c>
       <c r="AK265" t="n">
         <v>-28.46</v>
@@ -38484,7 +38494,7 @@
         <v>6.67</v>
       </c>
       <c r="AM265" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AN265" t="n">
         <v>48</v>
@@ -38494,13 +38504,13 @@
       </c>
       <c r="AP265" t="inlineStr"/>
       <c r="AQ265" t="n">
-        <v>3.57</v>
+        <v>2.42</v>
       </c>
       <c r="AR265" t="n">
         <v>4.4</v>
       </c>
       <c r="AS265" t="n">
-        <v>-26.91</v>
+        <v>-29.51</v>
       </c>
       <c r="AT265" t="inlineStr">
         <is>
@@ -39733,7 +39743,7 @@
         <v>25.8</v>
       </c>
       <c r="H274" t="n">
-        <v>46.6</v>
+        <v>48.4</v>
       </c>
       <c r="I274" t="n">
         <v>12.95</v>
@@ -39748,7 +39758,7 @@
         <v>7.1</v>
       </c>
       <c r="M274" t="n">
-        <v>48.4</v>
+        <v>49.5</v>
       </c>
       <c r="N274" t="inlineStr"/>
       <c r="O274" t="n">
@@ -39786,7 +39796,7 @@
         <v>46231</v>
       </c>
       <c r="Y274" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="Z274" t="inlineStr">
         <is>
@@ -39815,13 +39825,13 @@
         <v>96.34</v>
       </c>
       <c r="AH274" t="n">
-        <v>151.99</v>
+        <v>153.26</v>
       </c>
       <c r="AI274" t="n">
-        <v>151.99</v>
+        <v>153.26</v>
       </c>
       <c r="AJ274" t="n">
-        <v>57.76</v>
+        <v>59.08</v>
       </c>
       <c r="AK274" t="n">
         <v>-6.51</v>
@@ -39830,7 +39840,7 @@
         <v>62.67</v>
       </c>
       <c r="AM274" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AN274" t="n">
         <v>62</v>
@@ -39840,13 +39850,13 @@
       </c>
       <c r="AP274" t="inlineStr"/>
       <c r="AQ274" t="n">
-        <v>3.57</v>
+        <v>2.42</v>
       </c>
       <c r="AR274" t="n">
         <v>4.4</v>
       </c>
       <c r="AS274" t="n">
-        <v>54.2</v>
+        <v>56.66</v>
       </c>
       <c r="AT274" t="inlineStr"/>
     </row>
@@ -40177,7 +40187,7 @@
         <v>5.5</v>
       </c>
       <c r="H277" t="n">
-        <v>11.5</v>
+        <v>15.6</v>
       </c>
       <c r="I277" t="n">
         <v>1.46</v>
@@ -40192,7 +40202,7 @@
         <v>-9.1</v>
       </c>
       <c r="M277" t="n">
-        <v>-2.7</v>
+        <v>-2.9</v>
       </c>
       <c r="N277" t="inlineStr"/>
       <c r="O277" t="n">
@@ -40230,7 +40240,7 @@
         <v>46295</v>
       </c>
       <c r="Y277" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z277" t="inlineStr">
         <is>
@@ -40257,13 +40267,13 @@
         <v>17.49</v>
       </c>
       <c r="AH277" t="n">
-        <v>18.05</v>
+        <v>17.98</v>
       </c>
       <c r="AI277" t="n">
-        <v>18.05</v>
+        <v>17.98</v>
       </c>
       <c r="AJ277" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="AK277" t="n">
         <v>-19.94</v>
@@ -40272,7 +40282,7 @@
         <v>6.06</v>
       </c>
       <c r="AM277" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AN277" t="n">
         <v>51</v>
@@ -40282,13 +40292,13 @@
       </c>
       <c r="AP277" t="inlineStr"/>
       <c r="AQ277" t="n">
-        <v>3.57</v>
+        <v>2.42</v>
       </c>
       <c r="AR277" t="n">
         <v>4.4</v>
       </c>
       <c r="AS277" t="n">
-        <v>-0.37</v>
+        <v>0.38</v>
       </c>
       <c r="AT277" t="inlineStr">
         <is>
@@ -40327,7 +40337,7 @@
         <v>-17.5</v>
       </c>
       <c r="H278" t="n">
-        <v>-26.2</v>
+        <v>-21.3</v>
       </c>
       <c r="I278" t="n">
         <v>11.63</v>
@@ -40342,7 +40352,7 @@
         <v>-42.2</v>
       </c>
       <c r="M278" t="n">
-        <v>-37.2</v>
+        <v>-37.7</v>
       </c>
       <c r="N278" t="inlineStr"/>
       <c r="O278" t="n">
@@ -40380,7 +40390,7 @@
         <v>46224</v>
       </c>
       <c r="Y278" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Z278" t="inlineStr">
         <is>
@@ -40409,13 +40419,13 @@
         <v>142.6</v>
       </c>
       <c r="AH278" t="n">
-        <v>123.22</v>
+        <v>121.79</v>
       </c>
       <c r="AI278" t="n">
-        <v>123.22</v>
+        <v>121.79</v>
       </c>
       <c r="AJ278" t="n">
-        <v>-13.59</v>
+        <v>-14.59</v>
       </c>
       <c r="AK278" t="n">
         <v>-18.35</v>
@@ -40424,7 +40434,7 @@
         <v>45.74</v>
       </c>
       <c r="AM278" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AN278" t="n">
         <v>19</v>
@@ -40434,13 +40444,13 @@
       </c>
       <c r="AP278" t="inlineStr"/>
       <c r="AQ278" t="n">
-        <v>3.57</v>
+        <v>2.42</v>
       </c>
       <c r="AR278" t="n">
         <v>4.4</v>
       </c>
       <c r="AS278" t="n">
-        <v>-17.16</v>
+        <v>-17.01</v>
       </c>
       <c r="AT278" t="inlineStr">
         <is>
@@ -40479,7 +40489,7 @@
         <v>-18.1</v>
       </c>
       <c r="H279" t="n">
-        <v>-20.1</v>
+        <v>-18.1</v>
       </c>
       <c r="I279" t="n">
         <v>-5.59</v>
@@ -40494,7 +40504,7 @@
         <v>-3.4</v>
       </c>
       <c r="M279" t="n">
-        <v>-23.2</v>
+        <v>-20.6</v>
       </c>
       <c r="N279" t="inlineStr"/>
       <c r="O279" t="n">
@@ -40532,7 +40542,7 @@
         <v>46247</v>
       </c>
       <c r="Y279" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="Z279" t="inlineStr">
         <is>
@@ -40561,13 +40571,13 @@
         <v>68.29000000000001</v>
       </c>
       <c r="AH279" t="n">
-        <v>55.4</v>
+        <v>57.25</v>
       </c>
       <c r="AI279" t="n">
-        <v>55.4</v>
+        <v>57.25</v>
       </c>
       <c r="AJ279" t="n">
-        <v>-18.88</v>
+        <v>-16.17</v>
       </c>
       <c r="AK279" t="n">
         <v>-27.26</v>
@@ -40576,7 +40586,7 @@
         <v>10.77</v>
       </c>
       <c r="AM279" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AN279" t="n">
         <v>19</v>
@@ -40586,13 +40596,13 @@
       </c>
       <c r="AP279" t="inlineStr"/>
       <c r="AQ279" t="n">
-        <v>3.57</v>
+        <v>2.42</v>
       </c>
       <c r="AR279" t="n">
         <v>4.4</v>
       </c>
       <c r="AS279" t="n">
-        <v>-22.44</v>
+        <v>-18.59</v>
       </c>
       <c r="AT279" t="inlineStr">
         <is>
@@ -40631,7 +40641,7 @@
         <v>1.6</v>
       </c>
       <c r="H280" t="n">
-        <v>-18.9</v>
+        <v>7.9</v>
       </c>
       <c r="I280" t="n">
         <v>4.01</v>
@@ -40646,14 +40656,14 @@
         <v>2.9</v>
       </c>
       <c r="M280" t="n">
-        <v>-13.9</v>
+        <v>-12.9</v>
       </c>
       <c r="N280" t="inlineStr"/>
       <c r="O280" t="n">
         <v>-0.1</v>
       </c>
       <c r="P280" t="n">
-        <v>51.74</v>
+        <v>51.73</v>
       </c>
       <c r="Q280" t="inlineStr">
         <is>
@@ -40684,7 +40694,7 @@
         <v>46225</v>
       </c>
       <c r="Y280" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Z280" t="inlineStr">
         <is>
@@ -40713,13 +40723,13 @@
         <v>53.22</v>
       </c>
       <c r="AH280" t="n">
-        <v>43.92</v>
+        <v>44.45</v>
       </c>
       <c r="AI280" t="n">
-        <v>43.92</v>
+        <v>44.45</v>
       </c>
       <c r="AJ280" t="n">
-        <v>-17.47</v>
+        <v>-16.48</v>
       </c>
       <c r="AK280" t="n">
         <v>-28.93</v>
@@ -40728,7 +40738,7 @@
         <v>12.6</v>
       </c>
       <c r="AM280" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AN280" t="n">
         <v>12</v>
@@ -40738,13 +40748,13 @@
       </c>
       <c r="AP280" t="inlineStr"/>
       <c r="AQ280" t="n">
-        <v>3.57</v>
+        <v>2.42</v>
       </c>
       <c r="AR280" t="n">
         <v>4.4</v>
       </c>
       <c r="AS280" t="n">
-        <v>-21.04</v>
+        <v>-18.9</v>
       </c>
       <c r="AT280" t="inlineStr">
         <is>
@@ -41213,7 +41223,7 @@
       </c>
       <c r="G284" t="inlineStr"/>
       <c r="H284" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="I284" t="n">
         <v>6.91</v>
@@ -41228,7 +41238,7 @@
         <v>13.6</v>
       </c>
       <c r="M284" t="n">
-        <v>31</v>
+        <v>35.9</v>
       </c>
       <c r="N284" t="inlineStr"/>
       <c r="O284" t="n">
@@ -41262,7 +41272,7 @@
         <v>46225</v>
       </c>
       <c r="Y284" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Z284" t="inlineStr">
         <is>
@@ -41291,38 +41301,38 @@
         <v>34.49</v>
       </c>
       <c r="AH284" t="n">
-        <v>47.23</v>
+        <v>49.15</v>
       </c>
       <c r="AI284" t="n">
-        <v>47.23</v>
+        <v>49.15</v>
       </c>
       <c r="AJ284" t="n">
-        <v>36.95</v>
+        <v>42.52</v>
       </c>
       <c r="AK284" t="n">
         <v>-1.07</v>
       </c>
       <c r="AL284" t="n">
-        <v>40.92</v>
+        <v>42.84</v>
       </c>
       <c r="AM284" t="n">
+        <v>64</v>
+      </c>
+      <c r="AN284" t="n">
         <v>63</v>
-      </c>
-      <c r="AN284" t="n">
-        <v>61</v>
       </c>
       <c r="AO284" t="n">
         <v>39.21</v>
       </c>
       <c r="AP284" t="inlineStr"/>
       <c r="AQ284" t="n">
-        <v>3.57</v>
+        <v>2.42</v>
       </c>
       <c r="AR284" t="n">
         <v>4.4</v>
       </c>
       <c r="AS284" t="n">
-        <v>33.38</v>
+        <v>40.1</v>
       </c>
       <c r="AT284" t="inlineStr"/>
     </row>
@@ -41505,7 +41515,7 @@
         <v>-3.5</v>
       </c>
       <c r="H286" t="n">
-        <v>-7.4</v>
+        <v>-7.9</v>
       </c>
       <c r="I286" t="n">
         <v>-6.74</v>
@@ -41520,7 +41530,7 @@
         <v>23.7</v>
       </c>
       <c r="M286" t="n">
-        <v>-8.4</v>
+        <v>-9.1</v>
       </c>
       <c r="N286" t="inlineStr"/>
       <c r="O286" t="n">
@@ -41554,7 +41564,7 @@
         <v>46238</v>
       </c>
       <c r="Y286" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Z286" t="inlineStr">
         <is>
@@ -41581,13 +41591,13 @@
         <v>890</v>
       </c>
       <c r="AH286" t="n">
-        <v>735.64</v>
+        <v>730.76</v>
       </c>
       <c r="AI286" t="n">
-        <v>735.64</v>
+        <v>730.76</v>
       </c>
       <c r="AJ286" t="n">
-        <v>-17.34</v>
+        <v>-17.89</v>
       </c>
       <c r="AK286" t="n">
         <v>-20.9</v>
@@ -41596,7 +41606,7 @@
         <v>5.06</v>
       </c>
       <c r="AM286" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AN286" t="n">
         <v>11</v>
@@ -41606,13 +41616,13 @@
       </c>
       <c r="AP286" t="inlineStr"/>
       <c r="AQ286" t="n">
-        <v>3.57</v>
+        <v>2.42</v>
       </c>
       <c r="AR286" t="n">
         <v>4.4</v>
       </c>
       <c r="AS286" t="n">
-        <v>-20.91</v>
+        <v>-20.31</v>
       </c>
       <c r="AT286" t="inlineStr">
         <is>
@@ -42178,7 +42188,7 @@
         <v>-38.26</v>
       </c>
       <c r="AK290" t="n">
-        <v>-38.63</v>
+        <v>-38.62</v>
       </c>
       <c r="AL290" t="n">
         <v>1.81</v>
@@ -43327,7 +43337,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>$48,115.83  (-2.87% price-weighted)</t>
+          <t>$47,981.63  (-3.14% price-weighted)</t>
         </is>
       </c>
     </row>
@@ -43339,7 +43349,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-2.89%  &lt;- judge the system by this line</t>
+          <t>-3.15%  &lt;- judge the system by this line</t>
         </is>
       </c>
     </row>
@@ -43351,7 +43361,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-4.09%</t>
+          <t>-4.18%</t>
         </is>
       </c>
     </row>
@@ -43439,19 +43449,19 @@
         <v>190</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.64</v>
+        <v>-0.82</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.84</v>
+        <v>-1.8</v>
       </c>
       <c r="E12" t="n">
         <v>1.96</v>
       </c>
       <c r="F12" t="n">
-        <v>48.42</v>
+        <v>47.89</v>
       </c>
       <c r="G12" t="n">
-        <v>-13.43</v>
+        <v>-13.46</v>
       </c>
     </row>
     <row r="13">
@@ -43464,10 +43474,10 @@
         <v>75</v>
       </c>
       <c r="C13" t="n">
-        <v>-4.95</v>
+        <v>-5.38</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.22</v>
+        <v>-6.54</v>
       </c>
       <c r="E13" t="n">
         <v>5.06</v>
@@ -43476,7 +43486,7 @@
         <v>30.67</v>
       </c>
       <c r="G13" t="n">
-        <v>-20.01</v>
+        <v>-20.04</v>
       </c>
     </row>
     <row r="14">
@@ -43489,10 +43499,10 @@
         <v>29</v>
       </c>
       <c r="C14" t="n">
-        <v>-12.3</v>
+        <v>-12.7</v>
       </c>
       <c r="D14" t="n">
-        <v>-13.37</v>
+        <v>-13.69</v>
       </c>
       <c r="E14" t="n">
         <v>7.06</v>
@@ -43501,7 +43511,7 @@
         <v>24.14</v>
       </c>
       <c r="G14" t="n">
-        <v>-21.64</v>
+        <v>-21.67</v>
       </c>
     </row>
     <row r="15"/>
@@ -43552,19 +43562,19 @@
         <v>95</v>
       </c>
       <c r="C17" t="n">
-        <v>-6.55</v>
+        <v>-6.91</v>
       </c>
       <c r="D17" t="n">
         <v>28.42</v>
       </c>
       <c r="E17" t="n">
-        <v>-7.55</v>
+        <v>-7.75</v>
       </c>
       <c r="F17" t="n">
         <v>3.79</v>
       </c>
       <c r="G17" t="n">
-        <v>-17.9</v>
+        <v>-17.93</v>
       </c>
     </row>
     <row r="18">
@@ -43577,19 +43587,19 @@
         <v>42</v>
       </c>
       <c r="C18" t="n">
-        <v>-2.06</v>
+        <v>-2.36</v>
       </c>
       <c r="D18" t="n">
         <v>54.76</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.41</v>
+        <v>-3.46</v>
       </c>
       <c r="F18" t="n">
         <v>3.32</v>
       </c>
       <c r="G18" t="n">
-        <v>-13.1</v>
+        <v>-13.18</v>
       </c>
     </row>
     <row r="19">
@@ -43627,19 +43637,19 @@
         <v>138</v>
       </c>
       <c r="C20" t="n">
-        <v>-1.47</v>
+        <v>-1.69</v>
       </c>
       <c r="D20" t="n">
-        <v>44.2</v>
+        <v>43.48</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.8</v>
+        <v>-2.83</v>
       </c>
       <c r="F20" t="n">
         <v>4.07</v>
       </c>
       <c r="G20" t="n">
-        <v>-15.84</v>
+        <v>-15.87</v>
       </c>
     </row>
     <row r="21">
@@ -43717,13 +43727,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.23</v>
+        <v>-0.21</v>
       </c>
       <c r="D25" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E25" t="n">
         <v>3.83</v>
@@ -43732,7 +43742,7 @@
         <v>64</v>
       </c>
       <c r="G25" t="n">
-        <v>-13.5</v>
+        <v>-13.4</v>
       </c>
     </row>
     <row r="26">
@@ -43817,7 +43827,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C29" t="n">
         <v>2.26</v>
@@ -43826,13 +43836,13 @@
         <v>61</v>
       </c>
       <c r="E29" t="n">
-        <v>6.52</v>
+        <v>6.51</v>
       </c>
       <c r="F29" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G29" t="n">
-        <v>-10.72</v>
+        <v>-10.7</v>
       </c>
     </row>
     <row r="30"/>
@@ -43878,13 +43888,13 @@
         <v>5</v>
       </c>
       <c r="C32" t="n">
-        <v>7.1</v>
+        <v>7.62</v>
       </c>
       <c r="D32" t="n">
         <v>80</v>
       </c>
       <c r="E32" t="n">
-        <v>7.26</v>
+        <v>8</v>
       </c>
       <c r="F32" t="n">
         <v>-13.73</v>
@@ -43900,13 +43910,13 @@
         <v>11</v>
       </c>
       <c r="C33" t="n">
-        <v>-5.72</v>
+        <v>-6.24</v>
       </c>
       <c r="D33" t="n">
         <v>36.36</v>
       </c>
       <c r="E33" t="n">
-        <v>-6.62</v>
+        <v>-6.93</v>
       </c>
       <c r="F33" t="n">
         <v>-16.65</v>
@@ -43922,13 +43932,13 @@
         <v>26</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.13</v>
+        <v>-0.25</v>
       </c>
       <c r="D34" t="n">
-        <v>46.15</v>
+        <v>42.31</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.78</v>
+        <v>-0.8</v>
       </c>
       <c r="F34" t="n">
         <v>-15.12</v>

--- a/sts_ml_paper_tracker.xlsx
+++ b/sts_ml_paper_tracker.xlsx
@@ -438,7 +438,7 @@
     <col width="6" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
     <col width="17" customWidth="1" min="16" max="16"/>
-    <col width="9" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
     <col width="60" customWidth="1" min="18" max="18"/>
     <col width="12" customWidth="1" min="19" max="19"/>
     <col width="12" customWidth="1" min="20" max="20"/>
@@ -711,21 +711,9 @@
           <t>ALAB</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>D200G</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
         <v>6.1</v>
       </c>
@@ -736,18 +724,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="n">
-        <v>2.3</v>
-      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
-      <c r="O2" t="n">
-        <v>2.3</v>
-      </c>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>NO PRICE</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -770,9 +754,7 @@
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="n">
-        <v>257.8200073242188</v>
-      </c>
+      <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="inlineStr"/>
@@ -795,21 +777,9 @@
           <t>SNDK</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>D200G</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
         <v>6</v>
       </c>
@@ -820,18 +790,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="n">
-        <v>2.4</v>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
-      <c r="O3" t="n">
-        <v>2.4</v>
-      </c>
+      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>NO PRICE</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -854,9 +820,7 @@
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="inlineStr"/>
-      <c r="AH3" t="n">
-        <v>1260.930053710938</v>
-      </c>
+      <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="inlineStr"/>
       <c r="AJ3" t="inlineStr"/>
       <c r="AK3" t="inlineStr"/>
@@ -879,21 +843,9 @@
           <t>FISV</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>DLB</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
         <v>5</v>
       </c>
@@ -904,22 +856,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="n">
-        <v>-8.1</v>
-      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>WR20</t>
-        </is>
-      </c>
-      <c r="O4" t="n">
-        <v>-21.8</v>
-      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>NO PRICE</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -942,9 +886,7 @@
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="inlineStr"/>
-      <c r="AH4" t="n">
-        <v>50.81999969482422</v>
-      </c>
+      <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="inlineStr"/>
       <c r="AK4" t="inlineStr"/>
@@ -967,21 +909,9 @@
           <t>CPRI</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>DLB</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
         <v>2.3</v>
       </c>
@@ -992,22 +922,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="n">
-        <v>-9.800000000000001</v>
-      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>WR30</t>
-        </is>
-      </c>
-      <c r="O5" t="n">
-        <v>-36.2</v>
-      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>NO PRICE</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1030,9 +952,7 @@
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="inlineStr"/>
-      <c r="AH5" t="n">
-        <v>16.36000061035156</v>
-      </c>
+      <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="inlineStr"/>
       <c r="AK5" t="inlineStr"/>
@@ -1055,21 +975,9 @@
           <t>POOL</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>DLB</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
         <v>2.2</v>
       </c>
@@ -1080,22 +988,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="n">
-        <v>-2.3</v>
-      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>WR20</t>
-        </is>
-      </c>
-      <c r="O6" t="n">
-        <v>-24.9</v>
-      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>NO PRICE</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1118,9 +1018,7 @@
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr"/>
-      <c r="AH6" t="n">
-        <v>197.2100067138672</v>
-      </c>
+      <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="inlineStr"/>
       <c r="AJ6" t="inlineStr"/>
       <c r="AK6" t="inlineStr"/>
@@ -1143,21 +1041,9 @@
           <t>TECH</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
         <v>2.1</v>
       </c>
@@ -1168,18 +1054,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="n">
-        <v>15.5</v>
-      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
-      <c r="O7" t="n">
-        <v>15.5</v>
-      </c>
+      <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>NO PRICE</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1202,9 +1084,7 @@
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="inlineStr"/>
-      <c r="AH7" t="n">
-        <v>72.62000274658203</v>
-      </c>
+      <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="inlineStr"/>
       <c r="AJ7" t="inlineStr"/>
       <c r="AK7" t="inlineStr"/>
@@ -1227,21 +1107,9 @@
           <t>LEN</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>DLB</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
         <v>2.1</v>
       </c>
@@ -1252,22 +1120,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="n">
-        <v>-7.2</v>
-      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>WR20</t>
-        </is>
-      </c>
-      <c r="O8" t="n">
-        <v>-20.2</v>
-      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>NO PRICE</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1290,9 +1150,7 @@
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="inlineStr"/>
-      <c r="AH8" t="n">
-        <v>84.44999694824219</v>
-      </c>
+      <c r="AH8" t="inlineStr"/>
       <c r="AI8" t="inlineStr"/>
       <c r="AJ8" t="inlineStr"/>
       <c r="AK8" t="inlineStr"/>
@@ -1347,9 +1205,7 @@
       <c r="L9" t="n">
         <v>-7</v>
       </c>
-      <c r="M9" t="n">
-        <v>-3.1</v>
-      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>WR30</t>
@@ -1480,14 +1336,12 @@
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="n">
-        <v>-7.42</v>
+        <v>-7.43</v>
       </c>
       <c r="L10" t="n">
         <v>-0</v>
       </c>
-      <c r="M10" t="n">
-        <v>-6.9</v>
-      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="n">
         <v>-1.6</v>
@@ -1552,7 +1406,7 @@
         <v>-6.63</v>
       </c>
       <c r="AK10" t="n">
-        <v>-7.42</v>
+        <v>-7.43</v>
       </c>
       <c r="AL10" t="n">
         <v>1.75</v>
@@ -1615,9 +1469,7 @@
       <c r="L11" t="n">
         <v>0.7</v>
       </c>
-      <c r="M11" t="n">
-        <v>-9.300000000000001</v>
-      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="n">
         <v>-4.9</v>
@@ -1745,9 +1597,7 @@
       <c r="L12" t="n">
         <v>11.4</v>
       </c>
-      <c r="M12" t="n">
-        <v>-0.1</v>
-      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="n">
         <v>6.3</v>
@@ -1875,9 +1725,7 @@
       <c r="L13" t="n">
         <v>6.2</v>
       </c>
-      <c r="M13" t="n">
-        <v>3.6</v>
-      </c>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="n">
         <v>-2.6</v>
@@ -2009,9 +1857,7 @@
       <c r="L14" t="n">
         <v>-8.1</v>
       </c>
-      <c r="M14" t="n">
-        <v>6.9</v>
-      </c>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -2149,9 +1995,7 @@
       <c r="L15" t="n">
         <v>1.5</v>
       </c>
-      <c r="M15" t="n">
-        <v>7.7</v>
-      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="n">
         <v>-22.3</v>
@@ -2285,9 +2129,7 @@
       <c r="L16" t="n">
         <v>1.2</v>
       </c>
-      <c r="M16" t="n">
-        <v>-5.7</v>
-      </c>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="n">
         <v>2.8</v>
@@ -2419,9 +2261,7 @@
       <c r="L17" t="n">
         <v>-8.300000000000001</v>
       </c>
-      <c r="M17" t="n">
-        <v>11.5</v>
-      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -2466,10 +2306,10 @@
       </c>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="n">
-        <v>19.74</v>
+        <v>19.77</v>
       </c>
       <c r="AB17" t="n">
-        <v>19.74</v>
+        <v>19.77</v>
       </c>
       <c r="AC17" t="n">
         <v>-1.74</v>
@@ -2499,7 +2339,7 @@
         <v>-1.74</v>
       </c>
       <c r="AL17" t="n">
-        <v>19.74</v>
+        <v>19.77</v>
       </c>
       <c r="AM17" t="n">
         <v>7</v>
@@ -2559,9 +2399,7 @@
       <c r="L18" t="n">
         <v>20.1</v>
       </c>
-      <c r="M18" t="n">
-        <v>26.4</v>
-      </c>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="n">
         <v>2.6</v>
@@ -2693,9 +2531,7 @@
       <c r="L19" t="n">
         <v>-8.4</v>
       </c>
-      <c r="M19" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="n">
         <v>-13.4</v>
@@ -2827,9 +2663,7 @@
       <c r="L20" t="n">
         <v>3.6</v>
       </c>
-      <c r="M20" t="n">
-        <v>25</v>
-      </c>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="n">
         <v>-6.7</v>
@@ -2870,10 +2704,10 @@
       </c>
       <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="n">
-        <v>20.06</v>
+        <v>20.1</v>
       </c>
       <c r="AB20" t="n">
-        <v>20.06</v>
+        <v>20.1</v>
       </c>
       <c r="AC20" t="n">
         <v>-0</v>
@@ -2903,7 +2737,7 @@
         <v>-0</v>
       </c>
       <c r="AL20" t="n">
-        <v>20.06</v>
+        <v>20.1</v>
       </c>
       <c r="AM20" t="n">
         <v>7</v>
@@ -2963,9 +2797,7 @@
       <c r="L21" t="n">
         <v>-9.199999999999999</v>
       </c>
-      <c r="M21" t="n">
-        <v>1.6</v>
-      </c>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
           <t>WR40</t>
@@ -3101,9 +2933,7 @@
       <c r="L22" t="n">
         <v>1</v>
       </c>
-      <c r="M22" t="n">
-        <v>20.2</v>
-      </c>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="n">
         <v>-5.4</v>
@@ -3239,9 +3069,7 @@
       <c r="L23" t="n">
         <v>-5.1</v>
       </c>
-      <c r="M23" t="n">
-        <v>-6.5</v>
-      </c>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -3379,9 +3207,7 @@
       <c r="L24" t="n">
         <v>-22.7</v>
       </c>
-      <c r="M24" t="n">
-        <v>-30.8</v>
-      </c>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="n">
         <v>-32.1</v>
@@ -3511,9 +3337,7 @@
       <c r="L25" t="n">
         <v>-3.2</v>
       </c>
-      <c r="M25" t="n">
-        <v>-33.5</v>
-      </c>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -3651,9 +3475,7 @@
       <c r="L26" t="n">
         <v>1.5</v>
       </c>
-      <c r="M26" t="n">
-        <v>-9.4</v>
-      </c>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="n">
         <v>-12.8</v>
@@ -3787,9 +3609,7 @@
       <c r="L27" t="n">
         <v>0.3</v>
       </c>
-      <c r="M27" t="n">
-        <v>-8.5</v>
-      </c>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="n">
         <v>-14.8</v>
@@ -3923,9 +3743,7 @@
       <c r="L28" t="n">
         <v>-0.6</v>
       </c>
-      <c r="M28" t="n">
-        <v>16.3</v>
-      </c>
+      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="n">
         <v>-3.8</v>
@@ -4061,9 +3879,7 @@
       <c r="L29" t="n">
         <v>2.2</v>
       </c>
-      <c r="M29" t="n">
-        <v>37</v>
-      </c>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="n">
         <v>-16.6</v>
@@ -4194,14 +4010,12 @@
       </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="n">
-        <v>-3.4</v>
+        <v>-3.36</v>
       </c>
       <c r="L30" t="n">
         <v>-8</v>
       </c>
-      <c r="M30" t="n">
-        <v>-9.6</v>
-      </c>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="n">
         <v>-9.199999999999999</v>
@@ -4266,7 +4080,7 @@
         <v>-2.13</v>
       </c>
       <c r="AK30" t="n">
-        <v>-3.4</v>
+        <v>-3.36</v>
       </c>
       <c r="AL30" t="n">
         <v>4.75</v>
@@ -4331,9 +4145,7 @@
       <c r="L31" t="n">
         <v>-29.1</v>
       </c>
-      <c r="M31" t="n">
-        <v>-17</v>
-      </c>
+      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="n">
         <v>-29.3</v>
@@ -4457,27 +4269,25 @@
         <v>-6.5</v>
       </c>
       <c r="H32" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="I32" t="n">
-        <v>6.91</v>
+        <v>6.15</v>
       </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="n">
-        <v>-1.34</v>
+        <v>-2.04</v>
       </c>
       <c r="L32" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="M32" t="n">
-        <v>7.6</v>
-      </c>
+        <v>0.4</v>
+      </c>
+      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="n">
         <v>-1.9</v>
       </c>
       <c r="P32" t="n">
-        <v>86.98</v>
+        <v>86.36</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -4512,13 +4322,13 @@
       </c>
       <c r="Z32" t="inlineStr"/>
       <c r="AA32" t="n">
-        <v>7.68</v>
+        <v>6.92</v>
       </c>
       <c r="AB32" t="n">
-        <v>9.890000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AC32" t="n">
-        <v>-1.34</v>
+        <v>-2.04</v>
       </c>
       <c r="AD32" t="inlineStr"/>
       <c r="AE32" t="n">
@@ -4540,16 +4350,16 @@
         <v>8.99</v>
       </c>
       <c r="AK32" t="n">
-        <v>-1.34</v>
+        <v>-2.04</v>
       </c>
       <c r="AL32" t="n">
-        <v>9.890000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AM32" t="n">
         <v>14</v>
       </c>
       <c r="AN32" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AO32" t="inlineStr"/>
       <c r="AP32" t="inlineStr"/>
@@ -4605,9 +4415,7 @@
       <c r="L33" t="n">
         <v>5.1</v>
       </c>
-      <c r="M33" t="n">
-        <v>7.1</v>
-      </c>
+      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="n">
         <v>-1</v>
@@ -4743,9 +4551,7 @@
       <c r="L34" t="n">
         <v>3.4</v>
       </c>
-      <c r="M34" t="n">
-        <v>7</v>
-      </c>
+      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="n">
         <v>-2.8</v>
@@ -4881,9 +4687,7 @@
       <c r="L35" t="n">
         <v>-8.800000000000001</v>
       </c>
-      <c r="M35" t="n">
-        <v>-2.4</v>
-      </c>
+      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -5021,9 +4825,7 @@
       <c r="L36" t="n">
         <v>-35.8</v>
       </c>
-      <c r="M36" t="n">
-        <v>-35.3</v>
-      </c>
+      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="n">
         <v>-38.7</v>
@@ -5153,9 +4955,7 @@
       <c r="L37" t="n">
         <v>-6.9</v>
       </c>
-      <c r="M37" t="n">
-        <v>-0.1</v>
-      </c>
+      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="n">
         <v>-7.1</v>
@@ -5217,10 +5017,10 @@
         <v>1714.99</v>
       </c>
       <c r="AH37" t="n">
-        <v>1824.95</v>
+        <v>1824.96</v>
       </c>
       <c r="AI37" t="n">
-        <v>1824.95</v>
+        <v>1824.96</v>
       </c>
       <c r="AJ37" t="n">
         <v>6.41</v>
@@ -5291,9 +5091,7 @@
       <c r="L38" t="n">
         <v>-12.6</v>
       </c>
-      <c r="M38" t="n">
-        <v>2.9</v>
-      </c>
+      <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="n">
         <v>-15</v>
@@ -5429,9 +5227,7 @@
       <c r="L39" t="n">
         <v>-8.6</v>
       </c>
-      <c r="M39" t="n">
-        <v>-36.6</v>
-      </c>
+      <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -5573,9 +5369,7 @@
       <c r="L40" t="n">
         <v>-3.7</v>
       </c>
-      <c r="M40" t="n">
-        <v>-3.5</v>
-      </c>
+      <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -5713,9 +5507,7 @@
       <c r="L41" t="n">
         <v>3.6</v>
       </c>
-      <c r="M41" t="n">
-        <v>18.1</v>
-      </c>
+      <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="n">
         <v>-8.6</v>
@@ -5759,7 +5551,7 @@
         <v>3.54</v>
       </c>
       <c r="AB41" t="n">
-        <v>14.92</v>
+        <v>14.97</v>
       </c>
       <c r="AC41" t="n">
         <v>-6.76</v>
@@ -5789,7 +5581,7 @@
         <v>-6.76</v>
       </c>
       <c r="AL41" t="n">
-        <v>14.92</v>
+        <v>14.97</v>
       </c>
       <c r="AM41" t="n">
         <v>20</v>
@@ -5853,9 +5645,7 @@
       <c r="L42" t="n">
         <v>1.2</v>
       </c>
-      <c r="M42" t="n">
-        <v>-10.6</v>
-      </c>
+      <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="n">
         <v>-9.1</v>
@@ -5930,7 +5720,7 @@
         <v>-8.619999999999999</v>
       </c>
       <c r="AK42" t="n">
-        <v>-10.14</v>
+        <v>-10.24</v>
       </c>
       <c r="AL42" t="n">
         <v>16.71</v>
@@ -5997,9 +5787,7 @@
       <c r="L43" t="n">
         <v>-25.1</v>
       </c>
-      <c r="M43" t="n">
-        <v>-11.4</v>
-      </c>
+      <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="n">
         <v>-26.9</v>
@@ -6141,9 +5929,7 @@
       <c r="L44" t="n">
         <v>-12.9</v>
       </c>
-      <c r="M44" t="n">
-        <v>-20</v>
-      </c>
+      <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="n">
         <v>-19.3</v>
@@ -6275,9 +6061,7 @@
       <c r="L45" t="n">
         <v>17.3</v>
       </c>
-      <c r="M45" t="n">
-        <v>20.5</v>
-      </c>
+      <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="n">
         <v>11.4</v>
@@ -6417,9 +6201,7 @@
       <c r="L46" t="n">
         <v>-12.3</v>
       </c>
-      <c r="M46" t="n">
-        <v>-5.4</v>
-      </c>
+      <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="n">
         <v>-16.1</v>
@@ -6561,9 +6343,7 @@
       <c r="L47" t="n">
         <v>-18.4</v>
       </c>
-      <c r="M47" t="n">
-        <v>-17.4</v>
-      </c>
+      <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="n">
         <v>-19.9</v>
@@ -6695,9 +6475,7 @@
       <c r="L48" t="n">
         <v>-17</v>
       </c>
-      <c r="M48" t="n">
-        <v>-14.1</v>
-      </c>
+      <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="n">
         <v>-20.1</v>
@@ -6837,9 +6615,7 @@
       <c r="L49" t="n">
         <v>7.7</v>
       </c>
-      <c r="M49" t="n">
-        <v>15.3</v>
-      </c>
+      <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="n">
         <v>5.6</v>
@@ -6979,9 +6755,7 @@
       <c r="L50" t="n">
         <v>3.5</v>
       </c>
-      <c r="M50" t="n">
-        <v>19.3</v>
-      </c>
+      <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="O50" t="n">
         <v>-30.3</v>
@@ -7123,9 +6897,7 @@
       <c r="L51" t="n">
         <v>2.4</v>
       </c>
-      <c r="M51" t="n">
-        <v>13.5</v>
-      </c>
+      <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="n">
         <v>-4.8</v>
@@ -7265,9 +7037,7 @@
       <c r="L52" t="n">
         <v>-17.5</v>
       </c>
-      <c r="M52" t="n">
-        <v>-7.2</v>
-      </c>
+      <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="O52" t="n">
         <v>-20</v>
@@ -7407,9 +7177,7 @@
       <c r="L53" t="n">
         <v>4.6</v>
       </c>
-      <c r="M53" t="n">
-        <v>17.5</v>
-      </c>
+      <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="n">
         <v>-8.6</v>
@@ -7439,9 +7207,7 @@
       <c r="V53" t="b">
         <v>1</v>
       </c>
-      <c r="W53" s="1" t="n">
-        <v>46317</v>
-      </c>
+      <c r="W53" t="inlineStr"/>
       <c r="X53" s="1" t="n">
         <v>46317</v>
       </c>
@@ -7551,9 +7317,7 @@
       <c r="L54" t="n">
         <v>-10.8</v>
       </c>
-      <c r="M54" t="n">
-        <v>32.5</v>
-      </c>
+      <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="O54" t="n">
         <v>-27.7</v>
@@ -7695,9 +7459,7 @@
       <c r="L55" t="n">
         <v>-23</v>
       </c>
-      <c r="M55" t="n">
-        <v>-19.1</v>
-      </c>
+      <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="O55" t="n">
         <v>-28</v>
@@ -7829,9 +7591,7 @@
       <c r="L56" t="n">
         <v>-10.3</v>
       </c>
-      <c r="M56" t="n">
-        <v>8.6</v>
-      </c>
+      <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="O56" t="n">
         <v>-19.9</v>
@@ -7973,9 +7733,7 @@
       <c r="L57" t="n">
         <v>-5.4</v>
       </c>
-      <c r="M57" t="n">
-        <v>-3.3</v>
-      </c>
+      <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="O57" t="n">
         <v>-12.5</v>
@@ -8111,9 +7869,7 @@
       <c r="L58" t="n">
         <v>-5.7</v>
       </c>
-      <c r="M58" t="n">
-        <v>7.1</v>
-      </c>
+      <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -8257,9 +8013,7 @@
       <c r="L59" t="n">
         <v>10</v>
       </c>
-      <c r="M59" t="n">
-        <v>-14.4</v>
-      </c>
+      <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="O59" t="n">
         <v>7.9</v>
@@ -8405,9 +8159,7 @@
       <c r="L60" t="n">
         <v>1.2</v>
       </c>
-      <c r="M60" t="n">
-        <v>25</v>
-      </c>
+      <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="O60" t="n">
         <v>-32.7</v>
@@ -8485,7 +8237,7 @@
         <v>-12.2</v>
       </c>
       <c r="AL60" t="n">
-        <v>18.62</v>
+        <v>18.65</v>
       </c>
       <c r="AM60" t="n">
         <v>27</v>
@@ -8549,9 +8301,7 @@
       <c r="L61" t="n">
         <v>6.7</v>
       </c>
-      <c r="M61" t="n">
-        <v>15.5</v>
-      </c>
+      <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="O61" t="n">
         <v>6.2</v>
@@ -8629,7 +8379,7 @@
         <v>-2.13</v>
       </c>
       <c r="AL61" t="n">
-        <v>12.01</v>
+        <v>12.39</v>
       </c>
       <c r="AM61" t="n">
         <v>27</v>
@@ -8693,9 +8443,7 @@
       <c r="L62" t="n">
         <v>-34.1</v>
       </c>
-      <c r="M62" t="n">
-        <v>-24</v>
-      </c>
+      <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="O62" t="n">
         <v>-36.2</v>
@@ -8835,9 +8583,7 @@
       <c r="L63" t="n">
         <v>-3.6</v>
       </c>
-      <c r="M63" t="n">
-        <v>-6.5</v>
-      </c>
+      <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr">
         <is>
           <t>WR30</t>
@@ -8983,9 +8729,7 @@
       <c r="L64" t="n">
         <v>5.1</v>
       </c>
-      <c r="M64" t="n">
-        <v>-18.6</v>
-      </c>
+      <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
       <c r="O64" t="n">
         <v>2.1</v>
@@ -9129,9 +8873,7 @@
       <c r="L65" t="n">
         <v>1.9</v>
       </c>
-      <c r="M65" t="n">
-        <v>15.1</v>
-      </c>
+      <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="O65" t="n">
         <v>-19.9</v>
@@ -9273,9 +9015,7 @@
       <c r="L66" t="n">
         <v>-10.3</v>
       </c>
-      <c r="M66" t="n">
-        <v>11.5</v>
-      </c>
+      <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="O66" t="n">
         <v>-41.2</v>
@@ -9353,7 +9093,7 @@
         <v>-14.74</v>
       </c>
       <c r="AL66" t="n">
-        <v>13.7</v>
+        <v>13.73</v>
       </c>
       <c r="AM66" t="n">
         <v>28</v>
@@ -9421,9 +9161,7 @@
       <c r="L67" t="n">
         <v>-3.1</v>
       </c>
-      <c r="M67" t="n">
-        <v>37</v>
-      </c>
+      <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr">
         <is>
           <t>WR30</t>
@@ -9569,9 +9307,7 @@
       <c r="L68" t="n">
         <v>9.9</v>
       </c>
-      <c r="M68" t="n">
-        <v>11.9</v>
-      </c>
+      <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="O68" t="n">
         <v>-21</v>
@@ -9715,9 +9451,7 @@
       <c r="L69" t="n">
         <v>6.2</v>
       </c>
-      <c r="M69" t="n">
-        <v>1</v>
-      </c>
+      <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="O69" t="n">
         <v>-12.3</v>
@@ -9849,9 +9583,7 @@
       <c r="L70" t="n">
         <v>31.8</v>
       </c>
-      <c r="M70" t="n">
-        <v>30.3</v>
-      </c>
+      <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
       <c r="O70" t="n">
         <v>26.6</v>
@@ -9991,9 +9723,7 @@
       <c r="L71" t="n">
         <v>-3.3</v>
       </c>
-      <c r="M71" t="n">
-        <v>-4.7</v>
-      </c>
+      <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -10133,9 +9863,7 @@
       <c r="L72" t="n">
         <v>16.3</v>
       </c>
-      <c r="M72" t="n">
-        <v>-18.8</v>
-      </c>
+      <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
       <c r="O72" t="n">
         <v>13.8</v>
@@ -10271,9 +9999,7 @@
       <c r="L73" t="n">
         <v>1.4</v>
       </c>
-      <c r="M73" t="n">
-        <v>-0.2</v>
-      </c>
+      <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
       <c r="O73" t="n">
         <v>-9.800000000000001</v>
@@ -10409,9 +10135,7 @@
       <c r="L74" t="n">
         <v>0.4</v>
       </c>
-      <c r="M74" t="n">
-        <v>8.5</v>
-      </c>
+      <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
       <c r="O74" t="n">
         <v>2.1</v>
@@ -10553,9 +10277,7 @@
       <c r="L75" t="n">
         <v>-30.4</v>
       </c>
-      <c r="M75" t="n">
-        <v>-36.6</v>
-      </c>
+      <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
       <c r="O75" t="n">
         <v>-33.7</v>
@@ -10620,7 +10342,7 @@
         <v>-15.42</v>
       </c>
       <c r="AK75" t="n">
-        <v>-16.86</v>
+        <v>-17.24</v>
       </c>
       <c r="AL75" t="n">
         <v>0.85</v>
@@ -10691,9 +10413,7 @@
       <c r="L76" t="n">
         <v>-4.9</v>
       </c>
-      <c r="M76" t="n">
-        <v>-5.6</v>
-      </c>
+      <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
       <c r="O76" t="n">
         <v>-6.3</v>
@@ -10835,9 +10555,7 @@
       <c r="L77" t="n">
         <v>4.9</v>
       </c>
-      <c r="M77" t="n">
-        <v>4.3</v>
-      </c>
+      <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
       <c r="O77" t="n">
         <v>3.8</v>
@@ -10977,9 +10695,7 @@
       <c r="L78" t="n">
         <v>4.1</v>
       </c>
-      <c r="M78" t="n">
-        <v>-4</v>
-      </c>
+      <c r="M78" t="inlineStr"/>
       <c r="N78" t="inlineStr"/>
       <c r="O78" t="n">
         <v>-6.5</v>
@@ -11115,9 +10831,7 @@
       <c r="L79" t="n">
         <v>-3.6</v>
       </c>
-      <c r="M79" t="n">
-        <v>43.4</v>
-      </c>
+      <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -11199,7 +10913,7 @@
         <v>-3.87</v>
       </c>
       <c r="AL79" t="n">
-        <v>45.59</v>
+        <v>45.63</v>
       </c>
       <c r="AM79" t="n">
         <v>33</v>
@@ -11263,9 +10977,7 @@
       <c r="L80" t="n">
         <v>-32.6</v>
       </c>
-      <c r="M80" t="n">
-        <v>-22.6</v>
-      </c>
+      <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
       <c r="O80" t="n">
         <v>-40.5</v>
@@ -11341,7 +11053,7 @@
         <v>-12.47</v>
       </c>
       <c r="AL80" t="n">
-        <v>8.779999999999999</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="AM80" t="n">
         <v>33</v>
@@ -11405,9 +11117,7 @@
       <c r="L81" t="n">
         <v>-4.7</v>
       </c>
-      <c r="M81" t="n">
-        <v>-20.4</v>
-      </c>
+      <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr">
         <is>
           <t>WR30</t>
@@ -11484,7 +11194,7 @@
         <v>-21.27</v>
       </c>
       <c r="AK81" t="n">
-        <v>-23.01</v>
+        <v>-23.02</v>
       </c>
       <c r="AL81" t="n">
         <v>6.65</v>
@@ -11555,9 +11265,7 @@
       <c r="L82" t="n">
         <v>-5.7</v>
       </c>
-      <c r="M82" t="n">
-        <v>-53.8</v>
-      </c>
+      <c r="M82" t="inlineStr"/>
       <c r="N82" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -11707,9 +11415,7 @@
       <c r="L83" t="n">
         <v>-29.7</v>
       </c>
-      <c r="M83" t="n">
-        <v>-20.8</v>
-      </c>
+      <c r="M83" t="inlineStr"/>
       <c r="N83" t="inlineStr"/>
       <c r="O83" t="n">
         <v>-44.3</v>
@@ -11841,9 +11547,7 @@
       <c r="L84" t="n">
         <v>0.3</v>
       </c>
-      <c r="M84" t="n">
-        <v>-60.1</v>
-      </c>
+      <c r="M84" t="inlineStr"/>
       <c r="N84" t="inlineStr"/>
       <c r="O84" t="n">
         <v>-32.8</v>
@@ -11979,9 +11683,7 @@
       <c r="L85" t="n">
         <v>10.7</v>
       </c>
-      <c r="M85" t="n">
-        <v>7</v>
-      </c>
+      <c r="M85" t="inlineStr"/>
       <c r="N85" t="inlineStr"/>
       <c r="O85" t="n">
         <v>-10.6</v>
@@ -12127,9 +11829,7 @@
       <c r="L86" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="M86" t="n">
-        <v>-14.8</v>
-      </c>
+      <c r="M86" t="inlineStr"/>
       <c r="N86" t="inlineStr"/>
       <c r="O86" t="n">
         <v>8.5</v>
@@ -12204,7 +11904,7 @@
         <v>-15.31</v>
       </c>
       <c r="AK86" t="n">
-        <v>-15.4</v>
+        <v>-15.41</v>
       </c>
       <c r="AL86" t="n">
         <v>23.39</v>
@@ -12275,9 +11975,7 @@
       <c r="L87" t="n">
         <v>3.3</v>
       </c>
-      <c r="M87" t="n">
-        <v>15.5</v>
-      </c>
+      <c r="M87" t="inlineStr"/>
       <c r="N87" t="inlineStr"/>
       <c r="O87" t="n">
         <v>-14.5</v>
@@ -12419,9 +12117,7 @@
       <c r="L88" t="n">
         <v>-0.9</v>
       </c>
-      <c r="M88" t="n">
-        <v>2.8</v>
-      </c>
+      <c r="M88" t="inlineStr"/>
       <c r="N88" t="inlineStr"/>
       <c r="O88" t="n">
         <v>-12.1</v>
@@ -12563,9 +12259,7 @@
       <c r="L89" t="n">
         <v>53.6</v>
       </c>
-      <c r="M89" t="n">
-        <v>47.9</v>
-      </c>
+      <c r="M89" t="inlineStr"/>
       <c r="N89" t="inlineStr"/>
       <c r="O89" t="n">
         <v>-11.8</v>
@@ -12701,9 +12395,7 @@
       <c r="L90" t="n">
         <v>-20.5</v>
       </c>
-      <c r="M90" t="n">
-        <v>-33.1</v>
-      </c>
+      <c r="M90" t="inlineStr"/>
       <c r="N90" t="inlineStr"/>
       <c r="O90" t="n">
         <v>-27.1</v>
@@ -12839,9 +12531,7 @@
       <c r="L91" t="n">
         <v>1.1</v>
       </c>
-      <c r="M91" t="n">
-        <v>-27.3</v>
-      </c>
+      <c r="M91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
       <c r="O91" t="n">
         <v>-9.199999999999999</v>
@@ -12987,9 +12677,7 @@
       <c r="L92" t="n">
         <v>-5</v>
       </c>
-      <c r="M92" t="n">
-        <v>7.7</v>
-      </c>
+      <c r="M92" t="inlineStr"/>
       <c r="N92" t="inlineStr">
         <is>
           <t>WR40</t>
@@ -13135,9 +12823,7 @@
       <c r="L93" t="n">
         <v>-4.1</v>
       </c>
-      <c r="M93" t="n">
-        <v>19.3</v>
-      </c>
+      <c r="M93" t="inlineStr"/>
       <c r="N93" t="inlineStr">
         <is>
           <t>WR30</t>
@@ -13283,9 +12969,7 @@
       <c r="L94" t="n">
         <v>1.4</v>
       </c>
-      <c r="M94" t="n">
-        <v>-11.9</v>
-      </c>
+      <c r="M94" t="inlineStr"/>
       <c r="N94" t="inlineStr"/>
       <c r="O94" t="n">
         <v>-3.5</v>
@@ -13421,9 +13105,7 @@
       <c r="L95" t="n">
         <v>4</v>
       </c>
-      <c r="M95" t="n">
-        <v>-6.7</v>
-      </c>
+      <c r="M95" t="inlineStr"/>
       <c r="N95" t="inlineStr"/>
       <c r="O95" t="n">
         <v>-14.9</v>
@@ -13559,9 +13241,7 @@
       <c r="L96" t="n">
         <v>24.9</v>
       </c>
-      <c r="M96" t="n">
-        <v>41.7</v>
-      </c>
+      <c r="M96" t="inlineStr"/>
       <c r="N96" t="inlineStr"/>
       <c r="O96" t="n">
         <v>-0.9</v>
@@ -13703,9 +13383,7 @@
       <c r="L97" t="n">
         <v>-1.2</v>
       </c>
-      <c r="M97" t="n">
-        <v>-34.6</v>
-      </c>
+      <c r="M97" t="inlineStr"/>
       <c r="N97" t="inlineStr"/>
       <c r="O97" t="n">
         <v>-10.6</v>
@@ -13851,9 +13529,7 @@
       <c r="L98" t="n">
         <v>-9.699999999999999</v>
       </c>
-      <c r="M98" t="n">
-        <v>-22.1</v>
-      </c>
+      <c r="M98" t="inlineStr"/>
       <c r="N98" t="inlineStr">
         <is>
           <t>WR30</t>
@@ -13922,7 +13598,7 @@
         <v>-20.65</v>
       </c>
       <c r="AK98" t="n">
-        <v>-21.24</v>
+        <v>-21.25</v>
       </c>
       <c r="AL98" t="n">
         <v>3.01</v>
@@ -13993,9 +13669,7 @@
       <c r="L99" t="n">
         <v>9.1</v>
       </c>
-      <c r="M99" t="n">
-        <v>-22.3</v>
-      </c>
+      <c r="M99" t="inlineStr"/>
       <c r="N99" t="inlineStr"/>
       <c r="O99" t="n">
         <v>8.6</v>
@@ -14141,9 +13815,7 @@
       <c r="L100" t="n">
         <v>-0.4</v>
       </c>
-      <c r="M100" t="n">
-        <v>15.1</v>
-      </c>
+      <c r="M100" t="inlineStr"/>
       <c r="N100" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -14289,9 +13961,7 @@
       <c r="L101" t="n">
         <v>15</v>
       </c>
-      <c r="M101" t="n">
-        <v>18.9</v>
-      </c>
+      <c r="M101" t="inlineStr"/>
       <c r="N101" t="inlineStr"/>
       <c r="O101" t="n">
         <v>11.6</v>
@@ -14431,9 +14101,7 @@
       <c r="L102" t="n">
         <v>6.2</v>
       </c>
-      <c r="M102" t="n">
-        <v>-10.1</v>
-      </c>
+      <c r="M102" t="inlineStr"/>
       <c r="N102" t="inlineStr"/>
       <c r="O102" t="n">
         <v>-3.5</v>
@@ -14569,9 +14237,7 @@
       <c r="L103" t="n">
         <v>-4.6</v>
       </c>
-      <c r="M103" t="n">
-        <v>-6.5</v>
-      </c>
+      <c r="M103" t="inlineStr"/>
       <c r="N103" t="inlineStr">
         <is>
           <t>WR30</t>
@@ -14721,9 +14387,7 @@
       <c r="L104" t="n">
         <v>6.9</v>
       </c>
-      <c r="M104" t="n">
-        <v>-18.5</v>
-      </c>
+      <c r="M104" t="inlineStr"/>
       <c r="N104" t="inlineStr"/>
       <c r="O104" t="n">
         <v>5.4</v>
@@ -14798,7 +14462,7 @@
         <v>-17.88</v>
       </c>
       <c r="AK104" t="n">
-        <v>-18.6</v>
+        <v>-18.59</v>
       </c>
       <c r="AL104" t="n">
         <v>15.92</v>
@@ -14869,9 +14533,7 @@
       <c r="L105" t="n">
         <v>-8.5</v>
       </c>
-      <c r="M105" t="n">
-        <v>-18.5</v>
-      </c>
+      <c r="M105" t="inlineStr"/>
       <c r="N105" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -15011,9 +14673,7 @@
       <c r="L106" t="n">
         <v>16</v>
       </c>
-      <c r="M106" t="n">
-        <v>21</v>
-      </c>
+      <c r="M106" t="inlineStr"/>
       <c r="N106" t="inlineStr"/>
       <c r="O106" t="n">
         <v>-20.2</v>
@@ -15149,9 +14809,7 @@
       <c r="L107" t="n">
         <v>-8</v>
       </c>
-      <c r="M107" t="n">
-        <v>37</v>
-      </c>
+      <c r="M107" t="inlineStr"/>
       <c r="N107" t="inlineStr">
         <is>
           <t>WR40</t>
@@ -15297,9 +14955,7 @@
       <c r="L108" t="n">
         <v>4.3</v>
       </c>
-      <c r="M108" t="n">
-        <v>-23.1</v>
-      </c>
+      <c r="M108" t="inlineStr"/>
       <c r="N108" t="inlineStr"/>
       <c r="O108" t="n">
         <v>-8.9</v>
@@ -15435,9 +15091,7 @@
       <c r="L109" t="n">
         <v>32.9</v>
       </c>
-      <c r="M109" t="n">
-        <v>29.9</v>
-      </c>
+      <c r="M109" t="inlineStr"/>
       <c r="N109" t="inlineStr"/>
       <c r="O109" t="n">
         <v>8.300000000000001</v>
@@ -15579,9 +15233,7 @@
       <c r="L110" t="n">
         <v>1.8</v>
       </c>
-      <c r="M110" t="n">
-        <v>7.1</v>
-      </c>
+      <c r="M110" t="inlineStr"/>
       <c r="N110" t="inlineStr"/>
       <c r="O110" t="n">
         <v>-29.3</v>
@@ -15725,9 +15377,7 @@
       <c r="L111" t="n">
         <v>9</v>
       </c>
-      <c r="M111" t="n">
-        <v>-23.4</v>
-      </c>
+      <c r="M111" t="inlineStr"/>
       <c r="N111" t="inlineStr"/>
       <c r="O111" t="n">
         <v>-13.5</v>
@@ -15871,9 +15521,7 @@
       <c r="L112" t="n">
         <v>5.4</v>
       </c>
-      <c r="M112" t="n">
-        <v>-33.5</v>
-      </c>
+      <c r="M112" t="inlineStr"/>
       <c r="N112" t="inlineStr"/>
       <c r="O112" t="n">
         <v>-20</v>
@@ -16019,9 +15667,7 @@
       <c r="L113" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="M113" t="n">
-        <v>6.5</v>
-      </c>
+      <c r="M113" t="inlineStr"/>
       <c r="N113" t="inlineStr"/>
       <c r="O113" t="n">
         <v>7.8</v>
@@ -16163,9 +15809,7 @@
       <c r="L114" t="n">
         <v>4.2</v>
       </c>
-      <c r="M114" t="n">
-        <v>-4.7</v>
-      </c>
+      <c r="M114" t="inlineStr"/>
       <c r="N114" t="inlineStr"/>
       <c r="O114" t="n">
         <v>-31.3</v>
@@ -16309,9 +15953,7 @@
       <c r="L115" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="M115" t="n">
-        <v>-19.5</v>
-      </c>
+      <c r="M115" t="inlineStr"/>
       <c r="N115" t="inlineStr"/>
       <c r="O115" t="n">
         <v>-7.7</v>
@@ -16457,9 +16099,7 @@
       <c r="L116" t="n">
         <v>4.9</v>
       </c>
-      <c r="M116" t="n">
-        <v>-10.9</v>
-      </c>
+      <c r="M116" t="inlineStr"/>
       <c r="N116" t="inlineStr"/>
       <c r="O116" t="n">
         <v>-9</v>
@@ -16605,9 +16245,7 @@
       <c r="L117" t="n">
         <v>8.9</v>
       </c>
-      <c r="M117" t="n">
-        <v>-19.7</v>
-      </c>
+      <c r="M117" t="inlineStr"/>
       <c r="N117" t="inlineStr"/>
       <c r="O117" t="n">
         <v>-5.4</v>
@@ -16753,9 +16391,7 @@
       <c r="L118" t="n">
         <v>-10.4</v>
       </c>
-      <c r="M118" t="n">
-        <v>-43.5</v>
-      </c>
+      <c r="M118" t="inlineStr"/>
       <c r="N118" t="inlineStr"/>
       <c r="O118" t="n">
         <v>-13.3</v>
@@ -16820,7 +16456,7 @@
         <v>-36.54</v>
       </c>
       <c r="AK118" t="n">
-        <v>-37.26</v>
+        <v>-37.27</v>
       </c>
       <c r="AL118" t="n">
         <v>3.06</v>
@@ -16891,9 +16527,7 @@
       <c r="L119" t="n">
         <v>-9.5</v>
       </c>
-      <c r="M119" t="n">
-        <v>-13.9</v>
-      </c>
+      <c r="M119" t="inlineStr"/>
       <c r="N119" t="inlineStr"/>
       <c r="O119" t="n">
         <v>-16.6</v>
@@ -17029,9 +16663,7 @@
       <c r="L120" t="n">
         <v>30.3</v>
       </c>
-      <c r="M120" t="n">
-        <v>34.7</v>
-      </c>
+      <c r="M120" t="inlineStr"/>
       <c r="N120" t="inlineStr"/>
       <c r="O120" t="n">
         <v>20.7</v>
@@ -17177,9 +16809,7 @@
       <c r="L121" t="n">
         <v>3.7</v>
       </c>
-      <c r="M121" t="n">
-        <v>-18.9</v>
-      </c>
+      <c r="M121" t="inlineStr"/>
       <c r="N121" t="inlineStr"/>
       <c r="O121" t="n">
         <v>1.7</v>
@@ -17325,9 +16955,7 @@
       <c r="L122" t="n">
         <v>-12.7</v>
       </c>
-      <c r="M122" t="n">
-        <v>-22.6</v>
-      </c>
+      <c r="M122" t="inlineStr"/>
       <c r="N122" t="inlineStr"/>
       <c r="O122" t="n">
         <v>-15.8</v>
@@ -17463,9 +17091,7 @@
       <c r="L123" t="n">
         <v>-29.6</v>
       </c>
-      <c r="M123" t="n">
-        <v>-16.1</v>
-      </c>
+      <c r="M123" t="inlineStr"/>
       <c r="N123" t="inlineStr"/>
       <c r="O123" t="n">
         <v>-39.2</v>
@@ -17601,9 +17227,7 @@
       <c r="L124" t="n">
         <v>-19.2</v>
       </c>
-      <c r="M124" t="n">
-        <v>-30</v>
-      </c>
+      <c r="M124" t="inlineStr"/>
       <c r="N124" t="inlineStr"/>
       <c r="O124" t="n">
         <v>-21.1</v>
@@ -17739,9 +17363,7 @@
       <c r="L125" t="n">
         <v>48</v>
       </c>
-      <c r="M125" t="n">
-        <v>47.2</v>
-      </c>
+      <c r="M125" t="inlineStr"/>
       <c r="N125" t="inlineStr"/>
       <c r="O125" t="n">
         <v>11.9</v>
@@ -17883,9 +17505,7 @@
       <c r="L126" t="n">
         <v>-25.1</v>
       </c>
-      <c r="M126" t="n">
-        <v>-20.5</v>
-      </c>
+      <c r="M126" t="inlineStr"/>
       <c r="N126" t="inlineStr"/>
       <c r="O126" t="n">
         <v>-31.4</v>
@@ -18029,9 +17649,7 @@
       <c r="L127" t="n">
         <v>-9.5</v>
       </c>
-      <c r="M127" t="n">
-        <v>-18.6</v>
-      </c>
+      <c r="M127" t="inlineStr"/>
       <c r="N127" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -18171,9 +17789,7 @@
       <c r="L128" t="n">
         <v>3.9</v>
       </c>
-      <c r="M128" t="n">
-        <v>14.7</v>
-      </c>
+      <c r="M128" t="inlineStr"/>
       <c r="N128" t="inlineStr"/>
       <c r="O128" t="n">
         <v>-18</v>
@@ -18317,9 +17933,7 @@
       <c r="L129" t="n">
         <v>31.7</v>
       </c>
-      <c r="M129" t="n">
-        <v>56.4</v>
-      </c>
+      <c r="M129" t="inlineStr"/>
       <c r="N129" t="inlineStr"/>
       <c r="O129" t="n">
         <v>27</v>
@@ -18461,9 +18075,7 @@
       <c r="L130" t="n">
         <v>4.4</v>
       </c>
-      <c r="M130" t="n">
-        <v>13.3</v>
-      </c>
+      <c r="M130" t="inlineStr"/>
       <c r="N130" t="inlineStr"/>
       <c r="O130" t="n">
         <v>-31</v>
@@ -18605,9 +18217,7 @@
       <c r="L131" t="n">
         <v>-0.7</v>
       </c>
-      <c r="M131" t="n">
-        <v>-47.8</v>
-      </c>
+      <c r="M131" t="inlineStr"/>
       <c r="N131" t="inlineStr">
         <is>
           <t>WR40</t>
@@ -18755,9 +18365,7 @@
       <c r="L132" t="n">
         <v>-5.6</v>
       </c>
-      <c r="M132" t="n">
-        <v>-51.6</v>
-      </c>
+      <c r="M132" t="inlineStr"/>
       <c r="N132" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -18897,9 +18505,7 @@
       <c r="L133" t="n">
         <v>3.8</v>
       </c>
-      <c r="M133" t="n">
-        <v>43.4</v>
-      </c>
+      <c r="M133" t="inlineStr"/>
       <c r="N133" t="inlineStr"/>
       <c r="O133" t="n">
         <v>-41.2</v>
@@ -18977,7 +18583,7 @@
         <v>-16.21</v>
       </c>
       <c r="AL133" t="n">
-        <v>26.91</v>
+        <v>26.94</v>
       </c>
       <c r="AM133" t="n">
         <v>49</v>
@@ -19045,9 +18651,7 @@
       <c r="L134" t="n">
         <v>-5.3</v>
       </c>
-      <c r="M134" t="n">
-        <v>-15.1</v>
-      </c>
+      <c r="M134" t="inlineStr"/>
       <c r="N134" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -19187,9 +18791,7 @@
       <c r="L135" t="n">
         <v>0.8</v>
       </c>
-      <c r="M135" t="n">
-        <v>3.4</v>
-      </c>
+      <c r="M135" t="inlineStr"/>
       <c r="N135" t="inlineStr"/>
       <c r="O135" t="n">
         <v>-13</v>
@@ -19331,9 +18933,7 @@
       <c r="L136" t="n">
         <v>3.7</v>
       </c>
-      <c r="M136" t="n">
-        <v>9.699999999999999</v>
-      </c>
+      <c r="M136" t="inlineStr"/>
       <c r="N136" t="inlineStr"/>
       <c r="O136" t="n">
         <v>-20.6</v>
@@ -19469,9 +19069,7 @@
       <c r="L137" t="n">
         <v>3</v>
       </c>
-      <c r="M137" t="n">
-        <v>24.7</v>
-      </c>
+      <c r="M137" t="inlineStr"/>
       <c r="N137" t="inlineStr"/>
       <c r="O137" t="n">
         <v>-30.4</v>
@@ -19613,9 +19211,7 @@
       <c r="L138" t="n">
         <v>1.5</v>
       </c>
-      <c r="M138" t="n">
-        <v>-36.6</v>
-      </c>
+      <c r="M138" t="inlineStr"/>
       <c r="N138" t="inlineStr"/>
       <c r="O138" t="n">
         <v>-24.7</v>
@@ -19759,9 +19355,7 @@
       <c r="L139" t="n">
         <v>7.1</v>
       </c>
-      <c r="M139" t="n">
-        <v>-10.7</v>
-      </c>
+      <c r="M139" t="inlineStr"/>
       <c r="N139" t="inlineStr"/>
       <c r="O139" t="n">
         <v>1.9</v>
@@ -19905,9 +19499,7 @@
       <c r="L140" t="n">
         <v>-2.7</v>
       </c>
-      <c r="M140" t="n">
-        <v>-31.1</v>
-      </c>
+      <c r="M140" t="inlineStr"/>
       <c r="N140" t="inlineStr">
         <is>
           <t>WR30</t>
@@ -20057,9 +19649,7 @@
       <c r="L141" t="n">
         <v>1.7</v>
       </c>
-      <c r="M141" t="n">
-        <v>-33.9</v>
-      </c>
+      <c r="M141" t="inlineStr"/>
       <c r="N141" t="inlineStr"/>
       <c r="O141" t="n">
         <v>-1.6</v>
@@ -20205,9 +19795,7 @@
       <c r="L142" t="n">
         <v>4.8</v>
       </c>
-      <c r="M142" t="n">
-        <v>36.4</v>
-      </c>
+      <c r="M142" t="inlineStr"/>
       <c r="N142" t="inlineStr"/>
       <c r="O142" t="n">
         <v>-33.7</v>
@@ -20349,9 +19937,7 @@
       <c r="L143" t="n">
         <v>1.7</v>
       </c>
-      <c r="M143" t="n">
-        <v>-23.8</v>
-      </c>
+      <c r="M143" t="inlineStr"/>
       <c r="N143" t="inlineStr"/>
       <c r="O143" t="n">
         <v>-12.3</v>
@@ -20487,9 +20073,7 @@
       <c r="L144" t="n">
         <v>52.9</v>
       </c>
-      <c r="M144" t="n">
-        <v>53.3</v>
-      </c>
+      <c r="M144" t="inlineStr"/>
       <c r="N144" t="inlineStr"/>
       <c r="O144" t="n">
         <v>18.6</v>
@@ -20519,9 +20103,7 @@
       <c r="V144" t="b">
         <v>1</v>
       </c>
-      <c r="W144" s="1" t="n">
-        <v>46317</v>
-      </c>
+      <c r="W144" t="inlineStr"/>
       <c r="X144" s="1" t="n">
         <v>46265</v>
       </c>
@@ -20631,9 +20213,7 @@
       <c r="L145" t="n">
         <v>1.4</v>
       </c>
-      <c r="M145" t="n">
-        <v>-5.7</v>
-      </c>
+      <c r="M145" t="inlineStr"/>
       <c r="N145" t="inlineStr"/>
       <c r="O145" t="n">
         <v>-14.9</v>
@@ -20775,9 +20355,7 @@
       <c r="L146" t="n">
         <v>52.3</v>
       </c>
-      <c r="M146" t="n">
-        <v>63.2</v>
-      </c>
+      <c r="M146" t="inlineStr"/>
       <c r="N146" t="inlineStr"/>
       <c r="O146" t="n">
         <v>18</v>
@@ -20919,9 +20497,7 @@
       <c r="L147" t="n">
         <v>-1.3</v>
       </c>
-      <c r="M147" t="n">
-        <v>17.5</v>
-      </c>
+      <c r="M147" t="inlineStr"/>
       <c r="N147" t="inlineStr"/>
       <c r="O147" t="n">
         <v>-19.9</v>
@@ -20951,9 +20527,7 @@
       <c r="V147" t="b">
         <v>1</v>
       </c>
-      <c r="W147" s="1" t="n">
-        <v>46317</v>
-      </c>
+      <c r="W147" t="inlineStr"/>
       <c r="X147" s="1" t="n">
         <v>46253</v>
       </c>
@@ -21063,9 +20637,7 @@
       <c r="L148" t="n">
         <v>37</v>
       </c>
-      <c r="M148" t="n">
-        <v>24.3</v>
-      </c>
+      <c r="M148" t="inlineStr"/>
       <c r="N148" t="inlineStr"/>
       <c r="O148" t="n">
         <v>5.2</v>
@@ -21207,9 +20779,7 @@
       <c r="L149" t="n">
         <v>13.5</v>
       </c>
-      <c r="M149" t="n">
-        <v>30</v>
-      </c>
+      <c r="M149" t="inlineStr"/>
       <c r="N149" t="inlineStr"/>
       <c r="O149" t="n">
         <v>-21.7</v>
@@ -21355,9 +20925,7 @@
       <c r="L150" t="n">
         <v>-11.1</v>
       </c>
-      <c r="M150" t="n">
-        <v>-9.4</v>
-      </c>
+      <c r="M150" t="inlineStr"/>
       <c r="N150" t="inlineStr"/>
       <c r="O150" t="n">
         <v>-25.3</v>
@@ -21499,9 +21067,7 @@
       <c r="L151" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="M151" t="n">
-        <v>-3.9</v>
-      </c>
+      <c r="M151" t="inlineStr"/>
       <c r="N151" t="inlineStr"/>
       <c r="O151" t="n">
         <v>3.2</v>
@@ -21641,9 +21207,7 @@
       <c r="L152" t="n">
         <v>-24.2</v>
       </c>
-      <c r="M152" t="n">
-        <v>-28.4</v>
-      </c>
+      <c r="M152" t="inlineStr"/>
       <c r="N152" t="inlineStr"/>
       <c r="O152" t="n">
         <v>-24.4</v>
@@ -21789,9 +21353,7 @@
       <c r="L153" t="n">
         <v>5.1</v>
       </c>
-      <c r="M153" t="n">
-        <v>28.2</v>
-      </c>
+      <c r="M153" t="inlineStr"/>
       <c r="N153" t="inlineStr"/>
       <c r="O153" t="n">
         <v>-32.6</v>
@@ -21933,9 +21495,7 @@
       <c r="L154" t="n">
         <v>-14.4</v>
       </c>
-      <c r="M154" t="n">
-        <v>-8.5</v>
-      </c>
+      <c r="M154" t="inlineStr"/>
       <c r="N154" t="inlineStr"/>
       <c r="O154" t="n">
         <v>-14.3</v>
@@ -22077,9 +21637,7 @@
       <c r="L155" t="n">
         <v>18.1</v>
       </c>
-      <c r="M155" t="n">
-        <v>5.6</v>
-      </c>
+      <c r="M155" t="inlineStr"/>
       <c r="N155" t="inlineStr"/>
       <c r="O155" t="n">
         <v>16.9</v>
@@ -22211,9 +21769,7 @@
       <c r="L156" t="n">
         <v>-11.4</v>
       </c>
-      <c r="M156" t="n">
-        <v>19.3</v>
-      </c>
+      <c r="M156" t="inlineStr"/>
       <c r="N156" t="inlineStr"/>
       <c r="O156" t="n">
         <v>-30.7</v>
@@ -22355,9 +21911,7 @@
       <c r="L157" t="n">
         <v>10.3</v>
       </c>
-      <c r="M157" t="n">
-        <v>17.6</v>
-      </c>
+      <c r="M157" t="inlineStr"/>
       <c r="N157" t="inlineStr"/>
       <c r="O157" t="n">
         <v>10.8</v>
@@ -22433,7 +21987,7 @@
         <v>-6.54</v>
       </c>
       <c r="AL157" t="n">
-        <v>18.6</v>
+        <v>18.66</v>
       </c>
       <c r="AM157" t="n">
         <v>56</v>
@@ -22497,9 +22051,7 @@
       <c r="L158" t="n">
         <v>30.9</v>
       </c>
-      <c r="M158" t="n">
-        <v>26.7</v>
-      </c>
+      <c r="M158" t="inlineStr"/>
       <c r="N158" t="inlineStr"/>
       <c r="O158" t="n">
         <v>12.6</v>
@@ -22639,9 +22191,7 @@
       <c r="L159" t="n">
         <v>-22.2</v>
       </c>
-      <c r="M159" t="n">
-        <v>-3.5</v>
-      </c>
+      <c r="M159" t="inlineStr"/>
       <c r="N159" t="inlineStr"/>
       <c r="O159" t="n">
         <v>-24.1</v>
@@ -22783,9 +22333,7 @@
       <c r="L160" t="n">
         <v>-25.3</v>
       </c>
-      <c r="M160" t="n">
-        <v>11.5</v>
-      </c>
+      <c r="M160" t="inlineStr"/>
       <c r="N160" t="inlineStr"/>
       <c r="O160" t="n">
         <v>-50.8</v>
@@ -22863,7 +22411,7 @@
         <v>-19.66</v>
       </c>
       <c r="AL160" t="n">
-        <v>28.49</v>
+        <v>28.52</v>
       </c>
       <c r="AM160" t="n">
         <v>58</v>
@@ -22931,9 +22479,7 @@
       <c r="L161" t="n">
         <v>14.7</v>
       </c>
-      <c r="M161" t="n">
-        <v>-7.5</v>
-      </c>
+      <c r="M161" t="inlineStr"/>
       <c r="N161" t="inlineStr"/>
       <c r="O161" t="n">
         <v>-0.5</v>
@@ -23077,9 +22623,7 @@
       <c r="L162" t="n">
         <v>0.4</v>
       </c>
-      <c r="M162" t="n">
-        <v>34.9</v>
-      </c>
+      <c r="M162" t="inlineStr"/>
       <c r="N162" t="inlineStr"/>
       <c r="O162" t="n">
         <v>-36.9</v>
@@ -23221,9 +22765,7 @@
       <c r="L163" t="n">
         <v>-11.6</v>
       </c>
-      <c r="M163" t="n">
-        <v>-4.7</v>
-      </c>
+      <c r="M163" t="inlineStr"/>
       <c r="N163" t="inlineStr"/>
       <c r="O163" t="n">
         <v>-32.4</v>
@@ -23369,9 +22911,7 @@
       <c r="L164" t="n">
         <v>-4</v>
       </c>
-      <c r="M164" t="n">
-        <v>11.9</v>
-      </c>
+      <c r="M164" t="inlineStr"/>
       <c r="N164" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -23517,9 +23057,7 @@
       <c r="L165" t="n">
         <v>-3</v>
       </c>
-      <c r="M165" t="n">
-        <v>56</v>
-      </c>
+      <c r="M165" t="inlineStr"/>
       <c r="N165" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -23665,9 +23203,7 @@
       <c r="L166" t="n">
         <v>-29.1</v>
       </c>
-      <c r="M166" t="n">
-        <v>-19</v>
-      </c>
+      <c r="M166" t="inlineStr"/>
       <c r="N166" t="inlineStr"/>
       <c r="O166" t="n">
         <v>-45.6</v>
@@ -23803,9 +23339,7 @@
       <c r="L167" t="n">
         <v>-11.2</v>
       </c>
-      <c r="M167" t="n">
-        <v>-12.5</v>
-      </c>
+      <c r="M167" t="inlineStr"/>
       <c r="N167" t="inlineStr"/>
       <c r="O167" t="n">
         <v>-31.4</v>
@@ -23941,9 +23475,7 @@
       <c r="L168" t="n">
         <v>23.1</v>
       </c>
-      <c r="M168" t="n">
-        <v>9.699999999999999</v>
-      </c>
+      <c r="M168" t="inlineStr"/>
       <c r="N168" t="inlineStr"/>
       <c r="O168" t="n">
         <v>21</v>
@@ -24083,9 +23615,7 @@
       <c r="L169" t="n">
         <v>4.2</v>
       </c>
-      <c r="M169" t="n">
-        <v>20.2</v>
-      </c>
+      <c r="M169" t="inlineStr"/>
       <c r="N169" t="inlineStr"/>
       <c r="O169" t="n">
         <v>-20.1</v>
@@ -24227,9 +23757,7 @@
       <c r="L170" t="n">
         <v>7.3</v>
       </c>
-      <c r="M170" t="n">
-        <v>8.5</v>
-      </c>
+      <c r="M170" t="inlineStr"/>
       <c r="N170" t="inlineStr"/>
       <c r="O170" t="n">
         <v>-6.2</v>
@@ -24371,9 +23899,7 @@
       <c r="L171" t="n">
         <v>-24</v>
       </c>
-      <c r="M171" t="n">
-        <v>-9.800000000000001</v>
-      </c>
+      <c r="M171" t="inlineStr"/>
       <c r="N171" t="inlineStr"/>
       <c r="O171" t="n">
         <v>-25.9</v>
@@ -24639,9 +24165,7 @@
       <c r="L173" t="n">
         <v>-14.9</v>
       </c>
-      <c r="M173" t="n">
-        <v>-2.3</v>
-      </c>
+      <c r="M173" t="inlineStr"/>
       <c r="N173" t="inlineStr"/>
       <c r="O173" t="n">
         <v>-27</v>
@@ -24789,9 +24313,7 @@
       <c r="L174" t="n">
         <v>47.6</v>
       </c>
-      <c r="M174" t="n">
-        <v>38.7</v>
-      </c>
+      <c r="M174" t="inlineStr"/>
       <c r="N174" t="inlineStr"/>
       <c r="O174" t="n">
         <v>31.8</v>
@@ -24937,9 +24459,7 @@
       <c r="L175" t="n">
         <v>25</v>
       </c>
-      <c r="M175" t="n">
-        <v>21</v>
-      </c>
+      <c r="M175" t="inlineStr"/>
       <c r="N175" t="inlineStr"/>
       <c r="O175" t="n">
         <v>-6.8</v>
@@ -25085,9 +24605,7 @@
       <c r="L176" t="n">
         <v>-21.4</v>
       </c>
-      <c r="M176" t="n">
-        <v>-18.6</v>
-      </c>
+      <c r="M176" t="inlineStr"/>
       <c r="N176" t="inlineStr"/>
       <c r="O176" t="n">
         <v>-27.7</v>
@@ -25233,9 +24751,7 @@
       <c r="L177" t="n">
         <v>-12.9</v>
       </c>
-      <c r="M177" t="n">
-        <v>-5.1</v>
-      </c>
+      <c r="M177" t="inlineStr"/>
       <c r="N177" t="inlineStr"/>
       <c r="O177" t="n">
         <v>-17.4</v>
@@ -25381,9 +24897,7 @@
       <c r="L178" t="n">
         <v>-8.4</v>
       </c>
-      <c r="M178" t="n">
-        <v>14.7</v>
-      </c>
+      <c r="M178" t="inlineStr"/>
       <c r="N178" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -25533,9 +25047,7 @@
       <c r="L179" t="n">
         <v>-3.5</v>
       </c>
-      <c r="M179" t="n">
-        <v>1</v>
-      </c>
+      <c r="M179" t="inlineStr"/>
       <c r="N179" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -25685,9 +25197,7 @@
       <c r="L180" t="n">
         <v>-24.2</v>
       </c>
-      <c r="M180" t="n">
-        <v>-21.9</v>
-      </c>
+      <c r="M180" t="inlineStr"/>
       <c r="N180" t="inlineStr"/>
       <c r="O180" t="n">
         <v>-25.7</v>
@@ -25835,9 +25345,7 @@
       <c r="L181" t="n">
         <v>-28.8</v>
       </c>
-      <c r="M181" t="n">
-        <v>-22.1</v>
-      </c>
+      <c r="M181" t="inlineStr"/>
       <c r="N181" t="inlineStr"/>
       <c r="O181" t="n">
         <v>-42.4</v>
@@ -25983,9 +25491,7 @@
       <c r="L182" t="n">
         <v>28.5</v>
       </c>
-      <c r="M182" t="n">
-        <v>5.4</v>
-      </c>
+      <c r="M182" t="inlineStr"/>
       <c r="N182" t="inlineStr"/>
       <c r="O182" t="n">
         <v>27</v>
@@ -26131,9 +25637,7 @@
       <c r="L183" t="n">
         <v>52.9</v>
       </c>
-      <c r="M183" t="n">
-        <v>66.7</v>
-      </c>
+      <c r="M183" t="inlineStr"/>
       <c r="N183" t="inlineStr"/>
       <c r="O183" t="n">
         <v>5.4</v>
@@ -26279,9 +25783,7 @@
       <c r="L184" t="n">
         <v>-37.8</v>
       </c>
-      <c r="M184" t="n">
-        <v>-3.1</v>
-      </c>
+      <c r="M184" t="inlineStr"/>
       <c r="N184" t="inlineStr"/>
       <c r="O184" t="n">
         <v>-50.4</v>
@@ -26427,9 +25929,7 @@
       <c r="L185" t="n">
         <v>-14.6</v>
       </c>
-      <c r="M185" t="n">
-        <v>-5.7</v>
-      </c>
+      <c r="M185" t="inlineStr"/>
       <c r="N185" t="inlineStr"/>
       <c r="O185" t="n">
         <v>-14.7</v>
@@ -26575,9 +26075,7 @@
       <c r="L186" t="n">
         <v>9</v>
       </c>
-      <c r="M186" t="n">
-        <v>-23.1</v>
-      </c>
+      <c r="M186" t="inlineStr"/>
       <c r="N186" t="inlineStr"/>
       <c r="O186" t="n">
         <v>-7.5</v>
@@ -26721,9 +26219,7 @@
       <c r="L187" t="n">
         <v>46.7</v>
       </c>
-      <c r="M187" t="n">
-        <v>-6.9</v>
-      </c>
+      <c r="M187" t="inlineStr"/>
       <c r="N187" t="inlineStr"/>
       <c r="O187" t="n">
         <v>42.3</v>
@@ -26873,9 +26369,7 @@
       <c r="L188" t="n">
         <v>48.1</v>
       </c>
-      <c r="M188" t="n">
-        <v>25</v>
-      </c>
+      <c r="M188" t="inlineStr"/>
       <c r="N188" t="inlineStr"/>
       <c r="O188" t="n">
         <v>45.4</v>
@@ -27021,9 +26515,7 @@
       <c r="L189" t="n">
         <v>56.6</v>
       </c>
-      <c r="M189" t="n">
-        <v>-14.4</v>
-      </c>
+      <c r="M189" t="inlineStr"/>
       <c r="N189" t="inlineStr"/>
       <c r="O189" t="n">
         <v>50.5</v>
@@ -27169,9 +26661,7 @@
       <c r="L190" t="n">
         <v>78.8</v>
       </c>
-      <c r="M190" t="n">
-        <v>2.4</v>
-      </c>
+      <c r="M190" t="inlineStr"/>
       <c r="N190" t="inlineStr"/>
       <c r="O190" t="n">
         <v>73.3</v>
@@ -27321,9 +26811,7 @@
       <c r="L191" t="n">
         <v>51.9</v>
       </c>
-      <c r="M191" t="n">
-        <v>2.3</v>
-      </c>
+      <c r="M191" t="inlineStr"/>
       <c r="N191" t="inlineStr"/>
       <c r="O191" t="n">
         <v>49.5</v>
@@ -27473,9 +26961,7 @@
       <c r="L192" t="n">
         <v>82.09999999999999</v>
       </c>
-      <c r="M192" t="n">
-        <v>17.5</v>
-      </c>
+      <c r="M192" t="inlineStr"/>
       <c r="N192" t="inlineStr"/>
       <c r="O192" t="n">
         <v>75.8</v>
@@ -27621,9 +27107,7 @@
       <c r="L193" t="n">
         <v>63.2</v>
       </c>
-      <c r="M193" t="n">
-        <v>40.3</v>
-      </c>
+      <c r="M193" t="inlineStr"/>
       <c r="N193" t="inlineStr"/>
       <c r="O193" t="n">
         <v>43.2</v>
@@ -27765,9 +27249,7 @@
       <c r="L194" t="n">
         <v>35.3</v>
       </c>
-      <c r="M194" t="n">
-        <v>-9.300000000000001</v>
-      </c>
+      <c r="M194" t="inlineStr"/>
       <c r="N194" t="inlineStr"/>
       <c r="O194" t="n">
         <v>24.9</v>
@@ -27917,9 +27399,7 @@
       <c r="L195" t="n">
         <v>65.3</v>
       </c>
-      <c r="M195" t="n">
-        <v>-5.7</v>
-      </c>
+      <c r="M195" t="inlineStr"/>
       <c r="N195" t="inlineStr"/>
       <c r="O195" t="n">
         <v>53.9</v>
@@ -28065,9 +27545,7 @@
       <c r="L196" t="n">
         <v>19.3</v>
       </c>
-      <c r="M196" t="n">
-        <v>-19.5</v>
-      </c>
+      <c r="M196" t="inlineStr"/>
       <c r="N196" t="inlineStr"/>
       <c r="O196" t="n">
         <v>15.7</v>
@@ -28213,9 +27691,7 @@
       <c r="L197" t="n">
         <v>51.8</v>
       </c>
-      <c r="M197" t="n">
-        <v>-14.8</v>
-      </c>
+      <c r="M197" t="inlineStr"/>
       <c r="N197" t="inlineStr"/>
       <c r="O197" t="n">
         <v>46.3</v>
@@ -28284,7 +27760,7 @@
         <v>-31.09</v>
       </c>
       <c r="AK197" t="n">
-        <v>-31.16</v>
+        <v>-31.17</v>
       </c>
       <c r="AL197" t="n">
         <v>5.66</v>
@@ -28359,9 +27835,7 @@
       <c r="L198" t="n">
         <v>51.3</v>
       </c>
-      <c r="M198" t="n">
-        <v>-0.1</v>
-      </c>
+      <c r="M198" t="inlineStr"/>
       <c r="N198" t="inlineStr"/>
       <c r="O198" t="n">
         <v>48.1</v>
@@ -28507,9 +27981,7 @@
       <c r="L199" t="n">
         <v>32.8</v>
       </c>
-      <c r="M199" t="n">
-        <v>-4.3</v>
-      </c>
+      <c r="M199" t="inlineStr"/>
       <c r="N199" t="inlineStr"/>
       <c r="O199" t="n">
         <v>24</v>
@@ -28655,9 +28127,7 @@
       <c r="L200" t="n">
         <v>98.5</v>
       </c>
-      <c r="M200" t="n">
-        <v>41.6</v>
-      </c>
+      <c r="M200" t="inlineStr"/>
       <c r="N200" t="inlineStr"/>
       <c r="O200" t="n">
         <v>70.09999999999999</v>
@@ -28799,9 +28269,7 @@
       <c r="L201" t="n">
         <v>40.9</v>
       </c>
-      <c r="M201" t="n">
-        <v>-25.1</v>
-      </c>
+      <c r="M201" t="inlineStr"/>
       <c r="N201" t="inlineStr"/>
       <c r="O201" t="n">
         <v>40</v>
@@ -28945,9 +28413,7 @@
       <c r="L202" t="n">
         <v>51.1</v>
       </c>
-      <c r="M202" t="n">
-        <v>-22.3</v>
-      </c>
+      <c r="M202" t="inlineStr"/>
       <c r="N202" t="inlineStr"/>
       <c r="O202" t="n">
         <v>36.8</v>
@@ -29097,9 +28563,7 @@
       <c r="L203" t="n">
         <v>37.5</v>
       </c>
-      <c r="M203" t="n">
-        <v>-18.5</v>
-      </c>
+      <c r="M203" t="inlineStr"/>
       <c r="N203" t="inlineStr"/>
       <c r="O203" t="n">
         <v>31.2</v>
@@ -29239,9 +28703,7 @@
       <c r="L204" t="n">
         <v>-14.6</v>
       </c>
-      <c r="M204" t="n">
-        <v>13.3</v>
-      </c>
+      <c r="M204" t="inlineStr"/>
       <c r="N204" t="inlineStr"/>
       <c r="O204" t="n">
         <v>-45.2</v>
@@ -29391,9 +28853,7 @@
       <c r="L205" t="n">
         <v>16.5</v>
       </c>
-      <c r="M205" t="n">
-        <v>-29.6</v>
-      </c>
+      <c r="M205" t="inlineStr"/>
       <c r="N205" t="inlineStr"/>
       <c r="O205" t="n">
         <v>12.5</v>
@@ -29539,9 +28999,7 @@
       <c r="L206" t="n">
         <v>-8.800000000000001</v>
       </c>
-      <c r="M206" t="n">
-        <v>-33.5</v>
-      </c>
+      <c r="M206" t="inlineStr"/>
       <c r="N206" t="inlineStr"/>
       <c r="O206" t="n">
         <v>-12.3</v>
@@ -29691,9 +29149,7 @@
       <c r="L207" t="n">
         <v>41.1</v>
       </c>
-      <c r="M207" t="n">
-        <v>149.1</v>
-      </c>
+      <c r="M207" t="inlineStr"/>
       <c r="N207" t="inlineStr"/>
       <c r="O207" t="n">
         <v>20.1</v>
@@ -29839,9 +29295,7 @@
       <c r="L208" t="n">
         <v>9.9</v>
       </c>
-      <c r="M208" t="n">
-        <v>-19.7</v>
-      </c>
+      <c r="M208" t="inlineStr"/>
       <c r="N208" t="inlineStr"/>
       <c r="O208" t="n">
         <v>10.1</v>
@@ -29987,9 +29441,7 @@
       <c r="L209" t="n">
         <v>-27.9</v>
       </c>
-      <c r="M209" t="n">
-        <v>-47.8</v>
-      </c>
+      <c r="M209" t="inlineStr"/>
       <c r="N209" t="inlineStr"/>
       <c r="O209" t="n">
         <v>-29.5</v>
@@ -30139,9 +29591,7 @@
       <c r="L210" t="n">
         <v>-28.3</v>
       </c>
-      <c r="M210" t="n">
-        <v>3.6</v>
-      </c>
+      <c r="M210" t="inlineStr"/>
       <c r="N210" t="inlineStr"/>
       <c r="O210" t="n">
         <v>-29.8</v>
@@ -30283,9 +29733,7 @@
       <c r="L211" t="n">
         <v>19.8</v>
       </c>
-      <c r="M211" t="n">
-        <v>-11</v>
-      </c>
+      <c r="M211" t="inlineStr"/>
       <c r="N211" t="inlineStr"/>
       <c r="O211" t="n">
         <v>15.6</v>
@@ -30427,9 +29875,7 @@
       <c r="L212" t="n">
         <v>37.4</v>
       </c>
-      <c r="M212" t="n">
-        <v>-18.6</v>
-      </c>
+      <c r="M212" t="inlineStr"/>
       <c r="N212" t="inlineStr"/>
       <c r="O212" t="n">
         <v>31.2</v>
@@ -30571,9 +30017,7 @@
       <c r="L213" t="n">
         <v>73.3</v>
       </c>
-      <c r="M213" t="n">
-        <v>26.8</v>
-      </c>
+      <c r="M213" t="inlineStr"/>
       <c r="N213" t="inlineStr"/>
       <c r="O213" t="n">
         <v>67.09999999999999</v>
@@ -30719,9 +30163,7 @@
       <c r="L214" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="M214" t="n">
-        <v>-37.5</v>
-      </c>
+      <c r="M214" t="inlineStr"/>
       <c r="N214" t="inlineStr"/>
       <c r="O214" t="n">
         <v>4.4</v>
@@ -30869,9 +30311,7 @@
       <c r="L215" t="n">
         <v>-20.5</v>
       </c>
-      <c r="M215" t="n">
-        <v>-22.1</v>
-      </c>
+      <c r="M215" t="inlineStr"/>
       <c r="N215" t="inlineStr"/>
       <c r="O215" t="n">
         <v>-34.2</v>
@@ -31011,9 +30451,7 @@
       <c r="L216" t="n">
         <v>-15.1</v>
       </c>
-      <c r="M216" t="n">
-        <v>-51.6</v>
-      </c>
+      <c r="M216" t="inlineStr"/>
       <c r="N216" t="inlineStr"/>
       <c r="O216" t="n">
         <v>-13.4</v>
@@ -31163,9 +30601,7 @@
       <c r="L217" t="n">
         <v>22.6</v>
       </c>
-      <c r="M217" t="n">
-        <v>-10.7</v>
-      </c>
+      <c r="M217" t="inlineStr"/>
       <c r="N217" t="inlineStr"/>
       <c r="O217" t="n">
         <v>18.2</v>
@@ -31305,9 +30741,7 @@
       <c r="L218" t="n">
         <v>26.4</v>
       </c>
-      <c r="M218" t="n">
-        <v>-22.2</v>
-      </c>
+      <c r="M218" t="inlineStr"/>
       <c r="N218" t="inlineStr"/>
       <c r="O218" t="n">
         <v>14.8</v>
@@ -31451,9 +30885,7 @@
       <c r="L219" t="n">
         <v>-28.1</v>
       </c>
-      <c r="M219" t="n">
-        <v>-60.1</v>
-      </c>
+      <c r="M219" t="inlineStr"/>
       <c r="N219" t="inlineStr"/>
       <c r="O219" t="n">
         <v>-42.6</v>
@@ -31603,9 +31035,7 @@
       <c r="L220" t="n">
         <v>3.7</v>
       </c>
-      <c r="M220" t="n">
-        <v>-23.8</v>
-      </c>
+      <c r="M220" t="inlineStr"/>
       <c r="N220" t="inlineStr"/>
       <c r="O220" t="n">
         <v>-1.3</v>
@@ -31749,9 +31179,7 @@
       <c r="L221" t="n">
         <v>61.4</v>
       </c>
-      <c r="M221" t="n">
-        <v>12.8</v>
-      </c>
+      <c r="M221" t="inlineStr"/>
       <c r="N221" t="inlineStr"/>
       <c r="O221" t="n">
         <v>59.4</v>
@@ -31895,9 +31323,7 @@
       <c r="L222" t="n">
         <v>-8.199999999999999</v>
       </c>
-      <c r="M222" t="n">
-        <v>42.9</v>
-      </c>
+      <c r="M222" t="inlineStr"/>
       <c r="N222" t="inlineStr">
         <is>
           <t>WR40</t>
@@ -32047,9 +31473,7 @@
       <c r="L223" t="n">
         <v>1.4</v>
       </c>
-      <c r="M223" t="n">
-        <v>-33.9</v>
-      </c>
+      <c r="M223" t="inlineStr"/>
       <c r="N223" t="inlineStr"/>
       <c r="O223" t="n">
         <v>-1.3</v>
@@ -32199,9 +31623,7 @@
       <c r="L224" t="n">
         <v>1.6</v>
       </c>
-      <c r="M224" t="n">
-        <v>-34.6</v>
-      </c>
+      <c r="M224" t="inlineStr"/>
       <c r="N224" t="inlineStr"/>
       <c r="O224" t="n">
         <v>-7.1</v>
@@ -32351,9 +31773,7 @@
       <c r="L225" t="n">
         <v>-34.2</v>
       </c>
-      <c r="M225" t="n">
-        <v>-20.4</v>
-      </c>
+      <c r="M225" t="inlineStr"/>
       <c r="N225" t="inlineStr"/>
       <c r="O225" t="n">
         <v>-35.9</v>
@@ -32495,9 +31915,7 @@
       <c r="L226" t="n">
         <v>-11.8</v>
       </c>
-      <c r="M226" t="n">
-        <v>-36.6</v>
-      </c>
+      <c r="M226" t="inlineStr"/>
       <c r="N226" t="inlineStr"/>
       <c r="O226" t="n">
         <v>-15.2</v>
@@ -32647,9 +32065,7 @@
       <c r="L227" t="n">
         <v>-30.4</v>
       </c>
-      <c r="M227" t="n">
-        <v>-27.6</v>
-      </c>
+      <c r="M227" t="inlineStr"/>
       <c r="N227" t="inlineStr"/>
       <c r="O227" t="n">
         <v>-44.5</v>
@@ -32793,9 +32209,7 @@
       <c r="L228" t="n">
         <v>2.3</v>
       </c>
-      <c r="M228" t="n">
-        <v>-53.8</v>
-      </c>
+      <c r="M228" t="inlineStr"/>
       <c r="N228" t="inlineStr"/>
       <c r="O228" t="n">
         <v>-4.2</v>
@@ -32945,9 +32359,7 @@
       <c r="L229" t="n">
         <v>-24.2</v>
       </c>
-      <c r="M229" t="n">
-        <v>-8.1</v>
-      </c>
+      <c r="M229" t="inlineStr"/>
       <c r="N229" t="inlineStr"/>
       <c r="O229" t="n">
         <v>-37.2</v>
@@ -33093,9 +32505,7 @@
       <c r="L230" t="n">
         <v>-1.1</v>
       </c>
-      <c r="M230" t="n">
-        <v>-10.9</v>
-      </c>
+      <c r="M230" t="inlineStr"/>
       <c r="N230" t="inlineStr"/>
       <c r="O230" t="n">
         <v>-16.6</v>
@@ -33241,9 +32651,7 @@
       <c r="L231" t="n">
         <v>-18.3</v>
       </c>
-      <c r="M231" t="n">
-        <v>92.90000000000001</v>
-      </c>
+      <c r="M231" t="inlineStr"/>
       <c r="N231" t="inlineStr"/>
       <c r="O231" t="n">
         <v>-36.7</v>
@@ -33389,9 +32797,7 @@
       <c r="L232" t="n">
         <v>-28.4</v>
       </c>
-      <c r="M232" t="n">
-        <v>-23.5</v>
-      </c>
+      <c r="M232" t="inlineStr"/>
       <c r="N232" t="inlineStr"/>
       <c r="O232" t="n">
         <v>-36.4</v>
@@ -33541,9 +32947,7 @@
       <c r="L233" t="n">
         <v>-26.9</v>
       </c>
-      <c r="M233" t="n">
-        <v>38.1</v>
-      </c>
+      <c r="M233" t="inlineStr"/>
       <c r="N233" t="inlineStr"/>
       <c r="O233" t="n">
         <v>-37.1</v>
@@ -33685,9 +33089,7 @@
       <c r="L234" t="n">
         <v>-11.5</v>
       </c>
-      <c r="M234" t="n">
-        <v>29.4</v>
-      </c>
+      <c r="M234" t="inlineStr"/>
       <c r="N234" t="inlineStr"/>
       <c r="O234" t="n">
         <v>-33.1</v>
@@ -33755,7 +33157,7 @@
         <v>-11.15</v>
       </c>
       <c r="AL234" t="n">
-        <v>30.74</v>
+        <v>30.78</v>
       </c>
       <c r="AM234" t="n">
         <v>68</v>
@@ -33823,9 +33225,7 @@
       <c r="L235" t="n">
         <v>-22.5</v>
       </c>
-      <c r="M235" t="n">
-        <v>-39.6</v>
-      </c>
+      <c r="M235" t="inlineStr"/>
       <c r="N235" t="inlineStr"/>
       <c r="O235" t="n">
         <v>-25.8</v>
@@ -33900,7 +33300,7 @@
         <v>-26.62</v>
       </c>
       <c r="AK235" t="n">
-        <v>-27.61</v>
+        <v>-29.39</v>
       </c>
       <c r="AL235" t="n">
         <v>55.07</v>
@@ -33975,9 +33375,7 @@
       <c r="L236" t="n">
         <v>1.1</v>
       </c>
-      <c r="M236" t="n">
-        <v>10.6</v>
-      </c>
+      <c r="M236" t="inlineStr"/>
       <c r="N236" t="inlineStr"/>
       <c r="O236" t="n">
         <v>-22.3</v>
@@ -34269,9 +33667,7 @@
       <c r="L238" t="n">
         <v>-34.3</v>
       </c>
-      <c r="M238" t="n">
-        <v>-33.4</v>
-      </c>
+      <c r="M238" t="inlineStr"/>
       <c r="N238" t="inlineStr"/>
       <c r="O238" t="n">
         <v>-41.1</v>
@@ -34417,9 +33813,7 @@
       <c r="L239" t="n">
         <v>11.2</v>
       </c>
-      <c r="M239" t="n">
-        <v>-12.7</v>
-      </c>
+      <c r="M239" t="inlineStr"/>
       <c r="N239" t="inlineStr"/>
       <c r="O239" t="n">
         <v>10.3</v>
@@ -34713,9 +34107,7 @@
       <c r="L241" t="n">
         <v>-25.2</v>
       </c>
-      <c r="M241" t="n">
-        <v>-31.1</v>
-      </c>
+      <c r="M241" t="inlineStr"/>
       <c r="N241" t="inlineStr"/>
       <c r="O241" t="n">
         <v>-25.6</v>
@@ -34865,9 +34257,7 @@
       <c r="L242" t="n">
         <v>-29.2</v>
       </c>
-      <c r="M242" t="n">
-        <v>1.6</v>
-      </c>
+      <c r="M242" t="inlineStr"/>
       <c r="N242" t="inlineStr"/>
       <c r="O242" t="n">
         <v>-50.8</v>
@@ -35015,9 +34405,7 @@
       <c r="L243" t="n">
         <v>22.2</v>
       </c>
-      <c r="M243" t="n">
-        <v>-27.3</v>
-      </c>
+      <c r="M243" t="inlineStr"/>
       <c r="N243" t="inlineStr"/>
       <c r="O243" t="n">
         <v>20.3</v>
@@ -35161,9 +34549,7 @@
       <c r="L244" t="n">
         <v>7.4</v>
       </c>
-      <c r="M244" t="n">
-        <v>-13.4</v>
-      </c>
+      <c r="M244" t="inlineStr"/>
       <c r="N244" t="inlineStr"/>
       <c r="O244" t="n">
         <v>5</v>
@@ -35307,9 +34693,7 @@
       <c r="L245" t="n">
         <v>64.90000000000001</v>
       </c>
-      <c r="M245" t="n">
-        <v>37.6</v>
-      </c>
+      <c r="M245" t="inlineStr"/>
       <c r="N245" t="inlineStr"/>
       <c r="O245" t="n">
         <v>51.1</v>
@@ -35451,9 +34835,7 @@
       <c r="L246" t="n">
         <v>22.5</v>
       </c>
-      <c r="M246" t="n">
-        <v>8.699999999999999</v>
-      </c>
+      <c r="M246" t="inlineStr"/>
       <c r="N246" t="inlineStr"/>
       <c r="O246" t="n">
         <v>17.1</v>
@@ -35587,9 +34969,7 @@
       <c r="L247" t="n">
         <v>-28.7</v>
       </c>
-      <c r="M247" t="n">
-        <v>-6.5</v>
-      </c>
+      <c r="M247" t="inlineStr"/>
       <c r="N247" t="inlineStr"/>
       <c r="O247" t="n">
         <v>-39.4</v>
@@ -35731,9 +35111,7 @@
       <c r="L248" t="n">
         <v>3.4</v>
       </c>
-      <c r="M248" t="n">
-        <v>35.3</v>
-      </c>
+      <c r="M248" t="inlineStr"/>
       <c r="N248" t="inlineStr"/>
       <c r="O248" t="n">
         <v>-17.1</v>
@@ -35875,9 +35253,7 @@
       <c r="L249" t="n">
         <v>-30.2</v>
       </c>
-      <c r="M249" t="n">
-        <v>-51</v>
-      </c>
+      <c r="M249" t="inlineStr"/>
       <c r="N249" t="inlineStr"/>
       <c r="O249" t="n">
         <v>-33.9</v>
@@ -36027,9 +35403,7 @@
       <c r="L250" t="n">
         <v>-24.2</v>
       </c>
-      <c r="M250" t="n">
-        <v>-29.8</v>
-      </c>
+      <c r="M250" t="inlineStr"/>
       <c r="N250" t="inlineStr"/>
       <c r="O250" t="n">
         <v>-32.4</v>
@@ -36169,9 +35543,7 @@
       <c r="L251" t="n">
         <v>13.7</v>
       </c>
-      <c r="M251" t="n">
-        <v>-13.5</v>
-      </c>
+      <c r="M251" t="inlineStr"/>
       <c r="N251" t="inlineStr"/>
       <c r="O251" t="n">
         <v>-28.1</v>
@@ -36315,9 +35687,7 @@
       <c r="L252" t="n">
         <v>55.8</v>
       </c>
-      <c r="M252" t="n">
-        <v>6.5</v>
-      </c>
+      <c r="M252" t="inlineStr"/>
       <c r="N252" t="inlineStr"/>
       <c r="O252" t="n">
         <v>35.7</v>
@@ -36457,9 +35827,7 @@
       <c r="L253" t="n">
         <v>-20.1</v>
       </c>
-      <c r="M253" t="n">
-        <v>-32.1</v>
-      </c>
+      <c r="M253" t="inlineStr"/>
       <c r="N253" t="inlineStr"/>
       <c r="O253" t="n">
         <v>-21.7</v>
@@ -36607,9 +35975,7 @@
       <c r="L254" t="n">
         <v>-0.4</v>
       </c>
-      <c r="M254" t="n">
-        <v>9.699999999999999</v>
-      </c>
+      <c r="M254" t="inlineStr"/>
       <c r="N254" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -36763,9 +36129,7 @@
       <c r="L255" t="n">
         <v>58.8</v>
       </c>
-      <c r="M255" t="n">
-        <v>32.8</v>
-      </c>
+      <c r="M255" t="inlineStr"/>
       <c r="N255" t="inlineStr"/>
       <c r="O255" t="n">
         <v>44.2</v>
@@ -36911,9 +36275,7 @@
       <c r="L256" t="n">
         <v>28.6</v>
       </c>
-      <c r="M256" t="n">
-        <v>17.3</v>
-      </c>
+      <c r="M256" t="inlineStr"/>
       <c r="N256" t="inlineStr"/>
       <c r="O256" t="n">
         <v>21.9</v>
@@ -37055,9 +36417,7 @@
       <c r="L257" t="n">
         <v>69.59999999999999</v>
       </c>
-      <c r="M257" t="n">
-        <v>34.5</v>
-      </c>
+      <c r="M257" t="inlineStr"/>
       <c r="N257" t="inlineStr"/>
       <c r="O257" t="n">
         <v>31.9</v>
@@ -37203,9 +36563,7 @@
       <c r="L258" t="n">
         <v>25.2</v>
       </c>
-      <c r="M258" t="n">
-        <v>-19.9</v>
-      </c>
+      <c r="M258" t="inlineStr"/>
       <c r="N258" t="inlineStr"/>
       <c r="O258" t="n">
         <v>23.7</v>
@@ -37276,7 +36634,7 @@
         <v>-24.7</v>
       </c>
       <c r="AK258" t="n">
-        <v>-25.79</v>
+        <v>-25.8</v>
       </c>
       <c r="AL258" t="n">
         <v>10.86</v>
@@ -37351,9 +36709,7 @@
       <c r="L259" t="n">
         <v>-5.5</v>
       </c>
-      <c r="M259" t="n">
-        <v>-23.4</v>
-      </c>
+      <c r="M259" t="inlineStr"/>
       <c r="N259" t="inlineStr">
         <is>
           <t>WR30</t>
@@ -37507,9 +36863,7 @@
       <c r="L260" t="n">
         <v>15.6</v>
       </c>
-      <c r="M260" t="n">
-        <v>-43.5</v>
-      </c>
+      <c r="M260" t="inlineStr"/>
       <c r="N260" t="inlineStr"/>
       <c r="O260" t="n">
         <v>13.1</v>
@@ -37582,7 +36936,7 @@
         <v>-49.16</v>
       </c>
       <c r="AK260" t="n">
-        <v>-49.74</v>
+        <v>-49.75</v>
       </c>
       <c r="AL260" t="n">
         <v>8.56</v>
@@ -37657,9 +37011,7 @@
       <c r="L261" t="n">
         <v>-29.9</v>
       </c>
-      <c r="M261" t="n">
-        <v>-10.5</v>
-      </c>
+      <c r="M261" t="inlineStr"/>
       <c r="N261" t="inlineStr"/>
       <c r="O261" t="n">
         <v>-41.6</v>
@@ -37805,9 +37157,7 @@
       <c r="L262" t="n">
         <v>39.4</v>
       </c>
-      <c r="M262" t="n">
-        <v>45.5</v>
-      </c>
+      <c r="M262" t="inlineStr"/>
       <c r="N262" t="inlineStr"/>
       <c r="O262" t="n">
         <v>13.8</v>
@@ -37949,9 +37299,7 @@
       <c r="L263" t="n">
         <v>-4.2</v>
       </c>
-      <c r="M263" t="n">
-        <v>-14.5</v>
-      </c>
+      <c r="M263" t="inlineStr"/>
       <c r="N263" t="inlineStr">
         <is>
           <t>WR30</t>
@@ -38099,9 +37447,7 @@
       <c r="L264" t="n">
         <v>4.1</v>
       </c>
-      <c r="M264" t="n">
-        <v>4.9</v>
-      </c>
+      <c r="M264" t="inlineStr"/>
       <c r="N264" t="inlineStr"/>
       <c r="O264" t="n">
         <v>-6.3</v>
@@ -38243,9 +37589,7 @@
       <c r="L265" t="n">
         <v>-21.7</v>
       </c>
-      <c r="M265" t="n">
-        <v>36.4</v>
-      </c>
+      <c r="M265" t="inlineStr"/>
       <c r="N265" t="inlineStr"/>
       <c r="O265" t="n">
         <v>-33.7</v>
@@ -38387,9 +37731,7 @@
       <c r="L266" t="n">
         <v>-38.3</v>
       </c>
-      <c r="M266" t="n">
-        <v>6.9</v>
-      </c>
+      <c r="M266" t="inlineStr"/>
       <c r="N266" t="inlineStr"/>
       <c r="O266" t="n">
         <v>-48.2</v>
@@ -38535,9 +37877,7 @@
       <c r="L267" t="n">
         <v>-0.4</v>
       </c>
-      <c r="M267" t="n">
-        <v>-20.4</v>
-      </c>
+      <c r="M267" t="inlineStr"/>
       <c r="N267" t="inlineStr"/>
       <c r="O267" t="n">
         <v>-14.2</v>
@@ -38687,9 +38027,7 @@
       <c r="L268" t="n">
         <v>-12</v>
       </c>
-      <c r="M268" t="n">
-        <v>-15.1</v>
-      </c>
+      <c r="M268" t="inlineStr"/>
       <c r="N268" t="inlineStr"/>
       <c r="O268" t="n">
         <v>-24.6</v>
@@ -38835,9 +38173,7 @@
       <c r="L269" t="n">
         <v>-19.7</v>
       </c>
-      <c r="M269" t="n">
-        <v>-38.9</v>
-      </c>
+      <c r="M269" t="inlineStr"/>
       <c r="N269" t="inlineStr"/>
       <c r="O269" t="n">
         <v>-21.6</v>
@@ -38981,9 +38317,7 @@
       <c r="L270" t="n">
         <v>-6.4</v>
       </c>
-      <c r="M270" t="n">
-        <v>23.9</v>
-      </c>
+      <c r="M270" t="inlineStr"/>
       <c r="N270" t="inlineStr"/>
       <c r="O270" t="n">
         <v>-12.3</v>
@@ -39125,9 +38459,7 @@
       <c r="L271" t="n">
         <v>4.6</v>
       </c>
-      <c r="M271" t="n">
-        <v>2.8</v>
-      </c>
+      <c r="M271" t="inlineStr"/>
       <c r="N271" t="inlineStr"/>
       <c r="O271" t="n">
         <v>1.5</v>
@@ -39273,9 +38605,7 @@
       <c r="L272" t="n">
         <v>-0.2</v>
       </c>
-      <c r="M272" t="n">
-        <v>70.2</v>
-      </c>
+      <c r="M272" t="inlineStr"/>
       <c r="N272" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -39357,7 +38687,7 @@
         <v>-6.51</v>
       </c>
       <c r="AL272" t="n">
-        <v>87.08</v>
+        <v>87.12</v>
       </c>
       <c r="AM272" t="n">
         <v>68</v>
@@ -39425,9 +38755,7 @@
       <c r="L273" t="n">
         <v>0.9</v>
       </c>
-      <c r="M273" t="n">
-        <v>3.4</v>
-      </c>
+      <c r="M273" t="inlineStr"/>
       <c r="N273" t="inlineStr"/>
       <c r="O273" t="n">
         <v>-29.6</v>
@@ -39571,9 +38899,7 @@
       <c r="L274" t="n">
         <v>16.5</v>
       </c>
-      <c r="M274" t="n">
-        <v>-18.9</v>
-      </c>
+      <c r="M274" t="inlineStr"/>
       <c r="N274" t="inlineStr"/>
       <c r="O274" t="n">
         <v>11.6</v>
@@ -39717,9 +39043,7 @@
       <c r="L275" t="n">
         <v>-9.6</v>
       </c>
-      <c r="M275" t="n">
-        <v>24.7</v>
-      </c>
+      <c r="M275" t="inlineStr"/>
       <c r="N275" t="inlineStr">
         <is>
           <t>WR30</t>
@@ -39869,9 +39193,7 @@
       <c r="L276" t="n">
         <v>-11.3</v>
       </c>
-      <c r="M276" t="n">
-        <v>-27.4</v>
-      </c>
+      <c r="M276" t="inlineStr"/>
       <c r="N276" t="inlineStr"/>
       <c r="O276" t="n">
         <v>-25.4</v>
@@ -40015,9 +39337,7 @@
       <c r="L277" t="n">
         <v>14.9</v>
       </c>
-      <c r="M277" t="n">
-        <v>-11.1</v>
-      </c>
+      <c r="M277" t="inlineStr"/>
       <c r="N277" t="inlineStr"/>
       <c r="O277" t="n">
         <v>14.1</v>
@@ -40163,9 +39483,7 @@
       <c r="L278" t="n">
         <v>-32.8</v>
       </c>
-      <c r="M278" t="n">
-        <v>-26.1</v>
-      </c>
+      <c r="M278" t="inlineStr"/>
       <c r="N278" t="inlineStr"/>
       <c r="O278" t="n">
         <v>-50.4</v>
@@ -40313,9 +39631,7 @@
       <c r="L279" t="n">
         <v>-40.3</v>
       </c>
-      <c r="M279" t="n">
-        <v>-42.3</v>
-      </c>
+      <c r="M279" t="inlineStr"/>
       <c r="N279" t="inlineStr"/>
       <c r="O279" t="n">
         <v>-41.9</v>
@@ -40465,9 +39781,7 @@
       <c r="L280" t="n">
         <v>-48.5</v>
       </c>
-      <c r="M280" t="n">
-        <v>-51.8</v>
-      </c>
+      <c r="M280" t="inlineStr"/>
       <c r="N280" t="inlineStr"/>
       <c r="O280" t="n">
         <v>-48.8</v>
@@ -40617,9 +39931,7 @@
       <c r="L281" t="n">
         <v>-26.7</v>
       </c>
-      <c r="M281" t="n">
-        <v>-38.8</v>
-      </c>
+      <c r="M281" t="inlineStr"/>
       <c r="N281" t="inlineStr"/>
       <c r="O281" t="n">
         <v>-36.4</v>
@@ -40763,9 +40075,7 @@
       <c r="L282" t="n">
         <v>-0.5</v>
       </c>
-      <c r="M282" t="n">
-        <v>63.1</v>
-      </c>
+      <c r="M282" t="inlineStr"/>
       <c r="N282" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -40915,9 +40225,7 @@
       <c r="L283" t="n">
         <v>7.1</v>
       </c>
-      <c r="M283" t="n">
-        <v>56.4</v>
-      </c>
+      <c r="M283" t="inlineStr"/>
       <c r="N283" t="inlineStr"/>
       <c r="O283" t="n">
         <v>-17.9</v>
@@ -41063,9 +40371,7 @@
       <c r="L284" t="n">
         <v>7.6</v>
       </c>
-      <c r="M284" t="n">
-        <v>15.5</v>
-      </c>
+      <c r="M284" t="inlineStr"/>
       <c r="N284" t="inlineStr"/>
       <c r="O284" t="n">
         <v>-26.5</v>
@@ -41207,9 +40513,7 @@
       <c r="L285" t="n">
         <v>-2.1</v>
       </c>
-      <c r="M285" t="n">
-        <v>13.5</v>
-      </c>
+      <c r="M285" t="inlineStr"/>
       <c r="N285" t="inlineStr">
         <is>
           <t>WR30</t>
@@ -41359,9 +40663,7 @@
       <c r="L286" t="n">
         <v>-9</v>
       </c>
-      <c r="M286" t="n">
-        <v>-2.4</v>
-      </c>
+      <c r="M286" t="inlineStr"/>
       <c r="N286" t="inlineStr"/>
       <c r="O286" t="n">
         <v>-18</v>
@@ -41509,9 +40811,7 @@
       <c r="L287" t="n">
         <v>-42.2</v>
       </c>
-      <c r="M287" t="n">
-        <v>-38.8</v>
-      </c>
+      <c r="M287" t="inlineStr"/>
       <c r="N287" t="inlineStr"/>
       <c r="O287" t="n">
         <v>-46.7</v>
@@ -41586,7 +40886,7 @@
         <v>-17.46</v>
       </c>
       <c r="AK287" t="n">
-        <v>-19.88</v>
+        <v>-19.87</v>
       </c>
       <c r="AL287" t="n">
         <v>45.74</v>
@@ -41661,9 +40961,7 @@
       <c r="L288" t="n">
         <v>-3.4</v>
       </c>
-      <c r="M288" t="n">
-        <v>-24</v>
-      </c>
+      <c r="M288" t="inlineStr"/>
       <c r="N288" t="inlineStr"/>
       <c r="O288" t="n">
         <v>-10.1</v>
@@ -41813,9 +41111,7 @@
       <c r="L289" t="n">
         <v>2.9</v>
       </c>
-      <c r="M289" t="n">
-        <v>-8.699999999999999</v>
-      </c>
+      <c r="M289" t="inlineStr"/>
       <c r="N289" t="inlineStr"/>
       <c r="O289" t="n">
         <v>-0.1</v>
@@ -41965,9 +41261,7 @@
       <c r="L290" t="n">
         <v>-8.800000000000001</v>
       </c>
-      <c r="M290" t="n">
-        <v>-8.199999999999999</v>
-      </c>
+      <c r="M290" t="inlineStr"/>
       <c r="N290" t="inlineStr"/>
       <c r="O290" t="n">
         <v>-10.8</v>
@@ -42109,9 +41403,7 @@
       <c r="L291" t="n">
         <v>0.2</v>
       </c>
-      <c r="M291" t="n">
-        <v>-0.2</v>
-      </c>
+      <c r="M291" t="inlineStr"/>
       <c r="N291" t="inlineStr"/>
       <c r="O291" t="n">
         <v>-7.8</v>
@@ -42137,9 +41429,7 @@
       <c r="V291" t="b">
         <v>0</v>
       </c>
-      <c r="W291" s="1" t="n">
-        <v>46317</v>
-      </c>
+      <c r="W291" t="inlineStr"/>
       <c r="X291" s="1" t="n">
         <v>46224</v>
       </c>
@@ -42253,9 +41543,7 @@
       <c r="L292" t="n">
         <v>21.4</v>
       </c>
-      <c r="M292" t="n">
-        <v>-0.5</v>
-      </c>
+      <c r="M292" t="inlineStr"/>
       <c r="N292" t="inlineStr"/>
       <c r="O292" t="n">
         <v>19.8</v>
@@ -42381,29 +41669,27 @@
       </c>
       <c r="G293" t="inlineStr"/>
       <c r="H293" t="n">
-        <v>21.4</v>
+        <v>22</v>
       </c>
       <c r="I293" t="n">
-        <v>6.91</v>
+        <v>6.37</v>
       </c>
       <c r="J293" t="n">
-        <v>20.57</v>
+        <v>19.96</v>
       </c>
       <c r="K293" t="n">
-        <v>-1.07</v>
+        <v>-1.56</v>
       </c>
       <c r="L293" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="M293" t="n">
-        <v>34.8</v>
-      </c>
+        <v>14.2</v>
+      </c>
+      <c r="M293" t="inlineStr"/>
       <c r="N293" t="inlineStr"/>
       <c r="O293" t="n">
         <v>6.5</v>
       </c>
       <c r="P293" t="n">
-        <v>30.35</v>
+        <v>30.2</v>
       </c>
       <c r="Q293" t="inlineStr">
         <is>
@@ -42438,16 +41724,16 @@
         </is>
       </c>
       <c r="AA293" t="n">
-        <v>9.32</v>
+        <v>8.76</v>
       </c>
       <c r="AB293" t="n">
-        <v>20.62</v>
+        <v>20.02</v>
       </c>
       <c r="AC293" t="n">
-        <v>-0.92</v>
+        <v>-1.42</v>
       </c>
       <c r="AD293" t="n">
-        <v>-1.07</v>
+        <v>-1.56</v>
       </c>
       <c r="AE293" t="n">
         <v>34.49</v>
@@ -42468,10 +41754,10 @@
         <v>43.36</v>
       </c>
       <c r="AK293" t="n">
-        <v>-1.07</v>
+        <v>-1.56</v>
       </c>
       <c r="AL293" t="n">
-        <v>46.43</v>
+        <v>45.69</v>
       </c>
       <c r="AM293" t="n">
         <v>68</v>
@@ -42480,7 +41766,7 @@
         <v>66</v>
       </c>
       <c r="AO293" t="n">
-        <v>39.21</v>
+        <v>38.51</v>
       </c>
       <c r="AP293" t="inlineStr"/>
       <c r="AQ293" t="n">
@@ -42539,9 +41825,7 @@
       <c r="L294" t="n">
         <v>-8.6</v>
       </c>
-      <c r="M294" t="n">
-        <v>-21.4</v>
-      </c>
+      <c r="M294" t="inlineStr"/>
       <c r="N294" t="inlineStr"/>
       <c r="O294" t="n">
         <v>-12.7</v>
@@ -42687,9 +41971,7 @@
       <c r="L295" t="n">
         <v>23.7</v>
       </c>
-      <c r="M295" t="n">
-        <v>-12.7</v>
-      </c>
+      <c r="M295" t="inlineStr"/>
       <c r="N295" t="inlineStr"/>
       <c r="O295" t="n">
         <v>20.2</v>
@@ -42833,9 +42115,7 @@
       <c r="L296" t="n">
         <v>-43.3</v>
       </c>
-      <c r="M296" t="n">
-        <v>7.7</v>
-      </c>
+      <c r="M296" t="inlineStr"/>
       <c r="N296" t="inlineStr"/>
       <c r="O296" t="n">
         <v>-55.7</v>
@@ -42981,9 +42261,7 @@
       <c r="L297" t="n">
         <v>29.3</v>
       </c>
-      <c r="M297" t="n">
-        <v>-7.9</v>
-      </c>
+      <c r="M297" t="inlineStr"/>
       <c r="N297" t="inlineStr"/>
       <c r="O297" t="n">
         <v>5.2</v>
@@ -43127,9 +42405,7 @@
       <c r="L298" t="n">
         <v>-0.9</v>
       </c>
-      <c r="M298" t="n">
-        <v>-8.699999999999999</v>
-      </c>
+      <c r="M298" t="inlineStr"/>
       <c r="N298" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -43279,9 +42555,7 @@
       <c r="L299" t="n">
         <v>23</v>
       </c>
-      <c r="M299" t="n">
-        <v>-24.8</v>
-      </c>
+      <c r="M299" t="inlineStr"/>
       <c r="N299" t="inlineStr"/>
       <c r="O299" t="n">
         <v>5.7</v>
@@ -43421,9 +42695,7 @@
       <c r="L300" t="n">
         <v>12.2</v>
       </c>
-      <c r="M300" t="n">
-        <v>-10.6</v>
-      </c>
+      <c r="M300" t="inlineStr"/>
       <c r="N300" t="inlineStr"/>
       <c r="O300" t="n">
         <v>8.800000000000001</v>
@@ -43569,9 +42841,7 @@
       <c r="L301" t="n">
         <v>45.6</v>
       </c>
-      <c r="M301" t="n">
-        <v>11.4</v>
-      </c>
+      <c r="M301" t="inlineStr"/>
       <c r="N301" t="inlineStr"/>
       <c r="O301" t="n">
         <v>25</v>
@@ -43715,9 +42985,7 @@
       <c r="L302" t="n">
         <v>-20</v>
       </c>
-      <c r="M302" t="n">
-        <v>-18.5</v>
-      </c>
+      <c r="M302" t="inlineStr"/>
       <c r="N302" t="inlineStr"/>
       <c r="O302" t="n">
         <v>-33</v>
@@ -43867,9 +43135,7 @@
       <c r="L303" t="n">
         <v>56.3</v>
       </c>
-      <c r="M303" t="n">
-        <v>46</v>
-      </c>
+      <c r="M303" t="inlineStr"/>
       <c r="N303" t="inlineStr"/>
       <c r="O303" t="n">
         <v>34.3</v>
@@ -44019,9 +43285,7 @@
       <c r="L304" t="n">
         <v>-9</v>
       </c>
-      <c r="M304" t="n">
-        <v>26.6</v>
-      </c>
+      <c r="M304" t="inlineStr"/>
       <c r="N304" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -44171,9 +43435,7 @@
       <c r="L305" t="n">
         <v>-25.3</v>
       </c>
-      <c r="M305" t="n">
-        <v>43.4</v>
-      </c>
+      <c r="M305" t="inlineStr"/>
       <c r="N305" t="inlineStr"/>
       <c r="O305" t="n">
         <v>-43.3</v>
@@ -44251,7 +43513,7 @@
         <v>-5.49</v>
       </c>
       <c r="AL305" t="n">
-        <v>63.66</v>
+        <v>63.71</v>
       </c>
       <c r="AM305" t="n">
         <v>68</v>
@@ -44319,9 +43581,7 @@
       <c r="L306" t="n">
         <v>-4.1</v>
       </c>
-      <c r="M306" t="n">
-        <v>-17.9</v>
-      </c>
+      <c r="M306" t="inlineStr"/>
       <c r="N306" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -44471,7 +43731,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>298 (+7 pending)</t>
+          <t>298 (+0 pending)</t>
         </is>
       </c>
     </row>
@@ -44495,7 +43755,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>$48,992.72  (-2.74% price-weighted)</t>
+          <t>$48,992.73  (-2.74% price-weighted)</t>
         </is>
       </c>
     </row>
@@ -44613,13 +43873,13 @@
         <v>0.98</v>
       </c>
       <c r="E12" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="F12" t="n">
         <v>52.36</v>
       </c>
       <c r="G12" t="n">
-        <v>-14.03</v>
+        <v>-14.04</v>
       </c>
     </row>
     <row r="13">
@@ -44644,7 +43904,7 @@
         <v>31.58</v>
       </c>
       <c r="G13" t="n">
-        <v>-21.37</v>
+        <v>-21.39</v>
       </c>
     </row>
     <row r="14">
@@ -44754,10 +44014,10 @@
         <v>-1.9</v>
       </c>
       <c r="F18" t="n">
-        <v>3.4</v>
+        <v>3.36</v>
       </c>
       <c r="G18" t="n">
-        <v>-13.61</v>
+        <v>-13.63</v>
       </c>
     </row>
     <row r="19">
@@ -44807,7 +44067,7 @@
         <v>3.83</v>
       </c>
       <c r="G20" t="n">
-        <v>-16.37</v>
+        <v>-16.39</v>
       </c>
     </row>
     <row r="21">
@@ -44913,19 +44173,19 @@
         <v>34</v>
       </c>
       <c r="C26" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="D26" t="n">
         <v>59</v>
       </c>
       <c r="E26" t="n">
-        <v>4.03</v>
+        <v>4.01</v>
       </c>
       <c r="F26" t="n">
         <v>59</v>
       </c>
       <c r="G26" t="n">
-        <v>-8.66</v>
+        <v>-8.67</v>
       </c>
     </row>
     <row r="27">

--- a/sts_ml_paper_tracker.xlsx
+++ b/sts_ml_paper_tracker.xlsx
@@ -886,7 +886,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -900,22 +900,30 @@
       <c r="G4" t="n">
         <v>-9.800000000000001</v>
       </c>
-      <c r="H4" t="inlineStr"/>
+      <c r="H4" t="n">
+        <v>-13.6</v>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="n">
+        <v>-2.32</v>
+      </c>
       <c r="L4" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="M4" t="inlineStr"/>
+        <v>2.8</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.8</v>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="P4" t="inlineStr"/>
+        <v>1.8</v>
+      </c>
+      <c r="P4" t="n">
+        <v>252.5</v>
+      </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -923,35 +931,73 @@
           <t>RE-QUAL D200G 2026-10-22</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
+      <c r="S4" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="T4" t="n">
+        <v>-11.96</v>
+      </c>
+      <c r="U4" t="n">
+        <v>56</v>
+      </c>
+      <c r="V4" t="b">
+        <v>0</v>
+      </c>
+      <c r="W4" s="1" t="n">
+        <v>46329</v>
+      </c>
       <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
       <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
+      <c r="AA4" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>2.83</v>
+      </c>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr"/>
+      <c r="AE4" t="n">
+        <v>259.53</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>259.53</v>
+      </c>
       <c r="AH4" t="n">
-        <v>257.8200073242188</v>
-      </c>
-      <c r="AI4" t="inlineStr"/>
-      <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr"/>
-      <c r="AM4" t="inlineStr"/>
-      <c r="AN4" t="inlineStr"/>
+        <v>257.16</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>257.16</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>-0.91</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>-2.32</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0</v>
+      </c>
       <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="inlineStr"/>
-      <c r="AQ4" t="inlineStr"/>
+      <c r="AQ4" t="n">
+        <v>0.01</v>
+      </c>
       <c r="AR4" t="inlineStr"/>
-      <c r="AS4" t="inlineStr"/>
+      <c r="AS4" t="n">
+        <v>-0.92</v>
+      </c>
       <c r="AT4" t="inlineStr"/>
     </row>
     <row r="5">
@@ -1913,7 +1959,7 @@
         <v>-5.8</v>
       </c>
       <c r="H12" t="n">
-        <v>-14.5</v>
+        <v>-15.7</v>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
@@ -1924,7 +1970,7 @@
         <v>-0</v>
       </c>
       <c r="M12" t="n">
-        <v>-6.9</v>
+        <v>-7</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="n">
@@ -1981,13 +2027,13 @@
         <v>225.01</v>
       </c>
       <c r="AH12" t="n">
-        <v>210.1</v>
+        <v>210.33</v>
       </c>
       <c r="AI12" t="n">
-        <v>210.1</v>
+        <v>210.33</v>
       </c>
       <c r="AJ12" t="n">
-        <v>-6.63</v>
+        <v>-6.53</v>
       </c>
       <c r="AK12" t="n">
         <v>-7.43</v>
@@ -1996,7 +2042,7 @@
         <v>1.75</v>
       </c>
       <c r="AM12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN12" t="n">
         <v>0</v>
@@ -2004,11 +2050,11 @@
       <c r="AO12" t="inlineStr"/>
       <c r="AP12" t="inlineStr"/>
       <c r="AQ12" t="n">
-        <v>-0.93</v>
+        <v>-1.45</v>
       </c>
       <c r="AR12" t="inlineStr"/>
       <c r="AS12" t="n">
-        <v>-5.69</v>
+        <v>-5.07</v>
       </c>
       <c r="AT12" t="inlineStr"/>
     </row>
@@ -3121,7 +3167,7 @@
         <v>-8.800000000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>-5.1</v>
+        <v>-5.4</v>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
@@ -3132,7 +3178,7 @@
         <v>-8.4</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1</v>
+        <v>-1.3</v>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="n">
@@ -3170,7 +3216,7 @@
         <v>46310</v>
       </c>
       <c r="Y21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="n">
@@ -3193,13 +3239,13 @@
         <v>13.84</v>
       </c>
       <c r="AH21" t="n">
-        <v>15.07</v>
+        <v>14.86</v>
       </c>
       <c r="AI21" t="n">
-        <v>15.07</v>
+        <v>14.86</v>
       </c>
       <c r="AJ21" t="n">
-        <v>8.890000000000001</v>
+        <v>7.37</v>
       </c>
       <c r="AK21" t="n">
         <v>-1.66</v>
@@ -3208,7 +3254,7 @@
         <v>9.470000000000001</v>
       </c>
       <c r="AM21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AN21" t="n">
         <v>6</v>
@@ -3216,11 +3262,11 @@
       <c r="AO21" t="inlineStr"/>
       <c r="AP21" t="inlineStr"/>
       <c r="AQ21" t="n">
-        <v>-1.41</v>
+        <v>-1.93</v>
       </c>
       <c r="AR21" t="inlineStr"/>
       <c r="AS21" t="n">
-        <v>10.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AT21" t="inlineStr"/>
     </row>
@@ -4497,7 +4543,7 @@
         <v>14.7</v>
       </c>
       <c r="H31" t="n">
-        <v>45.6</v>
+        <v>36</v>
       </c>
       <c r="I31" t="n">
         <v>22.36</v>
@@ -4510,7 +4556,7 @@
         <v>2.2</v>
       </c>
       <c r="M31" t="n">
-        <v>37</v>
+        <v>32.1</v>
       </c>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="n">
@@ -4548,7 +4594,7 @@
         <v>46303</v>
       </c>
       <c r="Y31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z31" t="inlineStr"/>
       <c r="AA31" t="n">
@@ -4573,13 +4619,13 @@
         <v>195.43</v>
       </c>
       <c r="AH31" t="n">
-        <v>258.74</v>
+        <v>249.37</v>
       </c>
       <c r="AI31" t="n">
-        <v>258.74</v>
+        <v>249.37</v>
       </c>
       <c r="AJ31" t="n">
-        <v>32.4</v>
+        <v>27.6</v>
       </c>
       <c r="AK31" t="n">
         <v>-2.24</v>
@@ -4588,7 +4634,7 @@
         <v>32.73</v>
       </c>
       <c r="AM31" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AN31" t="n">
         <v>12</v>
@@ -4596,11 +4642,11 @@
       <c r="AO31" t="inlineStr"/>
       <c r="AP31" t="inlineStr"/>
       <c r="AQ31" t="n">
-        <v>-1.82</v>
+        <v>-2.34</v>
       </c>
       <c r="AR31" t="inlineStr"/>
       <c r="AS31" t="n">
-        <v>34.22</v>
+        <v>29.94</v>
       </c>
       <c r="AT31" t="inlineStr"/>
     </row>
@@ -5317,7 +5363,7 @@
         <v>2.8</v>
       </c>
       <c r="H37" t="n">
-        <v>4.3</v>
+        <v>9.9</v>
       </c>
       <c r="I37" t="n">
         <v>2.42</v>
@@ -5330,7 +5376,7 @@
         <v>-8.800000000000001</v>
       </c>
       <c r="M37" t="n">
-        <v>-2.4</v>
+        <v>-2.1</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>
@@ -5372,7 +5418,7 @@
         <v>46295</v>
       </c>
       <c r="Y37" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Z37" t="inlineStr"/>
       <c r="AA37" t="n">
@@ -5395,13 +5441,13 @@
         <v>17.36</v>
       </c>
       <c r="AH37" t="n">
-        <v>17.89</v>
+        <v>17.91</v>
       </c>
       <c r="AI37" t="n">
-        <v>17.89</v>
+        <v>17.91</v>
       </c>
       <c r="AJ37" t="n">
-        <v>3.05</v>
+        <v>3.17</v>
       </c>
       <c r="AK37" t="n">
         <v>-1.61</v>
@@ -5410,7 +5456,7 @@
         <v>6.86</v>
       </c>
       <c r="AM37" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AN37" t="n">
         <v>1</v>
@@ -5418,11 +5464,11 @@
       <c r="AO37" t="inlineStr"/>
       <c r="AP37" t="inlineStr"/>
       <c r="AQ37" t="n">
-        <v>-0.37</v>
+        <v>-0.89</v>
       </c>
       <c r="AR37" t="inlineStr"/>
       <c r="AS37" t="n">
-        <v>3.43</v>
+        <v>4.06</v>
       </c>
       <c r="AT37" t="inlineStr"/>
     </row>
@@ -6593,7 +6639,7 @@
         <v>-0.9</v>
       </c>
       <c r="H46" t="n">
-        <v>-13.2</v>
+        <v>-12.5</v>
       </c>
       <c r="I46" t="n">
         <v>-3.75</v>
@@ -6608,7 +6654,7 @@
         <v>-12.9</v>
       </c>
       <c r="M46" t="n">
-        <v>-20</v>
+        <v>-21.6</v>
       </c>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="n">
@@ -6665,22 +6711,22 @@
         <v>115.12</v>
       </c>
       <c r="AH46" t="n">
-        <v>101.82</v>
+        <v>99.64</v>
       </c>
       <c r="AI46" t="n">
-        <v>101.82</v>
+        <v>99.64</v>
       </c>
       <c r="AJ46" t="n">
-        <v>-11.55</v>
+        <v>-13.45</v>
       </c>
       <c r="AK46" t="n">
-        <v>-12.52</v>
+        <v>-13.6</v>
       </c>
       <c r="AL46" t="n">
         <v>4.59</v>
       </c>
       <c r="AM46" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AN46" t="n">
         <v>1</v>
@@ -6688,13 +6734,17 @@
       <c r="AO46" t="inlineStr"/>
       <c r="AP46" t="inlineStr"/>
       <c r="AQ46" t="n">
-        <v>-0.3</v>
+        <v>-0.82</v>
       </c>
       <c r="AR46" t="inlineStr"/>
       <c r="AS46" t="n">
-        <v>-11.25</v>
-      </c>
-      <c r="AT46" t="inlineStr"/>
+        <v>-12.63</v>
+      </c>
+      <c r="AT46" t="inlineStr">
+        <is>
+          <t>dipping</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
@@ -6727,7 +6777,7 @@
         <v>20.7</v>
       </c>
       <c r="H47" t="n">
-        <v>-4.7</v>
+        <v>-4.9</v>
       </c>
       <c r="I47" t="n">
         <v>-1.49</v>
@@ -6742,7 +6792,7 @@
         <v>17.3</v>
       </c>
       <c r="M47" t="n">
-        <v>20.5</v>
+        <v>17.8</v>
       </c>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="n">
@@ -6780,7 +6830,7 @@
         <v>46311</v>
       </c>
       <c r="Y47" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
@@ -6807,13 +6857,13 @@
         <v>166.56</v>
       </c>
       <c r="AH47" t="n">
-        <v>175.76</v>
+        <v>172.01</v>
       </c>
       <c r="AI47" t="n">
-        <v>175.76</v>
+        <v>172.01</v>
       </c>
       <c r="AJ47" t="n">
-        <v>5.52</v>
+        <v>3.27</v>
       </c>
       <c r="AK47" t="n">
         <v>-10.54</v>
@@ -6822,7 +6872,7 @@
         <v>7.55</v>
       </c>
       <c r="AM47" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AN47" t="n">
         <v>21</v>
@@ -6830,11 +6880,11 @@
       <c r="AO47" t="inlineStr"/>
       <c r="AP47" t="inlineStr"/>
       <c r="AQ47" t="n">
-        <v>-0.3</v>
+        <v>-0.82</v>
       </c>
       <c r="AR47" t="inlineStr"/>
       <c r="AS47" t="n">
-        <v>5.82</v>
+        <v>4.09</v>
       </c>
       <c r="AT47" t="inlineStr"/>
     </row>
@@ -7431,7 +7481,7 @@
         <v>31.3</v>
       </c>
       <c r="H52" t="n">
-        <v>25.9</v>
+        <v>22.5</v>
       </c>
       <c r="I52" t="n">
         <v>1.47</v>
@@ -7446,7 +7496,7 @@
         <v>3.5</v>
       </c>
       <c r="M52" t="n">
-        <v>19.3</v>
+        <v>23.6</v>
       </c>
       <c r="N52" t="inlineStr"/>
       <c r="O52" t="n">
@@ -7484,7 +7534,7 @@
         <v>46301</v>
       </c>
       <c r="Y52" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
@@ -7513,13 +7563,13 @@
         <v>10.85</v>
       </c>
       <c r="AH52" t="n">
-        <v>12.03</v>
+        <v>12.46</v>
       </c>
       <c r="AI52" t="n">
-        <v>12.03</v>
+        <v>12.46</v>
       </c>
       <c r="AJ52" t="n">
-        <v>10.88</v>
+        <v>14.84</v>
       </c>
       <c r="AK52" t="n">
         <v>-5.99</v>
@@ -7528,7 +7578,7 @@
         <v>18.71</v>
       </c>
       <c r="AM52" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AN52" t="n">
         <v>16</v>
@@ -7536,11 +7586,11 @@
       <c r="AO52" t="inlineStr"/>
       <c r="AP52" t="inlineStr"/>
       <c r="AQ52" t="n">
-        <v>0.35</v>
+        <v>-0.18</v>
       </c>
       <c r="AR52" t="inlineStr"/>
       <c r="AS52" t="n">
-        <v>10.53</v>
+        <v>15.01</v>
       </c>
       <c r="AT52" t="inlineStr"/>
     </row>
@@ -8279,7 +8329,7 @@
         <v>4.6</v>
       </c>
       <c r="H58" t="n">
-        <v>1.9</v>
+        <v>-4.9</v>
       </c>
       <c r="I58" t="n">
         <v>-3.41</v>
@@ -8294,7 +8344,7 @@
         <v>-10.3</v>
       </c>
       <c r="M58" t="n">
-        <v>8.6</v>
+        <v>7.5</v>
       </c>
       <c r="N58" t="inlineStr"/>
       <c r="O58" t="n">
@@ -8332,7 +8382,7 @@
         <v>46301</v>
       </c>
       <c r="Y58" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Z58" t="inlineStr">
         <is>
@@ -8361,13 +8411,13 @@
         <v>218.76</v>
       </c>
       <c r="AH58" t="n">
-        <v>254.95</v>
+        <v>252.2</v>
       </c>
       <c r="AI58" t="n">
-        <v>254.95</v>
+        <v>252.2</v>
       </c>
       <c r="AJ58" t="n">
-        <v>16.54</v>
+        <v>15.29</v>
       </c>
       <c r="AK58" t="n">
         <v>-8.949999999999999</v>
@@ -8376,7 +8426,7 @@
         <v>17.1</v>
       </c>
       <c r="AM58" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AN58" t="n">
         <v>25</v>
@@ -8384,11 +8434,11 @@
       <c r="AO58" t="inlineStr"/>
       <c r="AP58" t="inlineStr"/>
       <c r="AQ58" t="n">
-        <v>0.35</v>
+        <v>-0.17</v>
       </c>
       <c r="AR58" t="inlineStr"/>
       <c r="AS58" t="n">
-        <v>16.19</v>
+        <v>15.46</v>
       </c>
       <c r="AT58" t="inlineStr"/>
     </row>
@@ -8561,7 +8611,7 @@
         <v>10.5</v>
       </c>
       <c r="H60" t="n">
-        <v>0.8</v>
+        <v>-6.9</v>
       </c>
       <c r="I60" t="n">
         <v>-3.62</v>
@@ -8576,7 +8626,7 @@
         <v>-5.7</v>
       </c>
       <c r="M60" t="n">
-        <v>7.1</v>
+        <v>4.6</v>
       </c>
       <c r="N60" t="inlineStr">
         <is>
@@ -8618,7 +8668,7 @@
         <v>46317</v>
       </c>
       <c r="Y60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z60" t="inlineStr">
         <is>
@@ -8645,13 +8695,13 @@
         <v>250.35</v>
       </c>
       <c r="AH60" t="n">
-        <v>270.55</v>
+        <v>263.82</v>
       </c>
       <c r="AI60" t="n">
-        <v>270.55</v>
+        <v>263.82</v>
       </c>
       <c r="AJ60" t="n">
-        <v>8.07</v>
+        <v>5.38</v>
       </c>
       <c r="AK60" t="n">
         <v>-10.26</v>
@@ -8660,7 +8710,7 @@
         <v>8.69</v>
       </c>
       <c r="AM60" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AN60" t="n">
         <v>25</v>
@@ -8668,11 +8718,11 @@
       <c r="AO60" t="inlineStr"/>
       <c r="AP60" t="inlineStr"/>
       <c r="AQ60" t="n">
-        <v>0.35</v>
+        <v>-0.17</v>
       </c>
       <c r="AR60" t="inlineStr"/>
       <c r="AS60" t="n">
-        <v>7.71</v>
+        <v>5.55</v>
       </c>
       <c r="AT60" t="inlineStr"/>
     </row>
@@ -9871,7 +9921,7 @@
         <v>35.1</v>
       </c>
       <c r="H69" t="n">
-        <v>45.6</v>
+        <v>36</v>
       </c>
       <c r="I69" t="n">
         <v>-7.78</v>
@@ -9886,7 +9936,7 @@
         <v>-3.1</v>
       </c>
       <c r="M69" t="n">
-        <v>37</v>
+        <v>32.1</v>
       </c>
       <c r="N69" t="inlineStr">
         <is>
@@ -9928,7 +9978,7 @@
         <v>46296</v>
       </c>
       <c r="Y69" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Z69" t="inlineStr">
         <is>
@@ -9957,13 +10007,13 @@
         <v>190.53</v>
       </c>
       <c r="AH69" t="n">
-        <v>258.74</v>
+        <v>249.37</v>
       </c>
       <c r="AI69" t="n">
-        <v>258.74</v>
+        <v>249.37</v>
       </c>
       <c r="AJ69" t="n">
-        <v>35.8</v>
+        <v>30.88</v>
       </c>
       <c r="AK69" t="n">
         <v>-10.39</v>
@@ -9972,7 +10022,7 @@
         <v>36.14</v>
       </c>
       <c r="AM69" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AN69" t="n">
         <v>27</v>
@@ -9980,11 +10030,11 @@
       <c r="AO69" t="inlineStr"/>
       <c r="AP69" t="inlineStr"/>
       <c r="AQ69" t="n">
-        <v>0.75</v>
+        <v>0.23</v>
       </c>
       <c r="AR69" t="inlineStr"/>
       <c r="AS69" t="n">
-        <v>35.05</v>
+        <v>30.65</v>
       </c>
       <c r="AT69" t="inlineStr"/>
     </row>
@@ -10598,7 +10648,7 @@
         <v>16.3</v>
       </c>
       <c r="M74" t="n">
-        <v>-18.8</v>
+        <v>-19.3</v>
       </c>
       <c r="N74" t="inlineStr"/>
       <c r="O74" t="n">
@@ -10655,13 +10705,13 @@
         <v>83.75</v>
       </c>
       <c r="AH74" t="n">
-        <v>58.36</v>
+        <v>58.02</v>
       </c>
       <c r="AI74" t="n">
-        <v>58.36</v>
+        <v>58.02</v>
       </c>
       <c r="AJ74" t="n">
-        <v>-30.32</v>
+        <v>-30.72</v>
       </c>
       <c r="AK74" t="n">
         <v>-33.34</v>
@@ -10670,7 +10720,7 @@
         <v>2.66</v>
       </c>
       <c r="AM74" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AN74" t="n">
         <v>0</v>
@@ -10678,11 +10728,11 @@
       <c r="AO74" t="inlineStr"/>
       <c r="AP74" t="inlineStr"/>
       <c r="AQ74" t="n">
-        <v>0.15</v>
+        <v>-0.37</v>
       </c>
       <c r="AR74" t="inlineStr"/>
       <c r="AS74" t="n">
-        <v>-30.47</v>
+        <v>-30.35</v>
       </c>
       <c r="AT74" t="inlineStr">
         <is>
@@ -10721,7 +10771,7 @@
         <v>11.1</v>
       </c>
       <c r="H75" t="n">
-        <v>-10.1</v>
+        <v>-11.5</v>
       </c>
       <c r="I75" t="n">
         <v>-8.85</v>
@@ -10736,7 +10786,7 @@
         <v>1.4</v>
       </c>
       <c r="M75" t="n">
-        <v>-0.2</v>
+        <v>-1.3</v>
       </c>
       <c r="N75" t="inlineStr"/>
       <c r="O75" t="n">
@@ -10793,13 +10843,13 @@
         <v>131.78</v>
       </c>
       <c r="AH75" t="n">
-        <v>123.7</v>
+        <v>122.08</v>
       </c>
       <c r="AI75" t="n">
-        <v>123.7</v>
+        <v>122.08</v>
       </c>
       <c r="AJ75" t="n">
-        <v>-6.13</v>
+        <v>-7.36</v>
       </c>
       <c r="AK75" t="n">
         <v>-16.3</v>
@@ -10808,7 +10858,7 @@
         <v>0.74</v>
       </c>
       <c r="AM75" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AN75" t="n">
         <v>1</v>
@@ -10816,11 +10866,11 @@
       <c r="AO75" t="inlineStr"/>
       <c r="AP75" t="inlineStr"/>
       <c r="AQ75" t="n">
-        <v>1.03</v>
+        <v>0.5</v>
       </c>
       <c r="AR75" t="inlineStr"/>
       <c r="AS75" t="n">
-        <v>-7.16</v>
+        <v>-7.86</v>
       </c>
       <c r="AT75" t="inlineStr">
         <is>
@@ -10859,7 +10909,7 @@
         <v>-19.9</v>
       </c>
       <c r="H76" t="n">
-        <v>-3.5</v>
+        <v>-7.7</v>
       </c>
       <c r="I76" t="n">
         <v>7.04</v>
@@ -10874,7 +10924,7 @@
         <v>0.4</v>
       </c>
       <c r="M76" t="n">
-        <v>8.5</v>
+        <v>5.2</v>
       </c>
       <c r="N76" t="inlineStr"/>
       <c r="O76" t="n">
@@ -10912,7 +10962,7 @@
         <v>46276</v>
       </c>
       <c r="Y76" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Z76" t="inlineStr">
         <is>
@@ -10941,13 +10991,13 @@
         <v>66.86</v>
       </c>
       <c r="AH76" t="n">
-        <v>72.40000000000001</v>
+        <v>70.08</v>
       </c>
       <c r="AI76" t="n">
-        <v>72.40000000000001</v>
+        <v>70.08</v>
       </c>
       <c r="AJ76" t="n">
-        <v>8.289999999999999</v>
+        <v>4.82</v>
       </c>
       <c r="AK76" t="n">
         <v>-1.24</v>
@@ -10956,7 +11006,7 @@
         <v>21.85</v>
       </c>
       <c r="AM76" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AN76" t="n">
         <v>22</v>
@@ -10964,11 +11014,11 @@
       <c r="AO76" t="inlineStr"/>
       <c r="AP76" t="inlineStr"/>
       <c r="AQ76" t="n">
-        <v>1.03</v>
+        <v>0.5</v>
       </c>
       <c r="AR76" t="inlineStr"/>
       <c r="AS76" t="n">
-        <v>7.25</v>
+        <v>4.31</v>
       </c>
       <c r="AT76" t="inlineStr"/>
     </row>
@@ -11003,7 +11053,7 @@
         <v>-9.1</v>
       </c>
       <c r="H77" t="n">
-        <v>-14.7</v>
+        <v>-17.7</v>
       </c>
       <c r="I77" t="n">
         <v>-5.75</v>
@@ -11018,7 +11068,7 @@
         <v>-30.4</v>
       </c>
       <c r="M77" t="n">
-        <v>-36.6</v>
+        <v>-36.3</v>
       </c>
       <c r="N77" t="inlineStr"/>
       <c r="O77" t="n">
@@ -11075,13 +11125,13 @@
         <v>15.93</v>
       </c>
       <c r="AH77" t="n">
-        <v>13.47</v>
+        <v>13.48</v>
       </c>
       <c r="AI77" t="n">
-        <v>13.47</v>
+        <v>13.48</v>
       </c>
       <c r="AJ77" t="n">
-        <v>-15.42</v>
+        <v>-15.35</v>
       </c>
       <c r="AK77" t="n">
         <v>-17.24</v>
@@ -11090,7 +11140,7 @@
         <v>0.85</v>
       </c>
       <c r="AM77" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AN77" t="n">
         <v>0</v>
@@ -11098,11 +11148,11 @@
       <c r="AO77" t="inlineStr"/>
       <c r="AP77" t="inlineStr"/>
       <c r="AQ77" t="n">
-        <v>0.23</v>
+        <v>-0.29</v>
       </c>
       <c r="AR77" t="inlineStr"/>
       <c r="AS77" t="n">
-        <v>-15.65</v>
+        <v>-15.06</v>
       </c>
       <c r="AT77" t="inlineStr">
         <is>
@@ -11427,7 +11477,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="H80" t="n">
-        <v>-15.2</v>
+        <v>-16</v>
       </c>
       <c r="I80" t="n">
         <v>-10.83</v>
@@ -11442,7 +11492,7 @@
         <v>4.1</v>
       </c>
       <c r="M80" t="n">
-        <v>-4</v>
+        <v>-4.5</v>
       </c>
       <c r="N80" t="inlineStr"/>
       <c r="O80" t="n">
@@ -11499,13 +11549,13 @@
         <v>133.75</v>
       </c>
       <c r="AH80" t="n">
-        <v>118.75</v>
+        <v>117.97</v>
       </c>
       <c r="AI80" t="n">
-        <v>118.75</v>
+        <v>117.97</v>
       </c>
       <c r="AJ80" t="n">
-        <v>-11.21</v>
+        <v>-11.8</v>
       </c>
       <c r="AK80" t="n">
         <v>-21.17</v>
@@ -11514,7 +11564,7 @@
         <v>0.08</v>
       </c>
       <c r="AM80" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AN80" t="n">
         <v>0</v>
@@ -11522,11 +11572,11 @@
       <c r="AO80" t="inlineStr"/>
       <c r="AP80" t="inlineStr"/>
       <c r="AQ80" t="n">
-        <v>0.23</v>
+        <v>-0.29</v>
       </c>
       <c r="AR80" t="inlineStr"/>
       <c r="AS80" t="n">
-        <v>-11.45</v>
+        <v>-11.51</v>
       </c>
       <c r="AT80" t="inlineStr">
         <is>
@@ -12157,7 +12207,7 @@
         <v>1.3</v>
       </c>
       <c r="H85" t="n">
-        <v>-2.6</v>
+        <v>-0.3</v>
       </c>
       <c r="I85" t="n">
         <v>-6.82</v>
@@ -12172,7 +12222,7 @@
         <v>-29.7</v>
       </c>
       <c r="M85" t="n">
-        <v>-20.8</v>
+        <v>-21</v>
       </c>
       <c r="N85" t="inlineStr"/>
       <c r="O85" t="n">
@@ -12229,13 +12279,13 @@
         <v>46.92</v>
       </c>
       <c r="AH85" t="n">
-        <v>46.01</v>
+        <v>45.69</v>
       </c>
       <c r="AI85" t="n">
-        <v>46.01</v>
+        <v>45.69</v>
       </c>
       <c r="AJ85" t="n">
-        <v>-1.94</v>
+        <v>-2.62</v>
       </c>
       <c r="AK85" t="n">
         <v>-11.79</v>
@@ -12244,7 +12294,7 @@
         <v>2.43</v>
       </c>
       <c r="AM85" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AN85" t="n">
         <v>0</v>
@@ -12252,11 +12302,11 @@
       <c r="AO85" t="inlineStr"/>
       <c r="AP85" t="inlineStr"/>
       <c r="AQ85" t="n">
-        <v>-0.8</v>
+        <v>-1.32</v>
       </c>
       <c r="AR85" t="inlineStr"/>
       <c r="AS85" t="n">
-        <v>-1.14</v>
+        <v>-1.31</v>
       </c>
       <c r="AT85" t="inlineStr"/>
     </row>
@@ -12592,7 +12642,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="M88" t="n">
-        <v>-14.8</v>
+        <v>-14.5</v>
       </c>
       <c r="N88" t="inlineStr"/>
       <c r="O88" t="n">
@@ -12630,7 +12680,7 @@
         <v>46273</v>
       </c>
       <c r="Y88" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Z88" t="inlineStr">
         <is>
@@ -12659,22 +12709,22 @@
         <v>443.5</v>
       </c>
       <c r="AH88" t="n">
-        <v>375.58</v>
+        <v>377.24</v>
       </c>
       <c r="AI88" t="n">
-        <v>375.58</v>
+        <v>377.24</v>
       </c>
       <c r="AJ88" t="n">
-        <v>-15.31</v>
+        <v>-14.94</v>
       </c>
       <c r="AK88" t="n">
-        <v>-15.41</v>
+        <v>-15.94</v>
       </c>
       <c r="AL88" t="n">
         <v>23.39</v>
       </c>
       <c r="AM88" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AN88" t="n">
         <v>21</v>
@@ -12682,11 +12732,11 @@
       <c r="AO88" t="inlineStr"/>
       <c r="AP88" t="inlineStr"/>
       <c r="AQ88" t="n">
-        <v>0.45</v>
+        <v>-0.08</v>
       </c>
       <c r="AR88" t="inlineStr"/>
       <c r="AS88" t="n">
-        <v>-15.76</v>
+        <v>-14.86</v>
       </c>
       <c r="AT88" t="inlineStr">
         <is>
@@ -13151,7 +13201,7 @@
         <v>-17.1</v>
       </c>
       <c r="H92" t="n">
-        <v>-14.5</v>
+        <v>-18.5</v>
       </c>
       <c r="I92" t="n">
         <v>-7.68</v>
@@ -13166,7 +13216,7 @@
         <v>-20.5</v>
       </c>
       <c r="M92" t="n">
-        <v>-33.1</v>
+        <v>-33.6</v>
       </c>
       <c r="N92" t="inlineStr"/>
       <c r="O92" t="n">
@@ -13223,13 +13273,13 @@
         <v>97.91</v>
       </c>
       <c r="AH92" t="n">
-        <v>77.98</v>
+        <v>77.2</v>
       </c>
       <c r="AI92" t="n">
-        <v>77.98</v>
+        <v>77.2</v>
       </c>
       <c r="AJ92" t="n">
-        <v>-20.36</v>
+        <v>-21.15</v>
       </c>
       <c r="AK92" t="n">
         <v>-21.63</v>
@@ -13238,7 +13288,7 @@
         <v>1.77</v>
       </c>
       <c r="AM92" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AN92" t="n">
         <v>4</v>
@@ -13246,11 +13296,11 @@
       <c r="AO92" t="inlineStr"/>
       <c r="AP92" t="inlineStr"/>
       <c r="AQ92" t="n">
-        <v>-0.19</v>
+        <v>-0.71</v>
       </c>
       <c r="AR92" t="inlineStr"/>
       <c r="AS92" t="n">
-        <v>-20.16</v>
+        <v>-20.44</v>
       </c>
       <c r="AT92" t="inlineStr">
         <is>
@@ -13585,7 +13635,7 @@
         <v>5.8</v>
       </c>
       <c r="H95" t="n">
-        <v>25.9</v>
+        <v>22.5</v>
       </c>
       <c r="I95" t="n">
         <v>8.66</v>
@@ -13600,7 +13650,7 @@
         <v>-4.1</v>
       </c>
       <c r="M95" t="n">
-        <v>19.3</v>
+        <v>23.6</v>
       </c>
       <c r="N95" t="inlineStr">
         <is>
@@ -13642,7 +13692,7 @@
         <v>46262</v>
       </c>
       <c r="Y95" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="Z95" t="inlineStr">
         <is>
@@ -13671,13 +13721,13 @@
         <v>10.28</v>
       </c>
       <c r="AH95" t="n">
-        <v>12.03</v>
+        <v>12.46</v>
       </c>
       <c r="AI95" t="n">
-        <v>12.03</v>
+        <v>12.46</v>
       </c>
       <c r="AJ95" t="n">
-        <v>17.02</v>
+        <v>21.21</v>
       </c>
       <c r="AK95" t="n">
         <v>-2.14</v>
@@ -13686,7 +13736,7 @@
         <v>25.29</v>
       </c>
       <c r="AM95" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AN95" t="n">
         <v>30</v>
@@ -13694,11 +13744,11 @@
       <c r="AO95" t="inlineStr"/>
       <c r="AP95" t="inlineStr"/>
       <c r="AQ95" t="n">
-        <v>-0.76</v>
+        <v>-1.28</v>
       </c>
       <c r="AR95" t="inlineStr"/>
       <c r="AS95" t="n">
-        <v>17.79</v>
+        <v>22.49</v>
       </c>
       <c r="AT95" t="inlineStr"/>
     </row>
@@ -13733,7 +13783,7 @@
         <v>-4.2</v>
       </c>
       <c r="H96" t="n">
-        <v>-7.1</v>
+        <v>-11.4</v>
       </c>
       <c r="I96" t="n">
         <v>-7.73</v>
@@ -13748,7 +13798,7 @@
         <v>1.4</v>
       </c>
       <c r="M96" t="n">
-        <v>-11.9</v>
+        <v>-12.3</v>
       </c>
       <c r="N96" t="inlineStr"/>
       <c r="O96" t="n">
@@ -13805,22 +13855,22 @@
         <v>372.92</v>
       </c>
       <c r="AH96" t="n">
-        <v>323.24</v>
+        <v>321.68</v>
       </c>
       <c r="AI96" t="n">
-        <v>323.24</v>
+        <v>321.68</v>
       </c>
       <c r="AJ96" t="n">
-        <v>-13.32</v>
+        <v>-13.74</v>
       </c>
       <c r="AK96" t="n">
-        <v>-13.92</v>
+        <v>-14.13</v>
       </c>
       <c r="AL96" t="n">
         <v>2.12</v>
       </c>
       <c r="AM96" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AN96" t="n">
         <v>26</v>
@@ -13828,11 +13878,11 @@
       <c r="AO96" t="inlineStr"/>
       <c r="AP96" t="inlineStr"/>
       <c r="AQ96" t="n">
-        <v>-0.76</v>
+        <v>-1.28</v>
       </c>
       <c r="AR96" t="inlineStr"/>
       <c r="AS96" t="n">
-        <v>-12.56</v>
+        <v>-12.46</v>
       </c>
       <c r="AT96" t="inlineStr">
         <is>
@@ -15599,7 +15649,7 @@
         <v>44.3</v>
       </c>
       <c r="H109" t="n">
-        <v>45.6</v>
+        <v>36</v>
       </c>
       <c r="I109" t="n">
         <v>-3.81</v>
@@ -15614,7 +15664,7 @@
         <v>-8</v>
       </c>
       <c r="M109" t="n">
-        <v>37</v>
+        <v>32.1</v>
       </c>
       <c r="N109" t="inlineStr">
         <is>
@@ -15656,7 +15706,7 @@
         <v>46279</v>
       </c>
       <c r="Y109" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Z109" t="inlineStr">
         <is>
@@ -15685,13 +15735,13 @@
         <v>184.64</v>
       </c>
       <c r="AH109" t="n">
-        <v>258.74</v>
+        <v>249.37</v>
       </c>
       <c r="AI109" t="n">
-        <v>258.74</v>
+        <v>249.37</v>
       </c>
       <c r="AJ109" t="n">
-        <v>40.13</v>
+        <v>35.06</v>
       </c>
       <c r="AK109" t="n">
         <v>-7.53</v>
@@ -15700,7 +15750,7 @@
         <v>40.48</v>
       </c>
       <c r="AM109" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AN109" t="n">
         <v>42</v>
@@ -15708,11 +15758,11 @@
       <c r="AO109" t="inlineStr"/>
       <c r="AP109" t="inlineStr"/>
       <c r="AQ109" t="n">
-        <v>0.14</v>
+        <v>-0.38</v>
       </c>
       <c r="AR109" t="inlineStr"/>
       <c r="AS109" t="n">
-        <v>39.99</v>
+        <v>35.44</v>
       </c>
       <c r="AT109" t="inlineStr"/>
     </row>
@@ -16029,7 +16079,7 @@
         <v>37.7</v>
       </c>
       <c r="H112" t="n">
-        <v>0.8</v>
+        <v>-6.9</v>
       </c>
       <c r="I112" t="n">
         <v>-6.45</v>
@@ -16044,7 +16094,7 @@
         <v>1.8</v>
       </c>
       <c r="M112" t="n">
-        <v>7.1</v>
+        <v>4.6</v>
       </c>
       <c r="N112" t="inlineStr"/>
       <c r="O112" t="n">
@@ -16082,7 +16132,7 @@
         <v>46261</v>
       </c>
       <c r="Y112" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Z112" t="inlineStr">
         <is>
@@ -16109,13 +16159,13 @@
         <v>275</v>
       </c>
       <c r="AH112" t="n">
-        <v>270.55</v>
+        <v>263.82</v>
       </c>
       <c r="AI112" t="n">
-        <v>270.55</v>
+        <v>263.82</v>
       </c>
       <c r="AJ112" t="n">
-        <v>-1.62</v>
+        <v>-4.07</v>
       </c>
       <c r="AK112" t="n">
         <v>-18.3</v>
@@ -16124,7 +16174,7 @@
         <v>7.1</v>
       </c>
       <c r="AM112" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AN112" t="n">
         <v>6</v>
@@ -16132,11 +16182,11 @@
       <c r="AO112" t="inlineStr"/>
       <c r="AP112" t="inlineStr"/>
       <c r="AQ112" t="n">
-        <v>0.14</v>
+        <v>-0.38</v>
       </c>
       <c r="AR112" t="inlineStr"/>
       <c r="AS112" t="n">
-        <v>-1.76</v>
+        <v>-3.68</v>
       </c>
       <c r="AT112" t="inlineStr">
         <is>
@@ -16907,7 +16957,7 @@
         <v>-7.1</v>
       </c>
       <c r="H118" t="n">
-        <v>-15.1</v>
+        <v>-14.6</v>
       </c>
       <c r="I118" t="n">
         <v>2.22</v>
@@ -16922,7 +16972,7 @@
         <v>4.9</v>
       </c>
       <c r="M118" t="n">
-        <v>-10.9</v>
+        <v>-11.5</v>
       </c>
       <c r="N118" t="inlineStr"/>
       <c r="O118" t="n">
@@ -16960,7 +17010,7 @@
         <v>46258</v>
       </c>
       <c r="Y118" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Z118" t="inlineStr">
         <is>
@@ -16989,13 +17039,13 @@
         <v>50.78</v>
       </c>
       <c r="AH118" t="n">
-        <v>43.33</v>
+        <v>43.02</v>
       </c>
       <c r="AI118" t="n">
-        <v>43.33</v>
+        <v>43.02</v>
       </c>
       <c r="AJ118" t="n">
-        <v>-14.67</v>
+        <v>-15.28</v>
       </c>
       <c r="AK118" t="n">
         <v>-21.33</v>
@@ -17004,7 +17054,7 @@
         <v>11.12</v>
       </c>
       <c r="AM118" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AN118" t="n">
         <v>20</v>
@@ -17012,11 +17062,11 @@
       <c r="AO118" t="inlineStr"/>
       <c r="AP118" t="inlineStr"/>
       <c r="AQ118" t="n">
-        <v>-0.01</v>
+        <v>-0.54</v>
       </c>
       <c r="AR118" t="inlineStr"/>
       <c r="AS118" t="n">
-        <v>-14.66</v>
+        <v>-14.75</v>
       </c>
       <c r="AT118" t="inlineStr">
         <is>
@@ -17627,7 +17677,7 @@
         <v>-9.1</v>
       </c>
       <c r="H123" t="n">
-        <v>-13.8</v>
+        <v>-14.1</v>
       </c>
       <c r="I123" t="n">
         <v>-5.07</v>
@@ -17642,7 +17692,7 @@
         <v>3.7</v>
       </c>
       <c r="M123" t="n">
-        <v>-18.9</v>
+        <v>-16.7</v>
       </c>
       <c r="N123" t="inlineStr"/>
       <c r="O123" t="n">
@@ -17680,7 +17730,7 @@
         <v>46287</v>
       </c>
       <c r="Y123" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z123" t="inlineStr">
         <is>
@@ -17709,13 +17759,13 @@
         <v>112.19</v>
       </c>
       <c r="AH123" t="n">
-        <v>91.13</v>
+        <v>93.53</v>
       </c>
       <c r="AI123" t="n">
-        <v>91.13</v>
+        <v>93.53</v>
       </c>
       <c r="AJ123" t="n">
-        <v>-18.77</v>
+        <v>-16.63</v>
       </c>
       <c r="AK123" t="n">
         <v>-23.29</v>
@@ -17724,7 +17774,7 @@
         <v>14.5</v>
       </c>
       <c r="AM123" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AN123" t="n">
         <v>25</v>
@@ -17732,11 +17782,11 @@
       <c r="AO123" t="inlineStr"/>
       <c r="AP123" t="inlineStr"/>
       <c r="AQ123" t="n">
-        <v>-0.01</v>
+        <v>-0.54</v>
       </c>
       <c r="AR123" t="inlineStr"/>
       <c r="AS123" t="n">
-        <v>-18.76</v>
+        <v>-16.1</v>
       </c>
       <c r="AT123" t="inlineStr">
         <is>
@@ -17775,7 +17825,7 @@
         <v>-31.8</v>
       </c>
       <c r="H124" t="n">
-        <v>-16.7</v>
+        <v>-16.3</v>
       </c>
       <c r="I124" t="n">
         <v>-7.89</v>
@@ -17790,7 +17840,7 @@
         <v>-12.7</v>
       </c>
       <c r="M124" t="n">
-        <v>-22.6</v>
+        <v>-23</v>
       </c>
       <c r="N124" t="inlineStr"/>
       <c r="O124" t="n">
@@ -17847,13 +17897,13 @@
         <v>50.2</v>
       </c>
       <c r="AH124" t="n">
-        <v>41.75</v>
+        <v>41.49</v>
       </c>
       <c r="AI124" t="n">
-        <v>41.75</v>
+        <v>41.49</v>
       </c>
       <c r="AJ124" t="n">
-        <v>-16.83</v>
+        <v>-17.35</v>
       </c>
       <c r="AK124" t="n">
         <v>-27.27</v>
@@ -17862,7 +17912,7 @@
         <v>4.72</v>
       </c>
       <c r="AM124" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AN124" t="n">
         <v>3</v>
@@ -17870,11 +17920,11 @@
       <c r="AO124" t="inlineStr"/>
       <c r="AP124" t="inlineStr"/>
       <c r="AQ124" t="n">
-        <v>-0.01</v>
+        <v>-0.54</v>
       </c>
       <c r="AR124" t="inlineStr"/>
       <c r="AS124" t="n">
-        <v>-16.82</v>
+        <v>-16.81</v>
       </c>
       <c r="AT124" t="inlineStr">
         <is>
@@ -18333,7 +18383,7 @@
         <v>-11.7</v>
       </c>
       <c r="H128" t="n">
-        <v>-4.2</v>
+        <v>-6.4</v>
       </c>
       <c r="I128" t="n">
         <v>2.64</v>
@@ -18348,7 +18398,7 @@
         <v>-25.1</v>
       </c>
       <c r="M128" t="n">
-        <v>-20.5</v>
+        <v>-20.8</v>
       </c>
       <c r="N128" t="inlineStr"/>
       <c r="O128" t="n">
@@ -18386,7 +18436,7 @@
         <v>46262</v>
       </c>
       <c r="Y128" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="Z128" t="inlineStr">
         <is>
@@ -18413,13 +18463,13 @@
         <v>64.77</v>
       </c>
       <c r="AH128" t="n">
-        <v>60.83</v>
+        <v>60.49</v>
       </c>
       <c r="AI128" t="n">
-        <v>60.83</v>
+        <v>60.49</v>
       </c>
       <c r="AJ128" t="n">
-        <v>-6.08</v>
+        <v>-6.61</v>
       </c>
       <c r="AK128" t="n">
         <v>-13.39</v>
@@ -18428,7 +18478,7 @@
         <v>8.279999999999999</v>
       </c>
       <c r="AM128" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AN128" t="n">
         <v>6</v>
@@ -18436,7 +18486,7 @@
       <c r="AO128" t="inlineStr"/>
       <c r="AP128" t="inlineStr"/>
       <c r="AQ128" t="n">
-        <v>-0.01</v>
+        <v>-0.54</v>
       </c>
       <c r="AR128" t="inlineStr"/>
       <c r="AS128" t="n">
@@ -22657,7 +22707,7 @@
         <v>-10</v>
       </c>
       <c r="H158" t="n">
-        <v>25.9</v>
+        <v>22.5</v>
       </c>
       <c r="I158" t="n">
         <v>3.54</v>
@@ -22672,7 +22722,7 @@
         <v>-11.4</v>
       </c>
       <c r="M158" t="n">
-        <v>19.3</v>
+        <v>23.6</v>
       </c>
       <c r="N158" t="inlineStr"/>
       <c r="O158" t="n">
@@ -22710,7 +22760,7 @@
         <v>46245</v>
       </c>
       <c r="Y158" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Z158" t="inlineStr">
         <is>
@@ -22739,13 +22789,13 @@
         <v>10.03</v>
       </c>
       <c r="AH158" t="n">
-        <v>12.03</v>
+        <v>12.46</v>
       </c>
       <c r="AI158" t="n">
-        <v>12.03</v>
+        <v>12.46</v>
       </c>
       <c r="AJ158" t="n">
-        <v>20</v>
+        <v>24.29</v>
       </c>
       <c r="AK158" t="n">
         <v>-5.44</v>
@@ -22754,7 +22804,7 @@
         <v>28.48</v>
       </c>
       <c r="AM158" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AN158" t="n">
         <v>47</v>
@@ -22762,11 +22812,11 @@
       <c r="AO158" t="inlineStr"/>
       <c r="AP158" t="inlineStr"/>
       <c r="AQ158" t="n">
-        <v>-1.29</v>
+        <v>-1.8</v>
       </c>
       <c r="AR158" t="inlineStr"/>
       <c r="AS158" t="n">
-        <v>21.29</v>
+        <v>26.09</v>
       </c>
       <c r="AT158" t="inlineStr"/>
     </row>
@@ -23377,7 +23427,7 @@
         <v>9.4</v>
       </c>
       <c r="H163" t="n">
-        <v>-7.1</v>
+        <v>-9.9</v>
       </c>
       <c r="I163" t="n">
         <v>-8.5</v>
@@ -23392,7 +23442,7 @@
         <v>14.7</v>
       </c>
       <c r="M163" t="n">
-        <v>-7.5</v>
+        <v>-11</v>
       </c>
       <c r="N163" t="inlineStr"/>
       <c r="O163" t="n">
@@ -23430,7 +23480,7 @@
         <v>46238</v>
       </c>
       <c r="Y163" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="Z163" t="inlineStr">
         <is>
@@ -23457,13 +23507,13 @@
         <v>15.77</v>
       </c>
       <c r="AH163" t="n">
-        <v>12.6</v>
+        <v>12.11</v>
       </c>
       <c r="AI163" t="n">
-        <v>12.6</v>
+        <v>12.11</v>
       </c>
       <c r="AJ163" t="n">
-        <v>-20.1</v>
+        <v>-23.21</v>
       </c>
       <c r="AK163" t="n">
         <v>-26.25</v>
@@ -23472,7 +23522,7 @@
         <v>8.5</v>
       </c>
       <c r="AM163" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AN163" t="n">
         <v>2</v>
@@ -23480,11 +23530,11 @@
       <c r="AO163" t="inlineStr"/>
       <c r="AP163" t="inlineStr"/>
       <c r="AQ163" t="n">
-        <v>2.19</v>
+        <v>1.66</v>
       </c>
       <c r="AR163" t="inlineStr"/>
       <c r="AS163" t="n">
-        <v>-22.29</v>
+        <v>-24.87</v>
       </c>
       <c r="AT163" t="inlineStr">
         <is>
@@ -24689,7 +24739,7 @@
         <v>-7.4</v>
       </c>
       <c r="H172" t="n">
-        <v>-3.5</v>
+        <v>-7.7</v>
       </c>
       <c r="I172" t="n">
         <v>10.43</v>
@@ -24704,7 +24754,7 @@
         <v>7.3</v>
       </c>
       <c r="M172" t="n">
-        <v>8.5</v>
+        <v>5.2</v>
       </c>
       <c r="N172" t="inlineStr"/>
       <c r="O172" t="n">
@@ -24742,7 +24792,7 @@
         <v>46237</v>
       </c>
       <c r="Y172" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Z172" t="inlineStr">
         <is>
@@ -24771,13 +24821,13 @@
         <v>70.92</v>
       </c>
       <c r="AH172" t="n">
-        <v>72.40000000000001</v>
+        <v>70.08</v>
       </c>
       <c r="AI172" t="n">
-        <v>72.40000000000001</v>
+        <v>70.08</v>
       </c>
       <c r="AJ172" t="n">
-        <v>2.09</v>
+        <v>-1.18</v>
       </c>
       <c r="AK172" t="n">
         <v>-6.9</v>
@@ -24786,21 +24836,23 @@
         <v>27.52</v>
       </c>
       <c r="AM172" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AN172" t="n">
         <v>21</v>
       </c>
-      <c r="AO172" t="inlineStr"/>
+      <c r="AO172" t="n">
+        <v>-1.18</v>
+      </c>
       <c r="AP172" t="inlineStr"/>
       <c r="AQ172" t="n">
-        <v>4.05</v>
+        <v>3.51</v>
       </c>
       <c r="AR172" t="n">
         <v>3.51</v>
       </c>
       <c r="AS172" t="n">
-        <v>-1.96</v>
+        <v>-4.69</v>
       </c>
       <c r="AT172" t="inlineStr"/>
     </row>
@@ -25405,7 +25457,7 @@
         <v>25.1</v>
       </c>
       <c r="H177" t="n">
-        <v>-1.3</v>
+        <v>-0.5</v>
       </c>
       <c r="I177" t="n">
         <v>10.45</v>
@@ -25420,7 +25472,7 @@
         <v>25</v>
       </c>
       <c r="M177" t="n">
-        <v>21</v>
+        <v>19.2</v>
       </c>
       <c r="N177" t="inlineStr"/>
       <c r="O177" t="n">
@@ -25458,7 +25510,7 @@
         <v>46233</v>
       </c>
       <c r="Y177" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="Z177" t="inlineStr">
         <is>
@@ -25487,13 +25539,13 @@
         <v>24.39</v>
       </c>
       <c r="AH177" t="n">
-        <v>25.65</v>
+        <v>25.3</v>
       </c>
       <c r="AI177" t="n">
-        <v>25.65</v>
+        <v>25.3</v>
       </c>
       <c r="AJ177" t="n">
-        <v>5.16</v>
+        <v>3.73</v>
       </c>
       <c r="AK177" t="n">
         <v>-7.51</v>
@@ -25502,7 +25554,7 @@
         <v>22.95</v>
       </c>
       <c r="AM177" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AN177" t="n">
         <v>1</v>
@@ -25512,13 +25564,13 @@
       </c>
       <c r="AP177" t="inlineStr"/>
       <c r="AQ177" t="n">
-        <v>3.5</v>
+        <v>2.96</v>
       </c>
       <c r="AR177" t="n">
         <v>3.5</v>
       </c>
       <c r="AS177" t="n">
-        <v>1.67</v>
+        <v>0.77</v>
       </c>
       <c r="AT177" t="inlineStr"/>
     </row>
@@ -26153,7 +26205,7 @@
         <v>-11.5</v>
       </c>
       <c r="H182" t="n">
-        <v>-3.1</v>
+        <v>-3.4</v>
       </c>
       <c r="I182" t="n">
         <v>-18.43</v>
@@ -26168,7 +26220,7 @@
         <v>-24.2</v>
       </c>
       <c r="M182" t="n">
-        <v>-21.9</v>
+        <v>-22.7</v>
       </c>
       <c r="N182" t="inlineStr"/>
       <c r="O182" t="n">
@@ -26206,7 +26258,7 @@
         <v>46230</v>
       </c>
       <c r="Y182" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="Z182" t="inlineStr">
         <is>
@@ -26233,13 +26285,13 @@
         <v>268.74</v>
       </c>
       <c r="AH182" t="n">
-        <v>227.28</v>
+        <v>224.03</v>
       </c>
       <c r="AI182" t="n">
-        <v>227.28</v>
+        <v>224.03</v>
       </c>
       <c r="AJ182" t="n">
-        <v>-15.43</v>
+        <v>-16.64</v>
       </c>
       <c r="AK182" t="n">
         <v>-26.39</v>
@@ -26248,7 +26300,7 @@
         <v>8.130000000000001</v>
       </c>
       <c r="AM182" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AN182" t="n">
         <v>3</v>
@@ -26258,13 +26310,13 @@
       </c>
       <c r="AP182" t="inlineStr"/>
       <c r="AQ182" t="n">
-        <v>3.7</v>
+        <v>3.16</v>
       </c>
       <c r="AR182" t="n">
         <v>4.05</v>
       </c>
       <c r="AS182" t="n">
-        <v>-19.13</v>
+        <v>-19.8</v>
       </c>
       <c r="AT182" t="inlineStr">
         <is>
@@ -27189,7 +27241,7 @@
         <v>13.9</v>
       </c>
       <c r="H189" t="n">
-        <v>-14.5</v>
+        <v>-15.7</v>
       </c>
       <c r="I189" t="n">
         <v>-12.11</v>
@@ -27204,7 +27256,7 @@
         <v>46.7</v>
       </c>
       <c r="M189" t="n">
-        <v>-6.9</v>
+        <v>-7</v>
       </c>
       <c r="N189" t="inlineStr"/>
       <c r="O189" t="n">
@@ -27242,7 +27294,7 @@
         <v>46224</v>
       </c>
       <c r="Y189" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Z189" t="inlineStr">
         <is>
@@ -27271,13 +27323,13 @@
         <v>272</v>
       </c>
       <c r="AH189" t="n">
-        <v>210.1</v>
+        <v>210.33</v>
       </c>
       <c r="AI189" t="n">
-        <v>210.1</v>
+        <v>210.33</v>
       </c>
       <c r="AJ189" t="n">
-        <v>-22.76</v>
+        <v>-22.67</v>
       </c>
       <c r="AK189" t="n">
         <v>-23.42</v>
@@ -27286,7 +27338,7 @@
         <v>23.89</v>
       </c>
       <c r="AM189" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AN189" t="n">
         <v>46</v>
@@ -27296,13 +27348,13 @@
       </c>
       <c r="AP189" t="inlineStr"/>
       <c r="AQ189" t="n">
-        <v>2.52</v>
+        <v>1.98</v>
       </c>
       <c r="AR189" t="n">
         <v>4.4</v>
       </c>
       <c r="AS189" t="n">
-        <v>-25.27</v>
+        <v>-24.65</v>
       </c>
       <c r="AT189" t="inlineStr">
         <is>
@@ -27789,7 +27841,7 @@
         <v>18.5</v>
       </c>
       <c r="H193" t="n">
-        <v>-9.300000000000001</v>
+        <v>-13.6</v>
       </c>
       <c r="I193" t="n">
         <v>3.77</v>
@@ -27804,7 +27856,7 @@
         <v>51.9</v>
       </c>
       <c r="M193" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="N193" t="inlineStr"/>
       <c r="O193" t="n">
@@ -27842,7 +27894,7 @@
         <v>46224</v>
       </c>
       <c r="Y193" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Z193" t="inlineStr">
         <is>
@@ -27871,13 +27923,13 @@
         <v>309.39</v>
       </c>
       <c r="AH193" t="n">
-        <v>257.82</v>
+        <v>257.16</v>
       </c>
       <c r="AI193" t="n">
-        <v>257.82</v>
+        <v>257.16</v>
       </c>
       <c r="AJ193" t="n">
-        <v>-16.67</v>
+        <v>-16.88</v>
       </c>
       <c r="AK193" t="n">
         <v>-20.94</v>
@@ -27886,7 +27938,7 @@
         <v>29.85</v>
       </c>
       <c r="AM193" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AN193" t="n">
         <v>55</v>
@@ -27896,13 +27948,13 @@
       </c>
       <c r="AP193" t="inlineStr"/>
       <c r="AQ193" t="n">
-        <v>2.52</v>
+        <v>1.98</v>
       </c>
       <c r="AR193" t="n">
         <v>4.4</v>
       </c>
       <c r="AS193" t="n">
-        <v>-19.18</v>
+        <v>-18.86</v>
       </c>
       <c r="AT193" t="inlineStr">
         <is>
@@ -28696,7 +28748,7 @@
         <v>51.8</v>
       </c>
       <c r="M199" t="n">
-        <v>-14.8</v>
+        <v>-14.5</v>
       </c>
       <c r="N199" t="inlineStr"/>
       <c r="O199" t="n">
@@ -28730,7 +28782,7 @@
         <v>46226</v>
       </c>
       <c r="Y199" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="Z199" t="inlineStr">
         <is>
@@ -28757,22 +28809,22 @@
         <v>545.05</v>
       </c>
       <c r="AH199" t="n">
-        <v>375.58</v>
+        <v>377.24</v>
       </c>
       <c r="AI199" t="n">
-        <v>375.58</v>
+        <v>377.24</v>
       </c>
       <c r="AJ199" t="n">
-        <v>-31.09</v>
+        <v>-30.79</v>
       </c>
       <c r="AK199" t="n">
-        <v>-31.17</v>
+        <v>-31.6</v>
       </c>
       <c r="AL199" t="n">
         <v>5.66</v>
       </c>
       <c r="AM199" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AN199" t="n">
         <v>3</v>
@@ -28782,13 +28834,13 @@
       </c>
       <c r="AP199" t="inlineStr"/>
       <c r="AQ199" t="n">
-        <v>2.52</v>
+        <v>1.98</v>
       </c>
       <c r="AR199" t="n">
         <v>4.4</v>
       </c>
       <c r="AS199" t="n">
-        <v>-33.61</v>
+        <v>-32.77</v>
       </c>
       <c r="AT199" t="inlineStr">
         <is>
@@ -31039,7 +31091,7 @@
         <v>13.9</v>
       </c>
       <c r="H215" t="n">
-        <v>7.5</v>
+        <v>10.3</v>
       </c>
       <c r="I215" t="n">
         <v>-6.26</v>
@@ -31054,7 +31106,7 @@
         <v>73.3</v>
       </c>
       <c r="M215" t="n">
-        <v>26.8</v>
+        <v>28.5</v>
       </c>
       <c r="N215" t="inlineStr"/>
       <c r="O215" t="n">
@@ -31088,7 +31140,7 @@
         <v>46224</v>
       </c>
       <c r="Y215" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Z215" t="inlineStr">
         <is>
@@ -31117,13 +31169,13 @@
         <v>517</v>
       </c>
       <c r="AH215" t="n">
-        <v>507.93</v>
+        <v>516.79</v>
       </c>
       <c r="AI215" t="n">
-        <v>507.93</v>
+        <v>516.79</v>
       </c>
       <c r="AJ215" t="n">
-        <v>-1.75</v>
+        <v>-0.04</v>
       </c>
       <c r="AK215" t="n">
         <v>-17.98</v>
@@ -31132,7 +31184,7 @@
         <v>27.37</v>
       </c>
       <c r="AM215" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AN215" t="n">
         <v>55</v>
@@ -31142,13 +31194,13 @@
       </c>
       <c r="AP215" t="inlineStr"/>
       <c r="AQ215" t="n">
-        <v>2.52</v>
+        <v>1.98</v>
       </c>
       <c r="AR215" t="n">
         <v>4.4</v>
       </c>
       <c r="AS215" t="n">
-        <v>-4.27</v>
+        <v>-2.02</v>
       </c>
       <c r="AT215" t="inlineStr">
         <is>
@@ -33561,7 +33613,7 @@
         <v>3.7</v>
       </c>
       <c r="H232" t="n">
-        <v>-15.1</v>
+        <v>-14.6</v>
       </c>
       <c r="I232" t="n">
         <v>4.03</v>
@@ -33576,7 +33628,7 @@
         <v>-1.1</v>
       </c>
       <c r="M232" t="n">
-        <v>-10.9</v>
+        <v>-11.5</v>
       </c>
       <c r="N232" t="inlineStr"/>
       <c r="O232" t="n">
@@ -33610,7 +33662,7 @@
         <v>46231</v>
       </c>
       <c r="Y232" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Z232" t="inlineStr">
         <is>
@@ -33639,13 +33691,13 @@
         <v>50.22</v>
       </c>
       <c r="AH232" t="n">
-        <v>43.33</v>
+        <v>43.02</v>
       </c>
       <c r="AI232" t="n">
-        <v>43.33</v>
+        <v>43.02</v>
       </c>
       <c r="AJ232" t="n">
-        <v>-13.72</v>
+        <v>-14.34</v>
       </c>
       <c r="AK232" t="n">
         <v>-20.45</v>
@@ -33654,7 +33706,7 @@
         <v>12.36</v>
       </c>
       <c r="AM232" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AN232" t="n">
         <v>43</v>
@@ -33664,13 +33716,13 @@
       </c>
       <c r="AP232" t="inlineStr"/>
       <c r="AQ232" t="n">
-        <v>2.52</v>
+        <v>1.98</v>
       </c>
       <c r="AR232" t="n">
         <v>4.4</v>
       </c>
       <c r="AS232" t="n">
-        <v>-16.24</v>
+        <v>-16.32</v>
       </c>
       <c r="AT232" t="inlineStr">
         <is>
@@ -34443,7 +34495,7 @@
         <v>24.8</v>
       </c>
       <c r="H238" t="n">
-        <v>16.1</v>
+        <v>14.2</v>
       </c>
       <c r="I238" t="n">
         <v>0.72</v>
@@ -34458,7 +34510,7 @@
         <v>1.1</v>
       </c>
       <c r="M238" t="n">
-        <v>10.6</v>
+        <v>7.3</v>
       </c>
       <c r="N238" t="inlineStr"/>
       <c r="O238" t="n">
@@ -34519,13 +34571,13 @@
         <v>20.61</v>
       </c>
       <c r="AH238" t="n">
-        <v>21.6</v>
+        <v>20.95</v>
       </c>
       <c r="AI238" t="n">
-        <v>21.6</v>
+        <v>20.95</v>
       </c>
       <c r="AJ238" t="n">
-        <v>4.81</v>
+        <v>1.66</v>
       </c>
       <c r="AK238" t="n">
         <v>-23.57</v>
@@ -34534,7 +34586,7 @@
         <v>4.96</v>
       </c>
       <c r="AM238" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AN238" t="n">
         <v>67</v>
@@ -34544,13 +34596,13 @@
       </c>
       <c r="AP238" t="inlineStr"/>
       <c r="AQ238" t="n">
-        <v>2.52</v>
+        <v>1.98</v>
       </c>
       <c r="AR238" t="n">
         <v>4.4</v>
       </c>
       <c r="AS238" t="n">
-        <v>2.3</v>
+        <v>-0.32</v>
       </c>
       <c r="AT238" t="inlineStr">
         <is>
@@ -36358,7 +36410,7 @@
         <v>-30.2</v>
       </c>
       <c r="M251" t="n">
-        <v>-51</v>
+        <v>-49.5</v>
       </c>
       <c r="N251" t="inlineStr"/>
       <c r="O251" t="n">
@@ -36396,7 +36448,7 @@
         <v>46224</v>
       </c>
       <c r="Y251" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Z251" t="inlineStr">
         <is>
@@ -36425,22 +36477,22 @@
         <v>58.11</v>
       </c>
       <c r="AH251" t="n">
-        <v>38.77</v>
+        <v>39.79</v>
       </c>
       <c r="AI251" t="n">
-        <v>38.77</v>
+        <v>39.79</v>
       </c>
       <c r="AJ251" t="n">
-        <v>-33.28</v>
+        <v>-31.53</v>
       </c>
       <c r="AK251" t="n">
-        <v>-34.95</v>
+        <v>-36.81</v>
       </c>
       <c r="AL251" t="n">
         <v>29.2</v>
       </c>
       <c r="AM251" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AN251" t="n">
         <v>17</v>
@@ -36450,13 +36502,13 @@
       </c>
       <c r="AP251" t="inlineStr"/>
       <c r="AQ251" t="n">
-        <v>2.52</v>
+        <v>1.98</v>
       </c>
       <c r="AR251" t="n">
         <v>4.4</v>
       </c>
       <c r="AS251" t="n">
-        <v>-35.8</v>
+        <v>-33.51</v>
       </c>
       <c r="AT251" t="inlineStr">
         <is>
@@ -36495,7 +36547,7 @@
         <v>6</v>
       </c>
       <c r="H252" t="n">
-        <v>-14.4</v>
+        <v>-13.6</v>
       </c>
       <c r="I252" t="n">
         <v>-2.71</v>
@@ -36510,7 +36562,7 @@
         <v>-24.2</v>
       </c>
       <c r="M252" t="n">
-        <v>-29.8</v>
+        <v>-30.5</v>
       </c>
       <c r="N252" t="inlineStr"/>
       <c r="O252" t="n">
@@ -36567,13 +36619,13 @@
         <v>74.5</v>
       </c>
       <c r="AH252" t="n">
-        <v>57.54</v>
+        <v>56.85</v>
       </c>
       <c r="AI252" t="n">
-        <v>57.54</v>
+        <v>56.85</v>
       </c>
       <c r="AJ252" t="n">
-        <v>-22.77</v>
+        <v>-23.69</v>
       </c>
       <c r="AK252" t="n">
         <v>-33.33</v>
@@ -36582,7 +36634,7 @@
         <v>3.09</v>
       </c>
       <c r="AM252" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AN252" t="n">
         <v>14</v>
@@ -36592,13 +36644,13 @@
       </c>
       <c r="AP252" t="inlineStr"/>
       <c r="AQ252" t="n">
-        <v>2.52</v>
+        <v>1.98</v>
       </c>
       <c r="AR252" t="n">
         <v>4.4</v>
       </c>
       <c r="AS252" t="n">
-        <v>-25.28</v>
+        <v>-25.67</v>
       </c>
       <c r="AT252" t="inlineStr">
         <is>
@@ -36925,7 +36977,7 @@
         <v>-37.4</v>
       </c>
       <c r="H255" t="n">
-        <v>-20.3</v>
+        <v>-24.1</v>
       </c>
       <c r="I255" t="n">
         <v>1.06</v>
@@ -36940,7 +36992,7 @@
         <v>-20.1</v>
       </c>
       <c r="M255" t="n">
-        <v>-32.1</v>
+        <v>-33.3</v>
       </c>
       <c r="N255" t="inlineStr"/>
       <c r="O255" t="n">
@@ -36976,7 +37028,7 @@
         <v>46225</v>
       </c>
       <c r="Y255" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Z255" t="inlineStr">
         <is>
@@ -37005,22 +37057,22 @@
         <v>44.28</v>
       </c>
       <c r="AH255" t="n">
-        <v>38.7</v>
+        <v>37.91</v>
       </c>
       <c r="AI255" t="n">
-        <v>38.7</v>
+        <v>37.91</v>
       </c>
       <c r="AJ255" t="n">
-        <v>-12.61</v>
+        <v>-14.39</v>
       </c>
       <c r="AK255" t="n">
-        <v>-13.4</v>
+        <v>-14.42</v>
       </c>
       <c r="AL255" t="n">
         <v>24.31</v>
       </c>
       <c r="AM255" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AN255" t="n">
         <v>17</v>
@@ -37030,13 +37082,13 @@
       </c>
       <c r="AP255" t="inlineStr"/>
       <c r="AQ255" t="n">
-        <v>2.52</v>
+        <v>1.98</v>
       </c>
       <c r="AR255" t="n">
         <v>4.4</v>
       </c>
       <c r="AS255" t="n">
-        <v>-15.13</v>
+        <v>-16.37</v>
       </c>
       <c r="AT255" t="inlineStr">
         <is>
@@ -38417,7 +38469,7 @@
         <v>24.2</v>
       </c>
       <c r="H265" t="n">
-        <v>-29.9</v>
+        <v>-29.4</v>
       </c>
       <c r="I265" t="n">
         <v>14.8</v>
@@ -38432,7 +38484,7 @@
         <v>-4.2</v>
       </c>
       <c r="M265" t="n">
-        <v>-14.5</v>
+        <v>-13.1</v>
       </c>
       <c r="N265" t="inlineStr">
         <is>
@@ -38470,7 +38522,7 @@
         <v>46223</v>
       </c>
       <c r="Y265" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Z265" t="inlineStr">
         <is>
@@ -38499,13 +38551,13 @@
         <v>501.64</v>
       </c>
       <c r="AH265" t="n">
-        <v>414.6</v>
+        <v>420.37</v>
       </c>
       <c r="AI265" t="n">
-        <v>414.6</v>
+        <v>420.37</v>
       </c>
       <c r="AJ265" t="n">
-        <v>-17.35</v>
+        <v>-16.2</v>
       </c>
       <c r="AK265" t="n">
         <v>-24.85</v>
@@ -38514,7 +38566,7 @@
         <v>29.9</v>
       </c>
       <c r="AM265" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AN265" t="n">
         <v>22</v>
@@ -38524,13 +38576,13 @@
       </c>
       <c r="AP265" t="inlineStr"/>
       <c r="AQ265" t="n">
-        <v>2.52</v>
+        <v>1.98</v>
       </c>
       <c r="AR265" t="n">
         <v>4.4</v>
       </c>
       <c r="AS265" t="n">
-        <v>-19.87</v>
+        <v>-18.18</v>
       </c>
       <c r="AT265" t="inlineStr">
         <is>
@@ -39003,7 +39055,7 @@
         <v>19.4</v>
       </c>
       <c r="H269" t="n">
-        <v>-15.9</v>
+        <v>-16.6</v>
       </c>
       <c r="I269" t="n">
         <v>9.869999999999999</v>
@@ -39018,7 +39070,7 @@
         <v>-0.4</v>
       </c>
       <c r="M269" t="n">
-        <v>-20.4</v>
+        <v>-22.4</v>
       </c>
       <c r="N269" t="inlineStr"/>
       <c r="O269" t="n">
@@ -39056,7 +39108,7 @@
         <v>46230</v>
       </c>
       <c r="Y269" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="Z269" t="inlineStr">
         <is>
@@ -39085,13 +39137,13 @@
         <v>45.7</v>
       </c>
       <c r="AH269" t="n">
-        <v>35.38</v>
+        <v>34.4</v>
       </c>
       <c r="AI269" t="n">
-        <v>35.38</v>
+        <v>34.4</v>
       </c>
       <c r="AJ269" t="n">
-        <v>-22.58</v>
+        <v>-24.73</v>
       </c>
       <c r="AK269" t="n">
         <v>-29.26</v>
@@ -39100,7 +39152,7 @@
         <v>17.33</v>
       </c>
       <c r="AM269" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AN269" t="n">
         <v>12</v>
@@ -39110,13 +39162,13 @@
       </c>
       <c r="AP269" t="inlineStr"/>
       <c r="AQ269" t="n">
-        <v>2.52</v>
+        <v>1.98</v>
       </c>
       <c r="AR269" t="n">
         <v>4.4</v>
       </c>
       <c r="AS269" t="n">
-        <v>-25.1</v>
+        <v>-26.71</v>
       </c>
       <c r="AT269" t="inlineStr">
         <is>
@@ -39303,7 +39355,7 @@
       </c>
       <c r="G271" t="inlineStr"/>
       <c r="H271" t="n">
-        <v>-29.1</v>
+        <v>-28.9</v>
       </c>
       <c r="I271" t="n">
         <v>-1.89</v>
@@ -39318,7 +39370,7 @@
         <v>-19.7</v>
       </c>
       <c r="M271" t="n">
-        <v>-38.9</v>
+        <v>-38</v>
       </c>
       <c r="N271" t="inlineStr"/>
       <c r="O271" t="n">
@@ -39352,7 +39404,7 @@
         <v>46240</v>
       </c>
       <c r="Y271" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="Z271" t="inlineStr">
         <is>
@@ -39381,13 +39433,13 @@
         <v>120.59</v>
       </c>
       <c r="AH271" t="n">
-        <v>92.54000000000001</v>
+        <v>93.67</v>
       </c>
       <c r="AI271" t="n">
-        <v>92.54000000000001</v>
+        <v>93.67</v>
       </c>
       <c r="AJ271" t="n">
-        <v>-23.26</v>
+        <v>-22.33</v>
       </c>
       <c r="AK271" t="n">
         <v>-24.54</v>
@@ -39396,7 +39448,7 @@
         <v>19.06</v>
       </c>
       <c r="AM271" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AN271" t="n">
         <v>25</v>
@@ -39406,13 +39458,13 @@
       </c>
       <c r="AP271" t="inlineStr"/>
       <c r="AQ271" t="n">
-        <v>2.52</v>
+        <v>1.98</v>
       </c>
       <c r="AR271" t="n">
         <v>4.4</v>
       </c>
       <c r="AS271" t="n">
-        <v>-25.78</v>
+        <v>-24.31</v>
       </c>
       <c r="AT271" t="inlineStr">
         <is>
@@ -40039,7 +40091,7 @@
       </c>
       <c r="G276" t="inlineStr"/>
       <c r="H276" t="n">
-        <v>-13.8</v>
+        <v>-14.1</v>
       </c>
       <c r="I276" t="n">
         <v>-2.12</v>
@@ -40054,7 +40106,7 @@
         <v>16.5</v>
       </c>
       <c r="M276" t="n">
-        <v>-18.9</v>
+        <v>-16.7</v>
       </c>
       <c r="N276" t="inlineStr"/>
       <c r="O276" t="n">
@@ -40088,7 +40140,7 @@
         <v>46224</v>
       </c>
       <c r="Y276" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Z276" t="inlineStr">
         <is>
@@ -40115,13 +40167,13 @@
         <v>120.43</v>
       </c>
       <c r="AH276" t="n">
-        <v>91.13</v>
+        <v>93.53</v>
       </c>
       <c r="AI276" t="n">
-        <v>91.13</v>
+        <v>93.53</v>
       </c>
       <c r="AJ276" t="n">
-        <v>-24.33</v>
+        <v>-22.34</v>
       </c>
       <c r="AK276" t="n">
         <v>-28.54</v>
@@ -40130,7 +40182,7 @@
         <v>6.67</v>
       </c>
       <c r="AM276" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AN276" t="n">
         <v>48</v>
@@ -40140,13 +40192,13 @@
       </c>
       <c r="AP276" t="inlineStr"/>
       <c r="AQ276" t="n">
-        <v>2.52</v>
+        <v>1.98</v>
       </c>
       <c r="AR276" t="n">
         <v>4.4</v>
       </c>
       <c r="AS276" t="n">
-        <v>-26.85</v>
+        <v>-24.32</v>
       </c>
       <c r="AT276" t="inlineStr">
         <is>
@@ -41383,7 +41435,7 @@
         <v>25.8</v>
       </c>
       <c r="H285" t="n">
-        <v>11.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I285" t="n">
         <v>12.95</v>
@@ -41398,7 +41450,7 @@
         <v>7.1</v>
       </c>
       <c r="M285" t="n">
-        <v>56.4</v>
+        <v>50.7</v>
       </c>
       <c r="N285" t="inlineStr"/>
       <c r="O285" t="n">
@@ -41436,7 +41488,7 @@
         <v>46231</v>
       </c>
       <c r="Y285" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Z285" t="inlineStr">
         <is>
@@ -41465,13 +41517,13 @@
         <v>96.34</v>
       </c>
       <c r="AH285" t="n">
-        <v>161.49</v>
+        <v>155.82</v>
       </c>
       <c r="AI285" t="n">
-        <v>161.49</v>
+        <v>155.82</v>
       </c>
       <c r="AJ285" t="n">
-        <v>67.63</v>
+        <v>61.74</v>
       </c>
       <c r="AK285" t="n">
         <v>-6.51</v>
@@ -41480,7 +41532,7 @@
         <v>70.04000000000001</v>
       </c>
       <c r="AM285" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AN285" t="n">
         <v>65</v>
@@ -41490,13 +41542,13 @@
       </c>
       <c r="AP285" t="inlineStr"/>
       <c r="AQ285" t="n">
-        <v>2.52</v>
+        <v>1.98</v>
       </c>
       <c r="AR285" t="n">
         <v>4.4</v>
       </c>
       <c r="AS285" t="n">
-        <v>65.11</v>
+        <v>59.76</v>
       </c>
       <c r="AT285" t="inlineStr"/>
     </row>
@@ -41827,7 +41879,7 @@
         <v>5.5</v>
       </c>
       <c r="H288" t="n">
-        <v>4.3</v>
+        <v>9.9</v>
       </c>
       <c r="I288" t="n">
         <v>1.46</v>
@@ -41842,7 +41894,7 @@
         <v>-9</v>
       </c>
       <c r="M288" t="n">
-        <v>-2.4</v>
+        <v>-2.1</v>
       </c>
       <c r="N288" t="inlineStr"/>
       <c r="O288" t="n">
@@ -41880,7 +41932,7 @@
         <v>46295</v>
       </c>
       <c r="Y288" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Z288" t="inlineStr">
         <is>
@@ -41907,13 +41959,13 @@
         <v>17.49</v>
       </c>
       <c r="AH288" t="n">
-        <v>17.89</v>
+        <v>17.91</v>
       </c>
       <c r="AI288" t="n">
-        <v>17.89</v>
+        <v>17.91</v>
       </c>
       <c r="AJ288" t="n">
-        <v>2.29</v>
+        <v>2.4</v>
       </c>
       <c r="AK288" t="n">
         <v>-19.94</v>
@@ -41922,7 +41974,7 @@
         <v>6.06</v>
       </c>
       <c r="AM288" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AN288" t="n">
         <v>51</v>
@@ -41932,13 +41984,13 @@
       </c>
       <c r="AP288" t="inlineStr"/>
       <c r="AQ288" t="n">
-        <v>2.52</v>
+        <v>1.98</v>
       </c>
       <c r="AR288" t="n">
         <v>4.4</v>
       </c>
       <c r="AS288" t="n">
-        <v>-0.23</v>
+        <v>0.42</v>
       </c>
       <c r="AT288" t="inlineStr">
         <is>
@@ -41977,7 +42029,7 @@
         <v>-17.5</v>
       </c>
       <c r="H289" t="n">
-        <v>-18</v>
+        <v>-17.2</v>
       </c>
       <c r="I289" t="n">
         <v>11.63</v>
@@ -41992,7 +42044,7 @@
         <v>-42.2</v>
       </c>
       <c r="M289" t="n">
-        <v>-38.8</v>
+        <v>-35.6</v>
       </c>
       <c r="N289" t="inlineStr"/>
       <c r="O289" t="n">
@@ -42030,7 +42082,7 @@
         <v>46224</v>
       </c>
       <c r="Y289" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Z289" t="inlineStr">
         <is>
@@ -42059,22 +42111,22 @@
         <v>142.6</v>
       </c>
       <c r="AH289" t="n">
-        <v>117.7</v>
+        <v>123.25</v>
       </c>
       <c r="AI289" t="n">
-        <v>117.7</v>
+        <v>123.25</v>
       </c>
       <c r="AJ289" t="n">
-        <v>-17.46</v>
+        <v>-13.57</v>
       </c>
       <c r="AK289" t="n">
-        <v>-19.87</v>
+        <v>-20.59</v>
       </c>
       <c r="AL289" t="n">
         <v>45.74</v>
       </c>
       <c r="AM289" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AN289" t="n">
         <v>19</v>
@@ -42084,13 +42136,13 @@
       </c>
       <c r="AP289" t="inlineStr"/>
       <c r="AQ289" t="n">
-        <v>2.52</v>
+        <v>1.98</v>
       </c>
       <c r="AR289" t="n">
         <v>4.4</v>
       </c>
       <c r="AS289" t="n">
-        <v>-19.98</v>
+        <v>-15.55</v>
       </c>
       <c r="AT289" t="inlineStr">
         <is>
@@ -42281,7 +42333,7 @@
         <v>1.6</v>
       </c>
       <c r="H291" t="n">
-        <v>8.5</v>
+        <v>9.9</v>
       </c>
       <c r="I291" t="n">
         <v>4.01</v>
@@ -42296,7 +42348,7 @@
         <v>2.9</v>
       </c>
       <c r="M291" t="n">
-        <v>-8.699999999999999</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="N291" t="inlineStr"/>
       <c r="O291" t="n">
@@ -42334,7 +42386,7 @@
         <v>46225</v>
       </c>
       <c r="Y291" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Z291" t="inlineStr">
         <is>
@@ -42363,13 +42415,13 @@
         <v>53.22</v>
       </c>
       <c r="AH291" t="n">
-        <v>46.69</v>
+        <v>46.92</v>
       </c>
       <c r="AI291" t="n">
-        <v>46.69</v>
+        <v>46.92</v>
       </c>
       <c r="AJ291" t="n">
-        <v>-12.27</v>
+        <v>-11.84</v>
       </c>
       <c r="AK291" t="n">
         <v>-28.93</v>
@@ -42378,7 +42430,7 @@
         <v>12.6</v>
       </c>
       <c r="AM291" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AN291" t="n">
         <v>12</v>
@@ -42388,13 +42440,13 @@
       </c>
       <c r="AP291" t="inlineStr"/>
       <c r="AQ291" t="n">
-        <v>2.52</v>
+        <v>1.98</v>
       </c>
       <c r="AR291" t="n">
         <v>4.4</v>
       </c>
       <c r="AS291" t="n">
-        <v>-14.79</v>
+        <v>-13.82</v>
       </c>
       <c r="AT291" t="inlineStr">
         <is>
@@ -42861,7 +42913,7 @@
       </c>
       <c r="G295" t="inlineStr"/>
       <c r="H295" t="n">
-        <v>22.5</v>
+        <v>24.3</v>
       </c>
       <c r="I295" t="n">
         <v>6.37</v>
@@ -42876,7 +42928,7 @@
         <v>13.9</v>
       </c>
       <c r="M295" t="n">
-        <v>35.1</v>
+        <v>41.3</v>
       </c>
       <c r="N295" t="inlineStr"/>
       <c r="O295" t="n">
@@ -42910,7 +42962,7 @@
         <v>46225</v>
       </c>
       <c r="Y295" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Z295" t="inlineStr">
         <is>
@@ -42939,38 +42991,38 @@
         <v>34.49</v>
       </c>
       <c r="AH295" t="n">
-        <v>49.44</v>
+        <v>51.9</v>
       </c>
       <c r="AI295" t="n">
-        <v>49.44</v>
+        <v>51.9</v>
       </c>
       <c r="AJ295" t="n">
-        <v>43.36</v>
+        <v>50.49</v>
       </c>
       <c r="AK295" t="n">
         <v>-1.56</v>
       </c>
       <c r="AL295" t="n">
-        <v>46.43</v>
+        <v>51.91</v>
       </c>
       <c r="AM295" t="n">
+        <v>69</v>
+      </c>
+      <c r="AN295" t="n">
         <v>68</v>
-      </c>
-      <c r="AN295" t="n">
-        <v>66</v>
       </c>
       <c r="AO295" t="n">
         <v>39.21</v>
       </c>
       <c r="AP295" t="inlineStr"/>
       <c r="AQ295" t="n">
-        <v>2.52</v>
+        <v>1.98</v>
       </c>
       <c r="AR295" t="n">
         <v>4.4</v>
       </c>
       <c r="AS295" t="n">
-        <v>40.84</v>
+        <v>48.51</v>
       </c>
       <c r="AT295" t="inlineStr"/>
     </row>
@@ -44951,7 +45003,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>304 (+3 pending)</t>
+          <t>305 (+2 pending)</t>
         </is>
       </c>
     </row>
@@ -44963,7 +45015,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>$52,060.17</t>
+          <t>$52,319.70</t>
         </is>
       </c>
     </row>
@@ -44975,7 +45027,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>$50,423.43  (-3.14% price-weighted)</t>
+          <t>$50,640.28  (-3.21% price-weighted)</t>
         </is>
       </c>
     </row>
@@ -44987,7 +45039,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-1.65%  &lt;- judge the system by this line</t>
+          <t>-1.73%  &lt;- judge the system by this line</t>
         </is>
       </c>
     </row>
@@ -44999,7 +45051,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-2.30%</t>
+          <t>-2.29%</t>
         </is>
       </c>
     </row>
@@ -45011,7 +45063,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>136 reached, 64 wins (47%)</t>
+          <t>137 reached, 64 wins (47%)</t>
         </is>
       </c>
     </row>
@@ -45087,19 +45139,19 @@
         <v>195</v>
       </c>
       <c r="C12" t="n">
-        <v>1.66</v>
+        <v>1.48</v>
       </c>
       <c r="D12" t="n">
-        <v>1.03</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="F12" t="n">
-        <v>51.79</v>
+        <v>51.28</v>
       </c>
       <c r="G12" t="n">
-        <v>-13.97</v>
+        <v>-14</v>
       </c>
     </row>
     <row r="13">
@@ -45112,10 +45164,10 @@
         <v>77</v>
       </c>
       <c r="C13" t="n">
-        <v>-5.03</v>
+        <v>-4.94</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.79</v>
+        <v>-5.65</v>
       </c>
       <c r="E13" t="n">
         <v>5.06</v>
@@ -45124,7 +45176,7 @@
         <v>29.87</v>
       </c>
       <c r="G13" t="n">
-        <v>-21.41</v>
+        <v>-21.42</v>
       </c>
     </row>
     <row r="14">
@@ -45134,22 +45186,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C14" t="n">
-        <v>-13.69</v>
+        <v>-13.17</v>
       </c>
       <c r="D14" t="n">
-        <v>-14.19</v>
+        <v>-13.58</v>
       </c>
       <c r="E14" t="n">
         <v>7.05</v>
       </c>
       <c r="F14" t="n">
-        <v>21.88</v>
+        <v>21.21</v>
       </c>
       <c r="G14" t="n">
-        <v>-21.67</v>
+        <v>-21.09</v>
       </c>
     </row>
     <row r="15"/>
@@ -45197,22 +45249,22 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C17" t="n">
-        <v>-6.72</v>
+        <v>-6.83</v>
       </c>
       <c r="D17" t="n">
-        <v>31.63</v>
+        <v>30.3</v>
       </c>
       <c r="E17" t="n">
-        <v>-7.17</v>
+        <v>-7.19</v>
       </c>
       <c r="F17" t="n">
-        <v>3.95</v>
+        <v>3.83</v>
       </c>
       <c r="G17" t="n">
-        <v>-19.42</v>
+        <v>-19.26</v>
       </c>
     </row>
     <row r="18">
@@ -45225,19 +45277,19 @@
         <v>42</v>
       </c>
       <c r="C18" t="n">
-        <v>-1.04</v>
+        <v>-1</v>
       </c>
       <c r="D18" t="n">
         <v>52.38</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.81</v>
+        <v>-1.67</v>
       </c>
       <c r="F18" t="n">
         <v>3.4</v>
       </c>
       <c r="G18" t="n">
-        <v>-14.3</v>
+        <v>-14.31</v>
       </c>
     </row>
     <row r="19">
@@ -45275,19 +45327,19 @@
         <v>144</v>
       </c>
       <c r="C20" t="n">
-        <v>0.61</v>
+        <v>0.54</v>
       </c>
       <c r="D20" t="n">
         <v>44.44</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.15</v>
+        <v>-0.13</v>
       </c>
       <c r="F20" t="n">
         <v>3.45</v>
       </c>
       <c r="G20" t="n">
-        <v>-16.11</v>
+        <v>-16.14</v>
       </c>
     </row>
     <row r="21">
@@ -45526,13 +45578,13 @@
         <v>5</v>
       </c>
       <c r="C32" t="n">
-        <v>13.41</v>
+        <v>12.4</v>
       </c>
       <c r="D32" t="n">
         <v>80</v>
       </c>
       <c r="E32" t="n">
-        <v>14.12</v>
+        <v>13.21</v>
       </c>
       <c r="F32" t="n">
         <v>-13.85</v>
@@ -45548,13 +45600,13 @@
         <v>12</v>
       </c>
       <c r="C33" t="n">
-        <v>-4.7</v>
+        <v>-4.66</v>
       </c>
       <c r="D33" t="n">
         <v>41.67</v>
       </c>
       <c r="E33" t="n">
-        <v>-5</v>
+        <v>-4.84</v>
       </c>
       <c r="F33" t="n">
         <v>-16.62</v>
@@ -45570,13 +45622,13 @@
         <v>29</v>
       </c>
       <c r="C34" t="n">
-        <v>4.4</v>
+        <v>4.31</v>
       </c>
       <c r="D34" t="n">
         <v>48.28</v>
       </c>
       <c r="E34" t="n">
-        <v>4.25</v>
+        <v>4.19</v>
       </c>
       <c r="F34" t="n">
         <v>-14.24</v>
